--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3ACE2CE-8447-4391-B574-BD406AD02E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909C1CE6-9114-4FCC-80CC-C571DFFE4FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$514</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$514</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5099" uniqueCount="1075">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5100" uniqueCount="1076">
   <si>
     <t>ID_ACTIVIDAD</t>
   </si>
@@ -3259,6 +3259,9 @@
   </si>
   <si>
     <t>PALMA DE QUISPE ISABEL</t>
+  </si>
+  <si>
+    <t>COMPONENTE</t>
   </si>
 </sst>
 </file>
@@ -3330,7 +3333,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3350,19 +3353,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -3671,8 +3661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:N517"/>
+  <dimension ref="A1:O517"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -3687,9 +3676,10 @@
     <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3732,8 +3722,11 @@
       <c r="N1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -3777,7 +3770,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:14" hidden="1">
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -3820,8 +3813,11 @@
       <c r="N3" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" hidden="1">
+      <c r="O3">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -3864,8 +3860,11 @@
       <c r="N4" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -3909,7 +3908,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -3953,7 +3952,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -3997,7 +3996,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -4041,7 +4040,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -4085,7 +4084,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -4129,7 +4128,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -4173,7 +4172,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -4217,7 +4216,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -4261,7 +4260,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -4305,7 +4304,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -4349,7 +4348,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:15">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -4393,7 +4392,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -4437,7 +4436,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -4481,7 +4480,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -4525,7 +4524,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:15">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -4569,7 +4568,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:15">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -4613,7 +4612,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:15">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -4657,7 +4656,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:15">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -4701,7 +4700,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:15">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -4745,7 +4744,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:15">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -4789,7 +4788,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:15">
       <c r="A26" t="s">
         <v>37</v>
       </c>
@@ -4833,7 +4832,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:15">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -4877,7 +4876,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:15">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -4921,7 +4920,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:15">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -4965,7 +4964,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:15">
       <c r="A30" t="s">
         <v>41</v>
       </c>
@@ -5009,7 +5008,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:15">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -5053,7 +5052,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:14" hidden="1">
+    <row r="32" spans="1:15">
       <c r="A32" t="s">
         <v>43</v>
       </c>
@@ -5096,8 +5095,11 @@
       <c r="N32" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" hidden="1">
+      <c r="O32">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33" t="s">
         <v>44</v>
       </c>
@@ -5140,8 +5142,11 @@
       <c r="N33" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" hidden="1">
+      <c r="O33">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
       <c r="A34" t="s">
         <v>91</v>
       </c>
@@ -5184,8 +5189,11 @@
       <c r="N34" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" hidden="1">
+      <c r="O34">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
       <c r="A35" t="s">
         <v>92</v>
       </c>
@@ -5228,8 +5236,11 @@
       <c r="N35" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" hidden="1">
+      <c r="O35">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
       <c r="A36" t="s">
         <v>93</v>
       </c>
@@ -5272,8 +5283,11 @@
       <c r="N36" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" hidden="1">
+      <c r="O36">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
       <c r="A37" t="s">
         <v>94</v>
       </c>
@@ -5316,8 +5330,11 @@
       <c r="N37" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" hidden="1">
+      <c r="O37">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
       <c r="A38" t="s">
         <v>95</v>
       </c>
@@ -5360,8 +5377,11 @@
       <c r="N38" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" hidden="1">
+      <c r="O38">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
       <c r="A39" t="s">
         <v>96</v>
       </c>
@@ -5404,8 +5424,11 @@
       <c r="N39" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" hidden="1">
+      <c r="O39">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
       <c r="A40" t="s">
         <v>97</v>
       </c>
@@ -5448,8 +5471,11 @@
       <c r="N40" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" hidden="1">
+      <c r="O40">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
       <c r="A41" t="s">
         <v>98</v>
       </c>
@@ -5468,7 +5494,7 @@
       <c r="F41" t="s">
         <v>49</v>
       </c>
-      <c r="G41" s="13">
+      <c r="G41" s="4">
         <v>10238474651</v>
       </c>
       <c r="H41" t="s">
@@ -5492,8 +5518,11 @@
       <c r="N41" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" hidden="1">
+      <c r="O41">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
       <c r="A42" t="s">
         <v>99</v>
       </c>
@@ -5536,8 +5565,11 @@
       <c r="N42" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" hidden="1">
+      <c r="O42">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
       <c r="A43" t="s">
         <v>100</v>
       </c>
@@ -5580,8 +5612,11 @@
       <c r="N43" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" hidden="1">
+      <c r="O43">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
       <c r="A44" t="s">
         <v>101</v>
       </c>
@@ -5624,8 +5659,11 @@
       <c r="N44" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" hidden="1">
+      <c r="O44">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
       <c r="A45" t="s">
         <v>102</v>
       </c>
@@ -5644,7 +5682,7 @@
       <c r="F45" t="s">
         <v>49</v>
       </c>
-      <c r="G45" s="13">
+      <c r="G45" s="4">
         <v>10238474651</v>
       </c>
       <c r="H45" t="s">
@@ -5668,8 +5706,11 @@
       <c r="N45" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" hidden="1">
+      <c r="O45">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
       <c r="A46" t="s">
         <v>103</v>
       </c>
@@ -5712,8 +5753,11 @@
       <c r="N46" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" hidden="1">
+      <c r="O46">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
       <c r="A47" t="s">
         <v>104</v>
       </c>
@@ -5756,8 +5800,11 @@
       <c r="N47" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="48" spans="1:14">
+      <c r="O47">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
       <c r="A48" t="s">
         <v>105</v>
       </c>
@@ -5801,7 +5848,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="49" spans="1:14" hidden="1">
+    <row r="49" spans="1:15">
       <c r="A49" t="s">
         <v>106</v>
       </c>
@@ -5844,8 +5891,11 @@
       <c r="N49" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" hidden="1">
+      <c r="O49">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
       <c r="A50" t="s">
         <v>107</v>
       </c>
@@ -5888,8 +5938,11 @@
       <c r="N50" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" hidden="1">
+      <c r="O50">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
       <c r="A51" t="s">
         <v>108</v>
       </c>
@@ -5932,8 +5985,11 @@
       <c r="N51" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" hidden="1">
+      <c r="O51">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
       <c r="A52" t="s">
         <v>109</v>
       </c>
@@ -5976,8 +6032,11 @@
       <c r="N52" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" hidden="1">
+      <c r="O52">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
       <c r="A53" t="s">
         <v>110</v>
       </c>
@@ -6020,8 +6079,11 @@
       <c r="N53" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" hidden="1">
+      <c r="O53">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
       <c r="A54" t="s">
         <v>111</v>
       </c>
@@ -6064,27 +6126,30 @@
       <c r="N54" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" hidden="1">
+      <c r="O54">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
       <c r="A55" t="s">
         <v>112</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="4" t="s">
         <v>1010</v>
       </c>
-      <c r="C55" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D55" s="9">
+      <c r="C55">
+        <v>2026</v>
+      </c>
+      <c r="D55">
         <v>6</v>
       </c>
-      <c r="E55" s="9" t="s">
+      <c r="E55" t="s">
         <v>404</v>
       </c>
-      <c r="F55" s="9" t="s">
+      <c r="F55" t="s">
         <v>45</v>
       </c>
-      <c r="G55" s="13">
+      <c r="G55" s="4">
         <v>10417044227</v>
       </c>
       <c r="H55" t="s">
@@ -6099,17 +6164,20 @@
       <c r="K55" t="s">
         <v>1038</v>
       </c>
-      <c r="L55" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M55" s="9">
+      <c r="L55" t="s">
+        <v>88</v>
+      </c>
+      <c r="M55">
         <v>1</v>
       </c>
       <c r="N55" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="56" spans="1:14">
+      <c r="O55">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
       <c r="A56" t="s">
         <v>113</v>
       </c>
@@ -6153,7 +6221,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="57" spans="1:14">
+    <row r="57" spans="1:15">
       <c r="A57" t="s">
         <v>114</v>
       </c>
@@ -6197,7 +6265,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="58" spans="1:14" hidden="1">
+    <row r="58" spans="1:15">
       <c r="A58" t="s">
         <v>115</v>
       </c>
@@ -6240,8 +6308,11 @@
       <c r="N58" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" hidden="1">
+      <c r="O58">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
       <c r="A59" t="s">
         <v>116</v>
       </c>
@@ -6284,30 +6355,33 @@
       <c r="N59" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" hidden="1">
+      <c r="O59">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15">
       <c r="A60" t="s">
         <v>117</v>
       </c>
-      <c r="B60" s="10" t="s">
+      <c r="B60" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="C60" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D60" s="9">
+      <c r="C60">
+        <v>2026</v>
+      </c>
+      <c r="D60">
         <v>5</v>
       </c>
-      <c r="E60" s="9" t="s">
+      <c r="E60" t="s">
         <v>404</v>
       </c>
-      <c r="F60" s="9" t="s">
+      <c r="F60" t="s">
         <v>45</v>
       </c>
-      <c r="G60" s="12">
+      <c r="G60" s="4">
         <v>10487664958</v>
       </c>
-      <c r="H60" s="9" t="s">
+      <c r="H60" t="s">
         <v>265</v>
       </c>
       <c r="I60" t="s">
@@ -6316,42 +6390,45 @@
       <c r="J60" t="s">
         <v>456</v>
       </c>
-      <c r="K60" s="9" t="s">
+      <c r="K60" t="s">
         <v>648</v>
       </c>
-      <c r="L60" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M60" s="9">
+      <c r="L60" t="s">
+        <v>88</v>
+      </c>
+      <c r="M60">
         <v>3</v>
       </c>
-      <c r="N60" s="9" t="s">
+      <c r="N60" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="61" spans="1:14" hidden="1">
+      <c r="O60">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
       <c r="A61" t="s">
         <v>118</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B61" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="C61" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D61" s="9">
+      <c r="C61">
+        <v>2026</v>
+      </c>
+      <c r="D61">
         <v>5</v>
       </c>
-      <c r="E61" s="9" t="s">
+      <c r="E61" t="s">
         <v>404</v>
       </c>
-      <c r="F61" s="9" t="s">
+      <c r="F61" t="s">
         <v>45</v>
       </c>
-      <c r="G61" s="12">
+      <c r="G61" s="4">
         <v>10409054086</v>
       </c>
-      <c r="H61" s="9" t="s">
+      <c r="H61" t="s">
         <v>443</v>
       </c>
       <c r="I61" t="s">
@@ -6360,42 +6437,45 @@
       <c r="J61" t="s">
         <v>456</v>
       </c>
-      <c r="K61" s="9" t="s">
+      <c r="K61" t="s">
         <v>649</v>
       </c>
-      <c r="L61" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M61" s="9">
+      <c r="L61" t="s">
+        <v>88</v>
+      </c>
+      <c r="M61">
         <v>3</v>
       </c>
-      <c r="N61" s="9" t="s">
+      <c r="N61" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="62" spans="1:14" hidden="1">
+      <c r="O61">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15">
       <c r="A62" t="s">
         <v>119</v>
       </c>
-      <c r="B62" s="10" t="s">
+      <c r="B62" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="C62" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D62" s="9">
+      <c r="C62">
+        <v>2026</v>
+      </c>
+      <c r="D62">
         <v>5</v>
       </c>
-      <c r="E62" s="9" t="s">
+      <c r="E62" t="s">
         <v>404</v>
       </c>
-      <c r="F62" s="9" t="s">
+      <c r="F62" t="s">
         <v>45</v>
       </c>
-      <c r="G62" s="12">
+      <c r="G62" s="4">
         <v>10417044227</v>
       </c>
-      <c r="H62" s="9" t="s">
+      <c r="H62" t="s">
         <v>444</v>
       </c>
       <c r="I62" t="s">
@@ -6404,20 +6484,23 @@
       <c r="J62" t="s">
         <v>456</v>
       </c>
-      <c r="K62" s="9" t="s">
+      <c r="K62" t="s">
         <v>650</v>
       </c>
-      <c r="L62" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M62" s="9">
+      <c r="L62" t="s">
+        <v>88</v>
+      </c>
+      <c r="M62">
         <v>3</v>
       </c>
-      <c r="N62" s="9" t="s">
+      <c r="N62" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" hidden="1">
+      <c r="O62">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
       <c r="A63" t="s">
         <v>120</v>
       </c>
@@ -6460,8 +6543,11 @@
       <c r="N63" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" hidden="1">
+      <c r="O63">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15">
       <c r="A64" t="s">
         <v>121</v>
       </c>
@@ -6503,6 +6589,9 @@
       </c>
       <c r="N64" t="s">
         <v>90</v>
+      </c>
+      <c r="O64">
+        <v>3.3</v>
       </c>
     </row>
     <row r="65" spans="1:14">
@@ -6524,7 +6613,7 @@
       <c r="F65" t="s">
         <v>402</v>
       </c>
-      <c r="G65" s="13">
+      <c r="G65" s="4">
         <v>10248794386</v>
       </c>
       <c r="H65" t="s">
@@ -6568,7 +6657,7 @@
       <c r="F66" t="s">
         <v>402</v>
       </c>
-      <c r="G66" s="13">
+      <c r="G66" s="4">
         <v>10768336747</v>
       </c>
       <c r="H66" t="s">
@@ -6612,7 +6701,7 @@
       <c r="F67" t="s">
         <v>402</v>
       </c>
-      <c r="G67" s="13">
+      <c r="G67" s="4">
         <v>10781168772</v>
       </c>
       <c r="H67" t="s">
@@ -6656,7 +6745,7 @@
       <c r="F68" t="s">
         <v>402</v>
       </c>
-      <c r="G68" s="13">
+      <c r="G68" s="4">
         <v>10247103363</v>
       </c>
       <c r="H68" t="s">
@@ -6700,7 +6789,7 @@
       <c r="F69" t="s">
         <v>402</v>
       </c>
-      <c r="G69" s="13">
+      <c r="G69" s="4">
         <v>10748733910</v>
       </c>
       <c r="H69" t="s">
@@ -6744,7 +6833,7 @@
       <c r="F70" t="s">
         <v>402</v>
       </c>
-      <c r="G70" s="13">
+      <c r="G70" s="4">
         <v>10756599084</v>
       </c>
       <c r="H70" t="s">
@@ -6788,7 +6877,7 @@
       <c r="F71" t="s">
         <v>402</v>
       </c>
-      <c r="G71" s="13">
+      <c r="G71" s="4">
         <v>10409219999</v>
       </c>
       <c r="H71" t="s">
@@ -6832,7 +6921,7 @@
       <c r="F72" t="s">
         <v>402</v>
       </c>
-      <c r="G72" s="13">
+      <c r="G72" s="4">
         <v>10248714277</v>
       </c>
       <c r="H72" t="s">
@@ -6876,7 +6965,7 @@
       <c r="F73" t="s">
         <v>402</v>
       </c>
-      <c r="G73" s="13">
+      <c r="G73" s="4">
         <v>10248660908</v>
       </c>
       <c r="H73" t="s">
@@ -6920,7 +7009,7 @@
       <c r="F74" t="s">
         <v>402</v>
       </c>
-      <c r="G74" s="13">
+      <c r="G74" s="4">
         <v>10248900984</v>
       </c>
       <c r="H74" t="s">
@@ -6964,7 +7053,7 @@
       <c r="F75" t="s">
         <v>402</v>
       </c>
-      <c r="G75" s="13">
+      <c r="G75" s="4">
         <v>10482266130</v>
       </c>
       <c r="H75" t="s">
@@ -7008,7 +7097,7 @@
       <c r="F76" t="s">
         <v>402</v>
       </c>
-      <c r="G76" s="13">
+      <c r="G76" s="4">
         <v>10435553881</v>
       </c>
       <c r="H76" t="s">
@@ -7052,7 +7141,7 @@
       <c r="F77" t="s">
         <v>402</v>
       </c>
-      <c r="G77" s="13">
+      <c r="G77" s="4">
         <v>10239802821</v>
       </c>
       <c r="H77" t="s">
@@ -7096,7 +7185,7 @@
       <c r="F78" t="s">
         <v>402</v>
       </c>
-      <c r="G78" s="13">
+      <c r="G78" s="4">
         <v>10239106876</v>
       </c>
       <c r="H78" t="s">
@@ -7140,7 +7229,7 @@
       <c r="F79" t="s">
         <v>402</v>
       </c>
-      <c r="G79" s="13">
+      <c r="G79" s="4">
         <v>10238784986</v>
       </c>
       <c r="H79" t="s">
@@ -7184,7 +7273,7 @@
       <c r="F80" t="s">
         <v>402</v>
       </c>
-      <c r="G80" s="13">
+      <c r="G80" s="4">
         <v>40241978</v>
       </c>
       <c r="H80" t="s">
@@ -7209,7 +7298,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:15">
       <c r="A81" t="s">
         <v>138</v>
       </c>
@@ -7228,7 +7317,7 @@
       <c r="F81" t="s">
         <v>402</v>
       </c>
-      <c r="G81" s="13">
+      <c r="G81" s="4">
         <v>10462678571</v>
       </c>
       <c r="H81" t="s">
@@ -7253,7 +7342,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:15">
       <c r="A82" t="s">
         <v>139</v>
       </c>
@@ -7272,7 +7361,7 @@
       <c r="F82" t="s">
         <v>402</v>
       </c>
-      <c r="G82" s="13">
+      <c r="G82" s="4">
         <v>10092214023</v>
       </c>
       <c r="H82" t="s">
@@ -7297,7 +7386,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:15">
       <c r="A83" t="s">
         <v>140</v>
       </c>
@@ -7316,7 +7405,7 @@
       <c r="F83" t="s">
         <v>402</v>
       </c>
-      <c r="G83" s="13">
+      <c r="G83" s="4">
         <v>42421067</v>
       </c>
       <c r="H83" t="s">
@@ -7341,7 +7430,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:15">
       <c r="A84" t="s">
         <v>141</v>
       </c>
@@ -7360,7 +7449,7 @@
       <c r="F84" t="s">
         <v>402</v>
       </c>
-      <c r="G84" s="13">
+      <c r="G84" s="4">
         <v>10238643479</v>
       </c>
       <c r="H84" t="s">
@@ -7385,26 +7474,26 @@
         <v>89</v>
       </c>
     </row>
-    <row r="85" spans="1:14" hidden="1">
+    <row r="85" spans="1:15">
       <c r="A85" t="s">
         <v>142</v>
       </c>
-      <c r="B85" s="11" t="s">
+      <c r="B85" s="4" t="s">
         <v>923</v>
       </c>
-      <c r="C85" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D85" s="9">
+      <c r="C85">
+        <v>2026</v>
+      </c>
+      <c r="D85">
         <v>6</v>
       </c>
-      <c r="E85" s="9" t="s">
+      <c r="E85" t="s">
         <v>404</v>
       </c>
-      <c r="F85" s="9" t="s">
+      <c r="F85" t="s">
         <v>45</v>
       </c>
-      <c r="G85" s="13">
+      <c r="G85" s="4">
         <v>10409054086</v>
       </c>
       <c r="H85" t="s">
@@ -7419,17 +7508,20 @@
       <c r="K85" t="s">
         <v>1039</v>
       </c>
-      <c r="L85" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M85" s="9">
+      <c r="L85" t="s">
+        <v>88</v>
+      </c>
+      <c r="M85">
         <v>1</v>
       </c>
       <c r="N85" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="86" spans="1:14">
+      <c r="O85">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15">
       <c r="A86" t="s">
         <v>143</v>
       </c>
@@ -7473,7 +7565,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:15">
       <c r="A87" t="s">
         <v>144</v>
       </c>
@@ -7517,7 +7609,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="88" spans="1:14" hidden="1">
+    <row r="88" spans="1:15">
       <c r="A88" t="s">
         <v>145</v>
       </c>
@@ -7560,27 +7652,30 @@
       <c r="N88" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="89" spans="1:14" hidden="1">
+      <c r="O88">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15">
       <c r="A89" t="s">
         <v>146</v>
       </c>
-      <c r="B89" s="11" t="s">
+      <c r="B89" s="4" t="s">
         <v>1013</v>
       </c>
-      <c r="C89" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D89" s="9">
+      <c r="C89">
+        <v>2026</v>
+      </c>
+      <c r="D89">
         <v>6</v>
       </c>
-      <c r="E89" s="9" t="s">
+      <c r="E89" t="s">
         <v>404</v>
       </c>
-      <c r="F89" s="9" t="s">
+      <c r="F89" t="s">
         <v>45</v>
       </c>
-      <c r="G89" s="13">
+      <c r="G89" s="4">
         <v>10487664958</v>
       </c>
       <c r="H89" t="s">
@@ -7595,17 +7690,20 @@
       <c r="K89" t="s">
         <v>1040</v>
       </c>
-      <c r="L89" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M89" s="9">
+      <c r="L89" t="s">
+        <v>88</v>
+      </c>
+      <c r="M89">
         <v>1</v>
       </c>
       <c r="N89" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="90" spans="1:14">
+      <c r="O89">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15">
       <c r="A90" t="s">
         <v>147</v>
       </c>
@@ -7649,7 +7747,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:15">
       <c r="A91" t="s">
         <v>148</v>
       </c>
@@ -7693,7 +7791,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:15">
       <c r="A92" t="s">
         <v>149</v>
       </c>
@@ -7737,7 +7835,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:15">
       <c r="A93" t="s">
         <v>150</v>
       </c>
@@ -7781,7 +7879,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="94" spans="1:14" hidden="1">
+    <row r="94" spans="1:15">
       <c r="A94" t="s">
         <v>151</v>
       </c>
@@ -7824,8 +7922,11 @@
       <c r="N94" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="95" spans="1:14" hidden="1">
+      <c r="O94">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15">
       <c r="A95" t="s">
         <v>152</v>
       </c>
@@ -7868,8 +7969,11 @@
       <c r="N95" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="96" spans="1:14" hidden="1">
+      <c r="O95">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15">
       <c r="A96" t="s">
         <v>153</v>
       </c>
@@ -7912,8 +8016,11 @@
       <c r="N96" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="97" spans="1:14">
+      <c r="O96">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15">
       <c r="A97" t="s">
         <v>154</v>
       </c>
@@ -7957,29 +8064,29 @@
         <v>89</v>
       </c>
     </row>
-    <row r="98" spans="1:14" hidden="1">
+    <row r="98" spans="1:15">
       <c r="A98" t="s">
         <v>155</v>
       </c>
-      <c r="B98" s="10" t="s">
+      <c r="B98" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="C98" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D98" s="9">
+      <c r="C98">
+        <v>2026</v>
+      </c>
+      <c r="D98">
         <v>5</v>
       </c>
-      <c r="E98" s="9" t="s">
+      <c r="E98" t="s">
         <v>404</v>
       </c>
-      <c r="F98" s="9" t="s">
+      <c r="F98" t="s">
         <v>45</v>
       </c>
-      <c r="G98" s="12">
+      <c r="G98" s="4">
         <v>10487664958</v>
       </c>
-      <c r="H98" s="9" t="s">
+      <c r="H98" t="s">
         <v>265</v>
       </c>
       <c r="I98" t="s">
@@ -7988,42 +8095,45 @@
       <c r="J98" t="s">
         <v>455</v>
       </c>
-      <c r="K98" s="9" t="s">
+      <c r="K98" t="s">
         <v>647</v>
       </c>
-      <c r="L98" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M98" s="9">
+      <c r="L98" t="s">
+        <v>88</v>
+      </c>
+      <c r="M98">
         <v>3</v>
       </c>
-      <c r="N98" s="9" t="s">
+      <c r="N98" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="99" spans="1:14" hidden="1">
+      <c r="O98">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15">
       <c r="A99" t="s">
         <v>156</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B99" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="C99" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D99" s="9">
+      <c r="C99">
+        <v>2026</v>
+      </c>
+      <c r="D99">
         <v>5</v>
       </c>
-      <c r="E99" s="9" t="s">
+      <c r="E99" t="s">
         <v>404</v>
       </c>
-      <c r="F99" s="9" t="s">
+      <c r="F99" t="s">
         <v>45</v>
       </c>
-      <c r="G99" s="12">
+      <c r="G99" s="4">
         <v>10409054086</v>
       </c>
-      <c r="H99" s="9" t="s">
+      <c r="H99" t="s">
         <v>443</v>
       </c>
       <c r="I99" t="s">
@@ -8032,42 +8142,45 @@
       <c r="J99" t="s">
         <v>455</v>
       </c>
-      <c r="K99" s="9" t="s">
+      <c r="K99" t="s">
         <v>647</v>
       </c>
-      <c r="L99" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M99" s="9">
+      <c r="L99" t="s">
+        <v>88</v>
+      </c>
+      <c r="M99">
         <v>3</v>
       </c>
-      <c r="N99" s="9" t="s">
+      <c r="N99" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="100" spans="1:14" hidden="1">
+      <c r="O99">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15">
       <c r="A100" t="s">
         <v>157</v>
       </c>
-      <c r="B100" s="10" t="s">
+      <c r="B100" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="C100" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D100" s="9">
+      <c r="C100">
+        <v>2026</v>
+      </c>
+      <c r="D100">
         <v>5</v>
       </c>
-      <c r="E100" s="9" t="s">
+      <c r="E100" t="s">
         <v>404</v>
       </c>
-      <c r="F100" s="9" t="s">
+      <c r="F100" t="s">
         <v>45</v>
       </c>
-      <c r="G100" s="12">
+      <c r="G100" s="4">
         <v>10417044227</v>
       </c>
-      <c r="H100" s="9" t="s">
+      <c r="H100" t="s">
         <v>444</v>
       </c>
       <c r="I100" t="s">
@@ -8076,20 +8189,23 @@
       <c r="J100" t="s">
         <v>455</v>
       </c>
-      <c r="K100" s="9" t="s">
+      <c r="K100" t="s">
         <v>647</v>
       </c>
-      <c r="L100" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M100" s="9">
+      <c r="L100" t="s">
+        <v>88</v>
+      </c>
+      <c r="M100">
         <v>3</v>
       </c>
-      <c r="N100" s="9" t="s">
+      <c r="N100" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="101" spans="1:14" hidden="1">
+      <c r="O100">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15">
       <c r="A101" t="s">
         <v>158</v>
       </c>
@@ -8132,8 +8248,11 @@
       <c r="N101" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="102" spans="1:14" hidden="1">
+      <c r="O101">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15">
       <c r="A102" t="s">
         <v>159</v>
       </c>
@@ -8176,8 +8295,11 @@
       <c r="N102" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="103" spans="1:14">
+      <c r="O102">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15">
       <c r="A103" t="s">
         <v>160</v>
       </c>
@@ -8196,7 +8318,7 @@
       <c r="F103" t="s">
         <v>402</v>
       </c>
-      <c r="G103" s="13">
+      <c r="G103" s="4">
         <v>10755814615</v>
       </c>
       <c r="H103" t="s">
@@ -8221,7 +8343,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:15">
       <c r="A104" t="s">
         <v>161</v>
       </c>
@@ -8240,7 +8362,7 @@
       <c r="F104" t="s">
         <v>402</v>
       </c>
-      <c r="G104" s="13">
+      <c r="G104" s="4">
         <v>10238394711</v>
       </c>
       <c r="H104" t="s">
@@ -8265,7 +8387,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="105" spans="1:14">
+    <row r="105" spans="1:15">
       <c r="A105" t="s">
         <v>162</v>
       </c>
@@ -8284,7 +8406,7 @@
       <c r="F105" t="s">
         <v>402</v>
       </c>
-      <c r="G105" s="13">
+      <c r="G105" s="4">
         <v>10420101631</v>
       </c>
       <c r="H105" t="s">
@@ -8309,7 +8431,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:14">
+    <row r="106" spans="1:15">
       <c r="A106" t="s">
         <v>163</v>
       </c>
@@ -8328,7 +8450,7 @@
       <c r="F106" t="s">
         <v>402</v>
       </c>
-      <c r="G106" s="13">
+      <c r="G106" s="4">
         <v>10700932929</v>
       </c>
       <c r="H106" t="s">
@@ -8353,7 +8475,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="107" spans="1:14">
+    <row r="107" spans="1:15">
       <c r="A107" t="s">
         <v>164</v>
       </c>
@@ -8372,7 +8494,7 @@
       <c r="F107" t="s">
         <v>402</v>
       </c>
-      <c r="G107" s="13">
+      <c r="G107" s="4">
         <v>10700799889</v>
       </c>
       <c r="H107" t="s">
@@ -8397,7 +8519,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="108" spans="1:14">
+    <row r="108" spans="1:15">
       <c r="A108" t="s">
         <v>165</v>
       </c>
@@ -8416,7 +8538,7 @@
       <c r="F108" t="s">
         <v>402</v>
       </c>
-      <c r="G108" s="13">
+      <c r="G108" s="4">
         <v>10238643479</v>
       </c>
       <c r="H108" t="s">
@@ -8441,7 +8563,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="109" spans="1:14">
+    <row r="109" spans="1:15">
       <c r="A109" t="s">
         <v>166</v>
       </c>
@@ -8460,7 +8582,7 @@
       <c r="F109" t="s">
         <v>402</v>
       </c>
-      <c r="G109" s="13">
+      <c r="G109" s="4">
         <v>10204218736</v>
       </c>
       <c r="H109" t="s">
@@ -8485,7 +8607,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="110" spans="1:14">
+    <row r="110" spans="1:15">
       <c r="A110" t="s">
         <v>167</v>
       </c>
@@ -8504,7 +8626,7 @@
       <c r="F110" t="s">
         <v>402</v>
       </c>
-      <c r="G110" s="13">
+      <c r="G110" s="4">
         <v>10752532619</v>
       </c>
       <c r="H110" t="s">
@@ -8529,7 +8651,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="111" spans="1:14">
+    <row r="111" spans="1:15">
       <c r="A111" t="s">
         <v>168</v>
       </c>
@@ -8548,7 +8670,7 @@
       <c r="F111" t="s">
         <v>402</v>
       </c>
-      <c r="G111" s="13">
+      <c r="G111" s="4">
         <v>10421627733</v>
       </c>
       <c r="H111" t="s">
@@ -8573,7 +8695,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="112" spans="1:14">
+    <row r="112" spans="1:15">
       <c r="A112" t="s">
         <v>169</v>
       </c>
@@ -8592,7 +8714,7 @@
       <c r="F112" t="s">
         <v>402</v>
       </c>
-      <c r="G112" s="13">
+      <c r="G112" s="4">
         <v>20602367704</v>
       </c>
       <c r="H112" t="s">
@@ -8617,7 +8739,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="113" spans="1:14">
+    <row r="113" spans="1:15">
       <c r="A113" t="s">
         <v>170</v>
       </c>
@@ -8636,7 +8758,7 @@
       <c r="F113" t="s">
         <v>402</v>
       </c>
-      <c r="G113" s="13">
+      <c r="G113" s="4">
         <v>10712579566</v>
       </c>
       <c r="H113" t="s">
@@ -8661,7 +8783,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="114" spans="1:14">
+    <row r="114" spans="1:15">
       <c r="A114" t="s">
         <v>171</v>
       </c>
@@ -8680,7 +8802,7 @@
       <c r="F114" t="s">
         <v>402</v>
       </c>
-      <c r="G114" s="13">
+      <c r="G114" s="4">
         <v>10239455951</v>
       </c>
       <c r="H114" t="s">
@@ -8705,7 +8827,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="115" spans="1:14">
+    <row r="115" spans="1:15">
       <c r="A115" t="s">
         <v>172</v>
       </c>
@@ -8724,7 +8846,7 @@
       <c r="F115" t="s">
         <v>402</v>
       </c>
-      <c r="G115" s="13">
+      <c r="G115" s="4">
         <v>10454593494</v>
       </c>
       <c r="H115" t="s">
@@ -8749,7 +8871,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="116" spans="1:14">
+    <row r="116" spans="1:15">
       <c r="A116" t="s">
         <v>173</v>
       </c>
@@ -8768,7 +8890,7 @@
       <c r="F116" t="s">
         <v>402</v>
       </c>
-      <c r="G116" s="13">
+      <c r="G116" s="4">
         <v>10238394711</v>
       </c>
       <c r="H116" t="s">
@@ -8793,7 +8915,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="117" spans="1:14">
+    <row r="117" spans="1:15">
       <c r="A117" t="s">
         <v>174</v>
       </c>
@@ -8812,7 +8934,7 @@
       <c r="F117" t="s">
         <v>402</v>
       </c>
-      <c r="G117" s="13">
+      <c r="G117" s="4">
         <v>10096063038</v>
       </c>
       <c r="H117" t="s">
@@ -8837,7 +8959,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="118" spans="1:14">
+    <row r="118" spans="1:15">
       <c r="A118" t="s">
         <v>175</v>
       </c>
@@ -8856,7 +8978,7 @@
       <c r="F118" t="s">
         <v>402</v>
       </c>
-      <c r="G118" s="13">
+      <c r="G118" s="4">
         <v>10469043296</v>
       </c>
       <c r="H118" t="s">
@@ -8881,7 +9003,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="119" spans="1:14">
+    <row r="119" spans="1:15">
       <c r="A119" t="s">
         <v>176</v>
       </c>
@@ -8900,7 +9022,7 @@
       <c r="F119" t="s">
         <v>402</v>
       </c>
-      <c r="G119" s="13">
+      <c r="G119" s="4">
         <v>10440425696</v>
       </c>
       <c r="H119" t="s">
@@ -8925,29 +9047,29 @@
         <v>89</v>
       </c>
     </row>
-    <row r="120" spans="1:14" hidden="1">
+    <row r="120" spans="1:15">
       <c r="A120" t="s">
         <v>177</v>
       </c>
-      <c r="B120" s="10" t="s">
+      <c r="B120" s="3" t="s">
         <v>927</v>
       </c>
-      <c r="C120" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D120" s="9">
+      <c r="C120">
+        <v>2026</v>
+      </c>
+      <c r="D120">
         <v>6</v>
       </c>
-      <c r="E120" s="9" t="s">
+      <c r="E120" t="s">
         <v>404</v>
       </c>
-      <c r="F120" s="9" t="s">
+      <c r="F120" t="s">
         <v>45</v>
       </c>
-      <c r="G120" s="12">
+      <c r="G120" s="4">
         <v>10239802872</v>
       </c>
-      <c r="H120" s="9" t="s">
+      <c r="H120" t="s">
         <v>79</v>
       </c>
       <c r="I120" t="s">
@@ -8956,20 +9078,23 @@
       <c r="J120" t="s">
         <v>454</v>
       </c>
-      <c r="K120" s="9" t="s">
+      <c r="K120" t="s">
         <v>1041</v>
       </c>
-      <c r="L120" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M120" s="9">
-        <v>1</v>
-      </c>
-      <c r="N120" s="9" t="s">
+      <c r="L120" t="s">
+        <v>88</v>
+      </c>
+      <c r="M120">
+        <v>1</v>
+      </c>
+      <c r="N120" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="121" spans="1:14">
+      <c r="O120">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15">
       <c r="A121" t="s">
         <v>178</v>
       </c>
@@ -9013,7 +9138,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="122" spans="1:14">
+    <row r="122" spans="1:15">
       <c r="A122" t="s">
         <v>179</v>
       </c>
@@ -9057,7 +9182,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="123" spans="1:14">
+    <row r="123" spans="1:15">
       <c r="A123" t="s">
         <v>180</v>
       </c>
@@ -9101,7 +9226,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="124" spans="1:14">
+    <row r="124" spans="1:15">
       <c r="A124" t="s">
         <v>181</v>
       </c>
@@ -9145,7 +9270,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="125" spans="1:14">
+    <row r="125" spans="1:15">
       <c r="A125" t="s">
         <v>182</v>
       </c>
@@ -9189,7 +9314,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="126" spans="1:14" hidden="1">
+    <row r="126" spans="1:15">
       <c r="A126" t="s">
         <v>183</v>
       </c>
@@ -9232,8 +9357,11 @@
       <c r="N126" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="127" spans="1:14" hidden="1">
+      <c r="O126">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15">
       <c r="A127" t="s">
         <v>184</v>
       </c>
@@ -9276,8 +9404,11 @@
       <c r="N127" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="128" spans="1:14" hidden="1">
+      <c r="O127">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15">
       <c r="A128" t="s">
         <v>185</v>
       </c>
@@ -9320,8 +9451,11 @@
       <c r="N128" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="129" spans="1:14" hidden="1">
+      <c r="O128">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15">
       <c r="A129" t="s">
         <v>186</v>
       </c>
@@ -9364,30 +9498,33 @@
       <c r="N129" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="130" spans="1:14" hidden="1">
+      <c r="O129">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15">
       <c r="A130" t="s">
         <v>187</v>
       </c>
-      <c r="B130" s="10" t="s">
+      <c r="B130" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="C130" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D130" s="9">
+      <c r="C130">
+        <v>2026</v>
+      </c>
+      <c r="D130">
         <v>5</v>
       </c>
-      <c r="E130" s="9" t="s">
+      <c r="E130" t="s">
         <v>404</v>
       </c>
-      <c r="F130" s="9" t="s">
+      <c r="F130" t="s">
         <v>45</v>
       </c>
-      <c r="G130" s="12">
+      <c r="G130" s="4">
         <v>10239118211</v>
       </c>
-      <c r="H130" s="9" t="s">
+      <c r="H130" t="s">
         <v>258</v>
       </c>
       <c r="I130" t="s">
@@ -9396,42 +9533,45 @@
       <c r="J130" t="s">
         <v>456</v>
       </c>
-      <c r="K130" s="9" t="s">
+      <c r="K130" t="s">
         <v>648</v>
       </c>
-      <c r="L130" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M130" s="9">
+      <c r="L130" t="s">
+        <v>88</v>
+      </c>
+      <c r="M130">
         <v>3</v>
       </c>
-      <c r="N130" s="9" t="s">
+      <c r="N130" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="131" spans="1:14" hidden="1">
+      <c r="O130">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15">
       <c r="A131" t="s">
         <v>188</v>
       </c>
-      <c r="B131" s="10" t="s">
+      <c r="B131" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="C131" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D131" s="9">
+      <c r="C131">
+        <v>2026</v>
+      </c>
+      <c r="D131">
         <v>5</v>
       </c>
-      <c r="E131" s="9" t="s">
+      <c r="E131" t="s">
         <v>404</v>
       </c>
-      <c r="F131" s="9" t="s">
+      <c r="F131" t="s">
         <v>45</v>
       </c>
-      <c r="G131" s="12">
+      <c r="G131" s="4">
         <v>10239478676</v>
       </c>
-      <c r="H131" s="9" t="s">
+      <c r="H131" t="s">
         <v>306</v>
       </c>
       <c r="I131" t="s">
@@ -9440,42 +9580,45 @@
       <c r="J131" t="s">
         <v>456</v>
       </c>
-      <c r="K131" s="9" t="s">
+      <c r="K131" t="s">
         <v>648</v>
       </c>
-      <c r="L131" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M131" s="9">
+      <c r="L131" t="s">
+        <v>88</v>
+      </c>
+      <c r="M131">
         <v>3</v>
       </c>
-      <c r="N131" s="9" t="s">
+      <c r="N131" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="132" spans="1:14" hidden="1">
+      <c r="O131">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15">
       <c r="A132" t="s">
         <v>189</v>
       </c>
-      <c r="B132" s="10" t="s">
+      <c r="B132" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="C132" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D132" s="9">
+      <c r="C132">
+        <v>2026</v>
+      </c>
+      <c r="D132">
         <v>5</v>
       </c>
-      <c r="E132" s="9" t="s">
+      <c r="E132" t="s">
         <v>404</v>
       </c>
-      <c r="F132" s="9" t="s">
+      <c r="F132" t="s">
         <v>45</v>
       </c>
-      <c r="G132" s="12">
+      <c r="G132" s="4">
         <v>10239802872</v>
       </c>
-      <c r="H132" s="9" t="s">
+      <c r="H132" t="s">
         <v>79</v>
       </c>
       <c r="I132" t="s">
@@ -9484,20 +9627,23 @@
       <c r="J132" t="s">
         <v>456</v>
       </c>
-      <c r="K132" s="9" t="s">
+      <c r="K132" t="s">
         <v>648</v>
       </c>
-      <c r="L132" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M132" s="9">
+      <c r="L132" t="s">
+        <v>88</v>
+      </c>
+      <c r="M132">
         <v>3</v>
       </c>
-      <c r="N132" s="9" t="s">
+      <c r="N132" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="133" spans="1:14" hidden="1">
+      <c r="O132">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15">
       <c r="A133" t="s">
         <v>190</v>
       </c>
@@ -9540,8 +9686,11 @@
       <c r="N133" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="134" spans="1:14" hidden="1">
+      <c r="O133">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15">
       <c r="A134" t="s">
         <v>191</v>
       </c>
@@ -9584,8 +9733,11 @@
       <c r="N134" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="135" spans="1:14" hidden="1">
+      <c r="O134">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15">
       <c r="A135" t="s">
         <v>318</v>
       </c>
@@ -9628,8 +9780,11 @@
       <c r="N135" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="136" spans="1:14">
+      <c r="O135">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15">
       <c r="A136" t="s">
         <v>319</v>
       </c>
@@ -9648,7 +9803,7 @@
       <c r="F136" t="s">
         <v>467</v>
       </c>
-      <c r="G136" s="13">
+      <c r="G136" s="4">
         <v>10704606783</v>
       </c>
       <c r="H136" t="s">
@@ -9673,7 +9828,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="137" spans="1:14">
+    <row r="137" spans="1:15">
       <c r="A137" t="s">
         <v>320</v>
       </c>
@@ -9692,7 +9847,7 @@
       <c r="F137" t="s">
         <v>467</v>
       </c>
-      <c r="G137" s="13">
+      <c r="G137" s="4">
         <v>10448659068</v>
       </c>
       <c r="H137" t="s">
@@ -9717,7 +9872,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="138" spans="1:14">
+    <row r="138" spans="1:15">
       <c r="A138" t="s">
         <v>321</v>
       </c>
@@ -9736,7 +9891,7 @@
       <c r="F138" t="s">
         <v>467</v>
       </c>
-      <c r="G138" s="13">
+      <c r="G138" s="4">
         <v>10239756587</v>
       </c>
       <c r="H138" t="s">
@@ -9761,7 +9916,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="139" spans="1:14">
+    <row r="139" spans="1:15">
       <c r="A139" t="s">
         <v>322</v>
       </c>
@@ -9780,7 +9935,7 @@
       <c r="F139" t="s">
         <v>467</v>
       </c>
-      <c r="G139" s="13">
+      <c r="G139" s="4">
         <v>10473163450</v>
       </c>
       <c r="H139" t="s">
@@ -9805,7 +9960,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="140" spans="1:14">
+    <row r="140" spans="1:15">
       <c r="A140" t="s">
         <v>323</v>
       </c>
@@ -9824,7 +9979,7 @@
       <c r="F140" t="s">
         <v>467</v>
       </c>
-      <c r="G140" s="13">
+      <c r="G140" s="4">
         <v>10802446107</v>
       </c>
       <c r="H140" t="s">
@@ -9849,7 +10004,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="141" spans="1:14">
+    <row r="141" spans="1:15">
       <c r="A141" t="s">
         <v>324</v>
       </c>
@@ -9868,7 +10023,7 @@
       <c r="F141" t="s">
         <v>467</v>
       </c>
-      <c r="G141" s="13">
+      <c r="G141" s="4">
         <v>10409212480</v>
       </c>
       <c r="H141" t="s">
@@ -9893,7 +10048,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="142" spans="1:14">
+    <row r="142" spans="1:15">
       <c r="A142" t="s">
         <v>325</v>
       </c>
@@ -9912,7 +10067,7 @@
       <c r="F142" t="s">
         <v>467</v>
       </c>
-      <c r="G142" s="13">
+      <c r="G142" s="4">
         <v>10433498394</v>
       </c>
       <c r="H142" t="s">
@@ -9937,7 +10092,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="143" spans="1:14">
+    <row r="143" spans="1:15">
       <c r="A143" t="s">
         <v>326</v>
       </c>
@@ -9956,7 +10111,7 @@
       <c r="F143" t="s">
         <v>467</v>
       </c>
-      <c r="G143" s="13">
+      <c r="G143" s="4">
         <v>10477489261</v>
       </c>
       <c r="H143" t="s">
@@ -9981,7 +10136,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="144" spans="1:14">
+    <row r="144" spans="1:15">
       <c r="A144" t="s">
         <v>327</v>
       </c>
@@ -10000,7 +10155,7 @@
       <c r="F144" t="s">
         <v>467</v>
       </c>
-      <c r="G144" s="13">
+      <c r="G144" s="4">
         <v>10466170203</v>
       </c>
       <c r="H144" t="s">
@@ -10025,7 +10180,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="145" spans="1:14">
+    <row r="145" spans="1:15">
       <c r="A145" t="s">
         <v>328</v>
       </c>
@@ -10044,7 +10199,7 @@
       <c r="F145" t="s">
         <v>467</v>
       </c>
-      <c r="G145" s="13">
+      <c r="G145" s="4">
         <v>10760499493</v>
       </c>
       <c r="H145" t="s">
@@ -10069,7 +10224,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="146" spans="1:14">
+    <row r="146" spans="1:15">
       <c r="A146" t="s">
         <v>329</v>
       </c>
@@ -10088,7 +10243,7 @@
       <c r="F146" t="s">
         <v>467</v>
       </c>
-      <c r="G146" s="13">
+      <c r="G146" s="4">
         <v>10722810240</v>
       </c>
       <c r="H146" t="s">
@@ -10113,7 +10268,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="147" spans="1:14">
+    <row r="147" spans="1:15">
       <c r="A147" t="s">
         <v>330</v>
       </c>
@@ -10132,7 +10287,7 @@
       <c r="F147" t="s">
         <v>467</v>
       </c>
-      <c r="G147" s="13">
+      <c r="G147" s="4">
         <v>10419589859</v>
       </c>
       <c r="H147" t="s">
@@ -10157,7 +10312,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="148" spans="1:14">
+    <row r="148" spans="1:15">
       <c r="A148" t="s">
         <v>331</v>
       </c>
@@ -10176,7 +10331,7 @@
       <c r="F148" t="s">
         <v>467</v>
       </c>
-      <c r="G148" s="13">
+      <c r="G148" s="4">
         <v>10426361936</v>
       </c>
       <c r="H148" t="s">
@@ -10201,7 +10356,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="149" spans="1:14">
+    <row r="149" spans="1:15">
       <c r="A149" t="s">
         <v>332</v>
       </c>
@@ -10220,7 +10375,7 @@
       <c r="F149" t="s">
         <v>467</v>
       </c>
-      <c r="G149" s="13">
+      <c r="G149" s="4">
         <v>10253224806</v>
       </c>
       <c r="H149" t="s">
@@ -10245,7 +10400,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="150" spans="1:14">
+    <row r="150" spans="1:15">
       <c r="A150" t="s">
         <v>333</v>
       </c>
@@ -10264,7 +10419,7 @@
       <c r="F150" t="s">
         <v>467</v>
       </c>
-      <c r="G150" s="13">
+      <c r="G150" s="4">
         <v>10249582862</v>
       </c>
       <c r="H150" t="s">
@@ -10289,29 +10444,29 @@
         <v>89</v>
       </c>
     </row>
-    <row r="151" spans="1:14" hidden="1">
+    <row r="151" spans="1:15">
       <c r="A151" t="s">
         <v>334</v>
       </c>
-      <c r="B151" s="10" t="s">
+      <c r="B151" s="3" t="s">
         <v>926</v>
       </c>
-      <c r="C151" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D151" s="9">
+      <c r="C151">
+        <v>2026</v>
+      </c>
+      <c r="D151">
         <v>6</v>
       </c>
-      <c r="E151" s="9" t="s">
+      <c r="E151" t="s">
         <v>404</v>
       </c>
-      <c r="F151" s="9" t="s">
+      <c r="F151" t="s">
         <v>45</v>
       </c>
-      <c r="G151" s="12">
+      <c r="G151" s="4">
         <v>10239478676</v>
       </c>
-      <c r="H151" s="9" t="s">
+      <c r="H151" t="s">
         <v>306</v>
       </c>
       <c r="I151" t="s">
@@ -10320,20 +10475,23 @@
       <c r="J151" t="s">
         <v>454</v>
       </c>
-      <c r="K151" s="9" t="s">
+      <c r="K151" t="s">
         <v>1042</v>
       </c>
-      <c r="L151" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M151" s="9">
-        <v>1</v>
-      </c>
-      <c r="N151" s="9" t="s">
+      <c r="L151" t="s">
+        <v>88</v>
+      </c>
+      <c r="M151">
+        <v>1</v>
+      </c>
+      <c r="N151" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="152" spans="1:14">
+      <c r="O151">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15">
       <c r="A152" t="s">
         <v>335</v>
       </c>
@@ -10377,7 +10535,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="153" spans="1:14">
+    <row r="153" spans="1:15">
       <c r="A153" t="s">
         <v>336</v>
       </c>
@@ -10421,7 +10579,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="154" spans="1:14">
+    <row r="154" spans="1:15">
       <c r="A154" t="s">
         <v>337</v>
       </c>
@@ -10465,7 +10623,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="155" spans="1:14">
+    <row r="155" spans="1:15">
       <c r="A155" t="s">
         <v>338</v>
       </c>
@@ -10509,7 +10667,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="156" spans="1:14" hidden="1">
+    <row r="156" spans="1:15">
       <c r="A156" t="s">
         <v>339</v>
       </c>
@@ -10552,8 +10710,11 @@
       <c r="N156" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="157" spans="1:14" hidden="1">
+      <c r="O156">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15">
       <c r="A157" t="s">
         <v>340</v>
       </c>
@@ -10596,8 +10757,11 @@
       <c r="N157" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="158" spans="1:14" hidden="1">
+      <c r="O157">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15">
       <c r="A158" t="s">
         <v>341</v>
       </c>
@@ -10640,8 +10804,11 @@
       <c r="N158" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="159" spans="1:14" hidden="1">
+      <c r="O158">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15">
       <c r="A159" t="s">
         <v>342</v>
       </c>
@@ -10684,8 +10851,11 @@
       <c r="N159" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="160" spans="1:14" hidden="1">
+      <c r="O159">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15">
       <c r="A160" t="s">
         <v>343</v>
       </c>
@@ -10728,8 +10898,11 @@
       <c r="N160" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="161" spans="1:14">
+      <c r="O160">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15">
       <c r="A161" t="s">
         <v>344</v>
       </c>
@@ -10773,7 +10946,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="162" spans="1:14" hidden="1">
+    <row r="162" spans="1:15">
       <c r="A162" t="s">
         <v>345</v>
       </c>
@@ -10816,30 +10989,33 @@
       <c r="N162" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="163" spans="1:14" hidden="1">
+      <c r="O162">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15">
       <c r="A163" t="s">
         <v>346</v>
       </c>
-      <c r="B163" s="10" t="s">
+      <c r="B163" s="3" t="s">
         <v>1011</v>
       </c>
-      <c r="C163" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D163" s="9">
+      <c r="C163">
+        <v>2026</v>
+      </c>
+      <c r="D163">
         <v>6</v>
       </c>
-      <c r="E163" s="9" t="s">
+      <c r="E163" t="s">
         <v>404</v>
       </c>
-      <c r="F163" s="9" t="s">
+      <c r="F163" t="s">
         <v>45</v>
       </c>
-      <c r="G163" s="12">
+      <c r="G163" s="4">
         <v>10239118211</v>
       </c>
-      <c r="H163" s="9" t="s">
+      <c r="H163" t="s">
         <v>258</v>
       </c>
       <c r="I163" t="s">
@@ -10848,20 +11024,23 @@
       <c r="J163" t="s">
         <v>454</v>
       </c>
-      <c r="K163" s="9" t="s">
+      <c r="K163" t="s">
         <v>1043</v>
       </c>
-      <c r="L163" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M163" s="9">
-        <v>1</v>
-      </c>
-      <c r="N163" s="9" t="s">
+      <c r="L163" t="s">
+        <v>88</v>
+      </c>
+      <c r="M163">
+        <v>1</v>
+      </c>
+      <c r="N163" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="164" spans="1:14">
+      <c r="O163">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15">
       <c r="A164" t="s">
         <v>347</v>
       </c>
@@ -10905,7 +11084,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="165" spans="1:14">
+    <row r="165" spans="1:15">
       <c r="A165" t="s">
         <v>348</v>
       </c>
@@ -10949,7 +11128,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="166" spans="1:14">
+    <row r="166" spans="1:15">
       <c r="A166" t="s">
         <v>349</v>
       </c>
@@ -10993,7 +11172,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="167" spans="1:14" hidden="1">
+    <row r="167" spans="1:15">
       <c r="A167" t="s">
         <v>350</v>
       </c>
@@ -11036,8 +11215,11 @@
       <c r="N167" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="168" spans="1:14" hidden="1">
+      <c r="O167">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15">
       <c r="A168" t="s">
         <v>351</v>
       </c>
@@ -11080,8 +11262,11 @@
       <c r="N168" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="169" spans="1:14" hidden="1">
+      <c r="O168">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15">
       <c r="A169" t="s">
         <v>374</v>
       </c>
@@ -11124,8 +11309,11 @@
       <c r="N169" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="170" spans="1:14" hidden="1">
+      <c r="O169">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15">
       <c r="A170" t="s">
         <v>375</v>
       </c>
@@ -11168,8 +11356,11 @@
       <c r="N170" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="171" spans="1:14" hidden="1">
+      <c r="O170">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15">
       <c r="A171" t="s">
         <v>376</v>
       </c>
@@ -11212,8 +11403,11 @@
       <c r="N171" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="172" spans="1:14" hidden="1">
+      <c r="O171">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15">
       <c r="A172" t="s">
         <v>377</v>
       </c>
@@ -11256,8 +11450,11 @@
       <c r="N172" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="173" spans="1:14">
+      <c r="O172">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15">
       <c r="A173" t="s">
         <v>378</v>
       </c>
@@ -11301,29 +11498,29 @@
         <v>89</v>
       </c>
     </row>
-    <row r="174" spans="1:14" hidden="1">
+    <row r="174" spans="1:15">
       <c r="A174" t="s">
         <v>379</v>
       </c>
-      <c r="B174" s="10" t="s">
+      <c r="B174" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="C174" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D174" s="9">
+      <c r="C174">
+        <v>2026</v>
+      </c>
+      <c r="D174">
         <v>5</v>
       </c>
-      <c r="E174" s="9" t="s">
+      <c r="E174" t="s">
         <v>404</v>
       </c>
-      <c r="F174" s="9" t="s">
+      <c r="F174" t="s">
         <v>45</v>
       </c>
-      <c r="G174" s="12">
+      <c r="G174" s="4">
         <v>10239118211</v>
       </c>
-      <c r="H174" s="9" t="s">
+      <c r="H174" t="s">
         <v>258</v>
       </c>
       <c r="I174" t="s">
@@ -11332,42 +11529,45 @@
       <c r="J174" t="s">
         <v>455</v>
       </c>
-      <c r="K174" s="9" t="s">
+      <c r="K174" t="s">
         <v>647</v>
       </c>
-      <c r="L174" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M174" s="9">
+      <c r="L174" t="s">
+        <v>88</v>
+      </c>
+      <c r="M174">
         <v>3</v>
       </c>
-      <c r="N174" s="9" t="s">
+      <c r="N174" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="175" spans="1:14" hidden="1">
+      <c r="O174">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15">
       <c r="A175" t="s">
         <v>380</v>
       </c>
-      <c r="B175" s="10" t="s">
+      <c r="B175" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="C175" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D175" s="9">
+      <c r="C175">
+        <v>2026</v>
+      </c>
+      <c r="D175">
         <v>5</v>
       </c>
-      <c r="E175" s="9" t="s">
+      <c r="E175" t="s">
         <v>404</v>
       </c>
-      <c r="F175" s="9" t="s">
+      <c r="F175" t="s">
         <v>45</v>
       </c>
-      <c r="G175" s="12">
+      <c r="G175" s="4">
         <v>10239478676</v>
       </c>
-      <c r="H175" s="9" t="s">
+      <c r="H175" t="s">
         <v>306</v>
       </c>
       <c r="I175" t="s">
@@ -11376,42 +11576,45 @@
       <c r="J175" t="s">
         <v>455</v>
       </c>
-      <c r="K175" s="9" t="s">
+      <c r="K175" t="s">
         <v>647</v>
       </c>
-      <c r="L175" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M175" s="9">
+      <c r="L175" t="s">
+        <v>88</v>
+      </c>
+      <c r="M175">
         <v>3</v>
       </c>
-      <c r="N175" s="9" t="s">
+      <c r="N175" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="176" spans="1:14" hidden="1">
+      <c r="O175">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15">
       <c r="A176" t="s">
         <v>381</v>
       </c>
-      <c r="B176" s="10" t="s">
+      <c r="B176" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="C176" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D176" s="9">
+      <c r="C176">
+        <v>2026</v>
+      </c>
+      <c r="D176">
         <v>5</v>
       </c>
-      <c r="E176" s="9" t="s">
+      <c r="E176" t="s">
         <v>404</v>
       </c>
-      <c r="F176" s="9" t="s">
+      <c r="F176" t="s">
         <v>45</v>
       </c>
-      <c r="G176" s="12">
+      <c r="G176" s="4">
         <v>10239802872</v>
       </c>
-      <c r="H176" s="9" t="s">
+      <c r="H176" t="s">
         <v>79</v>
       </c>
       <c r="I176" t="s">
@@ -11420,20 +11623,23 @@
       <c r="J176" t="s">
         <v>455</v>
       </c>
-      <c r="K176" s="9" t="s">
+      <c r="K176" t="s">
         <v>647</v>
       </c>
-      <c r="L176" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M176" s="9">
+      <c r="L176" t="s">
+        <v>88</v>
+      </c>
+      <c r="M176">
         <v>3</v>
       </c>
-      <c r="N176" s="9" t="s">
+      <c r="N176" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="177" spans="1:14" hidden="1">
+      <c r="O176">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15">
       <c r="A177" t="s">
         <v>382</v>
       </c>
@@ -11476,8 +11682,11 @@
       <c r="N177" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="178" spans="1:14" hidden="1">
+      <c r="O177">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15">
       <c r="A178" t="s">
         <v>383</v>
       </c>
@@ -11520,8 +11729,11 @@
       <c r="N178" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="179" spans="1:14" hidden="1">
+      <c r="O178">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15">
       <c r="A179" t="s">
         <v>384</v>
       </c>
@@ -11564,8 +11776,11 @@
       <c r="N179" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="180" spans="1:14" hidden="1">
+      <c r="O179">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15">
       <c r="A180" t="s">
         <v>385</v>
       </c>
@@ -11608,8 +11823,11 @@
       <c r="N180" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="181" spans="1:14" hidden="1">
+      <c r="O180">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15">
       <c r="A181" t="s">
         <v>386</v>
       </c>
@@ -11652,30 +11870,33 @@
       <c r="N181" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="182" spans="1:14" hidden="1">
+      <c r="O181">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15">
       <c r="A182" t="s">
         <v>387</v>
       </c>
-      <c r="B182" s="10" t="s">
+      <c r="B182" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="C182" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D182" s="9">
+      <c r="C182">
+        <v>2026</v>
+      </c>
+      <c r="D182">
         <v>5</v>
       </c>
-      <c r="E182" s="9" t="s">
+      <c r="E182" t="s">
         <v>404</v>
       </c>
-      <c r="F182" s="9" t="s">
+      <c r="F182" t="s">
         <v>45</v>
       </c>
-      <c r="G182" s="12">
+      <c r="G182" s="4">
         <v>10403881363</v>
       </c>
-      <c r="H182" s="9" t="s">
+      <c r="H182" t="s">
         <v>77</v>
       </c>
       <c r="I182" t="s">
@@ -11684,42 +11905,45 @@
       <c r="J182" t="s">
         <v>456</v>
       </c>
-      <c r="K182" s="9" t="s">
+      <c r="K182" t="s">
         <v>649</v>
       </c>
-      <c r="L182" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M182" s="9">
+      <c r="L182" t="s">
+        <v>88</v>
+      </c>
+      <c r="M182">
         <v>3</v>
       </c>
-      <c r="N182" s="9" t="s">
+      <c r="N182" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="183" spans="1:14" hidden="1">
+      <c r="O182">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15">
       <c r="A183" t="s">
         <v>388</v>
       </c>
-      <c r="B183" s="10" t="s">
+      <c r="B183" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="C183" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D183" s="9">
+      <c r="C183">
+        <v>2026</v>
+      </c>
+      <c r="D183">
         <v>5</v>
       </c>
-      <c r="E183" s="9" t="s">
+      <c r="E183" t="s">
         <v>404</v>
       </c>
-      <c r="F183" s="9" t="s">
+      <c r="F183" t="s">
         <v>45</v>
       </c>
-      <c r="G183" s="12">
+      <c r="G183" s="4">
         <v>10239486377</v>
       </c>
-      <c r="H183" s="9" t="s">
+      <c r="H183" t="s">
         <v>304</v>
       </c>
       <c r="I183" t="s">
@@ -11728,42 +11952,45 @@
       <c r="J183" t="s">
         <v>456</v>
       </c>
-      <c r="K183" s="9" t="s">
+      <c r="K183" t="s">
         <v>650</v>
       </c>
-      <c r="L183" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M183" s="9">
+      <c r="L183" t="s">
+        <v>88</v>
+      </c>
+      <c r="M183">
         <v>3</v>
       </c>
-      <c r="N183" s="9" t="s">
+      <c r="N183" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="184" spans="1:14" hidden="1">
+      <c r="O183">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15">
       <c r="A184" t="s">
         <v>389</v>
       </c>
-      <c r="B184" s="10" t="s">
+      <c r="B184" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="C184" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D184" s="9">
+      <c r="C184">
+        <v>2026</v>
+      </c>
+      <c r="D184">
         <v>5</v>
       </c>
-      <c r="E184" s="9" t="s">
+      <c r="E184" t="s">
         <v>404</v>
       </c>
-      <c r="F184" s="9" t="s">
+      <c r="F184" t="s">
         <v>45</v>
       </c>
-      <c r="G184" s="12">
+      <c r="G184" s="4">
         <v>10013070585</v>
       </c>
-      <c r="H184" s="9" t="s">
+      <c r="H184" t="s">
         <v>441</v>
       </c>
       <c r="I184" t="s">
@@ -11772,20 +11999,23 @@
       <c r="J184" t="s">
         <v>456</v>
       </c>
-      <c r="K184" s="9" t="s">
+      <c r="K184" t="s">
         <v>649</v>
       </c>
-      <c r="L184" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M184" s="9">
+      <c r="L184" t="s">
+        <v>88</v>
+      </c>
+      <c r="M184">
         <v>2</v>
       </c>
-      <c r="N184" s="9" t="s">
+      <c r="N184" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="185" spans="1:14" hidden="1">
+      <c r="O184">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15">
       <c r="A185" t="s">
         <v>390</v>
       </c>
@@ -11828,8 +12058,11 @@
       <c r="N185" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="186" spans="1:14" hidden="1">
+      <c r="O185">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15">
       <c r="A186" t="s">
         <v>391</v>
       </c>
@@ -11872,8 +12105,11 @@
       <c r="N186" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="187" spans="1:14" hidden="1">
+      <c r="O186">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15">
       <c r="A187" t="s">
         <v>392</v>
       </c>
@@ -11916,24 +12152,27 @@
       <c r="N187" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="188" spans="1:14" hidden="1">
+      <c r="O187">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15">
       <c r="A188" t="s">
         <v>393</v>
       </c>
-      <c r="B188" s="11" t="s">
+      <c r="B188" s="4" t="s">
         <v>1014</v>
       </c>
-      <c r="C188" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D188" s="9">
+      <c r="C188">
+        <v>2026</v>
+      </c>
+      <c r="D188">
         <v>6</v>
       </c>
-      <c r="E188" s="9" t="s">
+      <c r="E188" t="s">
         <v>404</v>
       </c>
-      <c r="F188" s="9" t="s">
+      <c r="F188" t="s">
         <v>45</v>
       </c>
       <c r="G188" s="4">
@@ -11951,36 +12190,39 @@
       <c r="K188" t="s">
         <v>1048</v>
       </c>
-      <c r="L188" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M188" s="9">
+      <c r="L188" t="s">
+        <v>88</v>
+      </c>
+      <c r="M188">
         <v>2</v>
       </c>
       <c r="N188" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="189" spans="1:14" hidden="1">
+      <c r="O188">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15">
       <c r="A189" t="s">
         <v>394</v>
       </c>
-      <c r="B189" s="11" t="s">
+      <c r="B189" s="4" t="s">
         <v>1014</v>
       </c>
-      <c r="C189" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D189" s="9">
+      <c r="C189">
+        <v>2026</v>
+      </c>
+      <c r="D189">
         <v>6</v>
       </c>
-      <c r="E189" s="9" t="s">
+      <c r="E189" t="s">
         <v>404</v>
       </c>
-      <c r="F189" s="9" t="s">
+      <c r="F189" t="s">
         <v>45</v>
       </c>
-      <c r="G189" s="13">
+      <c r="G189" s="4">
         <v>10239510197</v>
       </c>
       <c r="H189" t="s">
@@ -11995,17 +12237,20 @@
       <c r="K189" t="s">
         <v>1060</v>
       </c>
-      <c r="L189" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M189" s="9">
+      <c r="L189" t="s">
+        <v>88</v>
+      </c>
+      <c r="M189">
         <v>2</v>
       </c>
       <c r="N189" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="190" spans="1:14" hidden="1">
+      <c r="O189">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15">
       <c r="A190" t="s">
         <v>395</v>
       </c>
@@ -12048,8 +12293,11 @@
       <c r="N190" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="191" spans="1:14" hidden="1">
+      <c r="O190">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15">
       <c r="A191" t="s">
         <v>396</v>
       </c>
@@ -12092,8 +12340,11 @@
       <c r="N191" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="192" spans="1:14" hidden="1">
+      <c r="O191">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15">
       <c r="A192" t="s">
         <v>397</v>
       </c>
@@ -12136,8 +12387,11 @@
       <c r="N192" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="193" spans="1:14" hidden="1">
+      <c r="O192">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15">
       <c r="A193" t="s">
         <v>398</v>
       </c>
@@ -12180,8 +12434,11 @@
       <c r="N193" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="194" spans="1:14" hidden="1">
+      <c r="O193">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15">
       <c r="A194" t="s">
         <v>399</v>
       </c>
@@ -12224,30 +12481,33 @@
       <c r="N194" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="195" spans="1:14" hidden="1">
+      <c r="O194">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15">
       <c r="A195" t="s">
         <v>400</v>
       </c>
-      <c r="B195" s="10" t="s">
+      <c r="B195" s="3" t="s">
         <v>1023</v>
       </c>
-      <c r="C195" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D195" s="9">
+      <c r="C195">
+        <v>2026</v>
+      </c>
+      <c r="D195">
         <v>5</v>
       </c>
-      <c r="E195" s="9" t="s">
+      <c r="E195" t="s">
         <v>404</v>
       </c>
-      <c r="F195" s="9" t="s">
+      <c r="F195" t="s">
         <v>45</v>
       </c>
-      <c r="G195" s="12">
+      <c r="G195" s="4">
         <v>10403881363</v>
       </c>
-      <c r="H195" s="9" t="s">
+      <c r="H195" t="s">
         <v>77</v>
       </c>
       <c r="I195" t="s">
@@ -12256,42 +12516,45 @@
       <c r="J195" t="s">
         <v>455</v>
       </c>
-      <c r="K195" s="9" t="s">
+      <c r="K195" t="s">
         <v>647</v>
       </c>
-      <c r="L195" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M195" s="9">
+      <c r="L195" t="s">
+        <v>88</v>
+      </c>
+      <c r="M195">
         <v>3</v>
       </c>
-      <c r="N195" s="9" t="s">
+      <c r="N195" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="196" spans="1:14" hidden="1">
+      <c r="O195">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15">
       <c r="A196" t="s">
         <v>468</v>
       </c>
-      <c r="B196" s="10" t="s">
+      <c r="B196" s="3" t="s">
         <v>1023</v>
       </c>
-      <c r="C196" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D196" s="9">
+      <c r="C196">
+        <v>2026</v>
+      </c>
+      <c r="D196">
         <v>5</v>
       </c>
-      <c r="E196" s="9" t="s">
+      <c r="E196" t="s">
         <v>404</v>
       </c>
-      <c r="F196" s="9" t="s">
+      <c r="F196" t="s">
         <v>45</v>
       </c>
-      <c r="G196" s="12">
+      <c r="G196" s="4">
         <v>10239486377</v>
       </c>
-      <c r="H196" s="9" t="s">
+      <c r="H196" t="s">
         <v>304</v>
       </c>
       <c r="I196" t="s">
@@ -12300,42 +12563,45 @@
       <c r="J196" t="s">
         <v>455</v>
       </c>
-      <c r="K196" s="9" t="s">
+      <c r="K196" t="s">
         <v>647</v>
       </c>
-      <c r="L196" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M196" s="9">
+      <c r="L196" t="s">
+        <v>88</v>
+      </c>
+      <c r="M196">
         <v>3</v>
       </c>
-      <c r="N196" s="9" t="s">
+      <c r="N196" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="197" spans="1:14" hidden="1">
+      <c r="O196">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15">
       <c r="A197" t="s">
         <v>469</v>
       </c>
-      <c r="B197" s="10" t="s">
+      <c r="B197" s="3" t="s">
         <v>1023</v>
       </c>
-      <c r="C197" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D197" s="9">
+      <c r="C197">
+        <v>2026</v>
+      </c>
+      <c r="D197">
         <v>5</v>
       </c>
-      <c r="E197" s="9" t="s">
+      <c r="E197" t="s">
         <v>404</v>
       </c>
-      <c r="F197" s="9" t="s">
+      <c r="F197" t="s">
         <v>45</v>
       </c>
-      <c r="G197" s="12">
+      <c r="G197" s="4">
         <v>10013070585</v>
       </c>
-      <c r="H197" s="9" t="s">
+      <c r="H197" t="s">
         <v>441</v>
       </c>
       <c r="I197" t="s">
@@ -12344,20 +12610,23 @@
       <c r="J197" t="s">
         <v>455</v>
       </c>
-      <c r="K197" s="9" t="s">
+      <c r="K197" t="s">
         <v>647</v>
       </c>
-      <c r="L197" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M197" s="9">
+      <c r="L197" t="s">
+        <v>88</v>
+      </c>
+      <c r="M197">
         <v>2</v>
       </c>
-      <c r="N197" s="9" t="s">
+      <c r="N197" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="198" spans="1:14" hidden="1">
+      <c r="O197">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15">
       <c r="A198" t="s">
         <v>470</v>
       </c>
@@ -12400,8 +12669,11 @@
       <c r="N198" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="199" spans="1:14" hidden="1">
+      <c r="O198">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15">
       <c r="A199" t="s">
         <v>471</v>
       </c>
@@ -12444,8 +12716,11 @@
       <c r="N199" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="200" spans="1:14" hidden="1">
+      <c r="O199">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15">
       <c r="A200" t="s">
         <v>472</v>
       </c>
@@ -12488,8 +12763,11 @@
       <c r="N200" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="201" spans="1:14" hidden="1">
+      <c r="O200">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15">
       <c r="A201" t="s">
         <v>473</v>
       </c>
@@ -12532,27 +12810,30 @@
       <c r="N201" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="202" spans="1:14" hidden="1">
+      <c r="O201">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15">
       <c r="A202" t="s">
         <v>474</v>
       </c>
-      <c r="B202" s="11" t="s">
+      <c r="B202" s="4" t="s">
         <v>1015</v>
       </c>
-      <c r="C202" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D202" s="9">
+      <c r="C202">
+        <v>2026</v>
+      </c>
+      <c r="D202">
         <v>6</v>
       </c>
-      <c r="E202" s="9" t="s">
+      <c r="E202" t="s">
         <v>404</v>
       </c>
-      <c r="F202" s="9" t="s">
+      <c r="F202" t="s">
         <v>45</v>
       </c>
-      <c r="G202" s="13">
+      <c r="G202" s="4">
         <v>10239802821</v>
       </c>
       <c r="H202" t="s">
@@ -12567,17 +12848,20 @@
       <c r="K202" t="s">
         <v>1049</v>
       </c>
-      <c r="L202" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M202" s="9">
+      <c r="L202" t="s">
+        <v>88</v>
+      </c>
+      <c r="M202">
         <v>2</v>
       </c>
       <c r="N202" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="203" spans="1:14" hidden="1">
+      <c r="O202">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15">
       <c r="A203" t="s">
         <v>475</v>
       </c>
@@ -12620,8 +12904,11 @@
       <c r="N203" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="204" spans="1:14" hidden="1">
+      <c r="O203">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15">
       <c r="A204" t="s">
         <v>476</v>
       </c>
@@ -12664,8 +12951,11 @@
       <c r="N204" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="205" spans="1:14">
+      <c r="O204">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15">
       <c r="A205" t="s">
         <v>477</v>
       </c>
@@ -12709,7 +12999,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="206" spans="1:14" hidden="1">
+    <row r="206" spans="1:15">
       <c r="A206" t="s">
         <v>478</v>
       </c>
@@ -12752,8 +13042,11 @@
       <c r="N206" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="207" spans="1:14" hidden="1">
+      <c r="O206">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15">
       <c r="A207" t="s">
         <v>479</v>
       </c>
@@ -12796,8 +13089,11 @@
       <c r="N207" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="208" spans="1:14" hidden="1">
+      <c r="O207">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15">
       <c r="A208" t="s">
         <v>480</v>
       </c>
@@ -12840,8 +13136,11 @@
       <c r="N208" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="209" spans="1:14" hidden="1">
+      <c r="O208">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="209" spans="1:15">
       <c r="A209" t="s">
         <v>481</v>
       </c>
@@ -12884,8 +13183,11 @@
       <c r="N209" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="210" spans="1:14" hidden="1">
+      <c r="O209">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15">
       <c r="A210" t="s">
         <v>482</v>
       </c>
@@ -12928,8 +13230,11 @@
       <c r="N210" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="211" spans="1:14" hidden="1">
+      <c r="O210">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15">
       <c r="A211" t="s">
         <v>483</v>
       </c>
@@ -12972,8 +13277,11 @@
       <c r="N211" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="212" spans="1:14" hidden="1">
+      <c r="O211">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:15">
       <c r="A212" t="s">
         <v>484</v>
       </c>
@@ -13016,27 +13324,30 @@
       <c r="N212" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="213" spans="1:14" hidden="1">
+      <c r="O212">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:15">
       <c r="A213" t="s">
         <v>485</v>
       </c>
-      <c r="B213" s="11" t="s">
+      <c r="B213" s="4" t="s">
         <v>1012</v>
       </c>
-      <c r="C213" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D213" s="9">
+      <c r="C213">
+        <v>2026</v>
+      </c>
+      <c r="D213">
         <v>6</v>
       </c>
-      <c r="E213" s="9" t="s">
+      <c r="E213" t="s">
         <v>404</v>
       </c>
-      <c r="F213" s="9" t="s">
+      <c r="F213" t="s">
         <v>45</v>
       </c>
-      <c r="G213" s="13">
+      <c r="G213" s="4">
         <v>10800860321</v>
       </c>
       <c r="H213" t="s">
@@ -13051,17 +13362,20 @@
       <c r="K213" t="s">
         <v>1050</v>
       </c>
-      <c r="L213" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M213" s="9">
+      <c r="L213" t="s">
+        <v>88</v>
+      </c>
+      <c r="M213">
         <v>2</v>
       </c>
       <c r="N213" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="214" spans="1:14" hidden="1">
+      <c r="O213">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15">
       <c r="A214" t="s">
         <v>486</v>
       </c>
@@ -13104,8 +13418,11 @@
       <c r="N214" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="215" spans="1:14">
+      <c r="O214">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15">
       <c r="A215" t="s">
         <v>487</v>
       </c>
@@ -13149,29 +13466,29 @@
         <v>89</v>
       </c>
     </row>
-    <row r="216" spans="1:14" hidden="1">
+    <row r="216" spans="1:15">
       <c r="A216" t="s">
         <v>488</v>
       </c>
-      <c r="B216" s="10" t="s">
+      <c r="B216" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="C216" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D216" s="9">
+      <c r="C216">
+        <v>2026</v>
+      </c>
+      <c r="D216">
         <v>5</v>
       </c>
-      <c r="E216" s="9" t="s">
+      <c r="E216" t="s">
         <v>404</v>
       </c>
-      <c r="F216" s="9" t="s">
+      <c r="F216" t="s">
         <v>45</v>
       </c>
-      <c r="G216" s="12">
+      <c r="G216" s="4">
         <v>40347164</v>
       </c>
-      <c r="H216" s="9" t="s">
+      <c r="H216" t="s">
         <v>78</v>
       </c>
       <c r="I216" t="s">
@@ -13180,42 +13497,45 @@
       <c r="J216" t="s">
         <v>455</v>
       </c>
-      <c r="K216" s="9" t="s">
+      <c r="K216" t="s">
         <v>647</v>
       </c>
-      <c r="L216" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M216" s="9">
+      <c r="L216" t="s">
+        <v>88</v>
+      </c>
+      <c r="M216">
         <v>3</v>
       </c>
-      <c r="N216" s="9" t="s">
+      <c r="N216" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="217" spans="1:14" hidden="1">
+      <c r="O216">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15">
       <c r="A217" t="s">
         <v>489</v>
       </c>
-      <c r="B217" s="10" t="s">
+      <c r="B217" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="C217" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D217" s="9">
+      <c r="C217">
+        <v>2026</v>
+      </c>
+      <c r="D217">
         <v>5</v>
       </c>
-      <c r="E217" s="9" t="s">
+      <c r="E217" t="s">
         <v>404</v>
       </c>
-      <c r="F217" s="9" t="s">
+      <c r="F217" t="s">
         <v>45</v>
       </c>
-      <c r="G217" s="12">
+      <c r="G217" s="4">
         <v>40347164</v>
       </c>
-      <c r="H217" s="9" t="s">
+      <c r="H217" t="s">
         <v>78</v>
       </c>
       <c r="I217" t="s">
@@ -13224,20 +13544,23 @@
       <c r="J217" t="s">
         <v>456</v>
       </c>
-      <c r="K217" s="9" t="s">
+      <c r="K217" t="s">
         <v>650</v>
       </c>
-      <c r="L217" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M217" s="9">
+      <c r="L217" t="s">
+        <v>88</v>
+      </c>
+      <c r="M217">
         <v>3</v>
       </c>
-      <c r="N217" s="9" t="s">
+      <c r="N217" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="218" spans="1:14" hidden="1">
+      <c r="O217">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="218" spans="1:15">
       <c r="A218" t="s">
         <v>490</v>
       </c>
@@ -13280,8 +13603,11 @@
       <c r="N218" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="219" spans="1:14" hidden="1">
+      <c r="O218">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="219" spans="1:15">
       <c r="A219" t="s">
         <v>491</v>
       </c>
@@ -13324,8 +13650,11 @@
       <c r="N219" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="220" spans="1:14" hidden="1">
+      <c r="O219">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:15">
       <c r="A220" t="s">
         <v>492</v>
       </c>
@@ -13368,8 +13697,11 @@
       <c r="N220" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="221" spans="1:14" hidden="1">
+      <c r="O220">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:15">
       <c r="A221" t="s">
         <v>493</v>
       </c>
@@ -13412,8 +13744,11 @@
       <c r="N221" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="222" spans="1:14" hidden="1">
+      <c r="O221">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:15">
       <c r="A222" t="s">
         <v>494</v>
       </c>
@@ -13456,8 +13791,11 @@
       <c r="N222" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="223" spans="1:14" hidden="1">
+      <c r="O222">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:15">
       <c r="A223" t="s">
         <v>495</v>
       </c>
@@ -13500,27 +13838,30 @@
       <c r="N223" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="224" spans="1:14" hidden="1">
+      <c r="O223">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="224" spans="1:15">
       <c r="A224" t="s">
         <v>496</v>
       </c>
-      <c r="B224" s="11" t="s">
+      <c r="B224" s="4" t="s">
         <v>1017</v>
       </c>
-      <c r="C224" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D224" s="9">
+      <c r="C224">
+        <v>2026</v>
+      </c>
+      <c r="D224">
         <v>6</v>
       </c>
-      <c r="E224" s="9" t="s">
+      <c r="E224" t="s">
         <v>404</v>
       </c>
-      <c r="F224" s="9" t="s">
+      <c r="F224" t="s">
         <v>45</v>
       </c>
-      <c r="G224" s="13">
+      <c r="G224" s="4">
         <v>10403881363</v>
       </c>
       <c r="H224" t="s">
@@ -13535,17 +13876,20 @@
       <c r="K224" t="s">
         <v>1044</v>
       </c>
-      <c r="L224" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M224" s="9">
-        <v>1</v>
-      </c>
-      <c r="N224" s="9" t="s">
+      <c r="L224" t="s">
+        <v>88</v>
+      </c>
+      <c r="M224">
+        <v>1</v>
+      </c>
+      <c r="N224" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="225" spans="1:14" hidden="1">
+      <c r="O224">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:15">
       <c r="A225" t="s">
         <v>497</v>
       </c>
@@ -13588,27 +13932,30 @@
       <c r="N225" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="226" spans="1:14" hidden="1">
+      <c r="O225">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="226" spans="1:15">
       <c r="A226" t="s">
         <v>498</v>
       </c>
-      <c r="B226" s="11" t="s">
+      <c r="B226" s="4" t="s">
         <v>645</v>
       </c>
-      <c r="C226" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D226" s="9">
+      <c r="C226">
+        <v>2026</v>
+      </c>
+      <c r="D226">
         <v>5</v>
       </c>
-      <c r="E226" s="9" t="s">
+      <c r="E226" t="s">
         <v>404</v>
       </c>
-      <c r="F226" s="9" t="s">
+      <c r="F226" t="s">
         <v>45</v>
       </c>
-      <c r="G226" s="13">
+      <c r="G226" s="4">
         <v>10401531284</v>
       </c>
       <c r="H226" t="s">
@@ -13623,17 +13970,20 @@
       <c r="K226" t="s">
         <v>651</v>
       </c>
-      <c r="L226" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M226" s="9">
+      <c r="L226" t="s">
+        <v>88</v>
+      </c>
+      <c r="M226">
         <v>1</v>
       </c>
       <c r="N226" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="227" spans="1:14" hidden="1">
+      <c r="O226">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:15">
       <c r="A227" t="s">
         <v>499</v>
       </c>
@@ -13676,8 +14026,11 @@
       <c r="N227" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="228" spans="1:14" hidden="1">
+      <c r="O227">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="228" spans="1:15">
       <c r="A228" t="s">
         <v>500</v>
       </c>
@@ -13720,8 +14073,11 @@
       <c r="N228" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="229" spans="1:14" hidden="1">
+      <c r="O228">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:15">
       <c r="A229" t="s">
         <v>501</v>
       </c>
@@ -13764,8 +14120,11 @@
       <c r="N229" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="230" spans="1:14" hidden="1">
+      <c r="O229">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:15">
       <c r="A230" t="s">
         <v>502</v>
       </c>
@@ -13808,8 +14167,11 @@
       <c r="N230" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="231" spans="1:14">
+      <c r="O230">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:15">
       <c r="A231" t="s">
         <v>503</v>
       </c>
@@ -13828,7 +14190,7 @@
       <c r="F231" t="s">
         <v>401</v>
       </c>
-      <c r="G231" s="13">
+      <c r="G231" s="4">
         <v>24889807</v>
       </c>
       <c r="H231" t="s">
@@ -13853,7 +14215,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="232" spans="1:14">
+    <row r="232" spans="1:15">
       <c r="A232" t="s">
         <v>504</v>
       </c>
@@ -13872,7 +14234,7 @@
       <c r="F232" t="s">
         <v>401</v>
       </c>
-      <c r="G232" s="13">
+      <c r="G232" s="4">
         <v>24888829</v>
       </c>
       <c r="H232" t="s">
@@ -13897,7 +14259,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="233" spans="1:14">
+    <row r="233" spans="1:15">
       <c r="A233" t="s">
         <v>505</v>
       </c>
@@ -13916,7 +14278,7 @@
       <c r="F233" t="s">
         <v>401</v>
       </c>
-      <c r="G233" s="13">
+      <c r="G233" s="4">
         <v>24889807</v>
       </c>
       <c r="H233" t="s">
@@ -13941,7 +14303,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="234" spans="1:14">
+    <row r="234" spans="1:15">
       <c r="A234" t="s">
         <v>506</v>
       </c>
@@ -13960,7 +14322,7 @@
       <c r="F234" t="s">
         <v>401</v>
       </c>
-      <c r="G234" s="13">
+      <c r="G234" s="4">
         <v>10443205573</v>
       </c>
       <c r="H234" t="s">
@@ -13985,7 +14347,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="235" spans="1:14">
+    <row r="235" spans="1:15">
       <c r="A235" t="s">
         <v>507</v>
       </c>
@@ -14004,7 +14366,7 @@
       <c r="F235" t="s">
         <v>401</v>
       </c>
-      <c r="G235" s="13">
+      <c r="G235" s="4">
         <v>24884182</v>
       </c>
       <c r="H235" t="s">
@@ -14029,7 +14391,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="236" spans="1:14">
+    <row r="236" spans="1:15">
       <c r="A236" t="s">
         <v>508</v>
       </c>
@@ -14048,7 +14410,7 @@
       <c r="F236" t="s">
         <v>401</v>
       </c>
-      <c r="G236" s="13">
+      <c r="G236" s="4">
         <v>10248670075</v>
       </c>
       <c r="H236" t="s">
@@ -14073,7 +14435,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="237" spans="1:14">
+    <row r="237" spans="1:15">
       <c r="A237" t="s">
         <v>509</v>
       </c>
@@ -14092,7 +14454,7 @@
       <c r="F237" t="s">
         <v>401</v>
       </c>
-      <c r="G237" s="13">
+      <c r="G237" s="4">
         <v>40289959</v>
       </c>
       <c r="H237" t="s">
@@ -14117,7 +14479,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="238" spans="1:14">
+    <row r="238" spans="1:15">
       <c r="A238" t="s">
         <v>510</v>
       </c>
@@ -14136,7 +14498,7 @@
       <c r="F238" t="s">
         <v>401</v>
       </c>
-      <c r="G238" s="13">
+      <c r="G238" s="4">
         <v>10402988121</v>
       </c>
       <c r="H238" t="s">
@@ -14161,7 +14523,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="239" spans="1:14">
+    <row r="239" spans="1:15">
       <c r="A239" t="s">
         <v>511</v>
       </c>
@@ -14180,7 +14542,7 @@
       <c r="F239" t="s">
         <v>401</v>
       </c>
-      <c r="G239" s="13">
+      <c r="G239" s="4">
         <v>10408822641</v>
       </c>
       <c r="H239" t="s">
@@ -14205,7 +14567,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="240" spans="1:14">
+    <row r="240" spans="1:15">
       <c r="A240" t="s">
         <v>512</v>
       </c>
@@ -14224,7 +14586,7 @@
       <c r="F240" t="s">
         <v>401</v>
       </c>
-      <c r="G240" s="13">
+      <c r="G240" s="4">
         <v>10473551549</v>
       </c>
       <c r="H240" t="s">
@@ -14249,7 +14611,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="241" spans="1:14">
+    <row r="241" spans="1:15">
       <c r="A241" t="s">
         <v>513</v>
       </c>
@@ -14268,7 +14630,7 @@
       <c r="F241" t="s">
         <v>401</v>
       </c>
-      <c r="G241" s="13">
+      <c r="G241" s="4">
         <v>10408822641</v>
       </c>
       <c r="H241" t="s">
@@ -14293,7 +14655,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="242" spans="1:14">
+    <row r="242" spans="1:15">
       <c r="A242" t="s">
         <v>514</v>
       </c>
@@ -14312,7 +14674,7 @@
       <c r="F242" t="s">
         <v>401</v>
       </c>
-      <c r="G242" s="13">
+      <c r="G242" s="4">
         <v>10446727180</v>
       </c>
       <c r="H242" t="s">
@@ -14337,7 +14699,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="243" spans="1:14">
+    <row r="243" spans="1:15">
       <c r="A243" t="s">
         <v>515</v>
       </c>
@@ -14356,7 +14718,7 @@
       <c r="F243" t="s">
         <v>401</v>
       </c>
-      <c r="G243" s="13">
+      <c r="G243" s="4">
         <v>72198395</v>
       </c>
       <c r="H243" t="s">
@@ -14381,7 +14743,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="244" spans="1:14">
+    <row r="244" spans="1:15">
       <c r="A244" t="s">
         <v>516</v>
       </c>
@@ -14400,7 +14762,7 @@
       <c r="F244" t="s">
         <v>401</v>
       </c>
-      <c r="G244" s="13">
+      <c r="G244" s="4">
         <v>10411675179</v>
       </c>
       <c r="H244" t="s">
@@ -14425,7 +14787,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="245" spans="1:14">
+    <row r="245" spans="1:15">
       <c r="A245" t="s">
         <v>517</v>
       </c>
@@ -14444,7 +14806,7 @@
       <c r="F245" t="s">
         <v>401</v>
       </c>
-      <c r="G245" s="13">
+      <c r="G245" s="4">
         <v>25017176</v>
       </c>
       <c r="H245" t="s">
@@ -14469,7 +14831,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="246" spans="1:14">
+    <row r="246" spans="1:15">
       <c r="A246" t="s">
         <v>518</v>
       </c>
@@ -14488,7 +14850,7 @@
       <c r="F246" t="s">
         <v>401</v>
       </c>
-      <c r="G246" s="13">
+      <c r="G246" s="4">
         <v>24895254</v>
       </c>
       <c r="H246" t="s">
@@ -14513,7 +14875,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="247" spans="1:14">
+    <row r="247" spans="1:15">
       <c r="A247" t="s">
         <v>519</v>
       </c>
@@ -14532,7 +14894,7 @@
       <c r="F247" t="s">
         <v>401</v>
       </c>
-      <c r="G247" s="13">
+      <c r="G247" s="4">
         <v>43799579</v>
       </c>
       <c r="H247" t="s">
@@ -14557,26 +14919,26 @@
         <v>89</v>
       </c>
     </row>
-    <row r="248" spans="1:14" hidden="1">
+    <row r="248" spans="1:15">
       <c r="A248" t="s">
         <v>520</v>
       </c>
-      <c r="B248" s="11" t="s">
+      <c r="B248" s="4" t="s">
         <v>928</v>
       </c>
-      <c r="C248" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D248" s="9">
+      <c r="C248">
+        <v>2026</v>
+      </c>
+      <c r="D248">
         <v>6</v>
       </c>
-      <c r="E248" s="9" t="s">
+      <c r="E248" t="s">
         <v>404</v>
       </c>
-      <c r="F248" s="9" t="s">
+      <c r="F248" t="s">
         <v>45</v>
       </c>
-      <c r="G248" s="13">
+      <c r="G248" s="4">
         <v>10013070585</v>
       </c>
       <c r="H248" t="s">
@@ -14591,17 +14953,20 @@
       <c r="K248" t="s">
         <v>1045</v>
       </c>
-      <c r="L248" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M248" s="9">
+      <c r="L248" t="s">
+        <v>88</v>
+      </c>
+      <c r="M248">
         <v>1</v>
       </c>
       <c r="N248" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="249" spans="1:14">
+      <c r="O248">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="249" spans="1:15">
       <c r="A249" t="s">
         <v>521</v>
       </c>
@@ -14645,7 +15010,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="250" spans="1:14">
+    <row r="250" spans="1:15">
       <c r="A250" t="s">
         <v>522</v>
       </c>
@@ -14689,7 +15054,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="251" spans="1:14">
+    <row r="251" spans="1:15">
       <c r="A251" t="s">
         <v>523</v>
       </c>
@@ -14733,7 +15098,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="252" spans="1:14">
+    <row r="252" spans="1:15">
       <c r="A252" t="s">
         <v>524</v>
       </c>
@@ -14777,7 +15142,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="253" spans="1:14">
+    <row r="253" spans="1:15">
       <c r="A253" t="s">
         <v>525</v>
       </c>
@@ -14821,7 +15186,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="254" spans="1:14">
+    <row r="254" spans="1:15">
       <c r="A254" t="s">
         <v>526</v>
       </c>
@@ -14865,7 +15230,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="255" spans="1:14">
+    <row r="255" spans="1:15">
       <c r="A255" t="s">
         <v>527</v>
       </c>
@@ -14909,7 +15274,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="256" spans="1:14">
+    <row r="256" spans="1:15">
       <c r="A256" t="s">
         <v>528</v>
       </c>
@@ -14953,7 +15318,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="257" spans="1:14">
+    <row r="257" spans="1:15">
       <c r="A257" t="s">
         <v>529</v>
       </c>
@@ -14997,7 +15362,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="258" spans="1:14">
+    <row r="258" spans="1:15">
       <c r="A258" t="s">
         <v>530</v>
       </c>
@@ -15041,7 +15406,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="259" spans="1:14">
+    <row r="259" spans="1:15">
       <c r="A259" t="s">
         <v>531</v>
       </c>
@@ -15085,7 +15450,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="260" spans="1:14">
+    <row r="260" spans="1:15">
       <c r="A260" t="s">
         <v>532</v>
       </c>
@@ -15129,7 +15494,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="261" spans="1:14">
+    <row r="261" spans="1:15">
       <c r="A261" t="s">
         <v>533</v>
       </c>
@@ -15173,7 +15538,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="262" spans="1:14">
+    <row r="262" spans="1:15">
       <c r="A262" t="s">
         <v>534</v>
       </c>
@@ -15217,7 +15582,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="263" spans="1:14">
+    <row r="263" spans="1:15">
       <c r="A263" t="s">
         <v>535</v>
       </c>
@@ -15261,7 +15626,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="264" spans="1:14">
+    <row r="264" spans="1:15">
       <c r="A264" t="s">
         <v>536</v>
       </c>
@@ -15305,7 +15670,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="265" spans="1:14">
+    <row r="265" spans="1:15">
       <c r="A265" t="s">
         <v>537</v>
       </c>
@@ -15349,7 +15714,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="266" spans="1:14">
+    <row r="266" spans="1:15">
       <c r="A266" t="s">
         <v>538</v>
       </c>
@@ -15393,7 +15758,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="267" spans="1:14">
+    <row r="267" spans="1:15">
       <c r="A267" t="s">
         <v>539</v>
       </c>
@@ -15437,7 +15802,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="268" spans="1:14">
+    <row r="268" spans="1:15">
       <c r="A268" t="s">
         <v>540</v>
       </c>
@@ -15481,7 +15846,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="269" spans="1:14">
+    <row r="269" spans="1:15">
       <c r="A269" t="s">
         <v>541</v>
       </c>
@@ -15525,7 +15890,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="270" spans="1:14">
+    <row r="270" spans="1:15">
       <c r="A270" t="s">
         <v>542</v>
       </c>
@@ -15569,7 +15934,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="271" spans="1:14" hidden="1">
+    <row r="271" spans="1:15">
       <c r="A271" t="s">
         <v>543</v>
       </c>
@@ -15612,8 +15977,11 @@
       <c r="N271" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="272" spans="1:14" hidden="1">
+      <c r="O271">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="272" spans="1:15">
       <c r="A272" t="s">
         <v>544</v>
       </c>
@@ -15656,8 +16024,11 @@
       <c r="N272" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="273" spans="1:14" hidden="1">
+      <c r="O272">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="273" spans="1:15">
       <c r="A273" t="s">
         <v>545</v>
       </c>
@@ -15700,8 +16071,11 @@
       <c r="N273" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="274" spans="1:14" hidden="1">
+      <c r="O273">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="274" spans="1:15">
       <c r="A274" t="s">
         <v>546</v>
       </c>
@@ -15744,8 +16118,11 @@
       <c r="N274" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="275" spans="1:14" hidden="1">
+      <c r="O274">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="275" spans="1:15">
       <c r="A275" t="s">
         <v>547</v>
       </c>
@@ -15788,27 +16165,30 @@
       <c r="N275" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="276" spans="1:14" hidden="1">
+      <c r="O275">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="276" spans="1:15">
       <c r="A276" t="s">
         <v>548</v>
       </c>
-      <c r="B276" s="11" t="s">
+      <c r="B276" s="4" t="s">
         <v>1024</v>
       </c>
-      <c r="C276" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D276" s="9">
+      <c r="C276">
+        <v>2026</v>
+      </c>
+      <c r="D276">
         <v>5</v>
       </c>
-      <c r="E276" s="9" t="s">
+      <c r="E276" t="s">
         <v>404</v>
       </c>
-      <c r="F276" s="9" t="s">
+      <c r="F276" t="s">
         <v>45</v>
       </c>
-      <c r="G276" s="13">
+      <c r="G276" s="4">
         <v>10239802821</v>
       </c>
       <c r="H276" t="s">
@@ -15823,17 +16203,20 @@
       <c r="K276" t="s">
         <v>652</v>
       </c>
-      <c r="L276" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M276" s="9">
+      <c r="L276" t="s">
+        <v>88</v>
+      </c>
+      <c r="M276">
         <v>1</v>
       </c>
       <c r="N276" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="277" spans="1:14" hidden="1">
+      <c r="O276">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="277" spans="1:15">
       <c r="A277" t="s">
         <v>549</v>
       </c>
@@ -15876,8 +16259,11 @@
       <c r="N277" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="278" spans="1:14" hidden="1">
+      <c r="O277">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="278" spans="1:15">
       <c r="A278" t="s">
         <v>550</v>
       </c>
@@ -15920,8 +16306,11 @@
       <c r="N278" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="279" spans="1:14" hidden="1">
+      <c r="O278">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:15">
       <c r="A279" t="s">
         <v>551</v>
       </c>
@@ -15964,27 +16353,30 @@
       <c r="N279" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="280" spans="1:14" hidden="1">
+      <c r="O279">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:15">
       <c r="A280" t="s">
         <v>552</v>
       </c>
-      <c r="B280" s="11" t="s">
+      <c r="B280" s="4" t="s">
         <v>1016</v>
       </c>
-      <c r="C280" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D280" s="9">
+      <c r="C280">
+        <v>2026</v>
+      </c>
+      <c r="D280">
         <v>6</v>
       </c>
-      <c r="E280" s="9" t="s">
+      <c r="E280" t="s">
         <v>404</v>
       </c>
-      <c r="F280" s="9" t="s">
+      <c r="F280" t="s">
         <v>45</v>
       </c>
-      <c r="G280" s="13">
+      <c r="G280" s="4">
         <v>10239486377</v>
       </c>
       <c r="H280" t="s">
@@ -15999,17 +16391,20 @@
       <c r="K280" t="s">
         <v>1046</v>
       </c>
-      <c r="L280" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M280" s="9">
+      <c r="L280" t="s">
+        <v>88</v>
+      </c>
+      <c r="M280">
         <v>1</v>
       </c>
       <c r="N280" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="281" spans="1:14">
+      <c r="O280">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="281" spans="1:15">
       <c r="A281" t="s">
         <v>553</v>
       </c>
@@ -16053,7 +16448,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="282" spans="1:14">
+    <row r="282" spans="1:15">
       <c r="A282" t="s">
         <v>554</v>
       </c>
@@ -16097,7 +16492,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="283" spans="1:14">
+    <row r="283" spans="1:15">
       <c r="A283" t="s">
         <v>555</v>
       </c>
@@ -16141,7 +16536,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="284" spans="1:14">
+    <row r="284" spans="1:15">
       <c r="A284" t="s">
         <v>556</v>
       </c>
@@ -16185,7 +16580,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="285" spans="1:14">
+    <row r="285" spans="1:15">
       <c r="A285" t="s">
         <v>557</v>
       </c>
@@ -16229,7 +16624,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="286" spans="1:14">
+    <row r="286" spans="1:15">
       <c r="A286" t="s">
         <v>558</v>
       </c>
@@ -16273,7 +16668,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="287" spans="1:14">
+    <row r="287" spans="1:15">
       <c r="A287" t="s">
         <v>559</v>
       </c>
@@ -16317,7 +16712,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="288" spans="1:14">
+    <row r="288" spans="1:15">
       <c r="A288" t="s">
         <v>560</v>
       </c>
@@ -16361,7 +16756,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="289" spans="1:14">
+    <row r="289" spans="1:15">
       <c r="A289" t="s">
         <v>561</v>
       </c>
@@ -16405,7 +16800,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="290" spans="1:14">
+    <row r="290" spans="1:15">
       <c r="A290" t="s">
         <v>562</v>
       </c>
@@ -16449,7 +16844,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="291" spans="1:14">
+    <row r="291" spans="1:15">
       <c r="A291" t="s">
         <v>563</v>
       </c>
@@ -16493,7 +16888,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="292" spans="1:14">
+    <row r="292" spans="1:15">
       <c r="A292" t="s">
         <v>564</v>
       </c>
@@ -16537,7 +16932,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="293" spans="1:14">
+    <row r="293" spans="1:15">
       <c r="A293" t="s">
         <v>565</v>
       </c>
@@ -16581,7 +16976,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="294" spans="1:14">
+    <row r="294" spans="1:15">
       <c r="A294" t="s">
         <v>566</v>
       </c>
@@ -16625,7 +17020,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="295" spans="1:14">
+    <row r="295" spans="1:15">
       <c r="A295" t="s">
         <v>567</v>
       </c>
@@ -16669,7 +17064,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="296" spans="1:14">
+    <row r="296" spans="1:15">
       <c r="A296" t="s">
         <v>568</v>
       </c>
@@ -16713,7 +17108,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="297" spans="1:14" hidden="1">
+    <row r="297" spans="1:15">
       <c r="A297" t="s">
         <v>569</v>
       </c>
@@ -16756,8 +17151,11 @@
       <c r="N297" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="298" spans="1:14" hidden="1">
+      <c r="O297">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="298" spans="1:15">
       <c r="A298" t="s">
         <v>570</v>
       </c>
@@ -16800,8 +17198,11 @@
       <c r="N298" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="299" spans="1:14" hidden="1">
+      <c r="O298">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="299" spans="1:15">
       <c r="A299" t="s">
         <v>571</v>
       </c>
@@ -16844,8 +17245,11 @@
       <c r="N299" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="300" spans="1:14" s="2" customFormat="1" hidden="1">
+      <c r="O299">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="300" spans="1:15" s="2" customFormat="1">
       <c r="A300" t="s">
         <v>572</v>
       </c>
@@ -16888,8 +17292,11 @@
       <c r="N300" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="301" spans="1:14" s="2" customFormat="1" hidden="1">
+      <c r="O300">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="301" spans="1:15" s="2" customFormat="1">
       <c r="A301" t="s">
         <v>573</v>
       </c>
@@ -16932,27 +17339,30 @@
       <c r="N301" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="302" spans="1:14" hidden="1">
+      <c r="O301">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="302" spans="1:15">
       <c r="A302" t="s">
         <v>574</v>
       </c>
-      <c r="B302" s="11" t="s">
+      <c r="B302" s="4" t="s">
         <v>1022</v>
       </c>
-      <c r="C302" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D302" s="9">
+      <c r="C302">
+        <v>2026</v>
+      </c>
+      <c r="D302">
         <v>5</v>
       </c>
-      <c r="E302" s="9" t="s">
+      <c r="E302" t="s">
         <v>404</v>
       </c>
-      <c r="F302" s="9" t="s">
+      <c r="F302" t="s">
         <v>45</v>
       </c>
-      <c r="G302" s="13">
+      <c r="G302" s="4">
         <v>10800860321</v>
       </c>
       <c r="H302" t="s">
@@ -16967,17 +17377,20 @@
       <c r="K302" t="s">
         <v>646</v>
       </c>
-      <c r="L302" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M302" s="9">
+      <c r="L302" t="s">
+        <v>88</v>
+      </c>
+      <c r="M302">
         <v>1</v>
       </c>
       <c r="N302" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="303" spans="1:14" hidden="1">
+      <c r="O302">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="303" spans="1:15">
       <c r="A303" t="s">
         <v>575</v>
       </c>
@@ -17020,8 +17433,11 @@
       <c r="N303" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="304" spans="1:14" hidden="1">
+      <c r="O303">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:15">
       <c r="A304" t="s">
         <v>576</v>
       </c>
@@ -17064,8 +17480,11 @@
       <c r="N304" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="305" spans="1:14" hidden="1">
+      <c r="O304">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:15">
       <c r="A305" t="s">
         <v>577</v>
       </c>
@@ -17108,8 +17527,11 @@
       <c r="N305" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="306" spans="1:14" hidden="1">
+      <c r="O305">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="306" spans="1:15">
       <c r="A306" t="s">
         <v>578</v>
       </c>
@@ -17152,8 +17574,11 @@
       <c r="N306" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="307" spans="1:14" hidden="1">
+      <c r="O306">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="307" spans="1:15">
       <c r="A307" t="s">
         <v>579</v>
       </c>
@@ -17196,8 +17621,11 @@
       <c r="N307" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="308" spans="1:14" hidden="1">
+      <c r="O307">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="308" spans="1:15">
       <c r="A308" t="s">
         <v>580</v>
       </c>
@@ -17240,8 +17668,11 @@
       <c r="N308" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="309" spans="1:14" hidden="1">
+      <c r="O308">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="309" spans="1:15">
       <c r="A309" t="s">
         <v>581</v>
       </c>
@@ -17284,8 +17715,11 @@
       <c r="N309" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="310" spans="1:14" hidden="1">
+      <c r="O309">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="310" spans="1:15">
       <c r="A310" t="s">
         <v>582</v>
       </c>
@@ -17328,8 +17762,11 @@
       <c r="N310" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="311" spans="1:14" hidden="1">
+      <c r="O310">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:15">
       <c r="A311" t="s">
         <v>583</v>
       </c>
@@ -17372,27 +17809,30 @@
       <c r="N311" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="312" spans="1:14" hidden="1">
+      <c r="O311">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:15">
       <c r="A312" t="s">
         <v>584</v>
       </c>
-      <c r="B312" s="11" t="s">
+      <c r="B312" s="4" t="s">
         <v>1018</v>
       </c>
-      <c r="C312" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D312" s="9">
+      <c r="C312">
+        <v>2026</v>
+      </c>
+      <c r="D312">
         <v>6</v>
       </c>
-      <c r="E312" s="9" t="s">
+      <c r="E312" t="s">
         <v>404</v>
       </c>
-      <c r="F312" s="9" t="s">
+      <c r="F312" t="s">
         <v>45</v>
       </c>
-      <c r="G312" s="13">
+      <c r="G312" s="4">
         <v>40347164</v>
       </c>
       <c r="H312" t="s">
@@ -17407,36 +17847,39 @@
       <c r="K312" t="s">
         <v>1047</v>
       </c>
-      <c r="L312" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M312" s="9">
+      <c r="L312" t="s">
+        <v>88</v>
+      </c>
+      <c r="M312">
         <v>1</v>
       </c>
       <c r="N312" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="313" spans="1:14" hidden="1">
+      <c r="O312">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="313" spans="1:15">
       <c r="A313" t="s">
         <v>585</v>
       </c>
-      <c r="B313" s="11" t="s">
+      <c r="B313" s="4" t="s">
         <v>1018</v>
       </c>
-      <c r="C313" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D313" s="9">
+      <c r="C313">
+        <v>2026</v>
+      </c>
+      <c r="D313">
         <v>6</v>
       </c>
-      <c r="E313" s="9" t="s">
+      <c r="E313" t="s">
         <v>404</v>
       </c>
-      <c r="F313" s="9" t="s">
+      <c r="F313" t="s">
         <v>45</v>
       </c>
-      <c r="G313" s="13">
+      <c r="G313" s="4">
         <v>10239510197</v>
       </c>
       <c r="H313" t="s">
@@ -17451,17 +17894,20 @@
       <c r="K313" t="s">
         <v>1051</v>
       </c>
-      <c r="L313" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M313" s="9">
+      <c r="L313" t="s">
+        <v>88</v>
+      </c>
+      <c r="M313">
         <v>1</v>
       </c>
       <c r="N313" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="314" spans="1:14" hidden="1">
+      <c r="O313">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="314" spans="1:15">
       <c r="A314" t="s">
         <v>586</v>
       </c>
@@ -17504,8 +17950,11 @@
       <c r="N314" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="315" spans="1:14" hidden="1">
+      <c r="O314">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="315" spans="1:15">
       <c r="A315" t="s">
         <v>587</v>
       </c>
@@ -17548,8 +17997,11 @@
       <c r="N315" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="316" spans="1:14" hidden="1">
+      <c r="O315">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="316" spans="1:15">
       <c r="A316" t="s">
         <v>588</v>
       </c>
@@ -17592,8 +18044,11 @@
       <c r="N316" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="317" spans="1:14" hidden="1">
+      <c r="O316">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="317" spans="1:15">
       <c r="A317" t="s">
         <v>589</v>
       </c>
@@ -17612,7 +18067,7 @@
       <c r="F317" t="s">
         <v>467</v>
       </c>
-      <c r="G317" s="13">
+      <c r="G317" s="4">
         <v>10239486377</v>
       </c>
       <c r="H317" t="s">
@@ -17636,8 +18091,11 @@
       <c r="N317" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="318" spans="1:14" hidden="1">
+      <c r="O317">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="318" spans="1:15">
       <c r="A318" t="s">
         <v>590</v>
       </c>
@@ -17680,8 +18138,11 @@
       <c r="N318" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="319" spans="1:14" hidden="1">
+      <c r="O318">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="319" spans="1:15">
       <c r="A319" t="s">
         <v>591</v>
       </c>
@@ -17724,8 +18185,11 @@
       <c r="N319" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="320" spans="1:14">
+      <c r="O319">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:15">
       <c r="A320" t="s">
         <v>592</v>
       </c>
@@ -17744,7 +18208,7 @@
       <c r="F320" t="s">
         <v>402</v>
       </c>
-      <c r="G320" s="13">
+      <c r="G320" s="4">
         <v>23922343</v>
       </c>
       <c r="H320" t="s">
@@ -17769,26 +18233,26 @@
         <v>89</v>
       </c>
     </row>
-    <row r="321" spans="1:14" hidden="1">
+    <row r="321" spans="1:15">
       <c r="A321" t="s">
         <v>593</v>
       </c>
-      <c r="B321" s="11" t="s">
+      <c r="B321" s="4" t="s">
         <v>924</v>
       </c>
-      <c r="C321" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D321" s="9">
+      <c r="C321">
+        <v>2026</v>
+      </c>
+      <c r="D321">
         <v>6</v>
       </c>
-      <c r="E321" s="9" t="s">
+      <c r="E321" t="s">
         <v>404</v>
       </c>
-      <c r="F321" s="9" t="s">
+      <c r="F321" t="s">
         <v>45</v>
       </c>
-      <c r="G321" s="13">
+      <c r="G321" s="4">
         <v>10473163450</v>
       </c>
       <c r="H321" t="s">
@@ -17803,17 +18267,20 @@
       <c r="K321" t="s">
         <v>1061</v>
       </c>
-      <c r="L321" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M321" s="9">
+      <c r="L321" t="s">
+        <v>88</v>
+      </c>
+      <c r="M321">
         <v>2</v>
       </c>
       <c r="N321" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="322" spans="1:14">
+      <c r="O321">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="322" spans="1:15">
       <c r="A322" t="s">
         <v>594</v>
       </c>
@@ -17857,7 +18324,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="323" spans="1:14">
+    <row r="323" spans="1:15">
       <c r="A323" t="s">
         <v>595</v>
       </c>
@@ -17901,7 +18368,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="324" spans="1:14">
+    <row r="324" spans="1:15">
       <c r="A324" t="s">
         <v>596</v>
       </c>
@@ -17945,7 +18412,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="325" spans="1:14">
+    <row r="325" spans="1:15">
       <c r="A325" t="s">
         <v>597</v>
       </c>
@@ -17989,7 +18456,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="326" spans="1:14">
+    <row r="326" spans="1:15">
       <c r="A326" t="s">
         <v>598</v>
       </c>
@@ -18033,7 +18500,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="327" spans="1:14">
+    <row r="327" spans="1:15">
       <c r="A327" t="s">
         <v>599</v>
       </c>
@@ -18077,7 +18544,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="328" spans="1:14">
+    <row r="328" spans="1:15">
       <c r="A328" t="s">
         <v>600</v>
       </c>
@@ -18121,7 +18588,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="329" spans="1:14">
+    <row r="329" spans="1:15">
       <c r="A329" t="s">
         <v>610</v>
       </c>
@@ -18165,7 +18632,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="330" spans="1:14">
+    <row r="330" spans="1:15">
       <c r="A330" t="s">
         <v>611</v>
       </c>
@@ -18209,7 +18676,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="331" spans="1:14">
+    <row r="331" spans="1:15">
       <c r="A331" t="s">
         <v>739</v>
       </c>
@@ -18253,7 +18720,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="332" spans="1:14">
+    <row r="332" spans="1:15">
       <c r="A332" t="s">
         <v>740</v>
       </c>
@@ -18297,7 +18764,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="333" spans="1:14">
+    <row r="333" spans="1:15">
       <c r="A333" t="s">
         <v>741</v>
       </c>
@@ -18341,7 +18808,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="334" spans="1:14">
+    <row r="334" spans="1:15">
       <c r="A334" t="s">
         <v>742</v>
       </c>
@@ -18385,7 +18852,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="335" spans="1:14">
+    <row r="335" spans="1:15">
       <c r="A335" t="s">
         <v>743</v>
       </c>
@@ -18429,7 +18896,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="336" spans="1:14">
+    <row r="336" spans="1:15">
       <c r="A336" t="s">
         <v>744</v>
       </c>
@@ -18473,7 +18940,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="337" spans="1:14">
+    <row r="337" spans="1:15">
       <c r="A337" t="s">
         <v>745</v>
       </c>
@@ -18517,7 +18984,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="338" spans="1:14">
+    <row r="338" spans="1:15">
       <c r="A338" t="s">
         <v>746</v>
       </c>
@@ -18561,7 +19028,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="339" spans="1:14">
+    <row r="339" spans="1:15">
       <c r="A339" t="s">
         <v>747</v>
       </c>
@@ -18605,7 +19072,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="340" spans="1:14">
+    <row r="340" spans="1:15">
       <c r="A340" t="s">
         <v>748</v>
       </c>
@@ -18649,7 +19116,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="341" spans="1:14" hidden="1">
+    <row r="341" spans="1:15">
       <c r="A341" t="s">
         <v>749</v>
       </c>
@@ -18692,8 +19159,11 @@
       <c r="N341" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="342" spans="1:14" hidden="1">
+      <c r="O341">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="342" spans="1:15">
       <c r="A342" t="s">
         <v>750</v>
       </c>
@@ -18736,8 +19206,11 @@
       <c r="N342" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="343" spans="1:14" hidden="1">
+      <c r="O342">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="343" spans="1:15">
       <c r="A343" t="s">
         <v>751</v>
       </c>
@@ -18780,8 +19253,11 @@
       <c r="N343" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="344" spans="1:14" hidden="1">
+      <c r="O343">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="344" spans="1:15">
       <c r="A344" t="s">
         <v>752</v>
       </c>
@@ -18824,8 +19300,11 @@
       <c r="N344" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="345" spans="1:14" hidden="1">
+      <c r="O344">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="345" spans="1:15">
       <c r="A345" t="s">
         <v>753</v>
       </c>
@@ -18868,8 +19347,11 @@
       <c r="N345" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="346" spans="1:14" hidden="1">
+      <c r="O345">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="346" spans="1:15">
       <c r="A346" t="s">
         <v>754</v>
       </c>
@@ -18912,8 +19394,11 @@
       <c r="N346" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="347" spans="1:14" hidden="1">
+      <c r="O346">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:15">
       <c r="A347" t="s">
         <v>755</v>
       </c>
@@ -18956,8 +19441,11 @@
       <c r="N347" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="348" spans="1:14" hidden="1">
+      <c r="O347">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="348" spans="1:15">
       <c r="A348" t="s">
         <v>756</v>
       </c>
@@ -19000,8 +19488,11 @@
       <c r="N348" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="349" spans="1:14">
+      <c r="O348">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:15">
       <c r="A349" t="s">
         <v>757</v>
       </c>
@@ -19020,7 +19511,7 @@
       <c r="F349" t="s">
         <v>401</v>
       </c>
-      <c r="G349" s="13">
+      <c r="G349" s="4">
         <v>10450876700</v>
       </c>
       <c r="H349" t="s">
@@ -19045,7 +19536,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="350" spans="1:14">
+    <row r="350" spans="1:15">
       <c r="A350" t="s">
         <v>758</v>
       </c>
@@ -19064,7 +19555,7 @@
       <c r="F350" t="s">
         <v>401</v>
       </c>
-      <c r="G350" s="13">
+      <c r="G350" s="4">
         <v>10476142941</v>
       </c>
       <c r="H350" t="s">
@@ -19089,7 +19580,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="351" spans="1:14">
+    <row r="351" spans="1:15">
       <c r="A351" t="s">
         <v>759</v>
       </c>
@@ -19108,7 +19599,7 @@
       <c r="F351" t="s">
         <v>401</v>
       </c>
-      <c r="G351" s="13">
+      <c r="G351" s="4">
         <v>10454316903</v>
       </c>
       <c r="H351" t="s">
@@ -19133,7 +19624,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="352" spans="1:14">
+    <row r="352" spans="1:15">
       <c r="A352" t="s">
         <v>760</v>
       </c>
@@ -19152,7 +19643,7 @@
       <c r="F352" t="s">
         <v>401</v>
       </c>
-      <c r="G352" s="13">
+      <c r="G352" s="4">
         <v>10456258536</v>
       </c>
       <c r="H352" t="s">
@@ -19177,7 +19668,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="353" spans="1:14">
+    <row r="353" spans="1:15">
       <c r="A353" t="s">
         <v>761</v>
       </c>
@@ -19196,7 +19687,7 @@
       <c r="F353" t="s">
         <v>401</v>
       </c>
-      <c r="G353" s="13">
+      <c r="G353" s="4">
         <v>10462583996</v>
       </c>
       <c r="H353" t="s">
@@ -19221,7 +19712,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="354" spans="1:14">
+    <row r="354" spans="1:15">
       <c r="A354" t="s">
         <v>762</v>
       </c>
@@ -19240,7 +19731,7 @@
       <c r="F354" t="s">
         <v>401</v>
       </c>
-      <c r="G354" s="13">
+      <c r="G354" s="4">
         <v>46314028</v>
       </c>
       <c r="H354" t="s">
@@ -19265,7 +19756,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="355" spans="1:14">
+    <row r="355" spans="1:15">
       <c r="A355" t="s">
         <v>763</v>
       </c>
@@ -19284,7 +19775,7 @@
       <c r="F355" t="s">
         <v>401</v>
       </c>
-      <c r="G355" s="13">
+      <c r="G355" s="4">
         <v>43150763</v>
       </c>
       <c r="H355" t="s">
@@ -19309,7 +19800,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="356" spans="1:14">
+    <row r="356" spans="1:15">
       <c r="A356" t="s">
         <v>764</v>
       </c>
@@ -19328,7 +19819,7 @@
       <c r="F356" t="s">
         <v>401</v>
       </c>
-      <c r="G356" s="13">
+      <c r="G356" s="4">
         <v>42566234</v>
       </c>
       <c r="H356" t="s">
@@ -19353,7 +19844,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="357" spans="1:14">
+    <row r="357" spans="1:15">
       <c r="A357" t="s">
         <v>765</v>
       </c>
@@ -19372,7 +19863,7 @@
       <c r="F357" t="s">
         <v>401</v>
       </c>
-      <c r="G357" s="13">
+      <c r="G357" s="4">
         <v>40040306</v>
       </c>
       <c r="H357" t="s">
@@ -19397,7 +19888,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="358" spans="1:14">
+    <row r="358" spans="1:15">
       <c r="A358" t="s">
         <v>766</v>
       </c>
@@ -19416,7 +19907,7 @@
       <c r="F358" t="s">
         <v>401</v>
       </c>
-      <c r="G358" s="13">
+      <c r="G358" s="4">
         <v>73870421</v>
       </c>
       <c r="H358" t="s">
@@ -19441,7 +19932,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="359" spans="1:14">
+    <row r="359" spans="1:15">
       <c r="A359" t="s">
         <v>767</v>
       </c>
@@ -19460,7 +19951,7 @@
       <c r="F359" t="s">
         <v>401</v>
       </c>
-      <c r="G359" s="13">
+      <c r="G359" s="4">
         <v>24873839</v>
       </c>
       <c r="H359" t="s">
@@ -19485,7 +19976,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="360" spans="1:14">
+    <row r="360" spans="1:15">
       <c r="A360" t="s">
         <v>768</v>
       </c>
@@ -19504,7 +19995,7 @@
       <c r="F360" t="s">
         <v>401</v>
       </c>
-      <c r="G360" s="13">
+      <c r="G360" s="4">
         <v>47656632</v>
       </c>
       <c r="H360" t="s">
@@ -19529,7 +20020,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="361" spans="1:14">
+    <row r="361" spans="1:15">
       <c r="A361" t="s">
         <v>769</v>
       </c>
@@ -19548,7 +20039,7 @@
       <c r="F361" t="s">
         <v>401</v>
       </c>
-      <c r="G361" s="13">
+      <c r="G361" s="4">
         <v>47925279</v>
       </c>
       <c r="H361" t="s">
@@ -19573,7 +20064,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="362" spans="1:14">
+    <row r="362" spans="1:15">
       <c r="A362" t="s">
         <v>770</v>
       </c>
@@ -19592,7 +20083,7 @@
       <c r="F362" t="s">
         <v>401</v>
       </c>
-      <c r="G362" s="13">
+      <c r="G362" s="4">
         <v>46474063</v>
       </c>
       <c r="H362" t="s">
@@ -19617,7 +20108,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="363" spans="1:14">
+    <row r="363" spans="1:15">
       <c r="A363" t="s">
         <v>771</v>
       </c>
@@ -19636,7 +20127,7 @@
       <c r="F363" t="s">
         <v>401</v>
       </c>
-      <c r="G363" s="13">
+      <c r="G363" s="4">
         <v>42049412</v>
       </c>
       <c r="H363" t="s">
@@ -19661,26 +20152,26 @@
         <v>89</v>
       </c>
     </row>
-    <row r="364" spans="1:14" hidden="1">
+    <row r="364" spans="1:15">
       <c r="A364" t="s">
         <v>772</v>
       </c>
-      <c r="B364" s="11" t="s">
+      <c r="B364" s="4" t="s">
         <v>929</v>
       </c>
-      <c r="C364" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D364" s="9">
+      <c r="C364">
+        <v>2026</v>
+      </c>
+      <c r="D364">
         <v>6</v>
       </c>
-      <c r="E364" s="9" t="s">
+      <c r="E364" t="s">
         <v>404</v>
       </c>
-      <c r="F364" s="9" t="s">
+      <c r="F364" t="s">
         <v>45</v>
       </c>
-      <c r="G364" s="13">
+      <c r="G364" s="4">
         <v>10473163450</v>
       </c>
       <c r="H364" t="s">
@@ -19695,17 +20186,20 @@
       <c r="K364" t="s">
         <v>1062</v>
       </c>
-      <c r="L364" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M364" s="9">
+      <c r="L364" t="s">
+        <v>88</v>
+      </c>
+      <c r="M364">
         <v>1</v>
       </c>
       <c r="N364" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="365" spans="1:14" hidden="1">
+      <c r="O364">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="365" spans="1:15">
       <c r="A365" t="s">
         <v>773</v>
       </c>
@@ -19748,8 +20242,11 @@
       <c r="N365" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="366" spans="1:14" hidden="1">
+      <c r="O365">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="366" spans="1:15">
       <c r="A366" t="s">
         <v>774</v>
       </c>
@@ -19792,8 +20289,11 @@
       <c r="N366" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="367" spans="1:14" hidden="1">
+      <c r="O366">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="367" spans="1:15">
       <c r="A367" t="s">
         <v>775</v>
       </c>
@@ -19836,8 +20336,11 @@
       <c r="N367" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="368" spans="1:14" hidden="1">
+      <c r="O367">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="368" spans="1:15">
       <c r="A368" t="s">
         <v>776</v>
       </c>
@@ -19880,27 +20383,30 @@
       <c r="N368" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="369" spans="1:14" hidden="1">
+      <c r="O368">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="369" spans="1:15">
       <c r="A369" t="s">
         <v>777</v>
       </c>
-      <c r="B369" s="11" t="s">
+      <c r="B369" s="4" t="s">
         <v>1019</v>
       </c>
-      <c r="C369" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D369" s="9">
+      <c r="C369">
+        <v>2026</v>
+      </c>
+      <c r="D369">
         <v>6</v>
       </c>
-      <c r="E369" s="9" t="s">
+      <c r="E369" t="s">
         <v>404</v>
       </c>
-      <c r="F369" s="9" t="s">
+      <c r="F369" t="s">
         <v>45</v>
       </c>
-      <c r="G369" s="13">
+      <c r="G369" s="4">
         <v>10430636931</v>
       </c>
       <c r="H369" t="s">
@@ -19915,17 +20421,20 @@
       <c r="K369" t="s">
         <v>1060</v>
       </c>
-      <c r="L369" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M369" s="9">
+      <c r="L369" t="s">
+        <v>88</v>
+      </c>
+      <c r="M369">
         <v>2</v>
       </c>
       <c r="N369" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="370" spans="1:14">
+      <c r="O369">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="370" spans="1:15">
       <c r="A370" t="s">
         <v>778</v>
       </c>
@@ -19969,7 +20478,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="371" spans="1:14">
+    <row r="371" spans="1:15">
       <c r="A371" t="s">
         <v>779</v>
       </c>
@@ -20013,7 +20522,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="372" spans="1:14">
+    <row r="372" spans="1:15">
       <c r="A372" t="s">
         <v>780</v>
       </c>
@@ -20057,7 +20566,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="373" spans="1:14">
+    <row r="373" spans="1:15">
       <c r="A373" t="s">
         <v>781</v>
       </c>
@@ -20101,7 +20610,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="374" spans="1:14">
+    <row r="374" spans="1:15">
       <c r="A374" t="s">
         <v>782</v>
       </c>
@@ -20145,7 +20654,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="375" spans="1:14" hidden="1">
+    <row r="375" spans="1:15">
       <c r="A375" t="s">
         <v>783</v>
       </c>
@@ -20188,8 +20697,11 @@
       <c r="N375" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="376" spans="1:14">
+      <c r="O375">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="376" spans="1:15">
       <c r="A376" t="s">
         <v>784</v>
       </c>
@@ -20233,7 +20745,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="377" spans="1:14" hidden="1">
+    <row r="377" spans="1:15">
       <c r="A377" t="s">
         <v>785</v>
       </c>
@@ -20276,8 +20788,11 @@
       <c r="N377" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="378" spans="1:14" hidden="1">
+      <c r="O377">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="378" spans="1:15">
       <c r="A378" t="s">
         <v>786</v>
       </c>
@@ -20320,27 +20835,30 @@
       <c r="N378" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="379" spans="1:14" hidden="1">
+      <c r="O378">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="379" spans="1:15">
       <c r="A379" t="s">
         <v>787</v>
       </c>
-      <c r="B379" s="11" t="s">
+      <c r="B379" s="4" t="s">
         <v>1020</v>
       </c>
-      <c r="C379" s="9">
-        <v>2026</v>
-      </c>
-      <c r="D379" s="9">
+      <c r="C379">
+        <v>2026</v>
+      </c>
+      <c r="D379">
         <v>6</v>
       </c>
-      <c r="E379" s="9" t="s">
+      <c r="E379" t="s">
         <v>404</v>
       </c>
-      <c r="F379" s="9" t="s">
+      <c r="F379" t="s">
         <v>45</v>
       </c>
-      <c r="G379" s="13">
+      <c r="G379" s="4">
         <v>10430636931</v>
       </c>
       <c r="H379" t="s">
@@ -20355,17 +20873,20 @@
       <c r="K379" t="s">
         <v>1063</v>
       </c>
-      <c r="L379" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M379" s="9">
+      <c r="L379" t="s">
+        <v>88</v>
+      </c>
+      <c r="M379">
         <v>1</v>
       </c>
       <c r="N379" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="380" spans="1:14">
+      <c r="O379">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="380" spans="1:15">
       <c r="A380" t="s">
         <v>788</v>
       </c>
@@ -20409,7 +20930,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="381" spans="1:14">
+    <row r="381" spans="1:15">
       <c r="A381" t="s">
         <v>789</v>
       </c>
@@ -20453,7 +20974,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="382" spans="1:14">
+    <row r="382" spans="1:15">
       <c r="A382" t="s">
         <v>790</v>
       </c>
@@ -20497,7 +21018,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="383" spans="1:14">
+    <row r="383" spans="1:15">
       <c r="A383" t="s">
         <v>791</v>
       </c>
@@ -20541,7 +21062,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="384" spans="1:14">
+    <row r="384" spans="1:15">
       <c r="A384" t="s">
         <v>792</v>
       </c>
@@ -20585,7 +21106,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="385" spans="1:14">
+    <row r="385" spans="1:15">
       <c r="A385" t="s">
         <v>793</v>
       </c>
@@ -20629,7 +21150,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="386" spans="1:14">
+    <row r="386" spans="1:15">
       <c r="A386" t="s">
         <v>794</v>
       </c>
@@ -20673,7 +21194,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="387" spans="1:14">
+    <row r="387" spans="1:15">
       <c r="A387" t="s">
         <v>795</v>
       </c>
@@ -20717,7 +21238,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="388" spans="1:14">
+    <row r="388" spans="1:15">
       <c r="A388" t="s">
         <v>796</v>
       </c>
@@ -20761,7 +21282,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="389" spans="1:14">
+    <row r="389" spans="1:15">
       <c r="A389" t="s">
         <v>797</v>
       </c>
@@ -20805,7 +21326,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="390" spans="1:14">
+    <row r="390" spans="1:15">
       <c r="A390" t="s">
         <v>798</v>
       </c>
@@ -20849,7 +21370,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="391" spans="1:14">
+    <row r="391" spans="1:15">
       <c r="A391" t="s">
         <v>799</v>
       </c>
@@ -20893,7 +21414,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="392" spans="1:14">
+    <row r="392" spans="1:15">
       <c r="A392" t="s">
         <v>800</v>
       </c>
@@ -20937,7 +21458,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="393" spans="1:14" hidden="1">
+    <row r="393" spans="1:15">
       <c r="A393" t="s">
         <v>801</v>
       </c>
@@ -20980,8 +21501,11 @@
       <c r="N393" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="394" spans="1:14" hidden="1">
+      <c r="O393">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="394" spans="1:15">
       <c r="A394" t="s">
         <v>802</v>
       </c>
@@ -21024,8 +21548,11 @@
       <c r="N394" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="395" spans="1:14" hidden="1">
+      <c r="O394">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="395" spans="1:15">
       <c r="A395" t="s">
         <v>803</v>
       </c>
@@ -21068,8 +21595,11 @@
       <c r="N395" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="396" spans="1:14" hidden="1">
+      <c r="O395">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="396" spans="1:15">
       <c r="A396" t="s">
         <v>804</v>
       </c>
@@ -21112,8 +21642,11 @@
       <c r="N396" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="397" spans="1:14" hidden="1">
+      <c r="O396">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="397" spans="1:15">
       <c r="A397" t="s">
         <v>805</v>
       </c>
@@ -21156,8 +21689,11 @@
       <c r="N397" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="398" spans="1:14">
+      <c r="O397">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="398" spans="1:15">
       <c r="A398" t="s">
         <v>806</v>
       </c>
@@ -21201,7 +21737,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="399" spans="1:14">
+    <row r="399" spans="1:15">
       <c r="A399" t="s">
         <v>807</v>
       </c>
@@ -21245,7 +21781,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="400" spans="1:14">
+    <row r="400" spans="1:15">
       <c r="A400" t="s">
         <v>808</v>
       </c>
@@ -21289,7 +21825,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="401" spans="1:14">
+    <row r="401" spans="1:15">
       <c r="A401" t="s">
         <v>809</v>
       </c>
@@ -21333,7 +21869,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="402" spans="1:14" hidden="1">
+    <row r="402" spans="1:15">
       <c r="A402" t="s">
         <v>810</v>
       </c>
@@ -21376,8 +21912,11 @@
       <c r="N402" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="403" spans="1:14" hidden="1">
+      <c r="O402">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="403" spans="1:15">
       <c r="A403" t="s">
         <v>811</v>
       </c>
@@ -21420,8 +21959,11 @@
       <c r="N403" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="404" spans="1:14" hidden="1">
+      <c r="O403">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="404" spans="1:15">
       <c r="A404" t="s">
         <v>812</v>
       </c>
@@ -21464,8 +22006,11 @@
       <c r="N404" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="405" spans="1:14" hidden="1">
+      <c r="O404">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="405" spans="1:15">
       <c r="A405" t="s">
         <v>813</v>
       </c>
@@ -21508,8 +22053,11 @@
       <c r="N405" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="406" spans="1:14" hidden="1">
+      <c r="O405">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="406" spans="1:15">
       <c r="A406" t="s">
         <v>814</v>
       </c>
@@ -21552,8 +22100,11 @@
       <c r="N406" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="407" spans="1:14">
+      <c r="O406">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="407" spans="1:15">
       <c r="A407" t="s">
         <v>815</v>
       </c>
@@ -21597,7 +22148,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="408" spans="1:14" hidden="1">
+    <row r="408" spans="1:15">
       <c r="A408" t="s">
         <v>816</v>
       </c>
@@ -21640,8 +22191,11 @@
       <c r="N408" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="409" spans="1:14" hidden="1">
+      <c r="O408">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="409" spans="1:15">
       <c r="A409" t="s">
         <v>817</v>
       </c>
@@ -21684,8 +22238,11 @@
       <c r="N409" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="410" spans="1:14" hidden="1">
+      <c r="O409">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="410" spans="1:15">
       <c r="A410" t="s">
         <v>818</v>
       </c>
@@ -21728,8 +22285,11 @@
       <c r="N410" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="411" spans="1:14" hidden="1">
+      <c r="O410">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="411" spans="1:15">
       <c r="A411" t="s">
         <v>819</v>
       </c>
@@ -21748,7 +22308,7 @@
       <c r="F411" t="s">
         <v>46</v>
       </c>
-      <c r="G411" s="13">
+      <c r="G411" s="4">
         <v>10239510197</v>
       </c>
       <c r="H411" t="s">
@@ -21772,8 +22332,11 @@
       <c r="N411" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="412" spans="1:14" hidden="1">
+      <c r="O411">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="412" spans="1:15">
       <c r="A412" t="s">
         <v>820</v>
       </c>
@@ -21816,8 +22379,11 @@
       <c r="N412" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="413" spans="1:14" hidden="1">
+      <c r="O412">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="413" spans="1:15">
       <c r="A413" t="s">
         <v>821</v>
       </c>
@@ -21860,8 +22426,11 @@
       <c r="N413" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="414" spans="1:14" hidden="1">
+      <c r="O413">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="414" spans="1:15">
       <c r="A414" t="s">
         <v>822</v>
       </c>
@@ -21904,8 +22473,11 @@
       <c r="N414" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="415" spans="1:14" hidden="1">
+      <c r="O414">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="415" spans="1:15">
       <c r="A415" t="s">
         <v>823</v>
       </c>
@@ -21924,7 +22496,7 @@
       <c r="F415" t="s">
         <v>46</v>
       </c>
-      <c r="G415" s="13">
+      <c r="G415" s="4">
         <v>10239510197</v>
       </c>
       <c r="H415" t="s">
@@ -21948,8 +22520,11 @@
       <c r="N415" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="416" spans="1:14">
+      <c r="O415">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="416" spans="1:15">
       <c r="A416" t="s">
         <v>824</v>
       </c>
@@ -21993,7 +22568,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="417" spans="1:14">
+    <row r="417" spans="1:15">
       <c r="A417" t="s">
         <v>825</v>
       </c>
@@ -22037,7 +22612,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="418" spans="1:14">
+    <row r="418" spans="1:15">
       <c r="A418" t="s">
         <v>826</v>
       </c>
@@ -22081,7 +22656,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="419" spans="1:14">
+    <row r="419" spans="1:15">
       <c r="A419" t="s">
         <v>827</v>
       </c>
@@ -22125,7 +22700,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="420" spans="1:14" hidden="1">
+    <row r="420" spans="1:15">
       <c r="A420" t="s">
         <v>828</v>
       </c>
@@ -22168,8 +22743,11 @@
       <c r="N420" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="421" spans="1:14">
+      <c r="O420">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="421" spans="1:15">
       <c r="A421" t="s">
         <v>829</v>
       </c>
@@ -22213,7 +22791,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="422" spans="1:14">
+    <row r="422" spans="1:15">
       <c r="A422" t="s">
         <v>830</v>
       </c>
@@ -22257,7 +22835,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="423" spans="1:14">
+    <row r="423" spans="1:15">
       <c r="A423" t="s">
         <v>831</v>
       </c>
@@ -22301,7 +22879,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="424" spans="1:14">
+    <row r="424" spans="1:15">
       <c r="A424" t="s">
         <v>832</v>
       </c>
@@ -22345,7 +22923,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="425" spans="1:14" hidden="1">
+    <row r="425" spans="1:15">
       <c r="A425" t="s">
         <v>833</v>
       </c>
@@ -22388,8 +22966,11 @@
       <c r="N425" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="426" spans="1:14" hidden="1">
+      <c r="O425">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="426" spans="1:15">
       <c r="A426" t="s">
         <v>834</v>
       </c>
@@ -22432,8 +23013,11 @@
       <c r="N426" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="427" spans="1:14" hidden="1">
+      <c r="O426">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="427" spans="1:15">
       <c r="A427" t="s">
         <v>835</v>
       </c>
@@ -22476,8 +23060,11 @@
       <c r="N427" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="428" spans="1:14" hidden="1">
+      <c r="O427">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="428" spans="1:15">
       <c r="A428" t="s">
         <v>836</v>
       </c>
@@ -22520,8 +23107,11 @@
       <c r="N428" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="429" spans="1:14" hidden="1">
+      <c r="O428">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="429" spans="1:15">
       <c r="A429" t="s">
         <v>837</v>
       </c>
@@ -22564,8 +23154,11 @@
       <c r="N429" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="430" spans="1:14">
+      <c r="O429">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="430" spans="1:15">
       <c r="A430" t="s">
         <v>838</v>
       </c>
@@ -22609,7 +23202,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="431" spans="1:14">
+    <row r="431" spans="1:15">
       <c r="A431" t="s">
         <v>839</v>
       </c>
@@ -22653,7 +23246,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="432" spans="1:14">
+    <row r="432" spans="1:15">
       <c r="A432" t="s">
         <v>840</v>
       </c>
@@ -22697,7 +23290,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="433" spans="1:14">
+    <row r="433" spans="1:15">
       <c r="A433" t="s">
         <v>841</v>
       </c>
@@ -22741,7 +23334,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="434" spans="1:14">
+    <row r="434" spans="1:15">
       <c r="A434" t="s">
         <v>842</v>
       </c>
@@ -22785,7 +23378,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="435" spans="1:14">
+    <row r="435" spans="1:15">
       <c r="A435" t="s">
         <v>843</v>
       </c>
@@ -22829,7 +23422,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="436" spans="1:14">
+    <row r="436" spans="1:15">
       <c r="A436" t="s">
         <v>844</v>
       </c>
@@ -22873,7 +23466,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="437" spans="1:14">
+    <row r="437" spans="1:15">
       <c r="A437" t="s">
         <v>845</v>
       </c>
@@ -22917,7 +23510,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="438" spans="1:14" hidden="1">
+    <row r="438" spans="1:15">
       <c r="A438" t="s">
         <v>846</v>
       </c>
@@ -22960,8 +23553,11 @@
       <c r="N438" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="439" spans="1:14" hidden="1">
+      <c r="O438">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="439" spans="1:15">
       <c r="A439" t="s">
         <v>847</v>
       </c>
@@ -23004,8 +23600,11 @@
       <c r="N439" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="440" spans="1:14">
+      <c r="O439">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="440" spans="1:15">
       <c r="A440" t="s">
         <v>848</v>
       </c>
@@ -23049,7 +23648,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="441" spans="1:14">
+    <row r="441" spans="1:15">
       <c r="A441" t="s">
         <v>849</v>
       </c>
@@ -23093,7 +23692,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="442" spans="1:14">
+    <row r="442" spans="1:15">
       <c r="A442" t="s">
         <v>850</v>
       </c>
@@ -23137,7 +23736,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="443" spans="1:14">
+    <row r="443" spans="1:15">
       <c r="A443" t="s">
         <v>851</v>
       </c>
@@ -23181,7 +23780,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="444" spans="1:14">
+    <row r="444" spans="1:15">
       <c r="A444" t="s">
         <v>852</v>
       </c>
@@ -23225,7 +23824,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="445" spans="1:14">
+    <row r="445" spans="1:15">
       <c r="A445" t="s">
         <v>853</v>
       </c>
@@ -23269,7 +23868,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="446" spans="1:14">
+    <row r="446" spans="1:15">
       <c r="A446" t="s">
         <v>854</v>
       </c>
@@ -23313,7 +23912,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="447" spans="1:14">
+    <row r="447" spans="1:15">
       <c r="A447" t="s">
         <v>855</v>
       </c>
@@ -23357,7 +23956,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="448" spans="1:14">
+    <row r="448" spans="1:15">
       <c r="A448" t="s">
         <v>856</v>
       </c>
@@ -23948,7 +24547,7 @@
       <c r="F461" t="s">
         <v>401</v>
       </c>
-      <c r="G461" s="13">
+      <c r="G461" s="4">
         <v>10238869094</v>
       </c>
       <c r="H461" t="s">
@@ -23992,7 +24591,7 @@
       <c r="F462" t="s">
         <v>401</v>
       </c>
-      <c r="G462" s="13">
+      <c r="G462" s="4">
         <v>10247032270</v>
       </c>
       <c r="H462" t="s">
@@ -24809,7 +25408,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="481" spans="1:14">
+    <row r="481" spans="1:15">
       <c r="A481" t="s">
         <v>889</v>
       </c>
@@ -24853,7 +25452,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="482" spans="1:14">
+    <row r="482" spans="1:15">
       <c r="A482" t="s">
         <v>890</v>
       </c>
@@ -24897,7 +25496,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="483" spans="1:14">
+    <row r="483" spans="1:15">
       <c r="A483" t="s">
         <v>891</v>
       </c>
@@ -24941,7 +25540,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="484" spans="1:14">
+    <row r="484" spans="1:15">
       <c r="A484" t="s">
         <v>892</v>
       </c>
@@ -24985,7 +25584,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="485" spans="1:14" hidden="1">
+    <row r="485" spans="1:15">
       <c r="A485" t="s">
         <v>893</v>
       </c>
@@ -25028,8 +25627,11 @@
       <c r="N485" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="486" spans="1:14" hidden="1">
+      <c r="O485">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="486" spans="1:15">
       <c r="A486" t="s">
         <v>894</v>
       </c>
@@ -25072,8 +25674,11 @@
       <c r="N486" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="487" spans="1:14" hidden="1">
+      <c r="O486">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="487" spans="1:15">
       <c r="A487" t="s">
         <v>895</v>
       </c>
@@ -25116,8 +25721,11 @@
       <c r="N487" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="488" spans="1:14" hidden="1">
+      <c r="O487">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="488" spans="1:15">
       <c r="A488" t="s">
         <v>896</v>
       </c>
@@ -25136,7 +25744,7 @@
       <c r="F488" t="s">
         <v>46</v>
       </c>
-      <c r="G488" s="13">
+      <c r="G488" s="4">
         <v>10247107920</v>
       </c>
       <c r="H488" t="s">
@@ -25160,8 +25768,11 @@
       <c r="N488" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="489" spans="1:14" hidden="1">
+      <c r="O488">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="489" spans="1:15">
       <c r="A489" t="s">
         <v>897</v>
       </c>
@@ -25204,8 +25815,11 @@
       <c r="N489" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="490" spans="1:14" hidden="1">
+      <c r="O489">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="490" spans="1:15">
       <c r="A490" t="s">
         <v>898</v>
       </c>
@@ -25224,7 +25838,7 @@
       <c r="F490" t="s">
         <v>46</v>
       </c>
-      <c r="G490" s="13">
+      <c r="G490" s="4">
         <v>10247107920</v>
       </c>
       <c r="H490" t="s">
@@ -25248,8 +25862,11 @@
       <c r="N490" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="491" spans="1:14">
+      <c r="O490">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="491" spans="1:15">
       <c r="A491" t="s">
         <v>899</v>
       </c>
@@ -25293,7 +25910,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="492" spans="1:14">
+    <row r="492" spans="1:15">
       <c r="A492" t="s">
         <v>900</v>
       </c>
@@ -25337,7 +25954,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="493" spans="1:14">
+    <row r="493" spans="1:15">
       <c r="A493" t="s">
         <v>901</v>
       </c>
@@ -25381,7 +25998,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="494" spans="1:14">
+    <row r="494" spans="1:15">
       <c r="A494" t="s">
         <v>902</v>
       </c>
@@ -25425,7 +26042,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="495" spans="1:14" hidden="1">
+    <row r="495" spans="1:15">
       <c r="A495" t="s">
         <v>903</v>
       </c>
@@ -25468,8 +26085,11 @@
       <c r="N495" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="496" spans="1:14" hidden="1">
+      <c r="O495">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="496" spans="1:15">
       <c r="A496" t="s">
         <v>904</v>
       </c>
@@ -25512,8 +26132,11 @@
       <c r="N496" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="497" spans="1:14" hidden="1">
+      <c r="O496">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="497" spans="1:15">
       <c r="A497" t="s">
         <v>905</v>
       </c>
@@ -25556,8 +26179,11 @@
       <c r="N497" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="498" spans="1:14">
+      <c r="O497">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="498" spans="1:15">
       <c r="A498" t="s">
         <v>906</v>
       </c>
@@ -25601,7 +26227,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="499" spans="1:14">
+    <row r="499" spans="1:15">
       <c r="A499" t="s">
         <v>907</v>
       </c>
@@ -25645,7 +26271,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="500" spans="1:14" hidden="1">
+    <row r="500" spans="1:15">
       <c r="A500" t="s">
         <v>908</v>
       </c>
@@ -25688,8 +26314,11 @@
       <c r="N500" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="501" spans="1:14" hidden="1">
+      <c r="O500">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="501" spans="1:15">
       <c r="A501" t="s">
         <v>909</v>
       </c>
@@ -25732,8 +26361,11 @@
       <c r="N501" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="502" spans="1:14" hidden="1">
+      <c r="O501">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="502" spans="1:15">
       <c r="A502" t="s">
         <v>910</v>
       </c>
@@ -25776,8 +26408,11 @@
       <c r="N502" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="503" spans="1:14" hidden="1">
+      <c r="O502">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="503" spans="1:15">
       <c r="A503" t="s">
         <v>911</v>
       </c>
@@ -25796,7 +26431,7 @@
       <c r="F503" t="s">
         <v>46</v>
       </c>
-      <c r="G503" s="13">
+      <c r="G503" s="4">
         <v>10239470209</v>
       </c>
       <c r="H503" t="s">
@@ -25820,8 +26455,11 @@
       <c r="N503" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="504" spans="1:14" hidden="1">
+      <c r="O503">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="504" spans="1:15">
       <c r="A504" t="s">
         <v>912</v>
       </c>
@@ -25840,7 +26478,7 @@
       <c r="F504" t="s">
         <v>46</v>
       </c>
-      <c r="G504" s="13">
+      <c r="G504" s="4">
         <v>10238474651</v>
       </c>
       <c r="H504" t="s">
@@ -25864,8 +26502,11 @@
       <c r="N504" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="505" spans="1:14" hidden="1">
+      <c r="O504">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="505" spans="1:15">
       <c r="A505" t="s">
         <v>913</v>
       </c>
@@ -25884,7 +26525,7 @@
       <c r="F505" t="s">
         <v>46</v>
       </c>
-      <c r="G505" s="13">
+      <c r="G505" s="4">
         <v>10239470209</v>
       </c>
       <c r="H505" t="s">
@@ -25908,8 +26549,11 @@
       <c r="N505" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="506" spans="1:14" hidden="1">
+      <c r="O505">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="506" spans="1:15">
       <c r="A506" t="s">
         <v>914</v>
       </c>
@@ -25928,7 +26572,7 @@
       <c r="F506" t="s">
         <v>46</v>
       </c>
-      <c r="G506" s="13">
+      <c r="G506" s="4">
         <v>10238474651</v>
       </c>
       <c r="H506" t="s">
@@ -25952,8 +26596,11 @@
       <c r="N506" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="507" spans="1:14">
+      <c r="O506">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="507" spans="1:15">
       <c r="A507" t="s">
         <v>915</v>
       </c>
@@ -25997,7 +26644,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="508" spans="1:14">
+    <row r="508" spans="1:15">
       <c r="A508" t="s">
         <v>916</v>
       </c>
@@ -26041,7 +26688,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="509" spans="1:14">
+    <row r="509" spans="1:15">
       <c r="A509" t="s">
         <v>917</v>
       </c>
@@ -26085,7 +26732,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="510" spans="1:14" hidden="1">
+    <row r="510" spans="1:15">
       <c r="A510" t="s">
         <v>918</v>
       </c>
@@ -26128,8 +26775,11 @@
       <c r="N510" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="511" spans="1:14" hidden="1">
+      <c r="O510">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="511" spans="1:15">
       <c r="A511" t="s">
         <v>919</v>
       </c>
@@ -26172,8 +26822,11 @@
       <c r="N511" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="512" spans="1:14" hidden="1">
+      <c r="O511">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="512" spans="1:15">
       <c r="A512" t="s">
         <v>920</v>
       </c>
@@ -26215,6 +26868,9 @@
       </c>
       <c r="N512" t="s">
         <v>90</v>
+      </c>
+      <c r="O512">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="513" spans="1:14">
@@ -26236,7 +26892,7 @@
       <c r="F513" t="s">
         <v>48</v>
       </c>
-      <c r="G513" s="13">
+      <c r="G513" s="4">
         <v>10252188041</v>
       </c>
       <c r="H513" t="s">
@@ -26314,13 +26970,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N514" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="POI"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:O514" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3B5386-6664-40DA-AD7B-FAD85DEDFA82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F64F65-8EDD-4161-A8F3-6C98271C7959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$485</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$482</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5017" uniqueCount="1078">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4987" uniqueCount="1070">
   <si>
     <t>ID_ACTIVIDAD</t>
   </si>
@@ -2766,15 +2766,6 @@
     <t>A00500</t>
   </si>
   <si>
-    <t>A00501</t>
-  </si>
-  <si>
-    <t>A00502</t>
-  </si>
-  <si>
-    <t>A00503</t>
-  </si>
-  <si>
     <t>02/06/2026</t>
   </si>
   <si>
@@ -2910,15 +2901,6 @@
     <t>QUINTANA MAMANI CLAUDIA MILAGROS</t>
   </si>
   <si>
-    <t xml:space="preserve"> ESTELA</t>
-  </si>
-  <si>
-    <t>CORDOVA SAICO AMELIA</t>
-  </si>
-  <si>
-    <t>QQUEHUE HUISA SOFIA</t>
-  </si>
-  <si>
     <t>MILLA GELDRES GILMAR RICARDO</t>
   </si>
   <si>
@@ -2989,12 +2971,6 @@
   </si>
   <si>
     <t>CAPACITACION ESPECIALIZADA EN TEÑIDO TEXTIL CON ENFOQUE DE ECONOMÍA CIRCULAR: TECNOLOGÍAS INDUSTRIALES Y COLORANTES NATURALES</t>
-  </si>
-  <si>
-    <t>Teñido Textil con Enfoque de Economía Circular: Tecnologías Industriales y Colorantes Naturales</t>
-  </si>
-  <si>
-    <t>Teñidos con Economía Circular</t>
   </si>
   <si>
     <t>ANALISIS DE FIBRA DE ALPACA</t>
@@ -3667,7 +3643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O504"/>
+  <dimension ref="A1:O501"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -3729,7 +3705,7 @@
         <v>12</v>
       </c>
       <c r="O1" t="s">
-        <v>1052</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -7873,7 +7849,7 @@
         <v>147</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="C90">
         <v>2026</v>
@@ -7920,7 +7896,7 @@
         <v>148</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="C91">
         <v>2026</v>
@@ -7967,7 +7943,7 @@
         <v>149</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="C92">
         <v>2026</v>
@@ -8155,7 +8131,7 @@
         <v>153</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="C96">
         <v>2026</v>
@@ -8202,7 +8178,7 @@
         <v>154</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
       <c r="C97">
         <v>2026</v>
@@ -8972,7 +8948,7 @@
         <v>10239106876</v>
       </c>
       <c r="H113" t="s">
-        <v>1051</v>
+        <v>1043</v>
       </c>
       <c r="I113" t="s">
         <v>451</v>
@@ -9536,7 +9512,7 @@
         <v>10253055672</v>
       </c>
       <c r="H125" t="s">
-        <v>1004</v>
+        <v>996</v>
       </c>
       <c r="I125" t="s">
         <v>451</v>
@@ -9592,7 +9568,7 @@
         <v>454</v>
       </c>
       <c r="K126" t="s">
-        <v>1031</v>
+        <v>1023</v>
       </c>
       <c r="L126" t="s">
         <v>88</v>
@@ -9630,7 +9606,7 @@
         <v>10458755260</v>
       </c>
       <c r="H127" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="I127" t="s">
         <v>451</v>
@@ -9706,7 +9682,7 @@
         <v>186</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>988</v>
+        <v>980</v>
       </c>
       <c r="C129">
         <v>2026</v>
@@ -9733,7 +9709,7 @@
         <v>454</v>
       </c>
       <c r="K129" t="s">
-        <v>1012</v>
+        <v>1004</v>
       </c>
       <c r="L129" t="s">
         <v>88</v>
@@ -9753,7 +9729,7 @@
         <v>187</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>988</v>
+        <v>980</v>
       </c>
       <c r="C130">
         <v>2026</v>
@@ -9780,7 +9756,7 @@
         <v>454</v>
       </c>
       <c r="K130" t="s">
-        <v>1016</v>
+        <v>1008</v>
       </c>
       <c r="L130" t="s">
         <v>88</v>
@@ -9847,7 +9823,7 @@
         <v>189</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C132">
         <v>2026</v>
@@ -9874,7 +9850,7 @@
         <v>454</v>
       </c>
       <c r="K132" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="L132" t="s">
         <v>88</v>
@@ -9894,7 +9870,7 @@
         <v>190</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C133">
         <v>2026</v>
@@ -9906,7 +9882,7 @@
         <v>404</v>
       </c>
       <c r="F133" t="s">
-        <v>1050</v>
+        <v>1042</v>
       </c>
       <c r="G133" s="4">
         <v>10473163450</v>
@@ -9921,7 +9897,7 @@
         <v>455</v>
       </c>
       <c r="K133" t="s">
-        <v>1039</v>
+        <v>1031</v>
       </c>
       <c r="L133" t="s">
         <v>88</v>
@@ -9941,7 +9917,7 @@
         <v>191</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C134">
         <v>2026</v>
@@ -9968,7 +9944,7 @@
         <v>454</v>
       </c>
       <c r="K134" t="s">
-        <v>1017</v>
+        <v>1009</v>
       </c>
       <c r="L134" t="s">
         <v>88</v>
@@ -9988,7 +9964,7 @@
         <v>318</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>991</v>
+        <v>983</v>
       </c>
       <c r="C135">
         <v>2026</v>
@@ -10015,7 +9991,7 @@
         <v>456</v>
       </c>
       <c r="K135" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="L135" t="s">
         <v>88</v>
@@ -10035,7 +10011,7 @@
         <v>319</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>991</v>
+        <v>983</v>
       </c>
       <c r="C136">
         <v>2026</v>
@@ -10062,7 +10038,7 @@
         <v>454</v>
       </c>
       <c r="K136" t="s">
-        <v>1018</v>
+        <v>1010</v>
       </c>
       <c r="L136" t="s">
         <v>88</v>
@@ -10100,7 +10076,7 @@
         <v>10701892734</v>
       </c>
       <c r="H137" t="s">
-        <v>1007</v>
+        <v>999</v>
       </c>
       <c r="I137" t="s">
         <v>451</v>
@@ -10147,7 +10123,7 @@
         <v>10627334066</v>
       </c>
       <c r="H138" t="s">
-        <v>1008</v>
+        <v>1000</v>
       </c>
       <c r="I138" t="s">
         <v>451</v>
@@ -10176,7 +10152,7 @@
         <v>322</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C139">
         <v>2026</v>
@@ -10203,7 +10179,7 @@
         <v>456</v>
       </c>
       <c r="K139" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="L139" t="s">
         <v>88</v>
@@ -10223,7 +10199,7 @@
         <v>323</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C140">
         <v>2026</v>
@@ -10250,7 +10226,7 @@
         <v>454</v>
       </c>
       <c r="K140" t="s">
-        <v>1019</v>
+        <v>1011</v>
       </c>
       <c r="L140" t="s">
         <v>88</v>
@@ -10288,7 +10264,7 @@
         <v>10444412823</v>
       </c>
       <c r="H141" t="s">
-        <v>1006</v>
+        <v>998</v>
       </c>
       <c r="I141" t="s">
         <v>451</v>
@@ -10335,7 +10311,7 @@
         <v>10238268821</v>
       </c>
       <c r="H142" t="s">
-        <v>1009</v>
+        <v>1001</v>
       </c>
       <c r="I142" t="s">
         <v>451</v>
@@ -10458,7 +10434,7 @@
         <v>328</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C145">
         <v>2026</v>
@@ -10485,7 +10461,7 @@
         <v>454</v>
       </c>
       <c r="K145" t="s">
-        <v>1046</v>
+        <v>1038</v>
       </c>
       <c r="L145" t="s">
         <v>88</v>
@@ -10505,7 +10481,7 @@
         <v>329</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C146">
         <v>2026</v>
@@ -10532,7 +10508,7 @@
         <v>454</v>
       </c>
       <c r="K146" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="L146" t="s">
         <v>88</v>
@@ -10552,7 +10528,7 @@
         <v>330</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C147">
         <v>2026</v>
@@ -10564,7 +10540,7 @@
         <v>404</v>
       </c>
       <c r="F147" t="s">
-        <v>1050</v>
+        <v>1042</v>
       </c>
       <c r="G147" s="4">
         <v>10239510197</v>
@@ -10579,7 +10555,7 @@
         <v>456</v>
       </c>
       <c r="K147" t="s">
-        <v>1047</v>
+        <v>1039</v>
       </c>
       <c r="L147" t="s">
         <v>88</v>
@@ -10599,7 +10575,7 @@
         <v>331</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C148">
         <v>2026</v>
@@ -10626,7 +10602,7 @@
         <v>454</v>
       </c>
       <c r="K148" t="s">
-        <v>1020</v>
+        <v>1012</v>
       </c>
       <c r="L148" t="s">
         <v>88</v>
@@ -10711,7 +10687,7 @@
         <v>10243840738</v>
       </c>
       <c r="H150" t="s">
-        <v>1010</v>
+        <v>1002</v>
       </c>
       <c r="I150" t="s">
         <v>451</v>
@@ -10740,7 +10716,7 @@
         <v>334</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>989</v>
+        <v>981</v>
       </c>
       <c r="C151">
         <v>2026</v>
@@ -10767,7 +10743,7 @@
         <v>454</v>
       </c>
       <c r="K151" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="L151" t="s">
         <v>88</v>
@@ -10787,7 +10763,7 @@
         <v>335</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>989</v>
+        <v>981</v>
       </c>
       <c r="C152">
         <v>2026</v>
@@ -10814,7 +10790,7 @@
         <v>454</v>
       </c>
       <c r="K152" t="s">
-        <v>1021</v>
+        <v>1013</v>
       </c>
       <c r="L152" t="s">
         <v>88</v>
@@ -10899,7 +10875,7 @@
         <v>10704606783</v>
       </c>
       <c r="H154" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="I154" t="s">
         <v>451</v>
@@ -10946,7 +10922,7 @@
         <v>10238085042</v>
       </c>
       <c r="H155" t="s">
-        <v>1011</v>
+        <v>1003</v>
       </c>
       <c r="I155" t="s">
         <v>451</v>
@@ -10993,7 +10969,7 @@
         <v>10448659068</v>
       </c>
       <c r="H156" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="I156" t="s">
         <v>451</v>
@@ -11040,7 +11016,7 @@
         <v>10239756587</v>
       </c>
       <c r="H157" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="I157" t="s">
         <v>451</v>
@@ -11069,7 +11045,7 @@
         <v>341</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="C158">
         <v>2026</v>
@@ -11096,7 +11072,7 @@
         <v>454</v>
       </c>
       <c r="K158" t="s">
-        <v>1042</v>
+        <v>1034</v>
       </c>
       <c r="L158" t="s">
         <v>88</v>
@@ -11116,7 +11092,7 @@
         <v>342</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="C159">
         <v>2026</v>
@@ -11143,7 +11119,7 @@
         <v>454</v>
       </c>
       <c r="K159" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="L159" t="s">
         <v>88</v>
@@ -11163,7 +11139,7 @@
         <v>343</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="C160">
         <v>2026</v>
@@ -11190,7 +11166,7 @@
         <v>454</v>
       </c>
       <c r="K160" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="L160" t="s">
         <v>88</v>
@@ -11210,7 +11186,7 @@
         <v>344</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="C161">
         <v>2026</v>
@@ -11237,7 +11213,7 @@
         <v>455</v>
       </c>
       <c r="K161" t="s">
-        <v>1026</v>
+        <v>1018</v>
       </c>
       <c r="L161" t="s">
         <v>88</v>
@@ -11257,7 +11233,7 @@
         <v>345</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="C162">
         <v>2026</v>
@@ -11284,7 +11260,7 @@
         <v>455</v>
       </c>
       <c r="K162" t="s">
-        <v>1038</v>
+        <v>1030</v>
       </c>
       <c r="L162" t="s">
         <v>88</v>
@@ -11304,7 +11280,7 @@
         <v>346</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="C163">
         <v>2026</v>
@@ -11331,7 +11307,7 @@
         <v>457</v>
       </c>
       <c r="K163" t="s">
-        <v>1032</v>
+        <v>1024</v>
       </c>
       <c r="L163" t="s">
         <v>88</v>
@@ -11351,7 +11327,7 @@
         <v>347</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="C164">
         <v>2026</v>
@@ -11378,7 +11354,7 @@
         <v>456</v>
       </c>
       <c r="K164" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="L164" t="s">
         <v>88</v>
@@ -11398,7 +11374,7 @@
         <v>348</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="C165">
         <v>2026</v>
@@ -11425,7 +11401,7 @@
         <v>454</v>
       </c>
       <c r="K165" t="s">
-        <v>1044</v>
+        <v>1036</v>
       </c>
       <c r="L165" t="s">
         <v>88</v>
@@ -11445,7 +11421,7 @@
         <v>349</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="C166">
         <v>2026</v>
@@ -11472,7 +11448,7 @@
         <v>454</v>
       </c>
       <c r="K166" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="L166" t="s">
         <v>88</v>
@@ -11492,7 +11468,7 @@
         <v>350</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="C167">
         <v>2026</v>
@@ -11519,7 +11495,7 @@
         <v>454</v>
       </c>
       <c r="K167" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="L167" t="s">
         <v>88</v>
@@ -11539,7 +11515,7 @@
         <v>351</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="C168">
         <v>2026</v>
@@ -11551,7 +11527,7 @@
         <v>404</v>
       </c>
       <c r="F168" t="s">
-        <v>1050</v>
+        <v>1042</v>
       </c>
       <c r="G168" s="4">
         <v>10239486377</v>
@@ -11566,7 +11542,7 @@
         <v>456</v>
       </c>
       <c r="K168" t="s">
-        <v>1037</v>
+        <v>1029</v>
       </c>
       <c r="L168" t="s">
         <v>88</v>
@@ -11586,7 +11562,7 @@
         <v>374</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="C169">
         <v>2026</v>
@@ -11613,7 +11589,7 @@
         <v>455</v>
       </c>
       <c r="K169" t="s">
-        <v>1027</v>
+        <v>1019</v>
       </c>
       <c r="L169" t="s">
         <v>88</v>
@@ -11633,7 +11609,7 @@
         <v>375</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="C170">
         <v>2026</v>
@@ -11660,7 +11636,7 @@
         <v>456</v>
       </c>
       <c r="K170" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="L170" t="s">
         <v>88</v>
@@ -11680,7 +11656,7 @@
         <v>376</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="C171">
         <v>2026</v>
@@ -11707,7 +11683,7 @@
         <v>456</v>
       </c>
       <c r="K171" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="L171" t="s">
         <v>88</v>
@@ -11727,7 +11703,7 @@
         <v>377</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="C172">
         <v>2026</v>
@@ -11754,7 +11730,7 @@
         <v>454</v>
       </c>
       <c r="K172" t="s">
-        <v>1031</v>
+        <v>1023</v>
       </c>
       <c r="L172" t="s">
         <v>88</v>
@@ -11774,7 +11750,7 @@
         <v>378</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="C173">
         <v>2026</v>
@@ -11801,7 +11777,7 @@
         <v>454</v>
       </c>
       <c r="K173" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="L173" t="s">
         <v>88</v>
@@ -11821,7 +11797,7 @@
         <v>379</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="C174">
         <v>2026</v>
@@ -11848,7 +11824,7 @@
         <v>454</v>
       </c>
       <c r="K174" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="L174" t="s">
         <v>88</v>
@@ -11868,7 +11844,7 @@
         <v>380</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="C175">
         <v>2026</v>
@@ -11895,7 +11871,7 @@
         <v>454</v>
       </c>
       <c r="K175" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="L175" t="s">
         <v>88</v>
@@ -11915,7 +11891,7 @@
         <v>381</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="C176">
         <v>2026</v>
@@ -11942,7 +11918,7 @@
         <v>455</v>
       </c>
       <c r="K176" t="s">
-        <v>1028</v>
+        <v>1020</v>
       </c>
       <c r="L176" t="s">
         <v>88</v>
@@ -11962,7 +11938,7 @@
         <v>382</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="C177">
         <v>2026</v>
@@ -11989,7 +11965,7 @@
         <v>456</v>
       </c>
       <c r="K177" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="L177" t="s">
         <v>88</v>
@@ -12009,7 +11985,7 @@
         <v>383</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="C178">
         <v>2026</v>
@@ -12036,7 +12012,7 @@
         <v>454</v>
       </c>
       <c r="K178" t="s">
-        <v>1020</v>
+        <v>1012</v>
       </c>
       <c r="L178" t="s">
         <v>88</v>
@@ -12056,7 +12032,7 @@
         <v>384</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="C179">
         <v>2026</v>
@@ -12083,7 +12059,7 @@
         <v>454</v>
       </c>
       <c r="K179" t="s">
-        <v>1045</v>
+        <v>1037</v>
       </c>
       <c r="L179" t="s">
         <v>88</v>
@@ -12103,7 +12079,7 @@
         <v>385</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="C180">
         <v>2026</v>
@@ -12130,7 +12106,7 @@
         <v>454</v>
       </c>
       <c r="K180" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="L180" t="s">
         <v>88</v>
@@ -12150,7 +12126,7 @@
         <v>386</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="C181">
         <v>2026</v>
@@ -12177,7 +12153,7 @@
         <v>454</v>
       </c>
       <c r="K181" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="L181" t="s">
         <v>88</v>
@@ -12197,7 +12173,7 @@
         <v>387</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="C182">
         <v>2026</v>
@@ -12224,7 +12200,7 @@
         <v>454</v>
       </c>
       <c r="K182" t="s">
-        <v>1048</v>
+        <v>1040</v>
       </c>
       <c r="L182" t="s">
         <v>88</v>
@@ -12244,7 +12220,7 @@
         <v>388</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="C183">
         <v>2026</v>
@@ -12271,7 +12247,7 @@
         <v>457</v>
       </c>
       <c r="K183" t="s">
-        <v>1033</v>
+        <v>1025</v>
       </c>
       <c r="L183" t="s">
         <v>88</v>
@@ -12291,7 +12267,7 @@
         <v>389</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="C184">
         <v>2026</v>
@@ -12318,7 +12294,7 @@
         <v>454</v>
       </c>
       <c r="K184" t="s">
-        <v>1022</v>
+        <v>1014</v>
       </c>
       <c r="L184" t="s">
         <v>88</v>
@@ -12356,7 +12332,7 @@
         <v>10409212480</v>
       </c>
       <c r="H185" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="I185" t="s">
         <v>451</v>
@@ -12385,7 +12361,7 @@
         <v>391</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="C186">
         <v>2026</v>
@@ -12412,7 +12388,7 @@
         <v>454</v>
       </c>
       <c r="K186" t="s">
-        <v>1015</v>
+        <v>1007</v>
       </c>
       <c r="L186" t="s">
         <v>88</v>
@@ -12432,7 +12408,7 @@
         <v>392</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="C187">
         <v>2026</v>
@@ -12459,7 +12435,7 @@
         <v>454</v>
       </c>
       <c r="K187" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="L187" t="s">
         <v>88</v>
@@ -12479,7 +12455,7 @@
         <v>393</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="C188">
         <v>2026</v>
@@ -12506,7 +12482,7 @@
         <v>454</v>
       </c>
       <c r="K188" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="L188" t="s">
         <v>88</v>
@@ -12526,7 +12502,7 @@
         <v>394</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="C189">
         <v>2026</v>
@@ -12553,7 +12529,7 @@
         <v>456</v>
       </c>
       <c r="K189" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="L189" t="s">
         <v>88</v>
@@ -12573,7 +12549,7 @@
         <v>395</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="C190">
         <v>2026</v>
@@ -12600,7 +12576,7 @@
         <v>454</v>
       </c>
       <c r="K190" t="s">
-        <v>1023</v>
+        <v>1015</v>
       </c>
       <c r="L190" t="s">
         <v>88</v>
@@ -12620,7 +12596,7 @@
         <v>396</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="C191">
         <v>2026</v>
@@ -12638,7 +12614,7 @@
         <v>10426361936</v>
       </c>
       <c r="H191" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="I191" t="s">
         <v>451</v>
@@ -12667,7 +12643,7 @@
         <v>397</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="C192">
         <v>2026</v>
@@ -12685,7 +12661,7 @@
         <v>10238381954</v>
       </c>
       <c r="H192" t="s">
-        <v>1005</v>
+        <v>997</v>
       </c>
       <c r="I192" t="s">
         <v>451</v>
@@ -12714,7 +12690,7 @@
         <v>398</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="C193">
         <v>2026</v>
@@ -12732,7 +12708,7 @@
         <v>10249582862</v>
       </c>
       <c r="H193" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="I193" t="s">
         <v>451</v>
@@ -12761,7 +12737,7 @@
         <v>399</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="C194">
         <v>2026</v>
@@ -12773,7 +12749,7 @@
         <v>404</v>
       </c>
       <c r="F194" t="s">
-        <v>1050</v>
+        <v>1042</v>
       </c>
       <c r="G194" s="4">
         <v>10102207241</v>
@@ -12788,7 +12764,7 @@
         <v>456</v>
       </c>
       <c r="K194" t="s">
-        <v>1037</v>
+        <v>1029</v>
       </c>
       <c r="L194" t="s">
         <v>88</v>
@@ -12808,7 +12784,7 @@
         <v>400</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="C195">
         <v>2026</v>
@@ -12835,7 +12811,7 @@
         <v>456</v>
       </c>
       <c r="K195" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="L195" t="s">
         <v>88</v>
@@ -12855,7 +12831,7 @@
         <v>468</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="C196">
         <v>2026</v>
@@ -12882,7 +12858,7 @@
         <v>456</v>
       </c>
       <c r="K196" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="L196" t="s">
         <v>88</v>
@@ -12902,7 +12878,7 @@
         <v>469</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="C197">
         <v>2026</v>
@@ -12929,7 +12905,7 @@
         <v>454</v>
       </c>
       <c r="K197" t="s">
-        <v>1024</v>
+        <v>1016</v>
       </c>
       <c r="L197" t="s">
         <v>88</v>
@@ -12949,7 +12925,7 @@
         <v>470</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
       <c r="C198">
         <v>2026</v>
@@ -12996,7 +12972,7 @@
         <v>471</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
       <c r="C199">
         <v>2026</v>
@@ -13014,7 +12990,7 @@
         <v>10238869094</v>
       </c>
       <c r="H199" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="I199" t="s">
         <v>451</v>
@@ -13043,7 +13019,7 @@
         <v>472</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>999</v>
+        <v>991</v>
       </c>
       <c r="C200">
         <v>2026</v>
@@ -13070,7 +13046,7 @@
         <v>454</v>
       </c>
       <c r="K200" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="L200" t="s">
         <v>88</v>
@@ -13090,7 +13066,7 @@
         <v>473</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>999</v>
+        <v>991</v>
       </c>
       <c r="C201">
         <v>2026</v>
@@ -13117,7 +13093,7 @@
         <v>456</v>
       </c>
       <c r="K201" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="L201" t="s">
         <v>88</v>
@@ -13137,7 +13113,7 @@
         <v>474</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="C202">
         <v>2026</v>
@@ -13164,7 +13140,7 @@
         <v>454</v>
       </c>
       <c r="K202" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="L202" t="s">
         <v>88</v>
@@ -13184,7 +13160,7 @@
         <v>475</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="C203">
         <v>2026</v>
@@ -13211,7 +13187,7 @@
         <v>454</v>
       </c>
       <c r="K203" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="L203" t="s">
         <v>88</v>
@@ -13231,7 +13207,7 @@
         <v>476</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="C204">
         <v>2026</v>
@@ -13258,7 +13234,7 @@
         <v>454</v>
       </c>
       <c r="K204" t="s">
-        <v>1025</v>
+        <v>1017</v>
       </c>
       <c r="L204" t="s">
         <v>88</v>
@@ -13278,7 +13254,7 @@
         <v>477</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="C205">
         <v>2026</v>
@@ -13305,7 +13281,7 @@
         <v>454</v>
       </c>
       <c r="K205" t="s">
-        <v>1029</v>
+        <v>1021</v>
       </c>
       <c r="L205" t="s">
         <v>88</v>
@@ -13325,7 +13301,7 @@
         <v>478</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="C206">
         <v>2026</v>
@@ -13352,7 +13328,7 @@
         <v>454</v>
       </c>
       <c r="K206" t="s">
-        <v>1024</v>
+        <v>1016</v>
       </c>
       <c r="L206" t="s">
         <v>88</v>
@@ -13372,7 +13348,7 @@
         <v>479</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="C207">
         <v>2026</v>
@@ -13399,7 +13375,7 @@
         <v>454</v>
       </c>
       <c r="K207" t="s">
-        <v>1043</v>
+        <v>1035</v>
       </c>
       <c r="L207" t="s">
         <v>88</v>
@@ -13419,7 +13395,7 @@
         <v>480</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="C208">
         <v>2026</v>
@@ -13446,7 +13422,7 @@
         <v>454</v>
       </c>
       <c r="K208" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="L208" t="s">
         <v>88</v>
@@ -13466,7 +13442,7 @@
         <v>481</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="C209">
         <v>2026</v>
@@ -13493,7 +13469,7 @@
         <v>455</v>
       </c>
       <c r="K209" t="s">
-        <v>1039</v>
+        <v>1031</v>
       </c>
       <c r="L209" t="s">
         <v>88</v>
@@ -13513,7 +13489,7 @@
         <v>482</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>991</v>
+        <v>983</v>
       </c>
       <c r="C210">
         <v>2026</v>
@@ -13540,7 +13516,7 @@
         <v>454</v>
       </c>
       <c r="K210" t="s">
-        <v>1030</v>
+        <v>1022</v>
       </c>
       <c r="L210" t="s">
         <v>88</v>
@@ -13560,7 +13536,7 @@
         <v>483</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C211">
         <v>2026</v>
@@ -13587,7 +13563,7 @@
         <v>454</v>
       </c>
       <c r="K211" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="L211" t="s">
         <v>88</v>
@@ -13607,7 +13583,7 @@
         <v>484</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C212">
         <v>2026</v>
@@ -13634,7 +13610,7 @@
         <v>454</v>
       </c>
       <c r="K212" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="L212" t="s">
         <v>88</v>
@@ -13654,7 +13630,7 @@
         <v>485</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C213">
         <v>2026</v>
@@ -13666,7 +13642,7 @@
         <v>404</v>
       </c>
       <c r="F213" t="s">
-        <v>1049</v>
+        <v>1041</v>
       </c>
       <c r="G213" s="4">
         <v>10240067566</v>
@@ -13681,7 +13657,7 @@
         <v>454</v>
       </c>
       <c r="K213" t="s">
-        <v>1034</v>
+        <v>1026</v>
       </c>
       <c r="L213" t="s">
         <v>88</v>
@@ -13701,7 +13677,7 @@
         <v>486</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C214">
         <v>2026</v>
@@ -13728,7 +13704,7 @@
         <v>454</v>
       </c>
       <c r="K214" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="L214" t="s">
         <v>88</v>
@@ -13748,7 +13724,7 @@
         <v>487</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C215">
         <v>2026</v>
@@ -13775,7 +13751,7 @@
         <v>454</v>
       </c>
       <c r="K215" t="s">
-        <v>1040</v>
+        <v>1032</v>
       </c>
       <c r="L215" t="s">
         <v>88</v>
@@ -13795,7 +13771,7 @@
         <v>488</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
       <c r="C216">
         <v>2026</v>
@@ -13822,7 +13798,7 @@
         <v>454</v>
       </c>
       <c r="K216" t="s">
-        <v>1044</v>
+        <v>1036</v>
       </c>
       <c r="L216" t="s">
         <v>88</v>
@@ -13842,7 +13818,7 @@
         <v>489</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
       <c r="C217">
         <v>2026</v>
@@ -13854,7 +13830,7 @@
         <v>404</v>
       </c>
       <c r="F217" t="s">
-        <v>1049</v>
+        <v>1041</v>
       </c>
       <c r="G217" s="4">
         <v>10239510197</v>
@@ -13869,7 +13845,7 @@
         <v>454</v>
       </c>
       <c r="K217" t="s">
-        <v>1035</v>
+        <v>1027</v>
       </c>
       <c r="L217" t="s">
         <v>88</v>
@@ -13889,7 +13865,7 @@
         <v>490</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
       <c r="C218">
         <v>2026</v>
@@ -13916,7 +13892,7 @@
         <v>455</v>
       </c>
       <c r="K218" t="s">
-        <v>1038</v>
+        <v>1030</v>
       </c>
       <c r="L218" t="s">
         <v>88</v>
@@ -13936,7 +13912,7 @@
         <v>491</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C219">
         <v>2026</v>
@@ -13963,7 +13939,7 @@
         <v>457</v>
       </c>
       <c r="K219" t="s">
-        <v>1031</v>
+        <v>1023</v>
       </c>
       <c r="L219" t="s">
         <v>88</v>
@@ -13983,7 +13959,7 @@
         <v>492</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>998</v>
+        <v>990</v>
       </c>
       <c r="C220">
         <v>2026</v>
@@ -14010,7 +13986,7 @@
         <v>454</v>
       </c>
       <c r="K220" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="L220" t="s">
         <v>88</v>
@@ -14030,7 +14006,7 @@
         <v>493</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>998</v>
+        <v>990</v>
       </c>
       <c r="C221">
         <v>2026</v>
@@ -14057,7 +14033,7 @@
         <v>454</v>
       </c>
       <c r="K221" t="s">
-        <v>1041</v>
+        <v>1033</v>
       </c>
       <c r="L221" t="s">
         <v>88</v>
@@ -23102,7 +23078,7 @@
         <v>835</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C427">
         <v>2026</v>
@@ -23120,7 +23096,7 @@
         <v>10248794386</v>
       </c>
       <c r="H427" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="I427" t="s">
         <v>296</v>
@@ -23129,7 +23105,7 @@
         <v>461</v>
       </c>
       <c r="K427" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="L427" t="s">
         <v>297</v>
@@ -23146,7 +23122,7 @@
         <v>836</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C428">
         <v>2026</v>
@@ -23164,7 +23140,7 @@
         <v>10768336747</v>
       </c>
       <c r="H428" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="I428" t="s">
         <v>296</v>
@@ -23173,7 +23149,7 @@
         <v>461</v>
       </c>
       <c r="K428" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="L428" t="s">
         <v>297</v>
@@ -23190,7 +23166,7 @@
         <v>837</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C429">
         <v>2026</v>
@@ -23208,7 +23184,7 @@
         <v>10781168772</v>
       </c>
       <c r="H429" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="I429" t="s">
         <v>296</v>
@@ -23217,7 +23193,7 @@
         <v>461</v>
       </c>
       <c r="K429" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="L429" t="s">
         <v>297</v>
@@ -23234,7 +23210,7 @@
         <v>838</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C430">
         <v>2026</v>
@@ -23252,7 +23228,7 @@
         <v>10247103363</v>
       </c>
       <c r="H430" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="I430" t="s">
         <v>296</v>
@@ -23261,7 +23237,7 @@
         <v>461</v>
       </c>
       <c r="K430" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="L430" t="s">
         <v>297</v>
@@ -23278,7 +23254,7 @@
         <v>839</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C431">
         <v>2026</v>
@@ -23296,7 +23272,7 @@
         <v>10748733910</v>
       </c>
       <c r="H431" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="I431" t="s">
         <v>296</v>
@@ -23305,7 +23281,7 @@
         <v>461</v>
       </c>
       <c r="K431" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="L431" t="s">
         <v>297</v>
@@ -23322,7 +23298,7 @@
         <v>840</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C432">
         <v>2026</v>
@@ -23340,7 +23316,7 @@
         <v>10756599084</v>
       </c>
       <c r="H432" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="I432" t="s">
         <v>296</v>
@@ -23349,7 +23325,7 @@
         <v>461</v>
       </c>
       <c r="K432" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="L432" t="s">
         <v>297</v>
@@ -23366,7 +23342,7 @@
         <v>841</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C433">
         <v>2026</v>
@@ -23384,7 +23360,7 @@
         <v>10409219999</v>
       </c>
       <c r="H433" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="I433" t="s">
         <v>296</v>
@@ -23393,7 +23369,7 @@
         <v>461</v>
       </c>
       <c r="K433" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="L433" t="s">
         <v>297</v>
@@ -23410,7 +23386,7 @@
         <v>842</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C434">
         <v>2026</v>
@@ -23428,7 +23404,7 @@
         <v>10248714277</v>
       </c>
       <c r="H434" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="I434" t="s">
         <v>296</v>
@@ -23437,7 +23413,7 @@
         <v>461</v>
       </c>
       <c r="K434" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="L434" t="s">
         <v>297</v>
@@ -23454,7 +23430,7 @@
         <v>843</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C435">
         <v>2026</v>
@@ -23472,7 +23448,7 @@
         <v>10248660908</v>
       </c>
       <c r="H435" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="I435" t="s">
         <v>296</v>
@@ -23481,7 +23457,7 @@
         <v>461</v>
       </c>
       <c r="K435" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="L435" t="s">
         <v>297</v>
@@ -23498,7 +23474,7 @@
         <v>844</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C436">
         <v>2026</v>
@@ -23516,7 +23492,7 @@
         <v>10248900984</v>
       </c>
       <c r="H436" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="I436" t="s">
         <v>296</v>
@@ -23525,7 +23501,7 @@
         <v>461</v>
       </c>
       <c r="K436" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="L436" t="s">
         <v>297</v>
@@ -23542,7 +23518,7 @@
         <v>845</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C437">
         <v>2026</v>
@@ -23560,7 +23536,7 @@
         <v>10482266130</v>
       </c>
       <c r="H437" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="I437" t="s">
         <v>296</v>
@@ -23569,7 +23545,7 @@
         <v>461</v>
       </c>
       <c r="K437" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="L437" t="s">
         <v>297</v>
@@ -23586,7 +23562,7 @@
         <v>846</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C438">
         <v>2026</v>
@@ -23613,7 +23589,7 @@
         <v>461</v>
       </c>
       <c r="K438" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="L438" t="s">
         <v>297</v>
@@ -23630,7 +23606,7 @@
         <v>847</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C439">
         <v>2026</v>
@@ -23657,7 +23633,7 @@
         <v>461</v>
       </c>
       <c r="K439" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="L439" t="s">
         <v>297</v>
@@ -23674,7 +23650,7 @@
         <v>848</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C440">
         <v>2026</v>
@@ -23692,7 +23668,7 @@
         <v>10239106876</v>
       </c>
       <c r="H440" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="I440" t="s">
         <v>296</v>
@@ -23701,7 +23677,7 @@
         <v>461</v>
       </c>
       <c r="K440" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="L440" t="s">
         <v>297</v>
@@ -23718,7 +23694,7 @@
         <v>849</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C441">
         <v>2026</v>
@@ -23736,7 +23712,7 @@
         <v>10238784986</v>
       </c>
       <c r="H441" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="I441" t="s">
         <v>296</v>
@@ -23745,7 +23721,7 @@
         <v>461</v>
       </c>
       <c r="K441" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="L441" t="s">
         <v>297</v>
@@ -23762,7 +23738,7 @@
         <v>850</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C442">
         <v>2026</v>
@@ -23780,7 +23756,7 @@
         <v>40241978</v>
       </c>
       <c r="H442" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="I442" t="s">
         <v>296</v>
@@ -23789,7 +23765,7 @@
         <v>461</v>
       </c>
       <c r="K442" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="L442" t="s">
         <v>297</v>
@@ -23806,7 +23782,7 @@
         <v>851</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C443">
         <v>2026</v>
@@ -23824,7 +23800,7 @@
         <v>10462678571</v>
       </c>
       <c r="H443" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="I443" t="s">
         <v>296</v>
@@ -23833,7 +23809,7 @@
         <v>461</v>
       </c>
       <c r="K443" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="L443" t="s">
         <v>297</v>
@@ -23850,7 +23826,7 @@
         <v>852</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C444">
         <v>2026</v>
@@ -23868,7 +23844,7 @@
         <v>10092214023</v>
       </c>
       <c r="H444" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="I444" t="s">
         <v>296</v>
@@ -23877,7 +23853,7 @@
         <v>461</v>
       </c>
       <c r="K444" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="L444" t="s">
         <v>297</v>
@@ -23894,7 +23870,7 @@
         <v>853</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C445">
         <v>2026</v>
@@ -23912,7 +23888,7 @@
         <v>42421067</v>
       </c>
       <c r="H445" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="I445" t="s">
         <v>296</v>
@@ -23921,7 +23897,7 @@
         <v>461</v>
       </c>
       <c r="K445" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="L445" t="s">
         <v>297</v>
@@ -23938,7 +23914,7 @@
         <v>854</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C446">
         <v>2026</v>
@@ -23965,7 +23941,7 @@
         <v>461</v>
       </c>
       <c r="K446" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="L446" t="s">
         <v>297</v>
@@ -23982,7 +23958,7 @@
         <v>855</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C447">
         <v>2026</v>
@@ -24000,7 +23976,7 @@
         <v>10755814615</v>
       </c>
       <c r="H447" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="I447" t="s">
         <v>296</v>
@@ -24009,7 +23985,7 @@
         <v>461</v>
       </c>
       <c r="K447" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="L447" t="s">
         <v>297</v>
@@ -24026,7 +24002,7 @@
         <v>856</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C448">
         <v>2026</v>
@@ -24053,7 +24029,7 @@
         <v>461</v>
       </c>
       <c r="K448" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="L448" t="s">
         <v>297</v>
@@ -24070,7 +24046,7 @@
         <v>857</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C449">
         <v>2026</v>
@@ -24088,7 +24064,7 @@
         <v>10420101631</v>
       </c>
       <c r="H449" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="I449" t="s">
         <v>296</v>
@@ -24097,7 +24073,7 @@
         <v>461</v>
       </c>
       <c r="K449" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="L449" t="s">
         <v>297</v>
@@ -24114,7 +24090,7 @@
         <v>858</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C450">
         <v>2026</v>
@@ -24132,7 +24108,7 @@
         <v>10700932929</v>
       </c>
       <c r="H450" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="I450" t="s">
         <v>296</v>
@@ -24141,7 +24117,7 @@
         <v>461</v>
       </c>
       <c r="K450" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="L450" t="s">
         <v>297</v>
@@ -24158,7 +24134,7 @@
         <v>859</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C451">
         <v>2026</v>
@@ -24176,7 +24152,7 @@
         <v>10700799889</v>
       </c>
       <c r="H451" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="I451" t="s">
         <v>296</v>
@@ -24185,7 +24161,7 @@
         <v>461</v>
       </c>
       <c r="K451" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="L451" t="s">
         <v>297</v>
@@ -24202,7 +24178,7 @@
         <v>860</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C452">
         <v>2026</v>
@@ -24229,7 +24205,7 @@
         <v>461</v>
       </c>
       <c r="K452" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="L452" t="s">
         <v>297</v>
@@ -24246,7 +24222,7 @@
         <v>861</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C453">
         <v>2026</v>
@@ -24264,7 +24240,7 @@
         <v>10204218736</v>
       </c>
       <c r="H453" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="I453" t="s">
         <v>296</v>
@@ -24273,7 +24249,7 @@
         <v>461</v>
       </c>
       <c r="K453" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="L453" t="s">
         <v>297</v>
@@ -24290,7 +24266,7 @@
         <v>862</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C454">
         <v>2026</v>
@@ -24308,7 +24284,7 @@
         <v>10752532619</v>
       </c>
       <c r="H454" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="I454" t="s">
         <v>296</v>
@@ -24317,7 +24293,7 @@
         <v>461</v>
       </c>
       <c r="K454" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="L454" t="s">
         <v>297</v>
@@ -24334,7 +24310,7 @@
         <v>863</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C455">
         <v>2026</v>
@@ -24352,7 +24328,7 @@
         <v>10421627733</v>
       </c>
       <c r="H455" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="I455" t="s">
         <v>296</v>
@@ -24361,7 +24337,7 @@
         <v>461</v>
       </c>
       <c r="K455" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="L455" t="s">
         <v>297</v>
@@ -24378,7 +24354,7 @@
         <v>864</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C456">
         <v>2026</v>
@@ -24405,7 +24381,7 @@
         <v>461</v>
       </c>
       <c r="K456" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="L456" t="s">
         <v>297</v>
@@ -24422,7 +24398,7 @@
         <v>865</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C457">
         <v>2026</v>
@@ -24449,7 +24425,7 @@
         <v>461</v>
       </c>
       <c r="K457" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="L457" t="s">
         <v>297</v>
@@ -24466,7 +24442,7 @@
         <v>866</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C458">
         <v>2026</v>
@@ -24493,7 +24469,7 @@
         <v>461</v>
       </c>
       <c r="K458" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="L458" t="s">
         <v>297</v>
@@ -24510,7 +24486,7 @@
         <v>867</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C459">
         <v>2026</v>
@@ -24537,7 +24513,7 @@
         <v>461</v>
       </c>
       <c r="K459" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="L459" t="s">
         <v>297</v>
@@ -24554,7 +24530,7 @@
         <v>868</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C460">
         <v>2026</v>
@@ -24581,7 +24557,7 @@
         <v>461</v>
       </c>
       <c r="K460" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="L460" t="s">
         <v>297</v>
@@ -24598,7 +24574,7 @@
         <v>869</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C461">
         <v>2026</v>
@@ -24616,7 +24592,7 @@
         <v>10096063038</v>
       </c>
       <c r="H461" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="I461" t="s">
         <v>296</v>
@@ -24625,7 +24601,7 @@
         <v>461</v>
       </c>
       <c r="K461" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="L461" t="s">
         <v>297</v>
@@ -24642,7 +24618,7 @@
         <v>870</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C462">
         <v>2026</v>
@@ -24669,7 +24645,7 @@
         <v>461</v>
       </c>
       <c r="K462" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="L462" t="s">
         <v>297</v>
@@ -24686,7 +24662,7 @@
         <v>871</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C463">
         <v>2026</v>
@@ -24704,7 +24680,7 @@
         <v>10440425696</v>
       </c>
       <c r="H463" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="I463" t="s">
         <v>296</v>
@@ -24713,7 +24689,7 @@
         <v>461</v>
       </c>
       <c r="K463" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="L463" t="s">
         <v>297</v>
@@ -24730,7 +24706,7 @@
         <v>872</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C464">
         <v>2026</v>
@@ -24748,7 +24724,7 @@
         <v>10704606783</v>
       </c>
       <c r="H464" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="I464" t="s">
         <v>296</v>
@@ -24757,7 +24733,7 @@
         <v>460</v>
       </c>
       <c r="K464" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="L464" t="s">
         <v>88</v>
@@ -24774,7 +24750,7 @@
         <v>873</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C465">
         <v>2026</v>
@@ -24792,7 +24768,7 @@
         <v>10448659068</v>
       </c>
       <c r="H465" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="I465" t="s">
         <v>296</v>
@@ -24801,7 +24777,7 @@
         <v>460</v>
       </c>
       <c r="K465" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="L465" t="s">
         <v>88</v>
@@ -24818,7 +24794,7 @@
         <v>874</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C466">
         <v>2026</v>
@@ -24836,7 +24812,7 @@
         <v>10239756587</v>
       </c>
       <c r="H466" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="I466" t="s">
         <v>296</v>
@@ -24845,7 +24821,7 @@
         <v>460</v>
       </c>
       <c r="K466" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="L466" t="s">
         <v>88</v>
@@ -24862,7 +24838,7 @@
         <v>875</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C467">
         <v>2026</v>
@@ -24889,7 +24865,7 @@
         <v>460</v>
       </c>
       <c r="K467" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="L467" t="s">
         <v>88</v>
@@ -24906,7 +24882,7 @@
         <v>876</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C468">
         <v>2026</v>
@@ -24924,7 +24900,7 @@
         <v>10802446107</v>
       </c>
       <c r="H468" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="I468" t="s">
         <v>296</v>
@@ -24933,7 +24909,7 @@
         <v>460</v>
       </c>
       <c r="K468" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="L468" t="s">
         <v>88</v>
@@ -24950,7 +24926,7 @@
         <v>877</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C469">
         <v>2026</v>
@@ -24968,7 +24944,7 @@
         <v>10409212480</v>
       </c>
       <c r="H469" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="I469" t="s">
         <v>296</v>
@@ -24977,7 +24953,7 @@
         <v>460</v>
       </c>
       <c r="K469" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="L469" t="s">
         <v>88</v>
@@ -24994,7 +24970,7 @@
         <v>878</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C470">
         <v>2026</v>
@@ -25012,7 +24988,7 @@
         <v>10433498394</v>
       </c>
       <c r="H470" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="I470" t="s">
         <v>296</v>
@@ -25021,7 +24997,7 @@
         <v>460</v>
       </c>
       <c r="K470" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="L470" t="s">
         <v>88</v>
@@ -25038,7 +25014,7 @@
         <v>879</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C471">
         <v>2026</v>
@@ -25065,7 +25041,7 @@
         <v>460</v>
       </c>
       <c r="K471" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="L471" t="s">
         <v>88</v>
@@ -25082,7 +25058,7 @@
         <v>880</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C472">
         <v>2026</v>
@@ -25100,7 +25076,7 @@
         <v>10466170203</v>
       </c>
       <c r="H472" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="I472" t="s">
         <v>296</v>
@@ -25109,7 +25085,7 @@
         <v>460</v>
       </c>
       <c r="K472" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="L472" t="s">
         <v>88</v>
@@ -25126,7 +25102,7 @@
         <v>881</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C473">
         <v>2026</v>
@@ -25144,7 +25120,7 @@
         <v>10760499493</v>
       </c>
       <c r="H473" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="I473" t="s">
         <v>296</v>
@@ -25153,7 +25129,7 @@
         <v>460</v>
       </c>
       <c r="K473" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="L473" t="s">
         <v>88</v>
@@ -25170,7 +25146,7 @@
         <v>882</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C474">
         <v>2026</v>
@@ -25188,7 +25164,7 @@
         <v>10722810240</v>
       </c>
       <c r="H474" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="I474" t="s">
         <v>296</v>
@@ -25197,7 +25173,7 @@
         <v>460</v>
       </c>
       <c r="K474" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="L474" t="s">
         <v>88</v>
@@ -25214,7 +25190,7 @@
         <v>883</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C475">
         <v>2026</v>
@@ -25241,7 +25217,7 @@
         <v>460</v>
       </c>
       <c r="K475" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="L475" t="s">
         <v>88</v>
@@ -25258,7 +25234,7 @@
         <v>884</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C476">
         <v>2026</v>
@@ -25276,7 +25252,7 @@
         <v>10426361936</v>
       </c>
       <c r="H476" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="I476" t="s">
         <v>296</v>
@@ -25285,7 +25261,7 @@
         <v>460</v>
       </c>
       <c r="K476" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="L476" t="s">
         <v>88</v>
@@ -25302,7 +25278,7 @@
         <v>885</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C477">
         <v>2026</v>
@@ -25329,7 +25305,7 @@
         <v>460</v>
       </c>
       <c r="K477" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="L477" t="s">
         <v>88</v>
@@ -25346,7 +25322,7 @@
         <v>886</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C478">
         <v>2026</v>
@@ -25364,7 +25340,7 @@
         <v>10249582862</v>
       </c>
       <c r="H478" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="I478" t="s">
         <v>296</v>
@@ -25373,7 +25349,7 @@
         <v>460</v>
       </c>
       <c r="K478" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="L478" t="s">
         <v>88</v>
@@ -25390,7 +25366,7 @@
         <v>887</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>918</v>
+        <v>911</v>
       </c>
       <c r="C479">
         <v>2026</v>
@@ -25402,22 +25378,22 @@
         <v>65</v>
       </c>
       <c r="F479" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G479" s="4">
-        <v>24889807</v>
+        <v>23922343</v>
       </c>
       <c r="H479" t="s">
-        <v>958</v>
+        <v>447</v>
       </c>
       <c r="I479" t="s">
-        <v>296</v>
+        <v>451</v>
       </c>
       <c r="J479" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="K479" t="s">
-        <v>985</v>
+        <v>973</v>
       </c>
       <c r="L479" t="s">
         <v>88</v>
@@ -25434,7 +25410,7 @@
         <v>888</v>
       </c>
       <c r="B480" s="4" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="C480">
         <v>2026</v>
@@ -25449,25 +25425,25 @@
         <v>401</v>
       </c>
       <c r="G480" s="4">
-        <v>10408822641</v>
+        <v>10238869094</v>
       </c>
       <c r="H480" t="s">
-        <v>959</v>
+        <v>935</v>
       </c>
       <c r="I480" t="s">
-        <v>296</v>
+        <v>403</v>
       </c>
       <c r="J480" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K480" t="s">
-        <v>986</v>
+        <v>974</v>
       </c>
       <c r="L480" t="s">
         <v>88</v>
       </c>
       <c r="M480">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N480" t="s">
         <v>89</v>
@@ -25478,7 +25454,7 @@
         <v>889</v>
       </c>
       <c r="B481" s="4" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="C481">
         <v>2026</v>
@@ -25493,25 +25469,25 @@
         <v>401</v>
       </c>
       <c r="G481" s="4">
-        <v>10446727180</v>
+        <v>10247032270</v>
       </c>
       <c r="H481" t="s">
-        <v>960</v>
+        <v>936</v>
       </c>
       <c r="I481" t="s">
-        <v>296</v>
+        <v>403</v>
       </c>
       <c r="J481" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K481" t="s">
-        <v>986</v>
+        <v>975</v>
       </c>
       <c r="L481" t="s">
         <v>88</v>
       </c>
       <c r="M481">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N481" t="s">
         <v>89</v>
@@ -25522,7 +25498,7 @@
         <v>890</v>
       </c>
       <c r="B482" s="4" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="C482">
         <v>2026</v>
@@ -25534,19 +25510,19 @@
         <v>65</v>
       </c>
       <c r="F482" t="s">
-        <v>402</v>
+        <v>48</v>
       </c>
       <c r="G482" s="4">
-        <v>23922343</v>
+        <v>10252188041</v>
       </c>
       <c r="H482" t="s">
-        <v>447</v>
+        <v>305</v>
       </c>
       <c r="I482" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="J482" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="K482" t="s">
         <v>979</v>
@@ -25555,7 +25531,7 @@
         <v>88</v>
       </c>
       <c r="M482">
-        <v>1</v>
+        <v>324</v>
       </c>
       <c r="N482" t="s">
         <v>89</v>
@@ -25566,7 +25542,7 @@
         <v>891</v>
       </c>
       <c r="B483" s="4" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C483">
         <v>2026</v>
@@ -25580,26 +25556,26 @@
       <c r="F483" t="s">
         <v>401</v>
       </c>
-      <c r="G483" s="4">
-        <v>10238869094</v>
+      <c r="G483" s="4" t="s">
+        <v>1045</v>
       </c>
       <c r="H483" t="s">
-        <v>938</v>
+        <v>957</v>
       </c>
       <c r="I483" t="s">
-        <v>403</v>
+        <v>296</v>
       </c>
       <c r="J483" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K483" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="L483" t="s">
         <v>88</v>
       </c>
       <c r="M483">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N483" t="s">
         <v>89</v>
@@ -25610,7 +25586,7 @@
         <v>892</v>
       </c>
       <c r="B484" s="4" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C484">
         <v>2026</v>
@@ -25624,26 +25600,26 @@
       <c r="F484" t="s">
         <v>401</v>
       </c>
-      <c r="G484" s="4">
-        <v>10247032270</v>
+      <c r="G484" s="4" t="s">
+        <v>1046</v>
       </c>
       <c r="H484" t="s">
-        <v>939</v>
+        <v>958</v>
       </c>
       <c r="I484" t="s">
-        <v>403</v>
+        <v>296</v>
       </c>
       <c r="J484" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K484" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="L484" t="s">
         <v>88</v>
       </c>
       <c r="M484">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N484" t="s">
         <v>89</v>
@@ -25654,7 +25630,7 @@
         <v>893</v>
       </c>
       <c r="B485" s="4" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="C485">
         <v>2026</v>
@@ -25666,28 +25642,28 @@
         <v>65</v>
       </c>
       <c r="F485" t="s">
-        <v>48</v>
-      </c>
-      <c r="G485" s="4">
-        <v>10252188041</v>
+        <v>401</v>
+      </c>
+      <c r="G485" s="4" t="s">
+        <v>1047</v>
       </c>
       <c r="H485" t="s">
-        <v>305</v>
+        <v>959</v>
       </c>
       <c r="I485" t="s">
-        <v>453</v>
+        <v>296</v>
       </c>
       <c r="J485" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K485" t="s">
-        <v>987</v>
+        <v>978</v>
       </c>
       <c r="L485" t="s">
         <v>88</v>
       </c>
       <c r="M485">
-        <v>324</v>
+        <v>1</v>
       </c>
       <c r="N485" t="s">
         <v>89</v>
@@ -25698,7 +25674,7 @@
         <v>894</v>
       </c>
       <c r="B486" s="4" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C486">
         <v>2026</v>
@@ -25713,10 +25689,10 @@
         <v>401</v>
       </c>
       <c r="G486" s="4" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="H486" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="I486" t="s">
         <v>296</v>
@@ -25725,7 +25701,7 @@
         <v>460</v>
       </c>
       <c r="K486" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="L486" t="s">
         <v>88</v>
@@ -25741,8 +25717,8 @@
       <c r="A487" t="s">
         <v>895</v>
       </c>
-      <c r="B487" s="4" t="s">
-        <v>919</v>
+      <c r="B487" s="3">
+        <v>46190</v>
       </c>
       <c r="C487">
         <v>2026</v>
@@ -25757,10 +25733,10 @@
         <v>401</v>
       </c>
       <c r="G487" s="4" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="H487" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="I487" t="s">
         <v>296</v>
@@ -25769,7 +25745,7 @@
         <v>460</v>
       </c>
       <c r="K487" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="L487" t="s">
         <v>88</v>
@@ -25786,7 +25762,7 @@
         <v>896</v>
       </c>
       <c r="B488" s="4" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C488">
         <v>2026</v>
@@ -25801,10 +25777,10 @@
         <v>401</v>
       </c>
       <c r="G488" s="4" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="H488" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="I488" t="s">
         <v>296</v>
@@ -25813,7 +25789,7 @@
         <v>460</v>
       </c>
       <c r="K488" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="L488" t="s">
         <v>88</v>
@@ -25830,7 +25806,7 @@
         <v>897</v>
       </c>
       <c r="B489" s="4" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C489">
         <v>2026</v>
@@ -25845,10 +25821,10 @@
         <v>401</v>
       </c>
       <c r="G489" s="4" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="H489" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="I489" t="s">
         <v>296</v>
@@ -25857,7 +25833,7 @@
         <v>460</v>
       </c>
       <c r="K489" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="L489" t="s">
         <v>88</v>
@@ -25873,8 +25849,8 @@
       <c r="A490" t="s">
         <v>898</v>
       </c>
-      <c r="B490" s="3">
-        <v>46190</v>
+      <c r="B490" s="4" t="s">
+        <v>916</v>
       </c>
       <c r="C490">
         <v>2026</v>
@@ -25889,10 +25865,10 @@
         <v>401</v>
       </c>
       <c r="G490" s="4" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="H490" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="I490" t="s">
         <v>296</v>
@@ -25901,7 +25877,7 @@
         <v>460</v>
       </c>
       <c r="K490" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="L490" t="s">
         <v>88</v>
@@ -25918,7 +25894,7 @@
         <v>899</v>
       </c>
       <c r="B491" s="4" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C491">
         <v>2026</v>
@@ -25933,10 +25909,10 @@
         <v>401</v>
       </c>
       <c r="G491" s="4" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="H491" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="I491" t="s">
         <v>296</v>
@@ -25945,7 +25921,7 @@
         <v>460</v>
       </c>
       <c r="K491" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="L491" t="s">
         <v>88</v>
@@ -25962,7 +25938,7 @@
         <v>900</v>
       </c>
       <c r="B492" s="4" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C492">
         <v>2026</v>
@@ -25977,10 +25953,10 @@
         <v>401</v>
       </c>
       <c r="G492" s="4" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="H492" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="I492" t="s">
         <v>296</v>
@@ -25989,7 +25965,7 @@
         <v>460</v>
       </c>
       <c r="K492" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="L492" t="s">
         <v>88</v>
@@ -26006,7 +25982,7 @@
         <v>901</v>
       </c>
       <c r="B493" s="4" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C493">
         <v>2026</v>
@@ -26021,10 +25997,10 @@
         <v>401</v>
       </c>
       <c r="G493" s="4" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="H493" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="I493" t="s">
         <v>296</v>
@@ -26033,7 +26009,7 @@
         <v>460</v>
       </c>
       <c r="K493" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="L493" t="s">
         <v>88</v>
@@ -26050,7 +26026,7 @@
         <v>902</v>
       </c>
       <c r="B494" s="4" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C494">
         <v>2026</v>
@@ -26065,10 +26041,10 @@
         <v>401</v>
       </c>
       <c r="G494" s="4" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="H494" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="I494" t="s">
         <v>296</v>
@@ -26077,7 +26053,7 @@
         <v>460</v>
       </c>
       <c r="K494" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="L494" t="s">
         <v>88</v>
@@ -26094,7 +26070,7 @@
         <v>903</v>
       </c>
       <c r="B495" s="4" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C495">
         <v>2026</v>
@@ -26109,10 +26085,10 @@
         <v>401</v>
       </c>
       <c r="G495" s="4" t="s">
-        <v>1062</v>
+        <v>1057</v>
       </c>
       <c r="H495" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="I495" t="s">
         <v>296</v>
@@ -26121,7 +26097,7 @@
         <v>460</v>
       </c>
       <c r="K495" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="L495" t="s">
         <v>88</v>
@@ -26138,7 +26114,7 @@
         <v>904</v>
       </c>
       <c r="B496" s="4" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C496">
         <v>2026</v>
@@ -26153,10 +26129,10 @@
         <v>401</v>
       </c>
       <c r="G496" s="4" t="s">
-        <v>1063</v>
+        <v>1058</v>
       </c>
       <c r="H496" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="I496" t="s">
         <v>296</v>
@@ -26165,7 +26141,7 @@
         <v>460</v>
       </c>
       <c r="K496" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="L496" t="s">
         <v>88</v>
@@ -26182,7 +26158,7 @@
         <v>905</v>
       </c>
       <c r="B497" s="4" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C497">
         <v>2026</v>
@@ -26197,10 +26173,10 @@
         <v>401</v>
       </c>
       <c r="G497" s="4" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="H497" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="I497" t="s">
         <v>296</v>
@@ -26209,7 +26185,7 @@
         <v>460</v>
       </c>
       <c r="K497" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="L497" t="s">
         <v>88</v>
@@ -26226,7 +26202,7 @@
         <v>906</v>
       </c>
       <c r="B498" s="4" t="s">
-        <v>919</v>
+        <v>1064</v>
       </c>
       <c r="C498">
         <v>2026</v>
@@ -26238,22 +26214,22 @@
         <v>65</v>
       </c>
       <c r="F498" t="s">
-        <v>401</v>
+        <v>354</v>
       </c>
       <c r="G498" s="4" t="s">
         <v>1065</v>
       </c>
       <c r="H498" t="s">
-        <v>975</v>
+        <v>302</v>
       </c>
       <c r="I498" t="s">
-        <v>296</v>
+        <v>50</v>
       </c>
       <c r="J498" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="K498" t="s">
-        <v>984</v>
+        <v>1060</v>
       </c>
       <c r="L498" t="s">
         <v>88</v>
@@ -26262,7 +26238,7 @@
         <v>1</v>
       </c>
       <c r="N498" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="499" spans="1:14">
@@ -26270,7 +26246,7 @@
         <v>907</v>
       </c>
       <c r="B499" s="4" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="C499">
         <v>2026</v>
@@ -26282,22 +26258,22 @@
         <v>65</v>
       </c>
       <c r="F499" t="s">
-        <v>401</v>
+        <v>354</v>
       </c>
       <c r="G499" s="4" t="s">
         <v>1066</v>
       </c>
       <c r="H499" t="s">
-        <v>976</v>
+        <v>1069</v>
       </c>
       <c r="I499" t="s">
-        <v>296</v>
+        <v>50</v>
       </c>
       <c r="J499" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="K499" t="s">
-        <v>984</v>
+        <v>1061</v>
       </c>
       <c r="L499" t="s">
         <v>88</v>
@@ -26306,7 +26282,7 @@
         <v>1</v>
       </c>
       <c r="N499" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="500" spans="1:14">
@@ -26314,7 +26290,7 @@
         <v>908</v>
       </c>
       <c r="B500" s="4" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C500">
         <v>2026</v>
@@ -26326,22 +26302,22 @@
         <v>65</v>
       </c>
       <c r="F500" t="s">
-        <v>401</v>
+        <v>354</v>
       </c>
       <c r="G500" s="4" t="s">
         <v>1067</v>
       </c>
       <c r="H500" t="s">
-        <v>977</v>
+        <v>300</v>
       </c>
       <c r="I500" t="s">
-        <v>296</v>
+        <v>50</v>
       </c>
       <c r="J500" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="K500" t="s">
-        <v>984</v>
+        <v>1062</v>
       </c>
       <c r="L500" t="s">
         <v>88</v>
@@ -26350,7 +26326,7 @@
         <v>1</v>
       </c>
       <c r="N500" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="501" spans="1:14">
@@ -26358,7 +26334,7 @@
         <v>909</v>
       </c>
       <c r="B501" s="4" t="s">
-        <v>1072</v>
+        <v>911</v>
       </c>
       <c r="C501">
         <v>2026</v>
@@ -26373,10 +26349,10 @@
         <v>354</v>
       </c>
       <c r="G501" s="4" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="H501" t="s">
-        <v>302</v>
+        <v>70</v>
       </c>
       <c r="I501" t="s">
         <v>50</v>
@@ -26385,7 +26361,7 @@
         <v>463</v>
       </c>
       <c r="K501" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="L501" t="s">
         <v>88</v>
@@ -26397,147 +26373,15 @@
         <v>90</v>
       </c>
     </row>
-    <row r="502" spans="1:14">
-      <c r="A502" t="s">
-        <v>910</v>
-      </c>
-      <c r="B502" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="C502">
-        <v>2026</v>
-      </c>
-      <c r="D502">
-        <v>6</v>
-      </c>
-      <c r="E502" t="s">
-        <v>65</v>
-      </c>
-      <c r="F502" t="s">
-        <v>354</v>
-      </c>
-      <c r="G502" s="4" t="s">
-        <v>1074</v>
-      </c>
-      <c r="H502" t="s">
-        <v>1077</v>
-      </c>
-      <c r="I502" t="s">
-        <v>50</v>
-      </c>
-      <c r="J502" t="s">
-        <v>463</v>
-      </c>
-      <c r="K502" t="s">
-        <v>1069</v>
-      </c>
-      <c r="L502" t="s">
-        <v>88</v>
-      </c>
-      <c r="M502">
-        <v>1</v>
-      </c>
-      <c r="N502" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="503" spans="1:14">
-      <c r="A503" t="s">
-        <v>911</v>
-      </c>
-      <c r="B503" s="4" t="s">
-        <v>919</v>
-      </c>
-      <c r="C503">
-        <v>2026</v>
-      </c>
-      <c r="D503">
-        <v>6</v>
-      </c>
-      <c r="E503" t="s">
-        <v>65</v>
-      </c>
-      <c r="F503" t="s">
-        <v>354</v>
-      </c>
-      <c r="G503" s="4" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H503" t="s">
-        <v>300</v>
-      </c>
-      <c r="I503" t="s">
-        <v>50</v>
-      </c>
-      <c r="J503" t="s">
-        <v>463</v>
-      </c>
-      <c r="K503" t="s">
-        <v>1070</v>
-      </c>
-      <c r="L503" t="s">
-        <v>88</v>
-      </c>
-      <c r="M503">
-        <v>1</v>
-      </c>
-      <c r="N503" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="504" spans="1:14">
-      <c r="A504" t="s">
-        <v>912</v>
-      </c>
-      <c r="B504" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="C504">
-        <v>2026</v>
-      </c>
-      <c r="D504">
-        <v>6</v>
-      </c>
-      <c r="E504" t="s">
-        <v>65</v>
-      </c>
-      <c r="F504" t="s">
-        <v>354</v>
-      </c>
-      <c r="G504" s="4" t="s">
-        <v>1076</v>
-      </c>
-      <c r="H504" t="s">
-        <v>70</v>
-      </c>
-      <c r="I504" t="s">
-        <v>50</v>
-      </c>
-      <c r="J504" t="s">
-        <v>463</v>
-      </c>
-      <c r="K504" t="s">
-        <v>1071</v>
-      </c>
-      <c r="L504" t="s">
-        <v>88</v>
-      </c>
-      <c r="M504">
-        <v>1</v>
-      </c>
-      <c r="N504" t="s">
-        <v>90</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O489">
-    <sortCondition ref="E480:E489"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O486">
+    <sortCondition ref="E479:E486"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="G486:G500 G501:G504" numberStoredAsText="1"/>
+    <ignoredError sqref="G483:G497 G498:G501" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F64F65-8EDD-4161-A8F3-6C98271C7959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56E6F75-5503-41F6-B5EE-0FC985031AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$482</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$481</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4987" uniqueCount="1070">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4970" uniqueCount="1079">
   <si>
     <t>ID_ACTIVIDAD</t>
   </si>
@@ -2856,57 +2856,15 @@
     <t>HUAMAN CARDENAS NANCY</t>
   </si>
   <si>
-    <t>MONTES SOLIS BERTONI</t>
-  </si>
-  <si>
     <t>ESPINOZA VALENZUELA ORLANDO</t>
   </si>
   <si>
-    <t>TRUJILLO OQUENDO OSCAR</t>
-  </si>
-  <si>
-    <t>CASTELO HUILLCA ROSA MILAGROS</t>
-  </si>
-  <si>
-    <t>GUTIERREZ SIHUIN KUKULI FLOR</t>
-  </si>
-  <si>
-    <t>INCA MEDINA WHENDY TATIANA</t>
-  </si>
-  <si>
     <t>CACERES RIVAS CINTHYA KUKULI</t>
   </si>
   <si>
     <t>SALAS MUÑOZ VICTORIA</t>
   </si>
   <si>
-    <t>ESPINOZA USCATA MOISES BENJAMIN</t>
-  </si>
-  <si>
-    <t>VALDEZ ZERPA MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CUTIPA RAMOS ADA VIRGINIA</t>
-  </si>
-  <si>
-    <t>PINTO LIMA KAREN CYNTHIA</t>
-  </si>
-  <si>
-    <t>SUCESION INDIVISA PERALES GUEVARA GLADYS DINA</t>
-  </si>
-  <si>
-    <t>YUCRA HERRERA MAYRA CARLAY</t>
-  </si>
-  <si>
-    <t>QUINTANA MAMANI CLAUDIA MILAGROS</t>
-  </si>
-  <si>
-    <t>MILLA GELDRES GILMAR RICARDO</t>
-  </si>
-  <si>
-    <t>SILVA SANCHEZ ISRAEL DE JESUS</t>
-  </si>
-  <si>
     <t>PACCOTACYA CRUZ ANITA</t>
   </si>
   <si>
@@ -2964,12 +2922,6 @@
     <t>Teñido artesanal con tintes sintéticos con las técnicas de teñido en sustratos textiles</t>
   </si>
   <si>
-    <t>FORMALIZACION Y GESTION EMPRESARIAL PARA EL ACCESO A MERCADOS INTERNACIONALES</t>
-  </si>
-  <si>
-    <t>CAPACITACION EN LIDERAZGO ORGANIZACIONAL: DE LA VISIÓN A LA TRANSFORMACIÓN</t>
-  </si>
-  <si>
     <t>CAPACITACION ESPECIALIZADA EN TEÑIDO TEXTIL CON ENFOQUE DE ECONOMÍA CIRCULAR: TECNOLOGÍAS INDUSTRIALES Y COLORANTES NATURALES</t>
   </si>
   <si>
@@ -3171,51 +3123,6 @@
     <t>COMPONENTE</t>
   </si>
   <si>
-    <t>10450876700</t>
-  </si>
-  <si>
-    <t>10476142941</t>
-  </si>
-  <si>
-    <t>10454316903</t>
-  </si>
-  <si>
-    <t>10456258536</t>
-  </si>
-  <si>
-    <t>10462583996</t>
-  </si>
-  <si>
-    <t>46314028</t>
-  </si>
-  <si>
-    <t>43150763</t>
-  </si>
-  <si>
-    <t>42566234</t>
-  </si>
-  <si>
-    <t>40040306</t>
-  </si>
-  <si>
-    <t>73870421</t>
-  </si>
-  <si>
-    <t>24873839</t>
-  </si>
-  <si>
-    <t>47656632</t>
-  </si>
-  <si>
-    <t>47925279</t>
-  </si>
-  <si>
-    <t>46474063</t>
-  </si>
-  <si>
-    <t>42049412</t>
-  </si>
-  <si>
     <t>Overcoming Texture Complexity in Textile Quality Control: A YOLOv11-Seg Approach for Alpaca Fiber Felt Balls</t>
   </si>
   <si>
@@ -3231,19 +3138,139 @@
     <t>01/07/2026</t>
   </si>
   <si>
-    <t>20172474501</t>
-  </si>
-  <si>
-    <t>73622059</t>
-  </si>
-  <si>
-    <t>20610561005</t>
-  </si>
-  <si>
-    <t>10700937645</t>
-  </si>
-  <si>
     <t>GUIDO CCAHUATA YAURI</t>
+  </si>
+  <si>
+    <t>CCAPA CUTI ESTELA</t>
+  </si>
+  <si>
+    <t>QUISPE GONZALES EMILIANA</t>
+  </si>
+  <si>
+    <t>ALVAREZ CCAPA AMELIA</t>
+  </si>
+  <si>
+    <t>AQUEPUCHO QUISPE LINA</t>
+  </si>
+  <si>
+    <t>OROZCO DE THAQUIMA ELENA</t>
+  </si>
+  <si>
+    <t>QQUELLHUA FLOREZ LUZMILA</t>
+  </si>
+  <si>
+    <t>SAICO CORDOVA JUSTINA</t>
+  </si>
+  <si>
+    <t>LLAVE PACCOTACYA ESTHER</t>
+  </si>
+  <si>
+    <t>CORDOVA SAICO AMELIA</t>
+  </si>
+  <si>
+    <t>QQUEHUE HUISA SOFIA</t>
+  </si>
+  <si>
+    <t>MACHACCA CCALLOCONDO ELIZABETH</t>
+  </si>
+  <si>
+    <t>QUISPE MOLLO GRACIELA</t>
+  </si>
+  <si>
+    <t>ALVAREZ CCAPA ELENA</t>
+  </si>
+  <si>
+    <t>LLAVE ALVAREZ LORENZA</t>
+  </si>
+  <si>
+    <t>CCALLOCONDO SALCEDO AYDEE</t>
+  </si>
+  <si>
+    <t>Sistema de trazabilidad y control de calidad en prendas tejidas a punto de fibra de alpaca en la cadena de valor textilalpaquera</t>
+  </si>
+  <si>
+    <t>Desarrollo y validación de un biosorbente obtenido a partir de mermas de fibra de alpaca mediante modificación química superficial, aplicado al tratamiento de efluentes textiles de la cadena productiva de la Macro Región Sur del Perú</t>
+  </si>
+  <si>
+    <t>Museo Virtual de la Alpaca</t>
+  </si>
+  <si>
+    <t>QAWAYSOFT</t>
+  </si>
+  <si>
+    <t>Heritaje by Eli</t>
+  </si>
+  <si>
+    <t>KAMAQ SUYU: Estudio de arte digital</t>
+  </si>
+  <si>
+    <t>8.4. Asesoramiento en el desarrollo de tesis de grado y/o postgrado en el ámbito de la cadena productiva</t>
+  </si>
+  <si>
+    <t>ELIZABETH VARGAS CONDORI</t>
+  </si>
+  <si>
+    <t>ELIZABETH TTURO CHAISA</t>
+  </si>
+  <si>
+    <t>David Reyes</t>
+  </si>
+  <si>
+    <t>Capacitación especializada en el proceso de transformación textil desde la clasificación hasta la comercialización</t>
+  </si>
+  <si>
+    <t>FOLLANO HERRERA ANGELA ELIZA</t>
+  </si>
+  <si>
+    <t>CORIHUAMAN MAYNICTA GUIDO JHUNIOR</t>
+  </si>
+  <si>
+    <t>CAMILLA MAMANI JANETH SHERALY</t>
+  </si>
+  <si>
+    <t>TICONA MIRANDA MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>PARIONA IRCAÑAUPA TOÑO</t>
+  </si>
+  <si>
+    <t>HILARI ALMIRON LEONEL DAVINCY</t>
+  </si>
+  <si>
+    <t>IRURI CHUCHULLO ELIZA PILAR</t>
+  </si>
+  <si>
+    <t>GUTIERREZ LAYME MOISES</t>
+  </si>
+  <si>
+    <t>CARI VILLA ANGEL LENYN</t>
+  </si>
+  <si>
+    <t>CAMPOS DELGADILLO RUDY</t>
+  </si>
+  <si>
+    <t>HUAMAN GARRIDO ROLANDO ALEXANDER</t>
+  </si>
+  <si>
+    <t>LOAIZA POLANCO CARLA ANDREA</t>
+  </si>
+  <si>
+    <t>LUNA RAMOS VANNERY GIOSABETH</t>
+  </si>
+  <si>
+    <t>TORRE ARIAS ABRAHAN JULIHO</t>
+  </si>
+  <si>
+    <t>CCOYCCOSI QUISPE ESMERALDA YUDITH</t>
+  </si>
+  <si>
+    <t>A00501</t>
+  </si>
+  <si>
+    <t>A00502</t>
+  </si>
+  <si>
+    <t>A00503</t>
   </si>
 </sst>
 </file>
@@ -3253,7 +3280,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3292,13 +3319,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -3310,12 +3356,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3337,10 +3384,24 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{3DD43B4D-3D2C-41B7-907B-1D2AD1FD5263}"/>
+    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{16BCF108-A20F-43F9-8F6B-297A868E1789}"/>
     <cellStyle name="Normal 5" xfId="2" xr:uid="{AFD6A24D-0EC0-4280-B213-19F29BC6D3D1}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3643,12 +3704,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O501"/>
+  <dimension ref="A1:O504"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="67.7109375" bestFit="1" customWidth="1"/>
@@ -3705,7 +3766,7 @@
         <v>12</v>
       </c>
       <c r="O1" t="s">
-        <v>1044</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -7849,7 +7910,7 @@
         <v>147</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>993</v>
+        <v>977</v>
       </c>
       <c r="C90">
         <v>2026</v>
@@ -7896,7 +7957,7 @@
         <v>148</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>993</v>
+        <v>977</v>
       </c>
       <c r="C91">
         <v>2026</v>
@@ -7943,7 +8004,7 @@
         <v>149</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>993</v>
+        <v>977</v>
       </c>
       <c r="C92">
         <v>2026</v>
@@ -8131,7 +8192,7 @@
         <v>153</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>994</v>
+        <v>978</v>
       </c>
       <c r="C96">
         <v>2026</v>
@@ -8178,7 +8239,7 @@
         <v>154</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>992</v>
+        <v>976</v>
       </c>
       <c r="C97">
         <v>2026</v>
@@ -8948,7 +9009,7 @@
         <v>10239106876</v>
       </c>
       <c r="H113" t="s">
-        <v>1043</v>
+        <v>1027</v>
       </c>
       <c r="I113" t="s">
         <v>451</v>
@@ -9512,7 +9573,7 @@
         <v>10253055672</v>
       </c>
       <c r="H125" t="s">
-        <v>996</v>
+        <v>980</v>
       </c>
       <c r="I125" t="s">
         <v>451</v>
@@ -9568,7 +9629,7 @@
         <v>454</v>
       </c>
       <c r="K126" t="s">
-        <v>1023</v>
+        <v>1007</v>
       </c>
       <c r="L126" t="s">
         <v>88</v>
@@ -9606,7 +9667,7 @@
         <v>10458755260</v>
       </c>
       <c r="H127" t="s">
-        <v>995</v>
+        <v>979</v>
       </c>
       <c r="I127" t="s">
         <v>451</v>
@@ -9682,7 +9743,7 @@
         <v>186</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>980</v>
+        <v>964</v>
       </c>
       <c r="C129">
         <v>2026</v>
@@ -9709,7 +9770,7 @@
         <v>454</v>
       </c>
       <c r="K129" t="s">
-        <v>1004</v>
+        <v>988</v>
       </c>
       <c r="L129" t="s">
         <v>88</v>
@@ -9729,7 +9790,7 @@
         <v>187</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>980</v>
+        <v>964</v>
       </c>
       <c r="C130">
         <v>2026</v>
@@ -9756,7 +9817,7 @@
         <v>454</v>
       </c>
       <c r="K130" t="s">
-        <v>1008</v>
+        <v>992</v>
       </c>
       <c r="L130" t="s">
         <v>88</v>
@@ -9850,7 +9911,7 @@
         <v>454</v>
       </c>
       <c r="K132" t="s">
-        <v>1005</v>
+        <v>989</v>
       </c>
       <c r="L132" t="s">
         <v>88</v>
@@ -9882,7 +9943,7 @@
         <v>404</v>
       </c>
       <c r="F133" t="s">
-        <v>1042</v>
+        <v>1026</v>
       </c>
       <c r="G133" s="4">
         <v>10473163450</v>
@@ -9897,7 +9958,7 @@
         <v>455</v>
       </c>
       <c r="K133" t="s">
-        <v>1031</v>
+        <v>1015</v>
       </c>
       <c r="L133" t="s">
         <v>88</v>
@@ -9944,7 +10005,7 @@
         <v>454</v>
       </c>
       <c r="K134" t="s">
-        <v>1009</v>
+        <v>993</v>
       </c>
       <c r="L134" t="s">
         <v>88</v>
@@ -9964,7 +10025,7 @@
         <v>318</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>983</v>
+        <v>967</v>
       </c>
       <c r="C135">
         <v>2026</v>
@@ -9991,7 +10052,7 @@
         <v>456</v>
       </c>
       <c r="K135" t="s">
-        <v>1006</v>
+        <v>990</v>
       </c>
       <c r="L135" t="s">
         <v>88</v>
@@ -10011,7 +10072,7 @@
         <v>319</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>983</v>
+        <v>967</v>
       </c>
       <c r="C136">
         <v>2026</v>
@@ -10038,7 +10099,7 @@
         <v>454</v>
       </c>
       <c r="K136" t="s">
-        <v>1010</v>
+        <v>994</v>
       </c>
       <c r="L136" t="s">
         <v>88</v>
@@ -10076,7 +10137,7 @@
         <v>10701892734</v>
       </c>
       <c r="H137" t="s">
-        <v>999</v>
+        <v>983</v>
       </c>
       <c r="I137" t="s">
         <v>451</v>
@@ -10123,7 +10184,7 @@
         <v>10627334066</v>
       </c>
       <c r="H138" t="s">
-        <v>1000</v>
+        <v>984</v>
       </c>
       <c r="I138" t="s">
         <v>451</v>
@@ -10179,7 +10240,7 @@
         <v>456</v>
       </c>
       <c r="K139" t="s">
-        <v>1006</v>
+        <v>990</v>
       </c>
       <c r="L139" t="s">
         <v>88</v>
@@ -10226,7 +10287,7 @@
         <v>454</v>
       </c>
       <c r="K140" t="s">
-        <v>1011</v>
+        <v>995</v>
       </c>
       <c r="L140" t="s">
         <v>88</v>
@@ -10264,7 +10325,7 @@
         <v>10444412823</v>
       </c>
       <c r="H141" t="s">
-        <v>998</v>
+        <v>982</v>
       </c>
       <c r="I141" t="s">
         <v>451</v>
@@ -10311,7 +10372,7 @@
         <v>10238268821</v>
       </c>
       <c r="H142" t="s">
-        <v>1001</v>
+        <v>985</v>
       </c>
       <c r="I142" t="s">
         <v>451</v>
@@ -10461,7 +10522,7 @@
         <v>454</v>
       </c>
       <c r="K145" t="s">
-        <v>1038</v>
+        <v>1022</v>
       </c>
       <c r="L145" t="s">
         <v>88</v>
@@ -10508,7 +10569,7 @@
         <v>454</v>
       </c>
       <c r="K146" t="s">
-        <v>1005</v>
+        <v>989</v>
       </c>
       <c r="L146" t="s">
         <v>88</v>
@@ -10540,7 +10601,7 @@
         <v>404</v>
       </c>
       <c r="F147" t="s">
-        <v>1042</v>
+        <v>1026</v>
       </c>
       <c r="G147" s="4">
         <v>10239510197</v>
@@ -10555,7 +10616,7 @@
         <v>456</v>
       </c>
       <c r="K147" t="s">
-        <v>1039</v>
+        <v>1023</v>
       </c>
       <c r="L147" t="s">
         <v>88</v>
@@ -10602,7 +10663,7 @@
         <v>454</v>
       </c>
       <c r="K148" t="s">
-        <v>1012</v>
+        <v>996</v>
       </c>
       <c r="L148" t="s">
         <v>88</v>
@@ -10687,7 +10748,7 @@
         <v>10243840738</v>
       </c>
       <c r="H150" t="s">
-        <v>1002</v>
+        <v>986</v>
       </c>
       <c r="I150" t="s">
         <v>451</v>
@@ -10716,7 +10777,7 @@
         <v>334</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>981</v>
+        <v>965</v>
       </c>
       <c r="C151">
         <v>2026</v>
@@ -10743,7 +10804,7 @@
         <v>454</v>
       </c>
       <c r="K151" t="s">
-        <v>1005</v>
+        <v>989</v>
       </c>
       <c r="L151" t="s">
         <v>88</v>
@@ -10763,7 +10824,7 @@
         <v>335</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>981</v>
+        <v>965</v>
       </c>
       <c r="C152">
         <v>2026</v>
@@ -10790,7 +10851,7 @@
         <v>454</v>
       </c>
       <c r="K152" t="s">
-        <v>1013</v>
+        <v>997</v>
       </c>
       <c r="L152" t="s">
         <v>88</v>
@@ -10922,7 +10983,7 @@
         <v>10238085042</v>
       </c>
       <c r="H155" t="s">
-        <v>1003</v>
+        <v>987</v>
       </c>
       <c r="I155" t="s">
         <v>451</v>
@@ -11045,7 +11106,7 @@
         <v>341</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>984</v>
+        <v>968</v>
       </c>
       <c r="C158">
         <v>2026</v>
@@ -11072,7 +11133,7 @@
         <v>454</v>
       </c>
       <c r="K158" t="s">
-        <v>1034</v>
+        <v>1018</v>
       </c>
       <c r="L158" t="s">
         <v>88</v>
@@ -11092,7 +11153,7 @@
         <v>342</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>984</v>
+        <v>968</v>
       </c>
       <c r="C159">
         <v>2026</v>
@@ -11119,7 +11180,7 @@
         <v>454</v>
       </c>
       <c r="K159" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
       <c r="L159" t="s">
         <v>88</v>
@@ -11139,7 +11200,7 @@
         <v>343</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>984</v>
+        <v>968</v>
       </c>
       <c r="C160">
         <v>2026</v>
@@ -11166,7 +11227,7 @@
         <v>454</v>
       </c>
       <c r="K160" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
       <c r="L160" t="s">
         <v>88</v>
@@ -11186,7 +11247,7 @@
         <v>344</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>984</v>
+        <v>968</v>
       </c>
       <c r="C161">
         <v>2026</v>
@@ -11213,7 +11274,7 @@
         <v>455</v>
       </c>
       <c r="K161" t="s">
-        <v>1018</v>
+        <v>1002</v>
       </c>
       <c r="L161" t="s">
         <v>88</v>
@@ -11233,7 +11294,7 @@
         <v>345</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>984</v>
+        <v>968</v>
       </c>
       <c r="C162">
         <v>2026</v>
@@ -11260,7 +11321,7 @@
         <v>455</v>
       </c>
       <c r="K162" t="s">
-        <v>1030</v>
+        <v>1014</v>
       </c>
       <c r="L162" t="s">
         <v>88</v>
@@ -11280,7 +11341,7 @@
         <v>346</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>984</v>
+        <v>968</v>
       </c>
       <c r="C163">
         <v>2026</v>
@@ -11307,7 +11368,7 @@
         <v>457</v>
       </c>
       <c r="K163" t="s">
-        <v>1024</v>
+        <v>1008</v>
       </c>
       <c r="L163" t="s">
         <v>88</v>
@@ -11327,7 +11388,7 @@
         <v>347</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>984</v>
+        <v>968</v>
       </c>
       <c r="C164">
         <v>2026</v>
@@ -11354,7 +11415,7 @@
         <v>456</v>
       </c>
       <c r="K164" t="s">
-        <v>1006</v>
+        <v>990</v>
       </c>
       <c r="L164" t="s">
         <v>88</v>
@@ -11374,7 +11435,7 @@
         <v>348</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>985</v>
+        <v>969</v>
       </c>
       <c r="C165">
         <v>2026</v>
@@ -11401,7 +11462,7 @@
         <v>454</v>
       </c>
       <c r="K165" t="s">
-        <v>1036</v>
+        <v>1020</v>
       </c>
       <c r="L165" t="s">
         <v>88</v>
@@ -11421,7 +11482,7 @@
         <v>349</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>985</v>
+        <v>969</v>
       </c>
       <c r="C166">
         <v>2026</v>
@@ -11448,7 +11509,7 @@
         <v>454</v>
       </c>
       <c r="K166" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
       <c r="L166" t="s">
         <v>88</v>
@@ -11468,7 +11529,7 @@
         <v>350</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>985</v>
+        <v>969</v>
       </c>
       <c r="C167">
         <v>2026</v>
@@ -11495,7 +11556,7 @@
         <v>454</v>
       </c>
       <c r="K167" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
       <c r="L167" t="s">
         <v>88</v>
@@ -11515,7 +11576,7 @@
         <v>351</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>985</v>
+        <v>969</v>
       </c>
       <c r="C168">
         <v>2026</v>
@@ -11527,7 +11588,7 @@
         <v>404</v>
       </c>
       <c r="F168" t="s">
-        <v>1042</v>
+        <v>1026</v>
       </c>
       <c r="G168" s="4">
         <v>10239486377</v>
@@ -11542,7 +11603,7 @@
         <v>456</v>
       </c>
       <c r="K168" t="s">
-        <v>1029</v>
+        <v>1013</v>
       </c>
       <c r="L168" t="s">
         <v>88</v>
@@ -11562,7 +11623,7 @@
         <v>374</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>985</v>
+        <v>969</v>
       </c>
       <c r="C169">
         <v>2026</v>
@@ -11589,7 +11650,7 @@
         <v>455</v>
       </c>
       <c r="K169" t="s">
-        <v>1019</v>
+        <v>1003</v>
       </c>
       <c r="L169" t="s">
         <v>88</v>
@@ -11609,7 +11670,7 @@
         <v>375</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>985</v>
+        <v>969</v>
       </c>
       <c r="C170">
         <v>2026</v>
@@ -11636,7 +11697,7 @@
         <v>456</v>
       </c>
       <c r="K170" t="s">
-        <v>1006</v>
+        <v>990</v>
       </c>
       <c r="L170" t="s">
         <v>88</v>
@@ -11656,7 +11717,7 @@
         <v>376</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>985</v>
+        <v>969</v>
       </c>
       <c r="C171">
         <v>2026</v>
@@ -11683,7 +11744,7 @@
         <v>456</v>
       </c>
       <c r="K171" t="s">
-        <v>1006</v>
+        <v>990</v>
       </c>
       <c r="L171" t="s">
         <v>88</v>
@@ -11703,7 +11764,7 @@
         <v>377</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>982</v>
+        <v>966</v>
       </c>
       <c r="C172">
         <v>2026</v>
@@ -11730,7 +11791,7 @@
         <v>454</v>
       </c>
       <c r="K172" t="s">
-        <v>1023</v>
+        <v>1007</v>
       </c>
       <c r="L172" t="s">
         <v>88</v>
@@ -11750,7 +11811,7 @@
         <v>378</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>982</v>
+        <v>966</v>
       </c>
       <c r="C173">
         <v>2026</v>
@@ -11777,7 +11838,7 @@
         <v>454</v>
       </c>
       <c r="K173" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
       <c r="L173" t="s">
         <v>88</v>
@@ -11797,7 +11858,7 @@
         <v>379</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>982</v>
+        <v>966</v>
       </c>
       <c r="C174">
         <v>2026</v>
@@ -11824,7 +11885,7 @@
         <v>454</v>
       </c>
       <c r="K174" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
       <c r="L174" t="s">
         <v>88</v>
@@ -11844,7 +11905,7 @@
         <v>380</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>982</v>
+        <v>966</v>
       </c>
       <c r="C175">
         <v>2026</v>
@@ -11871,7 +11932,7 @@
         <v>454</v>
       </c>
       <c r="K175" t="s">
-        <v>1005</v>
+        <v>989</v>
       </c>
       <c r="L175" t="s">
         <v>88</v>
@@ -11891,7 +11952,7 @@
         <v>381</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>982</v>
+        <v>966</v>
       </c>
       <c r="C176">
         <v>2026</v>
@@ -11918,7 +11979,7 @@
         <v>455</v>
       </c>
       <c r="K176" t="s">
-        <v>1020</v>
+        <v>1004</v>
       </c>
       <c r="L176" t="s">
         <v>88</v>
@@ -11938,7 +11999,7 @@
         <v>382</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>982</v>
+        <v>966</v>
       </c>
       <c r="C177">
         <v>2026</v>
@@ -11965,7 +12026,7 @@
         <v>456</v>
       </c>
       <c r="K177" t="s">
-        <v>1006</v>
+        <v>990</v>
       </c>
       <c r="L177" t="s">
         <v>88</v>
@@ -11985,7 +12046,7 @@
         <v>383</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>987</v>
+        <v>971</v>
       </c>
       <c r="C178">
         <v>2026</v>
@@ -12012,7 +12073,7 @@
         <v>454</v>
       </c>
       <c r="K178" t="s">
-        <v>1012</v>
+        <v>996</v>
       </c>
       <c r="L178" t="s">
         <v>88</v>
@@ -12032,7 +12093,7 @@
         <v>384</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>987</v>
+        <v>971</v>
       </c>
       <c r="C179">
         <v>2026</v>
@@ -12059,7 +12120,7 @@
         <v>454</v>
       </c>
       <c r="K179" t="s">
-        <v>1037</v>
+        <v>1021</v>
       </c>
       <c r="L179" t="s">
         <v>88</v>
@@ -12079,7 +12140,7 @@
         <v>385</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>987</v>
+        <v>971</v>
       </c>
       <c r="C180">
         <v>2026</v>
@@ -12106,7 +12167,7 @@
         <v>454</v>
       </c>
       <c r="K180" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
       <c r="L180" t="s">
         <v>88</v>
@@ -12126,7 +12187,7 @@
         <v>386</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>987</v>
+        <v>971</v>
       </c>
       <c r="C181">
         <v>2026</v>
@@ -12153,7 +12214,7 @@
         <v>454</v>
       </c>
       <c r="K181" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
       <c r="L181" t="s">
         <v>88</v>
@@ -12173,7 +12234,7 @@
         <v>387</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>987</v>
+        <v>971</v>
       </c>
       <c r="C182">
         <v>2026</v>
@@ -12200,7 +12261,7 @@
         <v>454</v>
       </c>
       <c r="K182" t="s">
-        <v>1040</v>
+        <v>1024</v>
       </c>
       <c r="L182" t="s">
         <v>88</v>
@@ -12220,7 +12281,7 @@
         <v>388</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>987</v>
+        <v>971</v>
       </c>
       <c r="C183">
         <v>2026</v>
@@ -12247,7 +12308,7 @@
         <v>457</v>
       </c>
       <c r="K183" t="s">
-        <v>1025</v>
+        <v>1009</v>
       </c>
       <c r="L183" t="s">
         <v>88</v>
@@ -12267,7 +12328,7 @@
         <v>389</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>987</v>
+        <v>971</v>
       </c>
       <c r="C184">
         <v>2026</v>
@@ -12294,7 +12355,7 @@
         <v>454</v>
       </c>
       <c r="K184" t="s">
-        <v>1014</v>
+        <v>998</v>
       </c>
       <c r="L184" t="s">
         <v>88</v>
@@ -12332,7 +12393,7 @@
         <v>10409212480</v>
       </c>
       <c r="H185" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="I185" t="s">
         <v>451</v>
@@ -12388,7 +12449,7 @@
         <v>454</v>
       </c>
       <c r="K186" t="s">
-        <v>1007</v>
+        <v>991</v>
       </c>
       <c r="L186" t="s">
         <v>88</v>
@@ -12435,7 +12496,7 @@
         <v>454</v>
       </c>
       <c r="K187" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
       <c r="L187" t="s">
         <v>88</v>
@@ -12482,7 +12543,7 @@
         <v>454</v>
       </c>
       <c r="K188" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
       <c r="L188" t="s">
         <v>88</v>
@@ -12529,7 +12590,7 @@
         <v>456</v>
       </c>
       <c r="K189" t="s">
-        <v>1006</v>
+        <v>990</v>
       </c>
       <c r="L189" t="s">
         <v>88</v>
@@ -12576,7 +12637,7 @@
         <v>454</v>
       </c>
       <c r="K190" t="s">
-        <v>1015</v>
+        <v>999</v>
       </c>
       <c r="L190" t="s">
         <v>88</v>
@@ -12596,7 +12657,7 @@
         <v>396</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>994</v>
+        <v>978</v>
       </c>
       <c r="C191">
         <v>2026</v>
@@ -12614,7 +12675,7 @@
         <v>10426361936</v>
       </c>
       <c r="H191" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="I191" t="s">
         <v>451</v>
@@ -12643,7 +12704,7 @@
         <v>397</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>994</v>
+        <v>978</v>
       </c>
       <c r="C192">
         <v>2026</v>
@@ -12661,7 +12722,7 @@
         <v>10238381954</v>
       </c>
       <c r="H192" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="I192" t="s">
         <v>451</v>
@@ -12690,7 +12751,7 @@
         <v>398</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>994</v>
+        <v>978</v>
       </c>
       <c r="C193">
         <v>2026</v>
@@ -12708,7 +12769,7 @@
         <v>10249582862</v>
       </c>
       <c r="H193" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="I193" t="s">
         <v>451</v>
@@ -12737,7 +12798,7 @@
         <v>399</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>986</v>
+        <v>970</v>
       </c>
       <c r="C194">
         <v>2026</v>
@@ -12749,7 +12810,7 @@
         <v>404</v>
       </c>
       <c r="F194" t="s">
-        <v>1042</v>
+        <v>1026</v>
       </c>
       <c r="G194" s="4">
         <v>10102207241</v>
@@ -12764,7 +12825,7 @@
         <v>456</v>
       </c>
       <c r="K194" t="s">
-        <v>1029</v>
+        <v>1013</v>
       </c>
       <c r="L194" t="s">
         <v>88</v>
@@ -12784,7 +12845,7 @@
         <v>400</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>986</v>
+        <v>970</v>
       </c>
       <c r="C195">
         <v>2026</v>
@@ -12811,7 +12872,7 @@
         <v>456</v>
       </c>
       <c r="K195" t="s">
-        <v>1006</v>
+        <v>990</v>
       </c>
       <c r="L195" t="s">
         <v>88</v>
@@ -12831,7 +12892,7 @@
         <v>468</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>986</v>
+        <v>970</v>
       </c>
       <c r="C196">
         <v>2026</v>
@@ -12858,7 +12919,7 @@
         <v>456</v>
       </c>
       <c r="K196" t="s">
-        <v>1006</v>
+        <v>990</v>
       </c>
       <c r="L196" t="s">
         <v>88</v>
@@ -12878,7 +12939,7 @@
         <v>469</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>986</v>
+        <v>970</v>
       </c>
       <c r="C197">
         <v>2026</v>
@@ -12905,7 +12966,7 @@
         <v>454</v>
       </c>
       <c r="K197" t="s">
-        <v>1016</v>
+        <v>1000</v>
       </c>
       <c r="L197" t="s">
         <v>88</v>
@@ -12925,7 +12986,7 @@
         <v>470</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>992</v>
+        <v>976</v>
       </c>
       <c r="C198">
         <v>2026</v>
@@ -12972,7 +13033,7 @@
         <v>471</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>992</v>
+        <v>976</v>
       </c>
       <c r="C199">
         <v>2026</v>
@@ -13019,7 +13080,7 @@
         <v>472</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>991</v>
+        <v>975</v>
       </c>
       <c r="C200">
         <v>2026</v>
@@ -13046,7 +13107,7 @@
         <v>454</v>
       </c>
       <c r="K200" t="s">
-        <v>1005</v>
+        <v>989</v>
       </c>
       <c r="L200" t="s">
         <v>88</v>
@@ -13066,7 +13127,7 @@
         <v>473</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>991</v>
+        <v>975</v>
       </c>
       <c r="C201">
         <v>2026</v>
@@ -13093,7 +13154,7 @@
         <v>456</v>
       </c>
       <c r="K201" t="s">
-        <v>1006</v>
+        <v>990</v>
       </c>
       <c r="L201" t="s">
         <v>88</v>
@@ -13113,7 +13174,7 @@
         <v>474</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>988</v>
+        <v>972</v>
       </c>
       <c r="C202">
         <v>2026</v>
@@ -13140,7 +13201,7 @@
         <v>454</v>
       </c>
       <c r="K202" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
       <c r="L202" t="s">
         <v>88</v>
@@ -13160,7 +13221,7 @@
         <v>475</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>988</v>
+        <v>972</v>
       </c>
       <c r="C203">
         <v>2026</v>
@@ -13187,7 +13248,7 @@
         <v>454</v>
       </c>
       <c r="K203" t="s">
-        <v>1005</v>
+        <v>989</v>
       </c>
       <c r="L203" t="s">
         <v>88</v>
@@ -13207,7 +13268,7 @@
         <v>476</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>988</v>
+        <v>972</v>
       </c>
       <c r="C204">
         <v>2026</v>
@@ -13234,7 +13295,7 @@
         <v>454</v>
       </c>
       <c r="K204" t="s">
-        <v>1017</v>
+        <v>1001</v>
       </c>
       <c r="L204" t="s">
         <v>88</v>
@@ -13254,7 +13315,7 @@
         <v>477</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>988</v>
+        <v>972</v>
       </c>
       <c r="C205">
         <v>2026</v>
@@ -13281,7 +13342,7 @@
         <v>454</v>
       </c>
       <c r="K205" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="L205" t="s">
         <v>88</v>
@@ -13328,7 +13389,7 @@
         <v>454</v>
       </c>
       <c r="K206" t="s">
-        <v>1016</v>
+        <v>1000</v>
       </c>
       <c r="L206" t="s">
         <v>88</v>
@@ -13375,7 +13436,7 @@
         <v>454</v>
       </c>
       <c r="K207" t="s">
-        <v>1035</v>
+        <v>1019</v>
       </c>
       <c r="L207" t="s">
         <v>88</v>
@@ -13422,7 +13483,7 @@
         <v>454</v>
       </c>
       <c r="K208" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
       <c r="L208" t="s">
         <v>88</v>
@@ -13469,7 +13530,7 @@
         <v>455</v>
       </c>
       <c r="K209" t="s">
-        <v>1031</v>
+        <v>1015</v>
       </c>
       <c r="L209" t="s">
         <v>88</v>
@@ -13489,7 +13550,7 @@
         <v>482</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>983</v>
+        <v>967</v>
       </c>
       <c r="C210">
         <v>2026</v>
@@ -13516,7 +13577,7 @@
         <v>454</v>
       </c>
       <c r="K210" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="L210" t="s">
         <v>88</v>
@@ -13563,7 +13624,7 @@
         <v>454</v>
       </c>
       <c r="K211" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
       <c r="L211" t="s">
         <v>88</v>
@@ -13610,7 +13671,7 @@
         <v>454</v>
       </c>
       <c r="K212" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
       <c r="L212" t="s">
         <v>88</v>
@@ -13642,7 +13703,7 @@
         <v>404</v>
       </c>
       <c r="F213" t="s">
-        <v>1041</v>
+        <v>1025</v>
       </c>
       <c r="G213" s="4">
         <v>10240067566</v>
@@ -13657,7 +13718,7 @@
         <v>454</v>
       </c>
       <c r="K213" t="s">
-        <v>1026</v>
+        <v>1010</v>
       </c>
       <c r="L213" t="s">
         <v>88</v>
@@ -13704,7 +13765,7 @@
         <v>454</v>
       </c>
       <c r="K214" t="s">
-        <v>1005</v>
+        <v>989</v>
       </c>
       <c r="L214" t="s">
         <v>88</v>
@@ -13751,7 +13812,7 @@
         <v>454</v>
       </c>
       <c r="K215" t="s">
-        <v>1032</v>
+        <v>1016</v>
       </c>
       <c r="L215" t="s">
         <v>88</v>
@@ -13771,7 +13832,7 @@
         <v>488</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>989</v>
+        <v>973</v>
       </c>
       <c r="C216">
         <v>2026</v>
@@ -13798,7 +13859,7 @@
         <v>454</v>
       </c>
       <c r="K216" t="s">
-        <v>1036</v>
+        <v>1020</v>
       </c>
       <c r="L216" t="s">
         <v>88</v>
@@ -13818,7 +13879,7 @@
         <v>489</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>989</v>
+        <v>973</v>
       </c>
       <c r="C217">
         <v>2026</v>
@@ -13830,7 +13891,7 @@
         <v>404</v>
       </c>
       <c r="F217" t="s">
-        <v>1041</v>
+        <v>1025</v>
       </c>
       <c r="G217" s="4">
         <v>10239510197</v>
@@ -13845,7 +13906,7 @@
         <v>454</v>
       </c>
       <c r="K217" t="s">
-        <v>1027</v>
+        <v>1011</v>
       </c>
       <c r="L217" t="s">
         <v>88</v>
@@ -13865,7 +13926,7 @@
         <v>490</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>989</v>
+        <v>973</v>
       </c>
       <c r="C218">
         <v>2026</v>
@@ -13892,7 +13953,7 @@
         <v>455</v>
       </c>
       <c r="K218" t="s">
-        <v>1030</v>
+        <v>1014</v>
       </c>
       <c r="L218" t="s">
         <v>88</v>
@@ -13939,7 +14000,7 @@
         <v>457</v>
       </c>
       <c r="K219" t="s">
-        <v>1023</v>
+        <v>1007</v>
       </c>
       <c r="L219" t="s">
         <v>88</v>
@@ -13959,7 +14020,7 @@
         <v>492</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="C220">
         <v>2026</v>
@@ -13986,7 +14047,7 @@
         <v>454</v>
       </c>
       <c r="K220" t="s">
-        <v>1005</v>
+        <v>989</v>
       </c>
       <c r="L220" t="s">
         <v>88</v>
@@ -14006,7 +14067,7 @@
         <v>493</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="C221">
         <v>2026</v>
@@ -14033,7 +14094,7 @@
         <v>454</v>
       </c>
       <c r="K221" t="s">
-        <v>1033</v>
+        <v>1017</v>
       </c>
       <c r="L221" t="s">
         <v>88</v>
@@ -23073,3315 +23134,3357 @@
         <v>90</v>
       </c>
     </row>
-    <row r="427" spans="1:14">
-      <c r="A427" t="s">
+    <row r="427" spans="1:14" s="9" customFormat="1">
+      <c r="A427" s="9" t="s">
         <v>835</v>
       </c>
-      <c r="B427" s="4" t="s">
+      <c r="B427" s="10" t="s">
         <v>910</v>
       </c>
-      <c r="C427">
-        <v>2026</v>
-      </c>
-      <c r="D427">
+      <c r="C427" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D427" s="9">
         <v>6</v>
       </c>
-      <c r="E427" t="s">
-        <v>65</v>
-      </c>
-      <c r="F427" t="s">
+      <c r="E427" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F427" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="G427" s="4">
+      <c r="G427" s="10">
         <v>10248794386</v>
       </c>
-      <c r="H427" t="s">
+      <c r="H427" s="9" t="s">
         <v>918</v>
       </c>
-      <c r="I427" t="s">
+      <c r="I427" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="J427" t="s">
+      <c r="J427" s="9" t="s">
         <v>461</v>
       </c>
-      <c r="K427" t="s">
+      <c r="K427" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="L427" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="M427" s="9">
+        <v>1</v>
+      </c>
+      <c r="N427" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="428" spans="1:14" s="9" customFormat="1">
+      <c r="A428" s="9" t="s">
+        <v>836</v>
+      </c>
+      <c r="B428" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="C428" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D428" s="9">
+        <v>6</v>
+      </c>
+      <c r="E428" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F428" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G428" s="10">
+        <v>10768336747</v>
+      </c>
+      <c r="H428" s="9" t="s">
+        <v>919</v>
+      </c>
+      <c r="I428" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J428" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="K428" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="L428" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="M428" s="9">
+        <v>1</v>
+      </c>
+      <c r="N428" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="429" spans="1:14" s="9" customFormat="1">
+      <c r="A429" s="9" t="s">
+        <v>837</v>
+      </c>
+      <c r="B429" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="C429" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D429" s="9">
+        <v>6</v>
+      </c>
+      <c r="E429" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F429" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G429" s="10">
+        <v>10781168772</v>
+      </c>
+      <c r="H429" s="9" t="s">
+        <v>920</v>
+      </c>
+      <c r="I429" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J429" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="K429" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="L429" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="M429" s="9">
+        <v>1</v>
+      </c>
+      <c r="N429" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="430" spans="1:14" s="9" customFormat="1">
+      <c r="A430" s="9" t="s">
+        <v>838</v>
+      </c>
+      <c r="B430" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="C430" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D430" s="9">
+        <v>6</v>
+      </c>
+      <c r="E430" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F430" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G430" s="10">
+        <v>10247103363</v>
+      </c>
+      <c r="H430" s="9" t="s">
+        <v>921</v>
+      </c>
+      <c r="I430" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J430" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="K430" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="L430" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="M430" s="9">
+        <v>1</v>
+      </c>
+      <c r="N430" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="431" spans="1:14" s="9" customFormat="1">
+      <c r="A431" s="9" t="s">
+        <v>839</v>
+      </c>
+      <c r="B431" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="C431" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D431" s="9">
+        <v>6</v>
+      </c>
+      <c r="E431" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F431" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G431" s="10">
+        <v>10748733910</v>
+      </c>
+      <c r="H431" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="I431" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J431" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="K431" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="L431" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="M431" s="9">
+        <v>1</v>
+      </c>
+      <c r="N431" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="432" spans="1:14" s="9" customFormat="1">
+      <c r="A432" s="9" t="s">
+        <v>840</v>
+      </c>
+      <c r="B432" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="C432" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D432" s="9">
+        <v>6</v>
+      </c>
+      <c r="E432" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F432" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G432" s="10">
+        <v>10756599084</v>
+      </c>
+      <c r="H432" s="9" t="s">
+        <v>923</v>
+      </c>
+      <c r="I432" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J432" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="K432" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="L432" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="M432" s="9">
+        <v>1</v>
+      </c>
+      <c r="N432" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="433" spans="1:14" s="9" customFormat="1">
+      <c r="A433" s="9" t="s">
+        <v>841</v>
+      </c>
+      <c r="B433" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="C433" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D433" s="9">
+        <v>6</v>
+      </c>
+      <c r="E433" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F433" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G433" s="10">
+        <v>10409219999</v>
+      </c>
+      <c r="H433" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="I433" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J433" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="K433" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="L433" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="M433" s="9">
+        <v>1</v>
+      </c>
+      <c r="N433" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="434" spans="1:14" s="9" customFormat="1">
+      <c r="A434" s="9" t="s">
+        <v>842</v>
+      </c>
+      <c r="B434" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="C434" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D434" s="9">
+        <v>6</v>
+      </c>
+      <c r="E434" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F434" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G434" s="10">
+        <v>10248714277</v>
+      </c>
+      <c r="H434" s="9" t="s">
+        <v>925</v>
+      </c>
+      <c r="I434" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J434" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="K434" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="L434" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="M434" s="9">
+        <v>1</v>
+      </c>
+      <c r="N434" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="435" spans="1:14" s="9" customFormat="1">
+      <c r="A435" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="B435" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="C435" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D435" s="9">
+        <v>6</v>
+      </c>
+      <c r="E435" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F435" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G435" s="10">
+        <v>10248660908</v>
+      </c>
+      <c r="H435" s="9" t="s">
+        <v>926</v>
+      </c>
+      <c r="I435" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J435" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="K435" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="L435" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="M435" s="9">
+        <v>1</v>
+      </c>
+      <c r="N435" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="436" spans="1:14" s="9" customFormat="1">
+      <c r="A436" s="9" t="s">
+        <v>844</v>
+      </c>
+      <c r="B436" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="C436" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D436" s="9">
+        <v>6</v>
+      </c>
+      <c r="E436" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F436" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G436" s="10">
+        <v>10248900984</v>
+      </c>
+      <c r="H436" s="9" t="s">
+        <v>927</v>
+      </c>
+      <c r="I436" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J436" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="K436" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="L436" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="M436" s="9">
+        <v>1</v>
+      </c>
+      <c r="N436" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="437" spans="1:14" s="9" customFormat="1">
+      <c r="A437" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="B437" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="C437" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D437" s="9">
+        <v>6</v>
+      </c>
+      <c r="E437" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F437" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G437" s="10">
+        <v>10482266130</v>
+      </c>
+      <c r="H437" s="9" t="s">
+        <v>928</v>
+      </c>
+      <c r="I437" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J437" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="K437" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="L437" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="M437" s="9">
+        <v>1</v>
+      </c>
+      <c r="N437" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="438" spans="1:14" s="9" customFormat="1">
+      <c r="A438" s="9" t="s">
+        <v>846</v>
+      </c>
+      <c r="B438" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="C438" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D438" s="9">
+        <v>6</v>
+      </c>
+      <c r="E438" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F438" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G438" s="10">
+        <v>10435553881</v>
+      </c>
+      <c r="H438" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="I438" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J438" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="K438" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="L438" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="M438" s="9">
+        <v>1</v>
+      </c>
+      <c r="N438" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="439" spans="1:14" s="9" customFormat="1">
+      <c r="A439" s="9" t="s">
+        <v>847</v>
+      </c>
+      <c r="B439" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="C439" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D439" s="9">
+        <v>6</v>
+      </c>
+      <c r="E439" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F439" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G439" s="10">
+        <v>10239802821</v>
+      </c>
+      <c r="H439" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I439" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J439" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="K439" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="L439" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="M439" s="9">
+        <v>1</v>
+      </c>
+      <c r="N439" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="440" spans="1:14" s="9" customFormat="1">
+      <c r="A440" s="9" t="s">
+        <v>848</v>
+      </c>
+      <c r="B440" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="C440" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D440" s="9">
+        <v>6</v>
+      </c>
+      <c r="E440" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F440" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G440" s="10">
+        <v>10239106876</v>
+      </c>
+      <c r="H440" s="9" t="s">
+        <v>929</v>
+      </c>
+      <c r="I440" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J440" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="K440" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="L440" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="M440" s="9">
+        <v>1</v>
+      </c>
+      <c r="N440" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="441" spans="1:14" s="9" customFormat="1">
+      <c r="A441" s="9" t="s">
+        <v>849</v>
+      </c>
+      <c r="B441" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="C441" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D441" s="9">
+        <v>6</v>
+      </c>
+      <c r="E441" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F441" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G441" s="10">
+        <v>10238784986</v>
+      </c>
+      <c r="H441" s="9" t="s">
+        <v>930</v>
+      </c>
+      <c r="I441" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J441" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="K441" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="L441" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="M441" s="9">
+        <v>1</v>
+      </c>
+      <c r="N441" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="442" spans="1:14" s="9" customFormat="1">
+      <c r="A442" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="B442" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="C442" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D442" s="9">
+        <v>6</v>
+      </c>
+      <c r="E442" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F442" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G442" s="10">
+        <v>40241978</v>
+      </c>
+      <c r="H442" s="9" t="s">
+        <v>931</v>
+      </c>
+      <c r="I442" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J442" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="K442" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="L442" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="M442" s="9">
+        <v>1</v>
+      </c>
+      <c r="N442" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="443" spans="1:14" s="9" customFormat="1">
+      <c r="A443" s="9" t="s">
+        <v>851</v>
+      </c>
+      <c r="B443" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="C443" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D443" s="9">
+        <v>6</v>
+      </c>
+      <c r="E443" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F443" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G443" s="10">
+        <v>10462678571</v>
+      </c>
+      <c r="H443" s="9" t="s">
+        <v>932</v>
+      </c>
+      <c r="I443" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J443" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="K443" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="L443" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="M443" s="9">
+        <v>1</v>
+      </c>
+      <c r="N443" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="444" spans="1:14" s="9" customFormat="1">
+      <c r="A444" s="9" t="s">
+        <v>852</v>
+      </c>
+      <c r="B444" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="C444" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D444" s="9">
+        <v>6</v>
+      </c>
+      <c r="E444" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F444" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G444" s="10">
+        <v>10092214023</v>
+      </c>
+      <c r="H444" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="I444" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J444" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="K444" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="L444" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="M444" s="9">
+        <v>1</v>
+      </c>
+      <c r="N444" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="445" spans="1:14" s="9" customFormat="1">
+      <c r="A445" s="9" t="s">
+        <v>853</v>
+      </c>
+      <c r="B445" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="C445" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D445" s="9">
+        <v>6</v>
+      </c>
+      <c r="E445" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F445" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G445" s="10">
+        <v>42421067</v>
+      </c>
+      <c r="H445" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="I445" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J445" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="K445" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="L445" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="M445" s="9">
+        <v>1</v>
+      </c>
+      <c r="N445" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="446" spans="1:14" s="9" customFormat="1">
+      <c r="A446" s="9" t="s">
+        <v>854</v>
+      </c>
+      <c r="B446" s="10" t="s">
+        <v>915</v>
+      </c>
+      <c r="C446" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D446" s="9">
+        <v>6</v>
+      </c>
+      <c r="E446" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F446" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G446" s="11">
+        <v>24889807</v>
+      </c>
+      <c r="H446" s="9" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I446" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J446" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K446" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L446" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M446" s="9">
+        <v>1</v>
+      </c>
+      <c r="N446" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="447" spans="1:14" s="9" customFormat="1">
+      <c r="A447" s="9" t="s">
+        <v>855</v>
+      </c>
+      <c r="B447" s="10" t="s">
+        <v>915</v>
+      </c>
+      <c r="C447" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D447" s="9">
+        <v>6</v>
+      </c>
+      <c r="E447" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F447" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G447" s="11">
+        <v>24888829</v>
+      </c>
+      <c r="H447" s="9" t="s">
+        <v>1036</v>
+      </c>
+      <c r="I447" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J447" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K447" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L447" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M447" s="9">
+        <v>1</v>
+      </c>
+      <c r="N447" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="448" spans="1:14" s="9" customFormat="1">
+      <c r="A448" s="9" t="s">
+        <v>856</v>
+      </c>
+      <c r="B448" s="10" t="s">
+        <v>915</v>
+      </c>
+      <c r="C448" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D448" s="9">
+        <v>6</v>
+      </c>
+      <c r="E448" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F448" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G448" s="11">
+        <v>10443205573</v>
+      </c>
+      <c r="H448" s="9" t="s">
+        <v>1037</v>
+      </c>
+      <c r="I448" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J448" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K448" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L448" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M448" s="9">
+        <v>1</v>
+      </c>
+      <c r="N448" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="449" spans="1:14" s="9" customFormat="1">
+      <c r="A449" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="B449" s="10" t="s">
+        <v>915</v>
+      </c>
+      <c r="C449" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D449" s="9">
+        <v>6</v>
+      </c>
+      <c r="E449" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F449" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G449" s="11">
+        <v>24884182</v>
+      </c>
+      <c r="H449" s="9" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I449" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J449" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K449" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L449" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M449" s="9">
+        <v>1</v>
+      </c>
+      <c r="N449" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="450" spans="1:14" s="9" customFormat="1">
+      <c r="A450" s="9" t="s">
+        <v>858</v>
+      </c>
+      <c r="B450" s="10" t="s">
+        <v>915</v>
+      </c>
+      <c r="C450" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D450" s="9">
+        <v>6</v>
+      </c>
+      <c r="E450" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F450" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G450" s="11">
+        <v>10248670075</v>
+      </c>
+      <c r="H450" s="9" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I450" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J450" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K450" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L450" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M450" s="9">
+        <v>1</v>
+      </c>
+      <c r="N450" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="451" spans="1:14" s="9" customFormat="1">
+      <c r="A451" s="9" t="s">
+        <v>859</v>
+      </c>
+      <c r="B451" s="10" t="s">
+        <v>915</v>
+      </c>
+      <c r="C451" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D451" s="9">
+        <v>6</v>
+      </c>
+      <c r="E451" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F451" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G451" s="11">
+        <v>40289959</v>
+      </c>
+      <c r="H451" s="9" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I451" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J451" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K451" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L451" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M451" s="9">
+        <v>1</v>
+      </c>
+      <c r="N451" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="452" spans="1:14" s="9" customFormat="1">
+      <c r="A452" s="9" t="s">
+        <v>860</v>
+      </c>
+      <c r="B452" s="10" t="s">
+        <v>915</v>
+      </c>
+      <c r="C452" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D452" s="9">
+        <v>6</v>
+      </c>
+      <c r="E452" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F452" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G452" s="11">
+        <v>10402988121</v>
+      </c>
+      <c r="H452" s="9" t="s">
+        <v>1041</v>
+      </c>
+      <c r="I452" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J452" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K452" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L452" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M452" s="9">
+        <v>1</v>
+      </c>
+      <c r="N452" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="453" spans="1:14" s="9" customFormat="1">
+      <c r="A453" s="9" t="s">
+        <v>861</v>
+      </c>
+      <c r="B453" s="10" t="s">
+        <v>915</v>
+      </c>
+      <c r="C453" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D453" s="9">
+        <v>6</v>
+      </c>
+      <c r="E453" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F453" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G453" s="11">
+        <v>10473551549</v>
+      </c>
+      <c r="H453" s="9" t="s">
+        <v>1042</v>
+      </c>
+      <c r="I453" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J453" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K453" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L453" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M453" s="9">
+        <v>1</v>
+      </c>
+      <c r="N453" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="454" spans="1:14" s="9" customFormat="1">
+      <c r="A454" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="B454" s="10" t="s">
+        <v>915</v>
+      </c>
+      <c r="C454" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D454" s="9">
+        <v>6</v>
+      </c>
+      <c r="E454" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F454" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G454" s="11">
+        <v>10408822641</v>
+      </c>
+      <c r="H454" s="9" t="s">
+        <v>1043</v>
+      </c>
+      <c r="I454" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J454" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K454" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L454" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M454" s="9">
+        <v>1</v>
+      </c>
+      <c r="N454" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="455" spans="1:14" s="9" customFormat="1">
+      <c r="A455" s="9" t="s">
+        <v>863</v>
+      </c>
+      <c r="B455" s="10" t="s">
+        <v>915</v>
+      </c>
+      <c r="C455" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D455" s="9">
+        <v>6</v>
+      </c>
+      <c r="E455" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F455" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G455" s="11">
+        <v>10446727180</v>
+      </c>
+      <c r="H455" s="9" t="s">
+        <v>1044</v>
+      </c>
+      <c r="I455" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J455" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K455" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L455" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M455" s="9">
+        <v>1</v>
+      </c>
+      <c r="N455" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="456" spans="1:14" s="9" customFormat="1">
+      <c r="A456" s="9" t="s">
+        <v>864</v>
+      </c>
+      <c r="B456" s="10" t="s">
+        <v>915</v>
+      </c>
+      <c r="C456" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D456" s="9">
+        <v>6</v>
+      </c>
+      <c r="E456" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F456" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G456" s="11">
+        <v>72198395</v>
+      </c>
+      <c r="H456" s="9" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I456" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J456" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K456" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L456" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M456" s="9">
+        <v>1</v>
+      </c>
+      <c r="N456" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="457" spans="1:14" s="9" customFormat="1">
+      <c r="A457" s="9" t="s">
+        <v>865</v>
+      </c>
+      <c r="B457" s="10" t="s">
+        <v>915</v>
+      </c>
+      <c r="C457" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D457" s="9">
+        <v>6</v>
+      </c>
+      <c r="E457" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F457" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G457" s="11">
+        <v>10411675179</v>
+      </c>
+      <c r="H457" s="9" t="s">
+        <v>1046</v>
+      </c>
+      <c r="I457" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J457" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K457" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L457" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M457" s="9">
+        <v>1</v>
+      </c>
+      <c r="N457" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="458" spans="1:14" s="9" customFormat="1">
+      <c r="A458" s="9" t="s">
+        <v>866</v>
+      </c>
+      <c r="B458" s="10" t="s">
+        <v>915</v>
+      </c>
+      <c r="C458" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D458" s="9">
+        <v>6</v>
+      </c>
+      <c r="E458" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F458" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G458" s="11">
+        <v>25017176</v>
+      </c>
+      <c r="H458" s="9" t="s">
+        <v>1047</v>
+      </c>
+      <c r="I458" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J458" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K458" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L458" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M458" s="9">
+        <v>1</v>
+      </c>
+      <c r="N458" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="459" spans="1:14" s="9" customFormat="1">
+      <c r="A459" s="9" t="s">
+        <v>867</v>
+      </c>
+      <c r="B459" s="10" t="s">
+        <v>915</v>
+      </c>
+      <c r="C459" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D459" s="9">
+        <v>6</v>
+      </c>
+      <c r="E459" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F459" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G459" s="11">
+        <v>24895254</v>
+      </c>
+      <c r="H459" s="9" t="s">
+        <v>1048</v>
+      </c>
+      <c r="I459" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J459" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K459" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L459" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M459" s="9">
+        <v>1</v>
+      </c>
+      <c r="N459" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="460" spans="1:14" s="9" customFormat="1">
+      <c r="A460" s="9" t="s">
+        <v>868</v>
+      </c>
+      <c r="B460" s="10" t="s">
+        <v>915</v>
+      </c>
+      <c r="C460" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D460" s="9">
+        <v>6</v>
+      </c>
+      <c r="E460" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F460" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G460" s="11">
+        <v>43799579</v>
+      </c>
+      <c r="H460" s="9" t="s">
+        <v>1049</v>
+      </c>
+      <c r="I460" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J460" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K460" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L460" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M460" s="9">
+        <v>1</v>
+      </c>
+      <c r="N460" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="461" spans="1:14" s="9" customFormat="1">
+      <c r="A461" s="9" t="s">
+        <v>869</v>
+      </c>
+      <c r="B461" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="C461" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D461" s="9">
+        <v>6</v>
+      </c>
+      <c r="E461" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F461" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G461" s="11">
+        <v>10450876700</v>
+      </c>
+      <c r="H461" s="9" t="s">
+        <v>943</v>
+      </c>
+      <c r="I461" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J461" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K461" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L461" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M461" s="9">
+        <v>1</v>
+      </c>
+      <c r="N461" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="462" spans="1:14" s="9" customFormat="1">
+      <c r="A462" s="9" t="s">
+        <v>870</v>
+      </c>
+      <c r="B462" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="C462" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D462" s="9">
+        <v>6</v>
+      </c>
+      <c r="E462" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F462" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G462" s="11">
+        <v>10476142941</v>
+      </c>
+      <c r="H462" s="9" t="s">
+        <v>944</v>
+      </c>
+      <c r="I462" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J462" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K462" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L462" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M462" s="9">
+        <v>1</v>
+      </c>
+      <c r="N462" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="463" spans="1:14" s="9" customFormat="1">
+      <c r="A463" s="9" t="s">
+        <v>871</v>
+      </c>
+      <c r="B463" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="C463" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D463" s="9">
+        <v>6</v>
+      </c>
+      <c r="E463" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F463" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G463" s="11">
+        <v>10454316903</v>
+      </c>
+      <c r="H463" s="9" t="s">
+        <v>945</v>
+      </c>
+      <c r="I463" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J463" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K463" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L463" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M463" s="9">
+        <v>1</v>
+      </c>
+      <c r="N463" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="464" spans="1:14" s="9" customFormat="1">
+      <c r="A464" s="9" t="s">
+        <v>872</v>
+      </c>
+      <c r="B464" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="C464" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D464" s="9">
+        <v>6</v>
+      </c>
+      <c r="E464" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F464" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G464" s="11">
+        <v>10456258536</v>
+      </c>
+      <c r="H464" s="9" t="s">
+        <v>946</v>
+      </c>
+      <c r="I464" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J464" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K464" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L464" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M464" s="12">
+        <v>1</v>
+      </c>
+      <c r="N464" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="465" spans="1:14" s="9" customFormat="1">
+      <c r="A465" s="9" t="s">
+        <v>873</v>
+      </c>
+      <c r="B465" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="C465" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D465" s="9">
+        <v>6</v>
+      </c>
+      <c r="E465" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F465" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G465" s="11">
+        <v>10462583996</v>
+      </c>
+      <c r="H465" s="9" t="s">
+        <v>947</v>
+      </c>
+      <c r="I465" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J465" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K465" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L465" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M465" s="12">
+        <v>1</v>
+      </c>
+      <c r="N465" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="466" spans="1:14" s="9" customFormat="1">
+      <c r="A466" s="9" t="s">
+        <v>874</v>
+      </c>
+      <c r="B466" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="C466" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D466" s="9">
+        <v>6</v>
+      </c>
+      <c r="E466" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F466" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G466" s="11">
+        <v>46314028</v>
+      </c>
+      <c r="H466" s="9" t="s">
+        <v>948</v>
+      </c>
+      <c r="I466" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J466" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K466" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L466" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M466" s="12">
+        <v>1</v>
+      </c>
+      <c r="N466" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="467" spans="1:14" s="9" customFormat="1">
+      <c r="A467" s="9" t="s">
+        <v>875</v>
+      </c>
+      <c r="B467" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="C467" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D467" s="9">
+        <v>6</v>
+      </c>
+      <c r="E467" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F467" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G467" s="11">
+        <v>43150763</v>
+      </c>
+      <c r="H467" s="9" t="s">
+        <v>949</v>
+      </c>
+      <c r="I467" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J467" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K467" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L467" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M467" s="12">
+        <v>1</v>
+      </c>
+      <c r="N467" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="468" spans="1:14" s="9" customFormat="1">
+      <c r="A468" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="B468" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="C468" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D468" s="9">
+        <v>6</v>
+      </c>
+      <c r="E468" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F468" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G468" s="11">
+        <v>42566234</v>
+      </c>
+      <c r="H468" s="9" t="s">
+        <v>950</v>
+      </c>
+      <c r="I468" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J468" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K468" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L468" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M468" s="12">
+        <v>1</v>
+      </c>
+      <c r="N468" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="469" spans="1:14" s="9" customFormat="1">
+      <c r="A469" s="9" t="s">
+        <v>877</v>
+      </c>
+      <c r="B469" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="C469" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D469" s="9">
+        <v>6</v>
+      </c>
+      <c r="E469" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F469" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G469" s="11">
+        <v>40040306</v>
+      </c>
+      <c r="H469" s="9" t="s">
+        <v>951</v>
+      </c>
+      <c r="I469" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J469" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K469" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L469" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M469" s="12">
+        <v>1</v>
+      </c>
+      <c r="N469" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="470" spans="1:14" s="9" customFormat="1">
+      <c r="A470" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="B470" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="C470" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D470" s="9">
+        <v>6</v>
+      </c>
+      <c r="E470" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F470" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G470" s="11">
+        <v>73870421</v>
+      </c>
+      <c r="H470" s="9" t="s">
+        <v>952</v>
+      </c>
+      <c r="I470" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J470" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K470" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L470" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M470" s="12">
+        <v>1</v>
+      </c>
+      <c r="N470" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="471" spans="1:14" s="9" customFormat="1">
+      <c r="A471" s="9" t="s">
+        <v>879</v>
+      </c>
+      <c r="B471" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="C471" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D471" s="9">
+        <v>6</v>
+      </c>
+      <c r="E471" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F471" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G471" s="11">
+        <v>24873839</v>
+      </c>
+      <c r="H471" s="9" t="s">
+        <v>953</v>
+      </c>
+      <c r="I471" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J471" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K471" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L471" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M471" s="12">
+        <v>1</v>
+      </c>
+      <c r="N471" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="472" spans="1:14" s="9" customFormat="1">
+      <c r="A472" s="9" t="s">
+        <v>880</v>
+      </c>
+      <c r="B472" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="C472" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D472" s="9">
+        <v>6</v>
+      </c>
+      <c r="E472" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F472" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G472" s="11">
+        <v>47656632</v>
+      </c>
+      <c r="H472" s="9" t="s">
+        <v>954</v>
+      </c>
+      <c r="I472" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J472" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K472" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L472" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M472" s="12">
+        <v>1</v>
+      </c>
+      <c r="N472" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="473" spans="1:14" s="9" customFormat="1">
+      <c r="A473" s="9" t="s">
+        <v>881</v>
+      </c>
+      <c r="B473" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="C473" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D473" s="9">
+        <v>6</v>
+      </c>
+      <c r="E473" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F473" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G473" s="11">
+        <v>47925279</v>
+      </c>
+      <c r="H473" s="9" t="s">
+        <v>955</v>
+      </c>
+      <c r="I473" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J473" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K473" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L473" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M473" s="12">
+        <v>1</v>
+      </c>
+      <c r="N473" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="474" spans="1:14" s="9" customFormat="1">
+      <c r="A474" s="9" t="s">
+        <v>882</v>
+      </c>
+      <c r="B474" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="C474" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D474" s="9">
+        <v>6</v>
+      </c>
+      <c r="E474" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F474" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G474" s="11">
+        <v>46474063</v>
+      </c>
+      <c r="H474" s="9" t="s">
+        <v>956</v>
+      </c>
+      <c r="I474" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J474" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K474" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L474" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M474" s="12">
+        <v>1</v>
+      </c>
+      <c r="N474" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="475" spans="1:14" s="9" customFormat="1">
+      <c r="A475" s="9" t="s">
+        <v>883</v>
+      </c>
+      <c r="B475" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="C475" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D475" s="9">
+        <v>6</v>
+      </c>
+      <c r="E475" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F475" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G475" s="11">
+        <v>42049412</v>
+      </c>
+      <c r="H475" s="9" t="s">
+        <v>957</v>
+      </c>
+      <c r="I475" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J475" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K475" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="L475" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M475" s="12">
+        <v>1</v>
+      </c>
+      <c r="N475" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="476" spans="1:14" s="9" customFormat="1">
+      <c r="A476" s="9" t="s">
+        <v>884</v>
+      </c>
+      <c r="B476" s="10" t="s">
+        <v>911</v>
+      </c>
+      <c r="C476" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D476" s="9">
+        <v>6</v>
+      </c>
+      <c r="E476" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F476" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G476" s="11">
+        <v>23922343</v>
+      </c>
+      <c r="H476" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="I476" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="J476" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="K476" s="9" t="s">
+        <v>959</v>
+      </c>
+      <c r="M476" s="13">
+        <v>1</v>
+      </c>
+      <c r="N476" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="477" spans="1:14" s="9" customFormat="1">
+      <c r="A477" s="9" t="s">
+        <v>885</v>
+      </c>
+      <c r="B477" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="C477" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D477" s="9">
+        <v>6</v>
+      </c>
+      <c r="E477" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F477" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G477" s="11">
+        <v>10238869094</v>
+      </c>
+      <c r="H477" s="9" t="s">
+        <v>935</v>
+      </c>
+      <c r="I477" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="J477" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="K477" s="9" t="s">
+        <v>960</v>
+      </c>
+      <c r="M477" s="13">
+        <v>4</v>
+      </c>
+      <c r="N477" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="478" spans="1:14" s="9" customFormat="1">
+      <c r="A478" s="9" t="s">
+        <v>886</v>
+      </c>
+      <c r="B478" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="C478" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D478" s="9">
+        <v>6</v>
+      </c>
+      <c r="E478" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F478" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G478" s="11">
+        <v>10247032270</v>
+      </c>
+      <c r="H478" s="9" t="s">
+        <v>936</v>
+      </c>
+      <c r="I478" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="J478" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="K478" s="9" t="s">
+        <v>961</v>
+      </c>
+      <c r="M478" s="13">
+        <v>4</v>
+      </c>
+      <c r="N478" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="479" spans="1:14" s="9" customFormat="1">
+      <c r="A479" s="9" t="s">
+        <v>887</v>
+      </c>
+      <c r="B479" s="10" t="s">
+        <v>917</v>
+      </c>
+      <c r="C479" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D479" s="9">
+        <v>6</v>
+      </c>
+      <c r="E479" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F479" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G479" s="11">
+        <v>10252188041</v>
+      </c>
+      <c r="H479" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="I479" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="J479" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="K479" s="9" t="s">
+        <v>963</v>
+      </c>
+      <c r="M479" s="14">
+        <v>324</v>
+      </c>
+      <c r="N479" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="480" spans="1:14" s="9" customFormat="1">
+      <c r="A480" s="9" t="s">
+        <v>888</v>
+      </c>
+      <c r="B480" s="10" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C480" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D480" s="9">
+        <v>6</v>
+      </c>
+      <c r="E480" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F480" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G480" s="11">
+        <v>20172474501</v>
+      </c>
+      <c r="H480" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="I480" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J480" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="K480" s="9" t="s">
+        <v>1029</v>
+      </c>
+      <c r="M480" s="9">
+        <v>1</v>
+      </c>
+      <c r="N480" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="481" spans="1:14" s="9" customFormat="1">
+      <c r="A481" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="B481" s="10" t="s">
         <v>972</v>
       </c>
-      <c r="L427" t="s">
-        <v>297</v>
-      </c>
-      <c r="M427">
-        <v>1</v>
-      </c>
-      <c r="N427" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="428" spans="1:14">
-      <c r="A428" t="s">
-        <v>836</v>
-      </c>
-      <c r="B428" s="4" t="s">
-        <v>910</v>
-      </c>
-      <c r="C428">
-        <v>2026</v>
-      </c>
-      <c r="D428">
+      <c r="C481" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D481" s="9">
         <v>6</v>
       </c>
-      <c r="E428" t="s">
-        <v>65</v>
-      </c>
-      <c r="F428" t="s">
-        <v>402</v>
-      </c>
-      <c r="G428" s="4">
-        <v>10768336747</v>
-      </c>
-      <c r="H428" t="s">
-        <v>919</v>
-      </c>
-      <c r="I428" t="s">
+      <c r="E481" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F481" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G481" s="11">
+        <v>20155945860</v>
+      </c>
+      <c r="H481" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="I481" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J481" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="K481" s="9" t="s">
+        <v>1050</v>
+      </c>
+      <c r="M481" s="9">
+        <v>1</v>
+      </c>
+      <c r="N481" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="482" spans="1:14" s="9" customFormat="1">
+      <c r="A482" s="9" t="s">
+        <v>890</v>
+      </c>
+      <c r="B482" s="10" t="s">
+        <v>972</v>
+      </c>
+      <c r="C482" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D482" s="9">
+        <v>6</v>
+      </c>
+      <c r="E482" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F482" s="9" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G482" s="11">
+        <v>20172474501</v>
+      </c>
+      <c r="H482" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="I482" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J482" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="K482" s="9" t="s">
+        <v>1051</v>
+      </c>
+      <c r="M482" s="9">
+        <v>1</v>
+      </c>
+      <c r="N482" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="483" spans="1:14" s="9" customFormat="1">
+      <c r="A483" s="9" t="s">
+        <v>891</v>
+      </c>
+      <c r="B483" s="10" t="s">
+        <v>911</v>
+      </c>
+      <c r="C483" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D483" s="9">
+        <v>6</v>
+      </c>
+      <c r="E483" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F483" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G483" s="11">
+        <v>73622059</v>
+      </c>
+      <c r="H483" s="9" t="s">
+        <v>1034</v>
+      </c>
+      <c r="I483" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J483" s="9" t="s">
+        <v>1056</v>
+      </c>
+      <c r="K483" s="9" t="s">
+        <v>1030</v>
+      </c>
+      <c r="M483" s="9">
+        <v>1</v>
+      </c>
+      <c r="N483" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="484" spans="1:14" s="9" customFormat="1">
+      <c r="A484" s="9" t="s">
+        <v>892</v>
+      </c>
+      <c r="B484" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="C484" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D484" s="9">
+        <v>6</v>
+      </c>
+      <c r="E484" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F484" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G484" s="11">
+        <v>20610561005</v>
+      </c>
+      <c r="H484" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="I484" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J484" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="K484" s="9" t="s">
+        <v>1031</v>
+      </c>
+      <c r="M484" s="9">
+        <v>1</v>
+      </c>
+      <c r="N484" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="485" spans="1:14" s="9" customFormat="1">
+      <c r="A485" s="9" t="s">
+        <v>893</v>
+      </c>
+      <c r="B485" s="10" t="s">
+        <v>911</v>
+      </c>
+      <c r="C485" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D485" s="9">
+        <v>6</v>
+      </c>
+      <c r="E485" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F485" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G485" s="11">
+        <v>10700937645</v>
+      </c>
+      <c r="H485" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I485" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J485" s="9" t="s">
+        <v>1056</v>
+      </c>
+      <c r="K485" s="9" t="s">
+        <v>1032</v>
+      </c>
+      <c r="M485" s="9">
+        <v>1</v>
+      </c>
+      <c r="N485" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="486" spans="1:14" s="9" customFormat="1">
+      <c r="A486" s="9" t="s">
+        <v>894</v>
+      </c>
+      <c r="B486" s="15" t="s">
+        <v>912</v>
+      </c>
+      <c r="C486" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D486" s="9">
+        <v>6</v>
+      </c>
+      <c r="E486" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F486" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G486" s="11">
+        <v>10742273674</v>
+      </c>
+      <c r="H486" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I486" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J486" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="K486" s="9" t="s">
+        <v>1052</v>
+      </c>
+      <c r="M486" s="9">
+        <v>1</v>
+      </c>
+      <c r="N486" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="487" spans="1:14" s="9" customFormat="1">
+      <c r="A487" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="B487" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="C487" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D487" s="9">
+        <v>6</v>
+      </c>
+      <c r="E487" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F487" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G487" s="11">
+        <v>40927397</v>
+      </c>
+      <c r="H487" s="9" t="s">
+        <v>1057</v>
+      </c>
+      <c r="I487" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J487" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="K487" s="9" t="s">
+        <v>1053</v>
+      </c>
+      <c r="M487" s="9">
+        <v>1</v>
+      </c>
+      <c r="N487" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="488" spans="1:14" s="9" customFormat="1">
+      <c r="A488" s="9" t="s">
+        <v>896</v>
+      </c>
+      <c r="B488" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="C488" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D488" s="9">
+        <v>6</v>
+      </c>
+      <c r="E488" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F488" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G488" s="11">
+        <v>10239510197</v>
+      </c>
+      <c r="H488" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="I488" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J488" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="K488" s="9" t="s">
+        <v>1054</v>
+      </c>
+      <c r="M488" s="9">
+        <v>1</v>
+      </c>
+      <c r="N488" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="489" spans="1:14" s="9" customFormat="1">
+      <c r="A489" s="9" t="s">
+        <v>897</v>
+      </c>
+      <c r="B489" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="C489" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D489" s="9">
+        <v>6</v>
+      </c>
+      <c r="E489" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F489" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G489" s="11">
+        <v>47388875</v>
+      </c>
+      <c r="H489" s="9" t="s">
+        <v>1058</v>
+      </c>
+      <c r="I489" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J489" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="K489" s="9" t="s">
+        <v>1055</v>
+      </c>
+      <c r="M489" s="9">
+        <v>1</v>
+      </c>
+      <c r="N489" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="490" spans="1:14" s="9" customFormat="1">
+      <c r="A490" s="9" t="s">
+        <v>898</v>
+      </c>
+      <c r="B490" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="C490" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D490" s="9">
+        <v>6</v>
+      </c>
+      <c r="E490" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F490" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="G490" s="11">
+        <v>74912836</v>
+      </c>
+      <c r="H490" s="9" t="s">
+        <v>1061</v>
+      </c>
+      <c r="I490" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="J428" t="s">
-        <v>461</v>
-      </c>
-      <c r="K428" t="s">
-        <v>972</v>
-      </c>
-      <c r="L428" t="s">
-        <v>297</v>
-      </c>
-      <c r="M428">
-        <v>1</v>
-      </c>
-      <c r="N428" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="429" spans="1:14">
-      <c r="A429" t="s">
-        <v>837</v>
-      </c>
-      <c r="B429" s="4" t="s">
-        <v>910</v>
-      </c>
-      <c r="C429">
-        <v>2026</v>
-      </c>
-      <c r="D429">
+      <c r="J490" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K490" s="9" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M490" s="9">
+        <v>1</v>
+      </c>
+      <c r="N490" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="491" spans="1:14" s="9" customFormat="1">
+      <c r="A491" s="9" t="s">
+        <v>899</v>
+      </c>
+      <c r="B491" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="C491" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D491" s="9">
         <v>6</v>
       </c>
-      <c r="E429" t="s">
-        <v>65</v>
-      </c>
-      <c r="F429" t="s">
-        <v>402</v>
-      </c>
-      <c r="G429" s="4">
-        <v>10781168772</v>
-      </c>
-      <c r="H429" t="s">
-        <v>920</v>
-      </c>
-      <c r="I429" t="s">
+      <c r="E491" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F491" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="G491" s="11">
+        <v>75817101</v>
+      </c>
+      <c r="H491" s="9" t="s">
+        <v>1062</v>
+      </c>
+      <c r="I491" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="J429" t="s">
-        <v>461</v>
-      </c>
-      <c r="K429" t="s">
-        <v>972</v>
-      </c>
-      <c r="L429" t="s">
-        <v>297</v>
-      </c>
-      <c r="M429">
-        <v>1</v>
-      </c>
-      <c r="N429" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="430" spans="1:14">
-      <c r="A430" t="s">
-        <v>838</v>
-      </c>
-      <c r="B430" s="4" t="s">
-        <v>910</v>
-      </c>
-      <c r="C430">
-        <v>2026</v>
-      </c>
-      <c r="D430">
+      <c r="J491" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K491" s="9" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M491" s="9">
+        <v>1</v>
+      </c>
+      <c r="N491" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="492" spans="1:14" s="9" customFormat="1">
+      <c r="A492" s="9" t="s">
+        <v>900</v>
+      </c>
+      <c r="B492" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="C492" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D492" s="9">
         <v>6</v>
       </c>
-      <c r="E430" t="s">
-        <v>65</v>
-      </c>
-      <c r="F430" t="s">
-        <v>402</v>
-      </c>
-      <c r="G430" s="4">
-        <v>10247103363</v>
-      </c>
-      <c r="H430" t="s">
-        <v>921</v>
-      </c>
-      <c r="I430" t="s">
+      <c r="E492" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F492" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="G492" s="11">
+        <v>77488158</v>
+      </c>
+      <c r="H492" s="9" t="s">
+        <v>1063</v>
+      </c>
+      <c r="I492" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="J430" t="s">
-        <v>461</v>
-      </c>
-      <c r="K430" t="s">
-        <v>972</v>
-      </c>
-      <c r="L430" t="s">
-        <v>297</v>
-      </c>
-      <c r="M430">
-        <v>1</v>
-      </c>
-      <c r="N430" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="431" spans="1:14">
-      <c r="A431" t="s">
-        <v>839</v>
-      </c>
-      <c r="B431" s="4" t="s">
-        <v>910</v>
-      </c>
-      <c r="C431">
-        <v>2026</v>
-      </c>
-      <c r="D431">
+      <c r="J492" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K492" s="9" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M492" s="9">
+        <v>1</v>
+      </c>
+      <c r="N492" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="493" spans="1:14" s="9" customFormat="1">
+      <c r="A493" s="9" t="s">
+        <v>901</v>
+      </c>
+      <c r="B493" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="C493" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D493" s="9">
         <v>6</v>
       </c>
-      <c r="E431" t="s">
-        <v>65</v>
-      </c>
-      <c r="F431" t="s">
-        <v>402</v>
-      </c>
-      <c r="G431" s="4">
-        <v>10748733910</v>
-      </c>
-      <c r="H431" t="s">
-        <v>922</v>
-      </c>
-      <c r="I431" t="s">
+      <c r="E493" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F493" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="G493" s="11">
+        <v>10022969205</v>
+      </c>
+      <c r="H493" s="9" t="s">
+        <v>1064</v>
+      </c>
+      <c r="I493" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="J431" t="s">
-        <v>461</v>
-      </c>
-      <c r="K431" t="s">
-        <v>972</v>
-      </c>
-      <c r="L431" t="s">
-        <v>297</v>
-      </c>
-      <c r="M431">
-        <v>1</v>
-      </c>
-      <c r="N431" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="432" spans="1:14">
-      <c r="A432" t="s">
-        <v>840</v>
-      </c>
-      <c r="B432" s="4" t="s">
-        <v>910</v>
-      </c>
-      <c r="C432">
-        <v>2026</v>
-      </c>
-      <c r="D432">
+      <c r="J493" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K493" s="9" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M493" s="9">
+        <v>1</v>
+      </c>
+      <c r="N493" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="494" spans="1:14" s="9" customFormat="1">
+      <c r="A494" s="9" t="s">
+        <v>902</v>
+      </c>
+      <c r="B494" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="C494" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D494" s="9">
         <v>6</v>
       </c>
-      <c r="E432" t="s">
-        <v>65</v>
-      </c>
-      <c r="F432" t="s">
-        <v>402</v>
-      </c>
-      <c r="G432" s="4">
-        <v>10756599084</v>
-      </c>
-      <c r="H432" t="s">
-        <v>923</v>
-      </c>
-      <c r="I432" t="s">
+      <c r="E494" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F494" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="G494" s="11">
+        <v>10466632061</v>
+      </c>
+      <c r="H494" s="9" t="s">
+        <v>1065</v>
+      </c>
+      <c r="I494" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="J432" t="s">
-        <v>461</v>
-      </c>
-      <c r="K432" t="s">
-        <v>972</v>
-      </c>
-      <c r="L432" t="s">
-        <v>297</v>
-      </c>
-      <c r="M432">
-        <v>1</v>
-      </c>
-      <c r="N432" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="433" spans="1:14">
-      <c r="A433" t="s">
-        <v>841</v>
-      </c>
-      <c r="B433" s="4" t="s">
-        <v>910</v>
-      </c>
-      <c r="C433">
-        <v>2026</v>
-      </c>
-      <c r="D433">
+      <c r="J494" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K494" s="9" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M494" s="9">
+        <v>1</v>
+      </c>
+      <c r="N494" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="495" spans="1:14" s="9" customFormat="1">
+      <c r="A495" s="9" t="s">
+        <v>903</v>
+      </c>
+      <c r="B495" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="C495" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D495" s="9">
         <v>6</v>
       </c>
-      <c r="E433" t="s">
-        <v>65</v>
-      </c>
-      <c r="F433" t="s">
-        <v>402</v>
-      </c>
-      <c r="G433" s="4">
-        <v>10409219999</v>
-      </c>
-      <c r="H433" t="s">
-        <v>924</v>
-      </c>
-      <c r="I433" t="s">
+      <c r="E495" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F495" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="G495" s="11">
+        <v>10478248275</v>
+      </c>
+      <c r="H495" s="9" t="s">
+        <v>1066</v>
+      </c>
+      <c r="I495" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="J433" t="s">
-        <v>461</v>
-      </c>
-      <c r="K433" t="s">
-        <v>972</v>
-      </c>
-      <c r="L433" t="s">
-        <v>297</v>
-      </c>
-      <c r="M433">
-        <v>1</v>
-      </c>
-      <c r="N433" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="434" spans="1:14">
-      <c r="A434" t="s">
-        <v>842</v>
-      </c>
-      <c r="B434" s="4" t="s">
-        <v>910</v>
-      </c>
-      <c r="C434">
-        <v>2026</v>
-      </c>
-      <c r="D434">
+      <c r="J495" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K495" s="9" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M495" s="9">
+        <v>1</v>
+      </c>
+      <c r="N495" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="496" spans="1:14" s="9" customFormat="1">
+      <c r="A496" s="9" t="s">
+        <v>904</v>
+      </c>
+      <c r="B496" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="C496" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D496" s="9">
         <v>6</v>
       </c>
-      <c r="E434" t="s">
-        <v>65</v>
-      </c>
-      <c r="F434" t="s">
-        <v>402</v>
-      </c>
-      <c r="G434" s="4">
-        <v>10248714277</v>
-      </c>
-      <c r="H434" t="s">
-        <v>925</v>
-      </c>
-      <c r="I434" t="s">
+      <c r="E496" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F496" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="G496" s="11">
+        <v>10709149062</v>
+      </c>
+      <c r="H496" s="9" t="s">
+        <v>1067</v>
+      </c>
+      <c r="I496" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="J434" t="s">
-        <v>461</v>
-      </c>
-      <c r="K434" t="s">
-        <v>972</v>
-      </c>
-      <c r="L434" t="s">
-        <v>297</v>
-      </c>
-      <c r="M434">
-        <v>1</v>
-      </c>
-      <c r="N434" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="435" spans="1:14">
-      <c r="A435" t="s">
-        <v>843</v>
-      </c>
-      <c r="B435" s="4" t="s">
-        <v>910</v>
-      </c>
-      <c r="C435">
-        <v>2026</v>
-      </c>
-      <c r="D435">
+      <c r="J496" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K496" s="9" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M496" s="9">
+        <v>1</v>
+      </c>
+      <c r="N496" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="497" spans="1:14" s="9" customFormat="1">
+      <c r="A497" s="9" t="s">
+        <v>905</v>
+      </c>
+      <c r="B497" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="C497" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D497" s="9">
         <v>6</v>
       </c>
-      <c r="E435" t="s">
-        <v>65</v>
-      </c>
-      <c r="F435" t="s">
-        <v>402</v>
-      </c>
-      <c r="G435" s="4">
-        <v>10248660908</v>
-      </c>
-      <c r="H435" t="s">
-        <v>926</v>
-      </c>
-      <c r="I435" t="s">
+      <c r="E497" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F497" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="G497" s="11">
+        <v>10712016499</v>
+      </c>
+      <c r="H497" s="9" t="s">
+        <v>1068</v>
+      </c>
+      <c r="I497" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="J435" t="s">
-        <v>461</v>
-      </c>
-      <c r="K435" t="s">
-        <v>972</v>
-      </c>
-      <c r="L435" t="s">
-        <v>297</v>
-      </c>
-      <c r="M435">
-        <v>1</v>
-      </c>
-      <c r="N435" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="436" spans="1:14">
-      <c r="A436" t="s">
-        <v>844</v>
-      </c>
-      <c r="B436" s="4" t="s">
-        <v>910</v>
-      </c>
-      <c r="C436">
-        <v>2026</v>
-      </c>
-      <c r="D436">
+      <c r="J497" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K497" s="9" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M497" s="9">
+        <v>1</v>
+      </c>
+      <c r="N497" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="498" spans="1:14" s="9" customFormat="1">
+      <c r="A498" s="9" t="s">
+        <v>906</v>
+      </c>
+      <c r="B498" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="C498" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D498" s="9">
         <v>6</v>
       </c>
-      <c r="E436" t="s">
-        <v>65</v>
-      </c>
-      <c r="F436" t="s">
-        <v>402</v>
-      </c>
-      <c r="G436" s="4">
-        <v>10248900984</v>
-      </c>
-      <c r="H436" t="s">
-        <v>927</v>
-      </c>
-      <c r="I436" t="s">
+      <c r="E498" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F498" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="G498" s="11">
+        <v>10715375210</v>
+      </c>
+      <c r="H498" s="9" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I498" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="J436" t="s">
-        <v>461</v>
-      </c>
-      <c r="K436" t="s">
-        <v>972</v>
-      </c>
-      <c r="L436" t="s">
-        <v>297</v>
-      </c>
-      <c r="M436">
-        <v>1</v>
-      </c>
-      <c r="N436" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="437" spans="1:14">
-      <c r="A437" t="s">
-        <v>845</v>
-      </c>
-      <c r="B437" s="4" t="s">
-        <v>910</v>
-      </c>
-      <c r="C437">
-        <v>2026</v>
-      </c>
-      <c r="D437">
+      <c r="J498" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K498" s="9" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M498" s="9">
+        <v>1</v>
+      </c>
+      <c r="N498" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="499" spans="1:14" s="9" customFormat="1">
+      <c r="A499" s="9" t="s">
+        <v>907</v>
+      </c>
+      <c r="B499" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="C499" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D499" s="9">
         <v>6</v>
       </c>
-      <c r="E437" t="s">
-        <v>65</v>
-      </c>
-      <c r="F437" t="s">
-        <v>402</v>
-      </c>
-      <c r="G437" s="4">
-        <v>10482266130</v>
-      </c>
-      <c r="H437" t="s">
-        <v>928</v>
-      </c>
-      <c r="I437" t="s">
+      <c r="E499" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F499" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="G499" s="11">
+        <v>10722542679</v>
+      </c>
+      <c r="H499" s="9" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I499" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="J437" t="s">
-        <v>461</v>
-      </c>
-      <c r="K437" t="s">
-        <v>972</v>
-      </c>
-      <c r="L437" t="s">
-        <v>297</v>
-      </c>
-      <c r="M437">
-        <v>1</v>
-      </c>
-      <c r="N437" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="438" spans="1:14">
-      <c r="A438" t="s">
-        <v>846</v>
-      </c>
-      <c r="B438" s="4" t="s">
-        <v>910</v>
-      </c>
-      <c r="C438">
-        <v>2026</v>
-      </c>
-      <c r="D438">
+      <c r="J499" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K499" s="9" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M499" s="9">
+        <v>1</v>
+      </c>
+      <c r="N499" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="500" spans="1:14" s="9" customFormat="1">
+      <c r="A500" s="9" t="s">
+        <v>908</v>
+      </c>
+      <c r="B500" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="C500" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D500" s="9">
         <v>6</v>
       </c>
-      <c r="E438" t="s">
-        <v>65</v>
-      </c>
-      <c r="F438" t="s">
-        <v>402</v>
-      </c>
-      <c r="G438" s="4">
-        <v>10435553881</v>
-      </c>
-      <c r="H438" t="s">
-        <v>295</v>
-      </c>
-      <c r="I438" t="s">
+      <c r="E500" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F500" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="G500" s="11">
+        <v>10727385261</v>
+      </c>
+      <c r="H500" s="9" t="s">
+        <v>1071</v>
+      </c>
+      <c r="I500" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="J438" t="s">
-        <v>461</v>
-      </c>
-      <c r="K438" t="s">
-        <v>972</v>
-      </c>
-      <c r="L438" t="s">
-        <v>297</v>
-      </c>
-      <c r="M438">
-        <v>1</v>
-      </c>
-      <c r="N438" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="439" spans="1:14">
-      <c r="A439" t="s">
-        <v>847</v>
-      </c>
-      <c r="B439" s="4" t="s">
-        <v>910</v>
-      </c>
-      <c r="C439">
-        <v>2026</v>
-      </c>
-      <c r="D439">
+      <c r="J500" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K500" s="9" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M500" s="9">
+        <v>1</v>
+      </c>
+      <c r="N500" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="501" spans="1:14" s="9" customFormat="1">
+      <c r="A501" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="B501" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="C501" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D501" s="9">
         <v>6</v>
       </c>
-      <c r="E439" t="s">
-        <v>65</v>
-      </c>
-      <c r="F439" t="s">
-        <v>402</v>
-      </c>
-      <c r="G439" s="4">
-        <v>10239802821</v>
-      </c>
-      <c r="H439" t="s">
-        <v>84</v>
-      </c>
-      <c r="I439" t="s">
+      <c r="E501" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F501" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="G501" s="11">
+        <v>10731500709</v>
+      </c>
+      <c r="H501" s="9" t="s">
+        <v>1072</v>
+      </c>
+      <c r="I501" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="J439" t="s">
-        <v>461</v>
-      </c>
-      <c r="K439" t="s">
-        <v>972</v>
-      </c>
-      <c r="L439" t="s">
-        <v>297</v>
-      </c>
-      <c r="M439">
-        <v>1</v>
-      </c>
-      <c r="N439" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="440" spans="1:14">
-      <c r="A440" t="s">
-        <v>848</v>
-      </c>
-      <c r="B440" s="4" t="s">
-        <v>910</v>
-      </c>
-      <c r="C440">
-        <v>2026</v>
-      </c>
-      <c r="D440">
+      <c r="J501" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K501" s="9" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M501" s="9">
+        <v>1</v>
+      </c>
+      <c r="N501" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="502" spans="1:14" s="9" customFormat="1">
+      <c r="A502" s="9" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B502" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="C502" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D502" s="9">
         <v>6</v>
       </c>
-      <c r="E440" t="s">
-        <v>65</v>
-      </c>
-      <c r="F440" t="s">
-        <v>402</v>
-      </c>
-      <c r="G440" s="4">
-        <v>10239106876</v>
-      </c>
-      <c r="H440" t="s">
-        <v>929</v>
-      </c>
-      <c r="I440" t="s">
+      <c r="E502" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F502" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="G502" s="11">
+        <v>10760888953</v>
+      </c>
+      <c r="H502" s="9" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I502" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="J440" t="s">
-        <v>461</v>
-      </c>
-      <c r="K440" t="s">
-        <v>972</v>
-      </c>
-      <c r="L440" t="s">
-        <v>297</v>
-      </c>
-      <c r="M440">
-        <v>1</v>
-      </c>
-      <c r="N440" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="441" spans="1:14">
-      <c r="A441" t="s">
-        <v>849</v>
-      </c>
-      <c r="B441" s="4" t="s">
-        <v>910</v>
-      </c>
-      <c r="C441">
-        <v>2026</v>
-      </c>
-      <c r="D441">
+      <c r="J502" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K502" s="9" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M502" s="9">
+        <v>1</v>
+      </c>
+      <c r="N502" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="503" spans="1:14" s="9" customFormat="1">
+      <c r="A503" s="9" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B503" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="C503" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D503" s="9">
         <v>6</v>
       </c>
-      <c r="E441" t="s">
-        <v>65</v>
-      </c>
-      <c r="F441" t="s">
-        <v>402</v>
-      </c>
-      <c r="G441" s="4">
-        <v>10238784986</v>
-      </c>
-      <c r="H441" t="s">
-        <v>930</v>
-      </c>
-      <c r="I441" t="s">
+      <c r="E503" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F503" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="G503" s="11">
+        <v>10761617309</v>
+      </c>
+      <c r="H503" s="9" t="s">
+        <v>1074</v>
+      </c>
+      <c r="I503" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="J441" t="s">
-        <v>461</v>
-      </c>
-      <c r="K441" t="s">
-        <v>972</v>
-      </c>
-      <c r="L441" t="s">
-        <v>297</v>
-      </c>
-      <c r="M441">
-        <v>1</v>
-      </c>
-      <c r="N441" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="442" spans="1:14">
-      <c r="A442" t="s">
-        <v>850</v>
-      </c>
-      <c r="B442" s="4" t="s">
-        <v>910</v>
-      </c>
-      <c r="C442">
-        <v>2026</v>
-      </c>
-      <c r="D442">
+      <c r="J503" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="K503" s="9" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M503" s="9">
+        <v>1</v>
+      </c>
+      <c r="N503" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="504" spans="1:14" s="9" customFormat="1">
+      <c r="A504" s="9" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B504" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="C504" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D504" s="9">
         <v>6</v>
       </c>
-      <c r="E442" t="s">
-        <v>65</v>
-      </c>
-      <c r="F442" t="s">
-        <v>402</v>
-      </c>
-      <c r="G442" s="4">
-        <v>40241978</v>
-      </c>
-      <c r="H442" t="s">
-        <v>931</v>
-      </c>
-      <c r="I442" t="s">
+      <c r="E504" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F504" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="G504" s="11">
+        <v>60695244</v>
+      </c>
+      <c r="H504" s="9" t="s">
+        <v>1075</v>
+      </c>
+      <c r="I504" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="J442" t="s">
-        <v>461</v>
-      </c>
-      <c r="K442" t="s">
-        <v>972</v>
-      </c>
-      <c r="L442" t="s">
-        <v>297</v>
-      </c>
-      <c r="M442">
-        <v>1</v>
-      </c>
-      <c r="N442" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="443" spans="1:14">
-      <c r="A443" t="s">
-        <v>851</v>
-      </c>
-      <c r="B443" s="4" t="s">
-        <v>910</v>
-      </c>
-      <c r="C443">
-        <v>2026</v>
-      </c>
-      <c r="D443">
-        <v>6</v>
-      </c>
-      <c r="E443" t="s">
-        <v>65</v>
-      </c>
-      <c r="F443" t="s">
-        <v>402</v>
-      </c>
-      <c r="G443" s="4">
-        <v>10462678571</v>
-      </c>
-      <c r="H443" t="s">
-        <v>932</v>
-      </c>
-      <c r="I443" t="s">
-        <v>296</v>
-      </c>
-      <c r="J443" t="s">
-        <v>461</v>
-      </c>
-      <c r="K443" t="s">
-        <v>972</v>
-      </c>
-      <c r="L443" t="s">
-        <v>297</v>
-      </c>
-      <c r="M443">
-        <v>1</v>
-      </c>
-      <c r="N443" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="444" spans="1:14">
-      <c r="A444" t="s">
-        <v>852</v>
-      </c>
-      <c r="B444" s="4" t="s">
-        <v>910</v>
-      </c>
-      <c r="C444">
-        <v>2026</v>
-      </c>
-      <c r="D444">
-        <v>6</v>
-      </c>
-      <c r="E444" t="s">
-        <v>65</v>
-      </c>
-      <c r="F444" t="s">
-        <v>402</v>
-      </c>
-      <c r="G444" s="4">
-        <v>10092214023</v>
-      </c>
-      <c r="H444" t="s">
-        <v>933</v>
-      </c>
-      <c r="I444" t="s">
-        <v>296</v>
-      </c>
-      <c r="J444" t="s">
-        <v>461</v>
-      </c>
-      <c r="K444" t="s">
-        <v>972</v>
-      </c>
-      <c r="L444" t="s">
-        <v>297</v>
-      </c>
-      <c r="M444">
-        <v>1</v>
-      </c>
-      <c r="N444" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="445" spans="1:14">
-      <c r="A445" t="s">
-        <v>853</v>
-      </c>
-      <c r="B445" s="4" t="s">
-        <v>910</v>
-      </c>
-      <c r="C445">
-        <v>2026</v>
-      </c>
-      <c r="D445">
-        <v>6</v>
-      </c>
-      <c r="E445" t="s">
-        <v>65</v>
-      </c>
-      <c r="F445" t="s">
-        <v>402</v>
-      </c>
-      <c r="G445" s="4">
-        <v>42421067</v>
-      </c>
-      <c r="H445" t="s">
-        <v>934</v>
-      </c>
-      <c r="I445" t="s">
-        <v>296</v>
-      </c>
-      <c r="J445" t="s">
-        <v>461</v>
-      </c>
-      <c r="K445" t="s">
-        <v>972</v>
-      </c>
-      <c r="L445" t="s">
-        <v>297</v>
-      </c>
-      <c r="M445">
-        <v>1</v>
-      </c>
-      <c r="N445" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="446" spans="1:14">
-      <c r="A446" t="s">
-        <v>854</v>
-      </c>
-      <c r="B446" s="4" t="s">
-        <v>910</v>
-      </c>
-      <c r="C446">
-        <v>2026</v>
-      </c>
-      <c r="D446">
-        <v>6</v>
-      </c>
-      <c r="E446" t="s">
-        <v>65</v>
-      </c>
-      <c r="F446" t="s">
-        <v>402</v>
-      </c>
-      <c r="G446" s="4">
-        <v>10238643479</v>
-      </c>
-      <c r="H446" t="s">
-        <v>262</v>
-      </c>
-      <c r="I446" t="s">
-        <v>296</v>
-      </c>
-      <c r="J446" t="s">
-        <v>461</v>
-      </c>
-      <c r="K446" t="s">
-        <v>972</v>
-      </c>
-      <c r="L446" t="s">
-        <v>297</v>
-      </c>
-      <c r="M446">
-        <v>1</v>
-      </c>
-      <c r="N446" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="447" spans="1:14">
-      <c r="A447" t="s">
-        <v>855</v>
-      </c>
-      <c r="B447" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="C447">
-        <v>2026</v>
-      </c>
-      <c r="D447">
-        <v>6</v>
-      </c>
-      <c r="E447" t="s">
-        <v>65</v>
-      </c>
-      <c r="F447" t="s">
-        <v>402</v>
-      </c>
-      <c r="G447" s="4">
-        <v>10755814615</v>
-      </c>
-      <c r="H447" t="s">
-        <v>948</v>
-      </c>
-      <c r="I447" t="s">
-        <v>296</v>
-      </c>
-      <c r="J447" t="s">
-        <v>461</v>
-      </c>
-      <c r="K447" t="s">
-        <v>977</v>
-      </c>
-      <c r="L447" t="s">
-        <v>297</v>
-      </c>
-      <c r="M447">
-        <v>1</v>
-      </c>
-      <c r="N447" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="448" spans="1:14">
-      <c r="A448" t="s">
-        <v>856</v>
-      </c>
-      <c r="B448" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="C448">
-        <v>2026</v>
-      </c>
-      <c r="D448">
-        <v>6</v>
-      </c>
-      <c r="E448" t="s">
-        <v>65</v>
-      </c>
-      <c r="F448" t="s">
-        <v>402</v>
-      </c>
-      <c r="G448" s="4">
-        <v>10238394711</v>
-      </c>
-      <c r="H448" t="s">
-        <v>271</v>
-      </c>
-      <c r="I448" t="s">
-        <v>296</v>
-      </c>
-      <c r="J448" t="s">
-        <v>461</v>
-      </c>
-      <c r="K448" t="s">
-        <v>977</v>
-      </c>
-      <c r="L448" t="s">
-        <v>297</v>
-      </c>
-      <c r="M448">
-        <v>1</v>
-      </c>
-      <c r="N448" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="449" spans="1:14">
-      <c r="A449" t="s">
-        <v>857</v>
-      </c>
-      <c r="B449" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="C449">
-        <v>2026</v>
-      </c>
-      <c r="D449">
-        <v>6</v>
-      </c>
-      <c r="E449" t="s">
-        <v>65</v>
-      </c>
-      <c r="F449" t="s">
-        <v>402</v>
-      </c>
-      <c r="G449" s="4">
-        <v>10420101631</v>
-      </c>
-      <c r="H449" t="s">
-        <v>949</v>
-      </c>
-      <c r="I449" t="s">
-        <v>296</v>
-      </c>
-      <c r="J449" t="s">
-        <v>461</v>
-      </c>
-      <c r="K449" t="s">
-        <v>977</v>
-      </c>
-      <c r="L449" t="s">
-        <v>297</v>
-      </c>
-      <c r="M449">
-        <v>1</v>
-      </c>
-      <c r="N449" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="450" spans="1:14">
-      <c r="A450" t="s">
-        <v>858</v>
-      </c>
-      <c r="B450" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="C450">
-        <v>2026</v>
-      </c>
-      <c r="D450">
-        <v>6</v>
-      </c>
-      <c r="E450" t="s">
-        <v>65</v>
-      </c>
-      <c r="F450" t="s">
-        <v>402</v>
-      </c>
-      <c r="G450" s="4">
-        <v>10700932929</v>
-      </c>
-      <c r="H450" t="s">
-        <v>950</v>
-      </c>
-      <c r="I450" t="s">
-        <v>296</v>
-      </c>
-      <c r="J450" t="s">
-        <v>461</v>
-      </c>
-      <c r="K450" t="s">
-        <v>977</v>
-      </c>
-      <c r="L450" t="s">
-        <v>297</v>
-      </c>
-      <c r="M450">
-        <v>1</v>
-      </c>
-      <c r="N450" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="451" spans="1:14">
-      <c r="A451" t="s">
-        <v>859</v>
-      </c>
-      <c r="B451" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="C451">
-        <v>2026</v>
-      </c>
-      <c r="D451">
-        <v>6</v>
-      </c>
-      <c r="E451" t="s">
-        <v>65</v>
-      </c>
-      <c r="F451" t="s">
-        <v>402</v>
-      </c>
-      <c r="G451" s="4">
-        <v>10700799889</v>
-      </c>
-      <c r="H451" t="s">
-        <v>951</v>
-      </c>
-      <c r="I451" t="s">
-        <v>296</v>
-      </c>
-      <c r="J451" t="s">
-        <v>461</v>
-      </c>
-      <c r="K451" t="s">
-        <v>977</v>
-      </c>
-      <c r="L451" t="s">
-        <v>297</v>
-      </c>
-      <c r="M451">
-        <v>1</v>
-      </c>
-      <c r="N451" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="452" spans="1:14">
-      <c r="A452" t="s">
-        <v>860</v>
-      </c>
-      <c r="B452" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="C452">
-        <v>2026</v>
-      </c>
-      <c r="D452">
-        <v>6</v>
-      </c>
-      <c r="E452" t="s">
-        <v>65</v>
-      </c>
-      <c r="F452" t="s">
-        <v>402</v>
-      </c>
-      <c r="G452" s="4">
-        <v>10238643479</v>
-      </c>
-      <c r="H452" t="s">
-        <v>262</v>
-      </c>
-      <c r="I452" t="s">
-        <v>296</v>
-      </c>
-      <c r="J452" t="s">
-        <v>461</v>
-      </c>
-      <c r="K452" t="s">
-        <v>977</v>
-      </c>
-      <c r="L452" t="s">
-        <v>297</v>
-      </c>
-      <c r="M452">
-        <v>1</v>
-      </c>
-      <c r="N452" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="453" spans="1:14">
-      <c r="A453" t="s">
-        <v>861</v>
-      </c>
-      <c r="B453" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="C453">
-        <v>2026</v>
-      </c>
-      <c r="D453">
-        <v>6</v>
-      </c>
-      <c r="E453" t="s">
-        <v>65</v>
-      </c>
-      <c r="F453" t="s">
-        <v>402</v>
-      </c>
-      <c r="G453" s="4">
-        <v>10204218736</v>
-      </c>
-      <c r="H453" t="s">
-        <v>952</v>
-      </c>
-      <c r="I453" t="s">
-        <v>296</v>
-      </c>
-      <c r="J453" t="s">
-        <v>461</v>
-      </c>
-      <c r="K453" t="s">
-        <v>977</v>
-      </c>
-      <c r="L453" t="s">
-        <v>297</v>
-      </c>
-      <c r="M453">
-        <v>1</v>
-      </c>
-      <c r="N453" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="454" spans="1:14">
-      <c r="A454" t="s">
-        <v>862</v>
-      </c>
-      <c r="B454" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="C454">
-        <v>2026</v>
-      </c>
-      <c r="D454">
-        <v>6</v>
-      </c>
-      <c r="E454" t="s">
-        <v>65</v>
-      </c>
-      <c r="F454" t="s">
-        <v>402</v>
-      </c>
-      <c r="G454" s="4">
-        <v>10752532619</v>
-      </c>
-      <c r="H454" t="s">
-        <v>953</v>
-      </c>
-      <c r="I454" t="s">
-        <v>296</v>
-      </c>
-      <c r="J454" t="s">
-        <v>461</v>
-      </c>
-      <c r="K454" t="s">
-        <v>977</v>
-      </c>
-      <c r="L454" t="s">
-        <v>297</v>
-      </c>
-      <c r="M454">
-        <v>1</v>
-      </c>
-      <c r="N454" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="455" spans="1:14">
-      <c r="A455" t="s">
-        <v>863</v>
-      </c>
-      <c r="B455" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="C455">
-        <v>2026</v>
-      </c>
-      <c r="D455">
-        <v>6</v>
-      </c>
-      <c r="E455" t="s">
-        <v>65</v>
-      </c>
-      <c r="F455" t="s">
-        <v>402</v>
-      </c>
-      <c r="G455" s="4">
-        <v>10421627733</v>
-      </c>
-      <c r="H455" t="s">
-        <v>954</v>
-      </c>
-      <c r="I455" t="s">
-        <v>296</v>
-      </c>
-      <c r="J455" t="s">
-        <v>461</v>
-      </c>
-      <c r="K455" t="s">
-        <v>977</v>
-      </c>
-      <c r="L455" t="s">
-        <v>297</v>
-      </c>
-      <c r="M455">
-        <v>1</v>
-      </c>
-      <c r="N455" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="456" spans="1:14">
-      <c r="A456" t="s">
-        <v>864</v>
-      </c>
-      <c r="B456" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="C456">
-        <v>2026</v>
-      </c>
-      <c r="D456">
-        <v>6</v>
-      </c>
-      <c r="E456" t="s">
-        <v>65</v>
-      </c>
-      <c r="F456" t="s">
-        <v>402</v>
-      </c>
-      <c r="G456" s="4">
-        <v>20602367704</v>
-      </c>
-      <c r="H456" t="s">
-        <v>361</v>
-      </c>
-      <c r="I456" t="s">
-        <v>296</v>
-      </c>
-      <c r="J456" t="s">
-        <v>461</v>
-      </c>
-      <c r="K456" t="s">
-        <v>977</v>
-      </c>
-      <c r="L456" t="s">
-        <v>297</v>
-      </c>
-      <c r="M456">
-        <v>1</v>
-      </c>
-      <c r="N456" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="457" spans="1:14">
-      <c r="A457" t="s">
-        <v>865</v>
-      </c>
-      <c r="B457" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="C457">
-        <v>2026</v>
-      </c>
-      <c r="D457">
-        <v>6</v>
-      </c>
-      <c r="E457" t="s">
-        <v>65</v>
-      </c>
-      <c r="F457" t="s">
-        <v>402</v>
-      </c>
-      <c r="G457" s="4">
-        <v>10712579566</v>
-      </c>
-      <c r="H457" t="s">
-        <v>364</v>
-      </c>
-      <c r="I457" t="s">
-        <v>296</v>
-      </c>
-      <c r="J457" t="s">
-        <v>461</v>
-      </c>
-      <c r="K457" t="s">
-        <v>977</v>
-      </c>
-      <c r="L457" t="s">
-        <v>297</v>
-      </c>
-      <c r="M457">
-        <v>1</v>
-      </c>
-      <c r="N457" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="458" spans="1:14">
-      <c r="A458" t="s">
-        <v>866</v>
-      </c>
-      <c r="B458" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="C458">
-        <v>2026</v>
-      </c>
-      <c r="D458">
-        <v>6</v>
-      </c>
-      <c r="E458" t="s">
-        <v>65</v>
-      </c>
-      <c r="F458" t="s">
-        <v>402</v>
-      </c>
-      <c r="G458" s="4">
-        <v>10239455951</v>
-      </c>
-      <c r="H458" t="s">
-        <v>274</v>
-      </c>
-      <c r="I458" t="s">
-        <v>296</v>
-      </c>
-      <c r="J458" t="s">
-        <v>461</v>
-      </c>
-      <c r="K458" t="s">
-        <v>977</v>
-      </c>
-      <c r="L458" t="s">
-        <v>297</v>
-      </c>
-      <c r="M458">
-        <v>1</v>
-      </c>
-      <c r="N458" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="459" spans="1:14">
-      <c r="A459" t="s">
-        <v>867</v>
-      </c>
-      <c r="B459" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="C459">
-        <v>2026</v>
-      </c>
-      <c r="D459">
-        <v>6</v>
-      </c>
-      <c r="E459" t="s">
-        <v>65</v>
-      </c>
-      <c r="F459" t="s">
-        <v>402</v>
-      </c>
-      <c r="G459" s="4">
-        <v>10454593494</v>
-      </c>
-      <c r="H459" t="s">
-        <v>365</v>
-      </c>
-      <c r="I459" t="s">
-        <v>296</v>
-      </c>
-      <c r="J459" t="s">
-        <v>461</v>
-      </c>
-      <c r="K459" t="s">
-        <v>977</v>
-      </c>
-      <c r="L459" t="s">
-        <v>297</v>
-      </c>
-      <c r="M459">
-        <v>1</v>
-      </c>
-      <c r="N459" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="460" spans="1:14">
-      <c r="A460" t="s">
-        <v>868</v>
-      </c>
-      <c r="B460" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="C460">
-        <v>2026</v>
-      </c>
-      <c r="D460">
-        <v>6</v>
-      </c>
-      <c r="E460" t="s">
-        <v>65</v>
-      </c>
-      <c r="F460" t="s">
-        <v>402</v>
-      </c>
-      <c r="G460" s="4">
-        <v>10238394711</v>
-      </c>
-      <c r="H460" t="s">
-        <v>271</v>
-      </c>
-      <c r="I460" t="s">
-        <v>296</v>
-      </c>
-      <c r="J460" t="s">
-        <v>461</v>
-      </c>
-      <c r="K460" t="s">
-        <v>977</v>
-      </c>
-      <c r="L460" t="s">
-        <v>297</v>
-      </c>
-      <c r="M460">
-        <v>1</v>
-      </c>
-      <c r="N460" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="461" spans="1:14">
-      <c r="A461" t="s">
-        <v>869</v>
-      </c>
-      <c r="B461" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="C461">
-        <v>2026</v>
-      </c>
-      <c r="D461">
-        <v>6</v>
-      </c>
-      <c r="E461" t="s">
-        <v>65</v>
-      </c>
-      <c r="F461" t="s">
-        <v>402</v>
-      </c>
-      <c r="G461" s="4">
-        <v>10096063038</v>
-      </c>
-      <c r="H461" t="s">
-        <v>955</v>
-      </c>
-      <c r="I461" t="s">
-        <v>296</v>
-      </c>
-      <c r="J461" t="s">
-        <v>461</v>
-      </c>
-      <c r="K461" t="s">
-        <v>977</v>
-      </c>
-      <c r="L461" t="s">
-        <v>297</v>
-      </c>
-      <c r="M461">
-        <v>1</v>
-      </c>
-      <c r="N461" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="462" spans="1:14">
-      <c r="A462" t="s">
-        <v>870</v>
-      </c>
-      <c r="B462" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="C462">
-        <v>2026</v>
-      </c>
-      <c r="D462">
-        <v>6</v>
-      </c>
-      <c r="E462" t="s">
-        <v>65</v>
-      </c>
-      <c r="F462" t="s">
-        <v>402</v>
-      </c>
-      <c r="G462" s="4">
-        <v>10469043296</v>
-      </c>
-      <c r="H462" t="s">
-        <v>366</v>
-      </c>
-      <c r="I462" t="s">
-        <v>296</v>
-      </c>
-      <c r="J462" t="s">
-        <v>461</v>
-      </c>
-      <c r="K462" t="s">
-        <v>977</v>
-      </c>
-      <c r="L462" t="s">
-        <v>297</v>
-      </c>
-      <c r="M462">
-        <v>1</v>
-      </c>
-      <c r="N462" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="463" spans="1:14">
-      <c r="A463" t="s">
-        <v>871</v>
-      </c>
-      <c r="B463" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="C463">
-        <v>2026</v>
-      </c>
-      <c r="D463">
-        <v>6</v>
-      </c>
-      <c r="E463" t="s">
-        <v>65</v>
-      </c>
-      <c r="F463" t="s">
-        <v>402</v>
-      </c>
-      <c r="G463" s="4">
-        <v>10440425696</v>
-      </c>
-      <c r="H463" t="s">
-        <v>956</v>
-      </c>
-      <c r="I463" t="s">
-        <v>296</v>
-      </c>
-      <c r="J463" t="s">
-        <v>461</v>
-      </c>
-      <c r="K463" t="s">
-        <v>977</v>
-      </c>
-      <c r="L463" t="s">
-        <v>297</v>
-      </c>
-      <c r="M463">
-        <v>1</v>
-      </c>
-      <c r="N463" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="464" spans="1:14">
-      <c r="A464" t="s">
-        <v>872</v>
-      </c>
-      <c r="B464" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="C464">
-        <v>2026</v>
-      </c>
-      <c r="D464">
-        <v>6</v>
-      </c>
-      <c r="E464" t="s">
-        <v>65</v>
-      </c>
-      <c r="F464" t="s">
-        <v>467</v>
-      </c>
-      <c r="G464" s="4">
-        <v>10704606783</v>
-      </c>
-      <c r="H464" t="s">
-        <v>937</v>
-      </c>
-      <c r="I464" t="s">
-        <v>296</v>
-      </c>
-      <c r="J464" t="s">
+      <c r="J504" s="9" t="s">
         <v>460</v>
       </c>
-      <c r="K464" t="s">
-        <v>976</v>
-      </c>
-      <c r="L464" t="s">
-        <v>88</v>
-      </c>
-      <c r="M464">
-        <v>0</v>
-      </c>
-      <c r="N464" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="465" spans="1:14">
-      <c r="A465" t="s">
-        <v>873</v>
-      </c>
-      <c r="B465" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="C465">
-        <v>2026</v>
-      </c>
-      <c r="D465">
-        <v>6</v>
-      </c>
-      <c r="E465" t="s">
-        <v>65</v>
-      </c>
-      <c r="F465" t="s">
-        <v>467</v>
-      </c>
-      <c r="G465" s="4">
-        <v>10448659068</v>
-      </c>
-      <c r="H465" t="s">
-        <v>938</v>
-      </c>
-      <c r="I465" t="s">
-        <v>296</v>
-      </c>
-      <c r="J465" t="s">
-        <v>460</v>
-      </c>
-      <c r="K465" t="s">
-        <v>976</v>
-      </c>
-      <c r="L465" t="s">
-        <v>88</v>
-      </c>
-      <c r="M465" s="1">
-        <v>0</v>
-      </c>
-      <c r="N465" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="466" spans="1:14">
-      <c r="A466" t="s">
-        <v>874</v>
-      </c>
-      <c r="B466" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="C466">
-        <v>2026</v>
-      </c>
-      <c r="D466">
-        <v>6</v>
-      </c>
-      <c r="E466" t="s">
-        <v>65</v>
-      </c>
-      <c r="F466" t="s">
-        <v>467</v>
-      </c>
-      <c r="G466" s="4">
-        <v>10239756587</v>
-      </c>
-      <c r="H466" t="s">
-        <v>939</v>
-      </c>
-      <c r="I466" t="s">
-        <v>296</v>
-      </c>
-      <c r="J466" t="s">
-        <v>460</v>
-      </c>
-      <c r="K466" t="s">
-        <v>976</v>
-      </c>
-      <c r="L466" t="s">
-        <v>88</v>
-      </c>
-      <c r="M466" s="1">
-        <v>0</v>
-      </c>
-      <c r="N466" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="467" spans="1:14">
-      <c r="A467" t="s">
-        <v>875</v>
-      </c>
-      <c r="B467" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="C467">
-        <v>2026</v>
-      </c>
-      <c r="D467">
-        <v>6</v>
-      </c>
-      <c r="E467" t="s">
-        <v>65</v>
-      </c>
-      <c r="F467" t="s">
-        <v>467</v>
-      </c>
-      <c r="G467" s="4">
-        <v>10473163450</v>
-      </c>
-      <c r="H467" t="s">
-        <v>411</v>
-      </c>
-      <c r="I467" t="s">
-        <v>296</v>
-      </c>
-      <c r="J467" t="s">
-        <v>460</v>
-      </c>
-      <c r="K467" t="s">
-        <v>976</v>
-      </c>
-      <c r="L467" t="s">
-        <v>88</v>
-      </c>
-      <c r="M467" s="1">
-        <v>0</v>
-      </c>
-      <c r="N467" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="468" spans="1:14">
-      <c r="A468" t="s">
-        <v>876</v>
-      </c>
-      <c r="B468" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="C468">
-        <v>2026</v>
-      </c>
-      <c r="D468">
-        <v>6</v>
-      </c>
-      <c r="E468" t="s">
-        <v>65</v>
-      </c>
-      <c r="F468" t="s">
-        <v>467</v>
-      </c>
-      <c r="G468" s="4">
-        <v>10802446107</v>
-      </c>
-      <c r="H468" t="s">
-        <v>940</v>
-      </c>
-      <c r="I468" t="s">
-        <v>296</v>
-      </c>
-      <c r="J468" t="s">
-        <v>460</v>
-      </c>
-      <c r="K468" t="s">
-        <v>976</v>
-      </c>
-      <c r="L468" t="s">
-        <v>88</v>
-      </c>
-      <c r="M468" s="1">
-        <v>0</v>
-      </c>
-      <c r="N468" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="469" spans="1:14">
-      <c r="A469" t="s">
-        <v>877</v>
-      </c>
-      <c r="B469" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="C469">
-        <v>2026</v>
-      </c>
-      <c r="D469">
-        <v>6</v>
-      </c>
-      <c r="E469" t="s">
-        <v>65</v>
-      </c>
-      <c r="F469" t="s">
-        <v>467</v>
-      </c>
-      <c r="G469" s="4">
-        <v>10409212480</v>
-      </c>
-      <c r="H469" t="s">
-        <v>941</v>
-      </c>
-      <c r="I469" t="s">
-        <v>296</v>
-      </c>
-      <c r="J469" t="s">
-        <v>460</v>
-      </c>
-      <c r="K469" t="s">
-        <v>976</v>
-      </c>
-      <c r="L469" t="s">
-        <v>88</v>
-      </c>
-      <c r="M469" s="1">
-        <v>0</v>
-      </c>
-      <c r="N469" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="470" spans="1:14">
-      <c r="A470" t="s">
-        <v>878</v>
-      </c>
-      <c r="B470" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="C470">
-        <v>2026</v>
-      </c>
-      <c r="D470">
-        <v>6</v>
-      </c>
-      <c r="E470" t="s">
-        <v>65</v>
-      </c>
-      <c r="F470" t="s">
-        <v>467</v>
-      </c>
-      <c r="G470" s="4">
-        <v>10433498394</v>
-      </c>
-      <c r="H470" t="s">
-        <v>942</v>
-      </c>
-      <c r="I470" t="s">
-        <v>296</v>
-      </c>
-      <c r="J470" t="s">
-        <v>460</v>
-      </c>
-      <c r="K470" t="s">
-        <v>976</v>
-      </c>
-      <c r="L470" t="s">
-        <v>88</v>
-      </c>
-      <c r="M470" s="1">
-        <v>0</v>
-      </c>
-      <c r="N470" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="471" spans="1:14">
-      <c r="A471" t="s">
-        <v>879</v>
-      </c>
-      <c r="B471" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="C471">
-        <v>2026</v>
-      </c>
-      <c r="D471">
-        <v>6</v>
-      </c>
-      <c r="E471" t="s">
-        <v>65</v>
-      </c>
-      <c r="F471" t="s">
-        <v>467</v>
-      </c>
-      <c r="G471" s="4">
-        <v>10477489261</v>
-      </c>
-      <c r="H471" t="s">
-        <v>446</v>
-      </c>
-      <c r="I471" t="s">
-        <v>296</v>
-      </c>
-      <c r="J471" t="s">
-        <v>460</v>
-      </c>
-      <c r="K471" t="s">
-        <v>976</v>
-      </c>
-      <c r="L471" t="s">
-        <v>88</v>
-      </c>
-      <c r="M471" s="1">
-        <v>0</v>
-      </c>
-      <c r="N471" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="472" spans="1:14">
-      <c r="A472" t="s">
-        <v>880</v>
-      </c>
-      <c r="B472" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="C472">
-        <v>2026</v>
-      </c>
-      <c r="D472">
-        <v>6</v>
-      </c>
-      <c r="E472" t="s">
-        <v>65</v>
-      </c>
-      <c r="F472" t="s">
-        <v>467</v>
-      </c>
-      <c r="G472" s="4">
-        <v>10466170203</v>
-      </c>
-      <c r="H472" t="s">
-        <v>943</v>
-      </c>
-      <c r="I472" t="s">
-        <v>296</v>
-      </c>
-      <c r="J472" t="s">
-        <v>460</v>
-      </c>
-      <c r="K472" t="s">
-        <v>976</v>
-      </c>
-      <c r="L472" t="s">
-        <v>88</v>
-      </c>
-      <c r="M472" s="1">
-        <v>0</v>
-      </c>
-      <c r="N472" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="473" spans="1:14">
-      <c r="A473" t="s">
-        <v>881</v>
-      </c>
-      <c r="B473" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="C473">
-        <v>2026</v>
-      </c>
-      <c r="D473">
-        <v>6</v>
-      </c>
-      <c r="E473" t="s">
-        <v>65</v>
-      </c>
-      <c r="F473" t="s">
-        <v>467</v>
-      </c>
-      <c r="G473" s="4">
-        <v>10760499493</v>
-      </c>
-      <c r="H473" t="s">
-        <v>944</v>
-      </c>
-      <c r="I473" t="s">
-        <v>296</v>
-      </c>
-      <c r="J473" t="s">
-        <v>460</v>
-      </c>
-      <c r="K473" t="s">
-        <v>976</v>
-      </c>
-      <c r="L473" t="s">
-        <v>88</v>
-      </c>
-      <c r="M473" s="1">
-        <v>0</v>
-      </c>
-      <c r="N473" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="474" spans="1:14">
-      <c r="A474" t="s">
-        <v>882</v>
-      </c>
-      <c r="B474" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="C474">
-        <v>2026</v>
-      </c>
-      <c r="D474">
-        <v>6</v>
-      </c>
-      <c r="E474" t="s">
-        <v>65</v>
-      </c>
-      <c r="F474" t="s">
-        <v>467</v>
-      </c>
-      <c r="G474" s="4">
-        <v>10722810240</v>
-      </c>
-      <c r="H474" t="s">
-        <v>945</v>
-      </c>
-      <c r="I474" t="s">
-        <v>296</v>
-      </c>
-      <c r="J474" t="s">
-        <v>460</v>
-      </c>
-      <c r="K474" t="s">
-        <v>976</v>
-      </c>
-      <c r="L474" t="s">
-        <v>88</v>
-      </c>
-      <c r="M474" s="1">
-        <v>0</v>
-      </c>
-      <c r="N474" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="475" spans="1:14">
-      <c r="A475" t="s">
-        <v>883</v>
-      </c>
-      <c r="B475" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="C475">
-        <v>2026</v>
-      </c>
-      <c r="D475">
-        <v>6</v>
-      </c>
-      <c r="E475" t="s">
-        <v>65</v>
-      </c>
-      <c r="F475" t="s">
-        <v>467</v>
-      </c>
-      <c r="G475" s="4">
-        <v>10419589859</v>
-      </c>
-      <c r="H475" t="s">
-        <v>449</v>
-      </c>
-      <c r="I475" t="s">
-        <v>296</v>
-      </c>
-      <c r="J475" t="s">
-        <v>460</v>
-      </c>
-      <c r="K475" t="s">
-        <v>976</v>
-      </c>
-      <c r="L475" t="s">
-        <v>88</v>
-      </c>
-      <c r="M475" s="1">
-        <v>0</v>
-      </c>
-      <c r="N475" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="476" spans="1:14">
-      <c r="A476" t="s">
-        <v>884</v>
-      </c>
-      <c r="B476" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="C476">
-        <v>2026</v>
-      </c>
-      <c r="D476">
-        <v>6</v>
-      </c>
-      <c r="E476" t="s">
-        <v>65</v>
-      </c>
-      <c r="F476" t="s">
-        <v>467</v>
-      </c>
-      <c r="G476" s="4">
-        <v>10426361936</v>
-      </c>
-      <c r="H476" t="s">
-        <v>946</v>
-      </c>
-      <c r="I476" t="s">
-        <v>296</v>
-      </c>
-      <c r="J476" t="s">
-        <v>460</v>
-      </c>
-      <c r="K476" t="s">
-        <v>976</v>
-      </c>
-      <c r="L476" t="s">
-        <v>88</v>
-      </c>
-      <c r="M476" s="1">
-        <v>0</v>
-      </c>
-      <c r="N476" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="477" spans="1:14">
-      <c r="A477" t="s">
-        <v>885</v>
-      </c>
-      <c r="B477" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="C477">
-        <v>2026</v>
-      </c>
-      <c r="D477">
-        <v>6</v>
-      </c>
-      <c r="E477" t="s">
-        <v>65</v>
-      </c>
-      <c r="F477" t="s">
-        <v>467</v>
-      </c>
-      <c r="G477" s="4">
-        <v>10253224806</v>
-      </c>
-      <c r="H477" t="s">
-        <v>407</v>
-      </c>
-      <c r="I477" t="s">
-        <v>296</v>
-      </c>
-      <c r="J477" t="s">
-        <v>460</v>
-      </c>
-      <c r="K477" t="s">
-        <v>976</v>
-      </c>
-      <c r="L477" t="s">
-        <v>88</v>
-      </c>
-      <c r="M477" s="1">
-        <v>0</v>
-      </c>
-      <c r="N477" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="478" spans="1:14">
-      <c r="A478" t="s">
-        <v>886</v>
-      </c>
-      <c r="B478" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="C478">
-        <v>2026</v>
-      </c>
-      <c r="D478">
-        <v>6</v>
-      </c>
-      <c r="E478" t="s">
-        <v>65</v>
-      </c>
-      <c r="F478" t="s">
-        <v>467</v>
-      </c>
-      <c r="G478" s="4">
-        <v>10249582862</v>
-      </c>
-      <c r="H478" t="s">
-        <v>947</v>
-      </c>
-      <c r="I478" t="s">
-        <v>296</v>
-      </c>
-      <c r="J478" t="s">
-        <v>460</v>
-      </c>
-      <c r="K478" t="s">
-        <v>976</v>
-      </c>
-      <c r="L478" t="s">
-        <v>88</v>
-      </c>
-      <c r="M478" s="1">
-        <v>0</v>
-      </c>
-      <c r="N478" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="479" spans="1:14">
-      <c r="A479" t="s">
-        <v>887</v>
-      </c>
-      <c r="B479" s="4" t="s">
-        <v>911</v>
-      </c>
-      <c r="C479">
-        <v>2026</v>
-      </c>
-      <c r="D479">
-        <v>6</v>
-      </c>
-      <c r="E479" t="s">
-        <v>65</v>
-      </c>
-      <c r="F479" t="s">
-        <v>402</v>
-      </c>
-      <c r="G479" s="4">
-        <v>23922343</v>
-      </c>
-      <c r="H479" t="s">
-        <v>447</v>
-      </c>
-      <c r="I479" t="s">
-        <v>451</v>
-      </c>
-      <c r="J479" t="s">
-        <v>454</v>
-      </c>
-      <c r="K479" t="s">
-        <v>973</v>
-      </c>
-      <c r="L479" t="s">
-        <v>88</v>
-      </c>
-      <c r="M479">
-        <v>1</v>
-      </c>
-      <c r="N479" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="480" spans="1:14">
-      <c r="A480" t="s">
-        <v>888</v>
-      </c>
-      <c r="B480" s="4" t="s">
-        <v>912</v>
-      </c>
-      <c r="C480">
-        <v>2026</v>
-      </c>
-      <c r="D480">
-        <v>6</v>
-      </c>
-      <c r="E480" t="s">
-        <v>65</v>
-      </c>
-      <c r="F480" t="s">
-        <v>401</v>
-      </c>
-      <c r="G480" s="4">
-        <v>10238869094</v>
-      </c>
-      <c r="H480" t="s">
-        <v>935</v>
-      </c>
-      <c r="I480" t="s">
-        <v>403</v>
-      </c>
-      <c r="J480" t="s">
-        <v>458</v>
-      </c>
-      <c r="K480" t="s">
-        <v>974</v>
-      </c>
-      <c r="L480" t="s">
-        <v>88</v>
-      </c>
-      <c r="M480">
-        <v>4</v>
-      </c>
-      <c r="N480" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="481" spans="1:14">
-      <c r="A481" t="s">
-        <v>889</v>
-      </c>
-      <c r="B481" s="4" t="s">
-        <v>912</v>
-      </c>
-      <c r="C481">
-        <v>2026</v>
-      </c>
-      <c r="D481">
-        <v>6</v>
-      </c>
-      <c r="E481" t="s">
-        <v>65</v>
-      </c>
-      <c r="F481" t="s">
-        <v>401</v>
-      </c>
-      <c r="G481" s="4">
-        <v>10247032270</v>
-      </c>
-      <c r="H481" t="s">
-        <v>936</v>
-      </c>
-      <c r="I481" t="s">
-        <v>403</v>
-      </c>
-      <c r="J481" t="s">
-        <v>458</v>
-      </c>
-      <c r="K481" t="s">
-        <v>975</v>
-      </c>
-      <c r="L481" t="s">
-        <v>88</v>
-      </c>
-      <c r="M481">
-        <v>4</v>
-      </c>
-      <c r="N481" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="482" spans="1:14">
-      <c r="A482" t="s">
-        <v>890</v>
-      </c>
-      <c r="B482" s="4" t="s">
-        <v>917</v>
-      </c>
-      <c r="C482">
-        <v>2026</v>
-      </c>
-      <c r="D482">
-        <v>6</v>
-      </c>
-      <c r="E482" t="s">
-        <v>65</v>
-      </c>
-      <c r="F482" t="s">
-        <v>48</v>
-      </c>
-      <c r="G482" s="4">
-        <v>10252188041</v>
-      </c>
-      <c r="H482" t="s">
-        <v>305</v>
-      </c>
-      <c r="I482" t="s">
-        <v>453</v>
-      </c>
-      <c r="J482" t="s">
-        <v>459</v>
-      </c>
-      <c r="K482" t="s">
-        <v>979</v>
-      </c>
-      <c r="L482" t="s">
-        <v>88</v>
-      </c>
-      <c r="M482">
-        <v>324</v>
-      </c>
-      <c r="N482" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="483" spans="1:14">
-      <c r="A483" t="s">
-        <v>891</v>
-      </c>
-      <c r="B483" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="C483">
-        <v>2026</v>
-      </c>
-      <c r="D483">
-        <v>6</v>
-      </c>
-      <c r="E483" t="s">
-        <v>65</v>
-      </c>
-      <c r="F483" t="s">
-        <v>401</v>
-      </c>
-      <c r="G483" s="4" t="s">
-        <v>1045</v>
-      </c>
-      <c r="H483" t="s">
-        <v>957</v>
-      </c>
-      <c r="I483" t="s">
-        <v>296</v>
-      </c>
-      <c r="J483" t="s">
-        <v>460</v>
-      </c>
-      <c r="K483" t="s">
-        <v>978</v>
-      </c>
-      <c r="L483" t="s">
-        <v>88</v>
-      </c>
-      <c r="M483">
-        <v>1</v>
-      </c>
-      <c r="N483" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="484" spans="1:14">
-      <c r="A484" t="s">
-        <v>892</v>
-      </c>
-      <c r="B484" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="C484">
-        <v>2026</v>
-      </c>
-      <c r="D484">
-        <v>6</v>
-      </c>
-      <c r="E484" t="s">
-        <v>65</v>
-      </c>
-      <c r="F484" t="s">
-        <v>401</v>
-      </c>
-      <c r="G484" s="4" t="s">
-        <v>1046</v>
-      </c>
-      <c r="H484" t="s">
-        <v>958</v>
-      </c>
-      <c r="I484" t="s">
-        <v>296</v>
-      </c>
-      <c r="J484" t="s">
-        <v>460</v>
-      </c>
-      <c r="K484" t="s">
-        <v>978</v>
-      </c>
-      <c r="L484" t="s">
-        <v>88</v>
-      </c>
-      <c r="M484">
-        <v>1</v>
-      </c>
-      <c r="N484" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="485" spans="1:14">
-      <c r="A485" t="s">
-        <v>893</v>
-      </c>
-      <c r="B485" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="C485">
-        <v>2026</v>
-      </c>
-      <c r="D485">
-        <v>6</v>
-      </c>
-      <c r="E485" t="s">
-        <v>65</v>
-      </c>
-      <c r="F485" t="s">
-        <v>401</v>
-      </c>
-      <c r="G485" s="4" t="s">
-        <v>1047</v>
-      </c>
-      <c r="H485" t="s">
-        <v>959</v>
-      </c>
-      <c r="I485" t="s">
-        <v>296</v>
-      </c>
-      <c r="J485" t="s">
-        <v>460</v>
-      </c>
-      <c r="K485" t="s">
-        <v>978</v>
-      </c>
-      <c r="L485" t="s">
-        <v>88</v>
-      </c>
-      <c r="M485">
-        <v>1</v>
-      </c>
-      <c r="N485" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="486" spans="1:14">
-      <c r="A486" t="s">
-        <v>894</v>
-      </c>
-      <c r="B486" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="C486">
-        <v>2026</v>
-      </c>
-      <c r="D486">
-        <v>6</v>
-      </c>
-      <c r="E486" t="s">
-        <v>65</v>
-      </c>
-      <c r="F486" t="s">
-        <v>401</v>
-      </c>
-      <c r="G486" s="4" t="s">
-        <v>1048</v>
-      </c>
-      <c r="H486" t="s">
-        <v>960</v>
-      </c>
-      <c r="I486" t="s">
-        <v>296</v>
-      </c>
-      <c r="J486" t="s">
-        <v>460</v>
-      </c>
-      <c r="K486" t="s">
-        <v>978</v>
-      </c>
-      <c r="L486" t="s">
-        <v>88</v>
-      </c>
-      <c r="M486">
-        <v>1</v>
-      </c>
-      <c r="N486" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="487" spans="1:14">
-      <c r="A487" t="s">
-        <v>895</v>
-      </c>
-      <c r="B487" s="3">
-        <v>46190</v>
-      </c>
-      <c r="C487">
-        <v>2026</v>
-      </c>
-      <c r="D487">
-        <v>6</v>
-      </c>
-      <c r="E487" t="s">
-        <v>65</v>
-      </c>
-      <c r="F487" t="s">
-        <v>401</v>
-      </c>
-      <c r="G487" s="4" t="s">
-        <v>1049</v>
-      </c>
-      <c r="H487" t="s">
-        <v>961</v>
-      </c>
-      <c r="I487" t="s">
-        <v>296</v>
-      </c>
-      <c r="J487" t="s">
-        <v>460</v>
-      </c>
-      <c r="K487" t="s">
-        <v>978</v>
-      </c>
-      <c r="L487" t="s">
-        <v>88</v>
-      </c>
-      <c r="M487">
-        <v>1</v>
-      </c>
-      <c r="N487" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="488" spans="1:14">
-      <c r="A488" t="s">
-        <v>896</v>
-      </c>
-      <c r="B488" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="C488">
-        <v>2026</v>
-      </c>
-      <c r="D488">
-        <v>6</v>
-      </c>
-      <c r="E488" t="s">
-        <v>65</v>
-      </c>
-      <c r="F488" t="s">
-        <v>401</v>
-      </c>
-      <c r="G488" s="4" t="s">
-        <v>1050</v>
-      </c>
-      <c r="H488" t="s">
-        <v>962</v>
-      </c>
-      <c r="I488" t="s">
-        <v>296</v>
-      </c>
-      <c r="J488" t="s">
-        <v>460</v>
-      </c>
-      <c r="K488" t="s">
-        <v>978</v>
-      </c>
-      <c r="L488" t="s">
-        <v>88</v>
-      </c>
-      <c r="M488">
-        <v>1</v>
-      </c>
-      <c r="N488" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="489" spans="1:14">
-      <c r="A489" t="s">
-        <v>897</v>
-      </c>
-      <c r="B489" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="C489">
-        <v>2026</v>
-      </c>
-      <c r="D489">
-        <v>6</v>
-      </c>
-      <c r="E489" t="s">
-        <v>65</v>
-      </c>
-      <c r="F489" t="s">
-        <v>401</v>
-      </c>
-      <c r="G489" s="4" t="s">
-        <v>1051</v>
-      </c>
-      <c r="H489" t="s">
-        <v>963</v>
-      </c>
-      <c r="I489" t="s">
-        <v>296</v>
-      </c>
-      <c r="J489" t="s">
-        <v>460</v>
-      </c>
-      <c r="K489" t="s">
-        <v>978</v>
-      </c>
-      <c r="L489" t="s">
-        <v>88</v>
-      </c>
-      <c r="M489">
-        <v>1</v>
-      </c>
-      <c r="N489" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="490" spans="1:14">
-      <c r="A490" t="s">
-        <v>898</v>
-      </c>
-      <c r="B490" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="C490">
-        <v>2026</v>
-      </c>
-      <c r="D490">
-        <v>6</v>
-      </c>
-      <c r="E490" t="s">
-        <v>65</v>
-      </c>
-      <c r="F490" t="s">
-        <v>401</v>
-      </c>
-      <c r="G490" s="4" t="s">
-        <v>1052</v>
-      </c>
-      <c r="H490" t="s">
-        <v>964</v>
-      </c>
-      <c r="I490" t="s">
-        <v>296</v>
-      </c>
-      <c r="J490" t="s">
-        <v>460</v>
-      </c>
-      <c r="K490" t="s">
-        <v>978</v>
-      </c>
-      <c r="L490" t="s">
-        <v>88</v>
-      </c>
-      <c r="M490">
-        <v>1</v>
-      </c>
-      <c r="N490" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="491" spans="1:14">
-      <c r="A491" t="s">
-        <v>899</v>
-      </c>
-      <c r="B491" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="C491">
-        <v>2026</v>
-      </c>
-      <c r="D491">
-        <v>6</v>
-      </c>
-      <c r="E491" t="s">
-        <v>65</v>
-      </c>
-      <c r="F491" t="s">
-        <v>401</v>
-      </c>
-      <c r="G491" s="4" t="s">
-        <v>1053</v>
-      </c>
-      <c r="H491" t="s">
-        <v>965</v>
-      </c>
-      <c r="I491" t="s">
-        <v>296</v>
-      </c>
-      <c r="J491" t="s">
-        <v>460</v>
-      </c>
-      <c r="K491" t="s">
-        <v>978</v>
-      </c>
-      <c r="L491" t="s">
-        <v>88</v>
-      </c>
-      <c r="M491">
-        <v>1</v>
-      </c>
-      <c r="N491" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="492" spans="1:14">
-      <c r="A492" t="s">
-        <v>900</v>
-      </c>
-      <c r="B492" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="C492">
-        <v>2026</v>
-      </c>
-      <c r="D492">
-        <v>6</v>
-      </c>
-      <c r="E492" t="s">
-        <v>65</v>
-      </c>
-      <c r="F492" t="s">
-        <v>401</v>
-      </c>
-      <c r="G492" s="4" t="s">
-        <v>1054</v>
-      </c>
-      <c r="H492" t="s">
-        <v>966</v>
-      </c>
-      <c r="I492" t="s">
-        <v>296</v>
-      </c>
-      <c r="J492" t="s">
-        <v>460</v>
-      </c>
-      <c r="K492" t="s">
-        <v>978</v>
-      </c>
-      <c r="L492" t="s">
-        <v>88</v>
-      </c>
-      <c r="M492">
-        <v>1</v>
-      </c>
-      <c r="N492" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="493" spans="1:14">
-      <c r="A493" t="s">
-        <v>901</v>
-      </c>
-      <c r="B493" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="C493">
-        <v>2026</v>
-      </c>
-      <c r="D493">
-        <v>6</v>
-      </c>
-      <c r="E493" t="s">
-        <v>65</v>
-      </c>
-      <c r="F493" t="s">
-        <v>401</v>
-      </c>
-      <c r="G493" s="4" t="s">
-        <v>1055</v>
-      </c>
-      <c r="H493" t="s">
-        <v>967</v>
-      </c>
-      <c r="I493" t="s">
-        <v>296</v>
-      </c>
-      <c r="J493" t="s">
-        <v>460</v>
-      </c>
-      <c r="K493" t="s">
-        <v>978</v>
-      </c>
-      <c r="L493" t="s">
-        <v>88</v>
-      </c>
-      <c r="M493">
-        <v>1</v>
-      </c>
-      <c r="N493" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="494" spans="1:14">
-      <c r="A494" t="s">
-        <v>902</v>
-      </c>
-      <c r="B494" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="C494">
-        <v>2026</v>
-      </c>
-      <c r="D494">
-        <v>6</v>
-      </c>
-      <c r="E494" t="s">
-        <v>65</v>
-      </c>
-      <c r="F494" t="s">
-        <v>401</v>
-      </c>
-      <c r="G494" s="4" t="s">
-        <v>1056</v>
-      </c>
-      <c r="H494" t="s">
-        <v>968</v>
-      </c>
-      <c r="I494" t="s">
-        <v>296</v>
-      </c>
-      <c r="J494" t="s">
-        <v>460</v>
-      </c>
-      <c r="K494" t="s">
-        <v>978</v>
-      </c>
-      <c r="L494" t="s">
-        <v>88</v>
-      </c>
-      <c r="M494">
-        <v>1</v>
-      </c>
-      <c r="N494" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="495" spans="1:14">
-      <c r="A495" t="s">
-        <v>903</v>
-      </c>
-      <c r="B495" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="C495">
-        <v>2026</v>
-      </c>
-      <c r="D495">
-        <v>6</v>
-      </c>
-      <c r="E495" t="s">
-        <v>65</v>
-      </c>
-      <c r="F495" t="s">
-        <v>401</v>
-      </c>
-      <c r="G495" s="4" t="s">
-        <v>1057</v>
-      </c>
-      <c r="H495" t="s">
-        <v>969</v>
-      </c>
-      <c r="I495" t="s">
-        <v>296</v>
-      </c>
-      <c r="J495" t="s">
-        <v>460</v>
-      </c>
-      <c r="K495" t="s">
-        <v>978</v>
-      </c>
-      <c r="L495" t="s">
-        <v>88</v>
-      </c>
-      <c r="M495">
-        <v>1</v>
-      </c>
-      <c r="N495" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="496" spans="1:14">
-      <c r="A496" t="s">
-        <v>904</v>
-      </c>
-      <c r="B496" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="C496">
-        <v>2026</v>
-      </c>
-      <c r="D496">
-        <v>6</v>
-      </c>
-      <c r="E496" t="s">
-        <v>65</v>
-      </c>
-      <c r="F496" t="s">
-        <v>401</v>
-      </c>
-      <c r="G496" s="4" t="s">
-        <v>1058</v>
-      </c>
-      <c r="H496" t="s">
-        <v>970</v>
-      </c>
-      <c r="I496" t="s">
-        <v>296</v>
-      </c>
-      <c r="J496" t="s">
-        <v>460</v>
-      </c>
-      <c r="K496" t="s">
-        <v>978</v>
-      </c>
-      <c r="L496" t="s">
-        <v>88</v>
-      </c>
-      <c r="M496">
-        <v>1</v>
-      </c>
-      <c r="N496" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="497" spans="1:14">
-      <c r="A497" t="s">
-        <v>905</v>
-      </c>
-      <c r="B497" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="C497">
-        <v>2026</v>
-      </c>
-      <c r="D497">
-        <v>6</v>
-      </c>
-      <c r="E497" t="s">
-        <v>65</v>
-      </c>
-      <c r="F497" t="s">
-        <v>401</v>
-      </c>
-      <c r="G497" s="4" t="s">
-        <v>1059</v>
-      </c>
-      <c r="H497" t="s">
-        <v>971</v>
-      </c>
-      <c r="I497" t="s">
-        <v>296</v>
-      </c>
-      <c r="J497" t="s">
-        <v>460</v>
-      </c>
-      <c r="K497" t="s">
-        <v>978</v>
-      </c>
-      <c r="L497" t="s">
-        <v>88</v>
-      </c>
-      <c r="M497">
-        <v>1</v>
-      </c>
-      <c r="N497" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="498" spans="1:14">
-      <c r="A498" t="s">
-        <v>906</v>
-      </c>
-      <c r="B498" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C498">
-        <v>2026</v>
-      </c>
-      <c r="D498">
-        <v>6</v>
-      </c>
-      <c r="E498" t="s">
-        <v>65</v>
-      </c>
-      <c r="F498" t="s">
-        <v>354</v>
-      </c>
-      <c r="G498" s="4" t="s">
-        <v>1065</v>
-      </c>
-      <c r="H498" t="s">
-        <v>302</v>
-      </c>
-      <c r="I498" t="s">
-        <v>50</v>
-      </c>
-      <c r="J498" t="s">
-        <v>463</v>
-      </c>
-      <c r="K498" t="s">
+      <c r="K504" s="9" t="s">
         <v>1060</v>
       </c>
-      <c r="L498" t="s">
-        <v>88</v>
-      </c>
-      <c r="M498">
-        <v>1</v>
-      </c>
-      <c r="N498" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="499" spans="1:14">
-      <c r="A499" t="s">
-        <v>907</v>
-      </c>
-      <c r="B499" s="4" t="s">
-        <v>911</v>
-      </c>
-      <c r="C499">
-        <v>2026</v>
-      </c>
-      <c r="D499">
-        <v>6</v>
-      </c>
-      <c r="E499" t="s">
-        <v>65</v>
-      </c>
-      <c r="F499" t="s">
-        <v>354</v>
-      </c>
-      <c r="G499" s="4" t="s">
-        <v>1066</v>
-      </c>
-      <c r="H499" t="s">
-        <v>1069</v>
-      </c>
-      <c r="I499" t="s">
-        <v>50</v>
-      </c>
-      <c r="J499" t="s">
-        <v>463</v>
-      </c>
-      <c r="K499" t="s">
-        <v>1061</v>
-      </c>
-      <c r="L499" t="s">
-        <v>88</v>
-      </c>
-      <c r="M499">
-        <v>1</v>
-      </c>
-      <c r="N499" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="500" spans="1:14">
-      <c r="A500" t="s">
-        <v>908</v>
-      </c>
-      <c r="B500" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="C500">
-        <v>2026</v>
-      </c>
-      <c r="D500">
-        <v>6</v>
-      </c>
-      <c r="E500" t="s">
-        <v>65</v>
-      </c>
-      <c r="F500" t="s">
-        <v>354</v>
-      </c>
-      <c r="G500" s="4" t="s">
-        <v>1067</v>
-      </c>
-      <c r="H500" t="s">
-        <v>300</v>
-      </c>
-      <c r="I500" t="s">
-        <v>50</v>
-      </c>
-      <c r="J500" t="s">
-        <v>463</v>
-      </c>
-      <c r="K500" t="s">
-        <v>1062</v>
-      </c>
-      <c r="L500" t="s">
-        <v>88</v>
-      </c>
-      <c r="M500">
-        <v>1</v>
-      </c>
-      <c r="N500" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="501" spans="1:14">
-      <c r="A501" t="s">
-        <v>909</v>
-      </c>
-      <c r="B501" s="4" t="s">
-        <v>911</v>
-      </c>
-      <c r="C501">
-        <v>2026</v>
-      </c>
-      <c r="D501">
-        <v>6</v>
-      </c>
-      <c r="E501" t="s">
-        <v>65</v>
-      </c>
-      <c r="F501" t="s">
-        <v>354</v>
-      </c>
-      <c r="G501" s="4" t="s">
-        <v>1068</v>
-      </c>
-      <c r="H501" t="s">
-        <v>70</v>
-      </c>
-      <c r="I501" t="s">
-        <v>50</v>
-      </c>
-      <c r="J501" t="s">
-        <v>463</v>
-      </c>
-      <c r="K501" t="s">
-        <v>1063</v>
-      </c>
-      <c r="L501" t="s">
-        <v>88</v>
-      </c>
-      <c r="M501">
-        <v>1</v>
-      </c>
-      <c r="N501" t="s">
+      <c r="M504" s="9">
+        <v>1</v>
+      </c>
+      <c r="N504" s="9" t="s">
         <v>90</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O486">
-    <sortCondition ref="E479:E486"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O485">
+    <sortCondition ref="E478:E485"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="G483:G497 G498:G501" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56E6F75-5503-41F6-B5EE-0FC985031AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE6CF33-11D7-4758-8F48-19472F8D9F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25471,7 +25471,7 @@
         <v>65</v>
       </c>
       <c r="F480" s="9" t="s">
-        <v>47</v>
+        <v>353</v>
       </c>
       <c r="G480" s="11">
         <v>20172474501</v>
@@ -25512,7 +25512,7 @@
         <v>65</v>
       </c>
       <c r="F481" s="9" t="s">
-        <v>47</v>
+        <v>353</v>
       </c>
       <c r="G481" s="11">
         <v>20155945860</v>
@@ -25594,7 +25594,7 @@
         <v>65</v>
       </c>
       <c r="F483" s="9" t="s">
-        <v>47</v>
+        <v>354</v>
       </c>
       <c r="G483" s="11">
         <v>73622059</v>
@@ -25635,7 +25635,7 @@
         <v>65</v>
       </c>
       <c r="F484" s="9" t="s">
-        <v>47</v>
+        <v>354</v>
       </c>
       <c r="G484" s="11">
         <v>20610561005</v>
@@ -25676,7 +25676,7 @@
         <v>65</v>
       </c>
       <c r="F485" s="9" t="s">
-        <v>47</v>
+        <v>353</v>
       </c>
       <c r="G485" s="11">
         <v>10700937645</v>
@@ -25717,7 +25717,7 @@
         <v>65</v>
       </c>
       <c r="F486" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G486" s="11">
         <v>10742273674</v>
@@ -25758,7 +25758,7 @@
         <v>65</v>
       </c>
       <c r="F487" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G487" s="11">
         <v>40927397</v>
@@ -25799,7 +25799,7 @@
         <v>65</v>
       </c>
       <c r="F488" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G488" s="11">
         <v>10239510197</v>
@@ -25840,7 +25840,7 @@
         <v>65</v>
       </c>
       <c r="F489" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G489" s="11">
         <v>47388875</v>

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E71CFB-001D-412D-84BC-8F795E456CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DDD0A85-94B5-4136-95FC-4425EFC4CC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7F4A73-A0AF-444B-B343-196055B44B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFB8EEC-54A5-407A-A092-E11D9C5E1754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33961,7 +33961,7 @@
         <v>529</v>
       </c>
       <c r="N609" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O609" s="1" t="s">
         <v>50</v>
@@ -34005,7 +34005,7 @@
         <v>529</v>
       </c>
       <c r="N610" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O610" s="1" t="s">
         <v>50</v>

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFB8EEC-54A5-407A-A092-E11D9C5E1754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54564F4C-2988-4F0E-B4EA-A24555FAB13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6791" uniqueCount="1300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6790" uniqueCount="1299">
   <si>
     <t>ID_ACTIVIDAD</t>
   </si>
@@ -3649,9 +3649,6 @@
   </si>
   <si>
     <t>07/07/2026</t>
-  </si>
-  <si>
-    <t>08/08/2026</t>
   </si>
   <si>
     <t>14/07/2026</t>
@@ -31225,7 +31222,7 @@
     </row>
     <row r="555" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="B555" s="7" t="s">
         <v>1176</v>
@@ -31246,7 +31243,7 @@
         <v>73870421</v>
       </c>
       <c r="H555" s="1" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="I555" s="1" t="s">
         <v>515</v>
@@ -31258,7 +31255,7 @@
         <v>245</v>
       </c>
       <c r="L555" s="1" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="M555" s="1" t="s">
         <v>529</v>
@@ -31275,7 +31272,7 @@
     </row>
     <row r="556" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="B556" s="7" t="s">
         <v>1177</v>
@@ -31308,7 +31305,7 @@
         <v>245</v>
       </c>
       <c r="L556" s="1" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="M556" s="1" t="s">
         <v>529</v>
@@ -31325,7 +31322,7 @@
     </row>
     <row r="557" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="B557" s="7" t="s">
         <v>1178</v>
@@ -31346,7 +31343,7 @@
         <v>10425662347</v>
       </c>
       <c r="H557" s="1" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="I557" s="1" t="s">
         <v>515</v>
@@ -31358,7 +31355,7 @@
         <v>245</v>
       </c>
       <c r="L557" s="1" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="M557" s="1" t="s">
         <v>529</v>
@@ -31375,7 +31372,7 @@
     </row>
     <row r="558" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="B558" s="7" t="s">
         <v>1179</v>
@@ -31408,7 +31405,7 @@
         <v>245</v>
       </c>
       <c r="L558" s="1" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="M558" s="1" t="s">
         <v>529</v>
@@ -31425,7 +31422,7 @@
     </row>
     <row r="559" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B559" s="7" t="s">
         <v>1179</v>
@@ -31458,7 +31455,7 @@
         <v>245</v>
       </c>
       <c r="L559" s="1" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="M559" s="1" t="s">
         <v>529</v>
@@ -31475,7 +31472,7 @@
     </row>
     <row r="560" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="B560" s="7" t="s">
         <v>1180</v>
@@ -31508,7 +31505,7 @@
         <v>245</v>
       </c>
       <c r="L560" s="1" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="M560" s="1" t="s">
         <v>529</v>
@@ -31525,7 +31522,7 @@
     </row>
     <row r="561" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B561" s="7" t="s">
         <v>1178</v>
@@ -31546,7 +31543,7 @@
         <v>43150763</v>
       </c>
       <c r="H561" s="1" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="I561" s="1" t="s">
         <v>515</v>
@@ -31558,7 +31555,7 @@
         <v>245</v>
       </c>
       <c r="L561" s="1" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="M561" s="1" t="s">
         <v>529</v>
@@ -31575,7 +31572,7 @@
     </row>
     <row r="562" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B562" s="7" t="s">
         <v>1177</v>
@@ -31608,7 +31605,7 @@
         <v>245</v>
       </c>
       <c r="L562" s="1" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="M562" s="1" t="s">
         <v>529</v>
@@ -31625,10 +31622,10 @@
     </row>
     <row r="563" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
-        <v>1204</v>
-      </c>
-      <c r="B563" s="7" t="s">
-        <v>1181</v>
+        <v>1203</v>
+      </c>
+      <c r="B563" s="8">
+        <v>46211</v>
       </c>
       <c r="C563" s="1">
         <v>2026</v>
@@ -31646,7 +31643,7 @@
         <v>10310385765</v>
       </c>
       <c r="H563" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="I563" s="1" t="s">
         <v>516</v>
@@ -31658,7 +31655,7 @@
         <v>245</v>
       </c>
       <c r="L563" s="1" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="M563" s="1" t="s">
         <v>529</v>
@@ -31675,10 +31672,10 @@
     </row>
     <row r="564" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="B564" s="7" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C564" s="1">
         <v>2026</v>
@@ -31708,7 +31705,7 @@
         <v>245</v>
       </c>
       <c r="L564" s="1" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="M564" s="1" t="s">
         <v>529</v>
@@ -31725,10 +31722,10 @@
     </row>
     <row r="565" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="B565" s="7" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C565" s="1">
         <v>2026</v>
@@ -31758,7 +31755,7 @@
         <v>245</v>
       </c>
       <c r="L565" s="1" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="M565" s="1" t="s">
         <v>529</v>
@@ -31775,7 +31772,7 @@
     </row>
     <row r="566" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B566" s="7" t="s">
         <v>1176</v>
@@ -31796,7 +31793,7 @@
         <v>46314028</v>
       </c>
       <c r="H566" s="1" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="I566" s="1" t="s">
         <v>515</v>
@@ -31808,7 +31805,7 @@
         <v>245</v>
       </c>
       <c r="L566" s="1" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="M566" s="1" t="s">
         <v>529</v>
@@ -31825,7 +31822,7 @@
     </row>
     <row r="567" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B567" s="7" t="s">
         <v>1142</v>
@@ -31846,7 +31843,7 @@
         <v>10484849337</v>
       </c>
       <c r="H567" s="1" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="I567" s="1" t="s">
         <v>515</v>
@@ -31858,7 +31855,7 @@
         <v>245</v>
       </c>
       <c r="L567" s="1" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="M567" s="1" t="s">
         <v>529</v>
@@ -31875,10 +31872,10 @@
     </row>
     <row r="568" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B568" s="7" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C568" s="1">
         <v>2026</v>
@@ -31908,7 +31905,7 @@
         <v>245</v>
       </c>
       <c r="L568" s="1" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="M568" s="1" t="s">
         <v>529</v>
@@ -31925,7 +31922,7 @@
     </row>
     <row r="569" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="B569" s="7" t="s">
         <v>1179</v>
@@ -31958,7 +31955,7 @@
         <v>247</v>
       </c>
       <c r="L569" s="1" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="M569" s="1" t="s">
         <v>529</v>
@@ -31975,7 +31972,7 @@
     </row>
     <row r="570" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="B570" s="7" t="s">
         <v>1178</v>
@@ -32008,7 +32005,7 @@
         <v>245</v>
       </c>
       <c r="L570" s="1" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="M570" s="1" t="s">
         <v>529</v>
@@ -32025,10 +32022,10 @@
     </row>
     <row r="571" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="B571" s="7" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C571" s="1">
         <v>2026</v>
@@ -32058,7 +32055,7 @@
         <v>246</v>
       </c>
       <c r="L571" s="1" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="M571" s="1" t="s">
         <v>529</v>
@@ -32075,10 +32072,10 @@
     </row>
     <row r="572" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="B572" s="7" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="C572" s="1">
         <v>2026</v>
@@ -32108,7 +32105,7 @@
         <v>245</v>
       </c>
       <c r="L572" s="1" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="M572" s="1" t="s">
         <v>529</v>
@@ -32125,10 +32122,10 @@
     </row>
     <row r="573" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="B573" s="7" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C573" s="1">
         <v>2026</v>
@@ -32158,7 +32155,7 @@
         <v>246</v>
       </c>
       <c r="L573" s="1" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="M573" s="1" t="s">
         <v>529</v>
@@ -32175,7 +32172,7 @@
     </row>
     <row r="574" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>1177</v>
@@ -32208,7 +32205,7 @@
         <v>245</v>
       </c>
       <c r="L574" s="1" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="M574" s="1" t="s">
         <v>529</v>
@@ -32225,10 +32222,10 @@
     </row>
     <row r="575" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B575" s="7" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C575" s="1">
         <v>2026</v>
@@ -32258,7 +32255,7 @@
         <v>246</v>
       </c>
       <c r="L575" s="1" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="M575" s="1" t="s">
         <v>529</v>
@@ -32275,7 +32272,7 @@
     </row>
     <row r="576" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="B576" s="7" t="s">
         <v>1141</v>
@@ -32308,7 +32305,7 @@
         <v>245</v>
       </c>
       <c r="L576" s="1" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="M576" s="1" t="s">
         <v>529</v>
@@ -32325,10 +32322,10 @@
     </row>
     <row r="577" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="B577" s="7" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C577" s="1">
         <v>2026</v>
@@ -32358,7 +32355,7 @@
         <v>246</v>
       </c>
       <c r="L577" s="1" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="M577" s="1" t="s">
         <v>529</v>
@@ -32375,10 +32372,10 @@
     </row>
     <row r="578" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="B578" s="7" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C578" s="1">
         <v>2026</v>
@@ -32408,7 +32405,7 @@
         <v>245</v>
       </c>
       <c r="L578" s="1" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="M578" s="1" t="s">
         <v>529</v>
@@ -32425,10 +32422,10 @@
     </row>
     <row r="579" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B579" s="7" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C579" s="1">
         <v>2026</v>
@@ -32458,7 +32455,7 @@
         <v>246</v>
       </c>
       <c r="L579" s="1" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="M579" s="1" t="s">
         <v>529</v>
@@ -32475,7 +32472,7 @@
     </row>
     <row r="580" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="B580" s="7" t="s">
         <v>1142</v>
@@ -32508,7 +32505,7 @@
         <v>245</v>
       </c>
       <c r="L580" s="1" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="M580" s="1" t="s">
         <v>529</v>
@@ -32525,10 +32522,10 @@
     </row>
     <row r="581" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="B581" s="7" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C581" s="1">
         <v>2026</v>
@@ -32558,7 +32555,7 @@
         <v>246</v>
       </c>
       <c r="L581" s="1" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="M581" s="1" t="s">
         <v>529</v>
@@ -32575,10 +32572,10 @@
     </row>
     <row r="582" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="B582" s="7" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C582" s="1">
         <v>2026</v>
@@ -32608,7 +32605,7 @@
         <v>245</v>
       </c>
       <c r="L582" s="1" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="M582" s="1" t="s">
         <v>529</v>
@@ -32625,10 +32622,10 @@
     </row>
     <row r="583" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="B583" s="7" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C583" s="1">
         <v>2026</v>
@@ -32658,7 +32655,7 @@
         <v>246</v>
       </c>
       <c r="L583" s="1" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="M583" s="1" t="s">
         <v>529</v>
@@ -32675,7 +32672,7 @@
     </row>
     <row r="584" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="B584" s="7" t="s">
         <v>1180</v>
@@ -32708,7 +32705,7 @@
         <v>245</v>
       </c>
       <c r="L584" s="1" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="M584" s="1" t="s">
         <v>529</v>
@@ -32725,10 +32722,10 @@
     </row>
     <row r="585" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="B585" s="7" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C585" s="1">
         <v>2026</v>
@@ -32758,7 +32755,7 @@
         <v>246</v>
       </c>
       <c r="L585" s="1" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="M585" s="1" t="s">
         <v>529</v>
@@ -32775,10 +32772,10 @@
     </row>
     <row r="586" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="B586" s="7" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C586" s="1">
         <v>2026</v>
@@ -32808,7 +32805,7 @@
         <v>245</v>
       </c>
       <c r="L586" s="1" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="M586" s="1" t="s">
         <v>529</v>
@@ -32825,10 +32822,10 @@
     </row>
     <row r="587" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="B587" s="7" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C587" s="1">
         <v>2026</v>
@@ -32858,7 +32855,7 @@
         <v>246</v>
       </c>
       <c r="L587" s="1" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="M587" s="1" t="s">
         <v>529</v>
@@ -32875,10 +32872,10 @@
     </row>
     <row r="588" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="B588" s="7" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C588" s="1">
         <v>2026</v>
@@ -32908,7 +32905,7 @@
         <v>245</v>
       </c>
       <c r="L588" s="1" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="M588" s="1" t="s">
         <v>529</v>
@@ -32925,10 +32922,10 @@
     </row>
     <row r="589" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="B589" s="7" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C589" s="1">
         <v>2026</v>
@@ -32958,7 +32955,7 @@
         <v>246</v>
       </c>
       <c r="L589" s="1" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="M589" s="1" t="s">
         <v>529</v>
@@ -32975,10 +32972,10 @@
     </row>
     <row r="590" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="B590" s="7" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C590" s="1">
         <v>2026</v>
@@ -33008,7 +33005,7 @@
         <v>245</v>
       </c>
       <c r="L590" s="1" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="M590" s="1" t="s">
         <v>529</v>
@@ -33025,10 +33022,10 @@
     </row>
     <row r="591" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="B591" s="7" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C591" s="1">
         <v>2026</v>
@@ -33058,7 +33055,7 @@
         <v>246</v>
       </c>
       <c r="L591" s="1" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="M591" s="1" t="s">
         <v>529</v>
@@ -33075,10 +33072,10 @@
     </row>
     <row r="592" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="B592" s="7" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C592" s="1">
         <v>2026</v>
@@ -33108,7 +33105,7 @@
         <v>245</v>
       </c>
       <c r="L592" s="1" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="M592" s="1" t="s">
         <v>529</v>
@@ -33125,10 +33122,10 @@
     </row>
     <row r="593" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="B593" s="7" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C593" s="1">
         <v>2026</v>
@@ -33158,7 +33155,7 @@
         <v>246</v>
       </c>
       <c r="L593" s="1" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="M593" s="1" t="s">
         <v>529</v>
@@ -33175,7 +33172,7 @@
     </row>
     <row r="594" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="B594" s="7" t="s">
         <v>1176</v>
@@ -33208,7 +33205,7 @@
         <v>245</v>
       </c>
       <c r="L594" s="1" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="M594" s="1" t="s">
         <v>529</v>
@@ -33225,10 +33222,10 @@
     </row>
     <row r="595" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="B595" s="7" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C595" s="1">
         <v>2026</v>
@@ -33258,7 +33255,7 @@
         <v>246</v>
       </c>
       <c r="L595" s="1" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="M595" s="1" t="s">
         <v>529</v>
@@ -33275,7 +33272,7 @@
     </row>
     <row r="596" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>1179</v>
@@ -33308,7 +33305,7 @@
         <v>245</v>
       </c>
       <c r="L596" s="1" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="M596" s="1" t="s">
         <v>529</v>
@@ -33325,10 +33322,10 @@
     </row>
     <row r="597" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="B597" s="7" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C597" s="1">
         <v>2026</v>
@@ -33358,7 +33355,7 @@
         <v>246</v>
       </c>
       <c r="L597" s="1" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="M597" s="1" t="s">
         <v>529</v>
@@ -33375,10 +33372,10 @@
     </row>
     <row r="598" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="B598" s="7" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C598" s="1">
         <v>2026</v>
@@ -33408,7 +33405,7 @@
         <v>245</v>
       </c>
       <c r="L598" s="1" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="M598" s="1" t="s">
         <v>529</v>
@@ -33425,10 +33422,10 @@
     </row>
     <row r="599" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="B599" s="7" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C599" s="1">
         <v>2026</v>
@@ -33458,7 +33455,7 @@
         <v>246</v>
       </c>
       <c r="L599" s="1" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="M599" s="1" t="s">
         <v>529</v>
@@ -33475,7 +33472,7 @@
     </row>
     <row r="600" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B600" s="7" t="s">
         <v>1179</v>
@@ -33508,7 +33505,7 @@
         <v>247</v>
       </c>
       <c r="L600" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="M600" s="1" t="s">
         <v>529</v>
@@ -33525,7 +33522,7 @@
     </row>
     <row r="601" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B601" s="7" t="s">
         <v>1179</v>
@@ -33558,7 +33555,7 @@
         <v>247</v>
       </c>
       <c r="L601" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="M601" s="1" t="s">
         <v>529</v>
@@ -33575,10 +33572,10 @@
     </row>
     <row r="602" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="B602" s="7" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C602" s="1">
         <v>2026</v>
@@ -33608,7 +33605,7 @@
         <v>245</v>
       </c>
       <c r="L602" s="1" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="M602" s="1" t="s">
         <v>529</v>
@@ -33625,7 +33622,7 @@
     </row>
     <row r="603" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="B603" s="7" t="s">
         <v>1141</v>
@@ -33658,7 +33655,7 @@
         <v>245</v>
       </c>
       <c r="L603" s="1" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="M603" s="1" t="s">
         <v>529</v>
@@ -33675,10 +33672,10 @@
     </row>
     <row r="604" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="B604" s="7" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C604" s="1">
         <v>2026</v>
@@ -33708,7 +33705,7 @@
         <v>245</v>
       </c>
       <c r="L604" s="1" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="M604" s="1" t="s">
         <v>529</v>
@@ -33725,7 +33722,7 @@
     </row>
     <row r="605" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="B605" s="7" t="s">
         <v>1177</v>
@@ -33758,7 +33755,7 @@
         <v>245</v>
       </c>
       <c r="L605" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="M605" s="1" t="s">
         <v>529</v>
@@ -33775,10 +33772,10 @@
     </row>
     <row r="606" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="B606" s="7" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C606" s="1">
         <v>2026</v>
@@ -33808,7 +33805,7 @@
         <v>245</v>
       </c>
       <c r="L606" s="1" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="M606" s="1" t="s">
         <v>529</v>
@@ -33825,10 +33822,10 @@
     </row>
     <row r="607" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B607" s="7" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C607" s="1">
         <v>2026</v>
@@ -33858,7 +33855,7 @@
         <v>245</v>
       </c>
       <c r="L607" s="1" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="M607" s="1" t="s">
         <v>529</v>
@@ -33875,7 +33872,7 @@
     </row>
     <row r="608" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B608" s="8">
         <v>46227</v>
@@ -33908,7 +33905,7 @@
         <v>245</v>
       </c>
       <c r="L608" s="1" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="M608" s="1" t="s">
         <v>529</v>
@@ -33925,10 +33922,10 @@
     </row>
     <row r="609" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="B609" s="7" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C609" s="1">
         <v>2026</v>
@@ -33955,7 +33952,7 @@
         <v>249</v>
       </c>
       <c r="L609" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="M609" s="1" t="s">
         <v>529</v>
@@ -33969,10 +33966,10 @@
     </row>
     <row r="610" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B610" s="7" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C610" s="1">
         <v>2026</v>
@@ -33999,7 +33996,7 @@
         <v>249</v>
       </c>
       <c r="L610" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="M610" s="1" t="s">
         <v>529</v>
@@ -34013,10 +34010,10 @@
     </row>
     <row r="611" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B611" s="7" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C611" s="1">
         <v>2026</v>
@@ -34034,7 +34031,7 @@
         <v>20606059338</v>
       </c>
       <c r="H611" s="1" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="J611" s="1" t="s">
         <v>194</v>
@@ -34043,7 +34040,7 @@
         <v>249</v>
       </c>
       <c r="L611" s="1" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="M611" s="1" t="s">
         <v>529</v>
@@ -34057,10 +34054,10 @@
     </row>
     <row r="612" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="B612" s="7" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C612" s="1">
         <v>2026</v>
@@ -34087,7 +34084,7 @@
         <v>245</v>
       </c>
       <c r="L612" s="1" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="M612" s="1" t="s">
         <v>529</v>
@@ -34101,10 +34098,10 @@
     </row>
     <row r="613" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="B613" s="7" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="C613" s="1">
         <v>2026</v>
@@ -34131,7 +34128,7 @@
         <v>245</v>
       </c>
       <c r="L613" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="M613" s="1" t="s">
         <v>529</v>
@@ -34145,10 +34142,10 @@
     </row>
     <row r="614" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="B614" s="7" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="C614" s="1">
         <v>2026</v>
@@ -34166,7 +34163,7 @@
         <v>10400403061</v>
       </c>
       <c r="H614" s="1" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="J614" s="1" t="s">
         <v>242</v>
@@ -34175,7 +34172,7 @@
         <v>245</v>
       </c>
       <c r="L614" s="1" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="M614" s="1" t="s">
         <v>529</v>
@@ -34189,10 +34186,10 @@
     </row>
     <row r="615" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="B615" s="7" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="C615" s="1">
         <v>2026</v>
@@ -34210,7 +34207,7 @@
         <v>47656632</v>
       </c>
       <c r="H615" s="1" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="J615" s="1" t="s">
         <v>242</v>
@@ -34219,7 +34216,7 @@
         <v>245</v>
       </c>
       <c r="L615" s="1" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="M615" s="1" t="s">
         <v>529</v>
@@ -34233,10 +34230,10 @@
     </row>
     <row r="616" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B616" s="7" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="C616" s="1">
         <v>2026</v>
@@ -34254,7 +34251,7 @@
         <v>47656632</v>
       </c>
       <c r="H616" s="1" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="J616" s="1" t="s">
         <v>242</v>
@@ -34263,7 +34260,7 @@
         <v>245</v>
       </c>
       <c r="L616" s="1" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="M616" s="1" t="s">
         <v>529</v>
@@ -34277,10 +34274,10 @@
     </row>
     <row r="617" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B617" s="7" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C617" s="1">
         <v>2026</v>
@@ -34307,7 +34304,7 @@
         <v>245</v>
       </c>
       <c r="L617" s="1" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="M617" s="1" t="s">
         <v>529</v>
@@ -34321,10 +34318,10 @@
     </row>
     <row r="618" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="B618" s="7" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C618" s="1">
         <v>2026</v>
@@ -34351,7 +34348,7 @@
         <v>249</v>
       </c>
       <c r="L618" s="1" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="M618" s="1" t="s">
         <v>529</v>
@@ -34365,10 +34362,10 @@
     </row>
     <row r="619" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B619" s="7" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C619" s="1">
         <v>2026</v>
@@ -34386,7 +34383,7 @@
         <v>47925279</v>
       </c>
       <c r="H619" s="1" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="J619" s="1" t="s">
         <v>242</v>
@@ -34395,7 +34392,7 @@
         <v>245</v>
       </c>
       <c r="L619" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="M619" s="1" t="s">
         <v>529</v>

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54564F4C-2988-4F0E-B4EA-A24555FAB13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360A7E21-DC87-49CB-92C2-122CAD083B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6790" uniqueCount="1299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7703" uniqueCount="1425">
   <si>
     <t>ID_ACTIVIDAD</t>
   </si>
@@ -4003,6 +4003,384 @@
   </si>
   <si>
     <t>23/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ROSENAL EVER</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RUTH KAREN</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ALEXANDER</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NANCY REBECA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> YULY LILIANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VANESA JENNIFER</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MAICOOL LEONEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MARISOL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MAGNET GABRIELA</t>
+  </si>
+  <si>
+    <t>Vilcapaza Cutipa Laly Marguth</t>
+  </si>
+  <si>
+    <t>Ccallohuanca Burgos Gary Jordan</t>
+  </si>
+  <si>
+    <t>Cahuana Mamani Nedy Abigail</t>
+  </si>
+  <si>
+    <t>Pelinco Suasaca Sandra Raquel</t>
+  </si>
+  <si>
+    <t>HANCCO CONDORI JAZMIN NAYSHA</t>
+  </si>
+  <si>
+    <t>APAZA YUJRA FLORA FERMINA</t>
+  </si>
+  <si>
+    <t>SUCAPUCA TICONA DANNI VIK</t>
+  </si>
+  <si>
+    <t>HANCCO LOAYZA ALEXANDRA ESTRELLA</t>
+  </si>
+  <si>
+    <t>HILASACA PAJSI FANNY JULIE</t>
+  </si>
+  <si>
+    <t>ZAPANA PARRA DINA YESSICA</t>
+  </si>
+  <si>
+    <t>QUISPE AUCCACUSI TORIBIA</t>
+  </si>
+  <si>
+    <t>USCAPI LEVITA SONIA</t>
+  </si>
+  <si>
+    <t>SILVA RAMOS ROXANA</t>
+  </si>
+  <si>
+    <t>QUISPE PAÑIHUARA NILDA</t>
+  </si>
+  <si>
+    <t>SALLO RAMOS MARLENY</t>
+  </si>
+  <si>
+    <t>QUISPE PAÑIHUARA JAIME HILARIO</t>
+  </si>
+  <si>
+    <t>LLIHUAC AYMA AMELIA</t>
+  </si>
+  <si>
+    <t>MAMANI TIPULA ROSENAL EVER</t>
+  </si>
+  <si>
+    <t>TIPO MULLISACA RUTH KAREN</t>
+  </si>
+  <si>
+    <t>PELINCO SUASACA NANCY REBECA</t>
+  </si>
+  <si>
+    <t>QUISPE HUAMAN YULY LILIANA</t>
+  </si>
+  <si>
+    <t>AGUILAR MAYTA VANESA JENNIFER</t>
+  </si>
+  <si>
+    <t>PARICELA MAMANI MAICOOL LEONEL</t>
+  </si>
+  <si>
+    <t>MALDONADO CHUMBES MARISOL</t>
+  </si>
+  <si>
+    <t>QUISPE CORIMAYHUA MAGNET GABRIELA</t>
+  </si>
+  <si>
+    <t>VILCAPAZA CUTIPA LALY MARGUTH</t>
+  </si>
+  <si>
+    <t>CCALLOHUANCA BURGOS GARY JORDAN</t>
+  </si>
+  <si>
+    <t>CAHUANA MAMANI NIDE</t>
+  </si>
+  <si>
+    <t>PELINCO SUASACA SANDRA RAQUEL</t>
+  </si>
+  <si>
+    <t>CAPACITACIÓN ESPECIALIZADA EN FIELTRO</t>
+  </si>
+  <si>
+    <t>CAPACITACION ESPECIALIZADA EN PRODUCCION SOSTENIBLE Y ECONOMIA CIRCULAR PARA LA EXPORTACION-I</t>
+  </si>
+  <si>
+    <t>CAPACITACIÓN EN ECONOMIA CIRCULAR</t>
+  </si>
+  <si>
+    <t>CONCEPTOS APLICABLES A LA ECONOMÍA CIRCULAR Y SOSTENIBILIDAD PARA LAS MIPYMES</t>
+  </si>
+  <si>
+    <t>ECONOMÍA CIRCULAR APLICADA AL ANÁLISIS DE LABORATORIO DE FIBRAS DE ALPACA</t>
+  </si>
+  <si>
+    <t>C000303</t>
+  </si>
+  <si>
+    <t>C000304</t>
+  </si>
+  <si>
+    <t>C000305</t>
+  </si>
+  <si>
+    <t>C000306</t>
+  </si>
+  <si>
+    <t>C000307</t>
+  </si>
+  <si>
+    <t>C000308</t>
+  </si>
+  <si>
+    <t>C000309</t>
+  </si>
+  <si>
+    <t>C000310</t>
+  </si>
+  <si>
+    <t>C000311</t>
+  </si>
+  <si>
+    <t>C000312</t>
+  </si>
+  <si>
+    <t>C000313</t>
+  </si>
+  <si>
+    <t>C000314</t>
+  </si>
+  <si>
+    <t>C000315</t>
+  </si>
+  <si>
+    <t>C000316</t>
+  </si>
+  <si>
+    <t>C000317</t>
+  </si>
+  <si>
+    <t>C000318</t>
+  </si>
+  <si>
+    <t>C000319</t>
+  </si>
+  <si>
+    <t>C000320</t>
+  </si>
+  <si>
+    <t>C000321</t>
+  </si>
+  <si>
+    <t>C000322</t>
+  </si>
+  <si>
+    <t>C000323</t>
+  </si>
+  <si>
+    <t>C000324</t>
+  </si>
+  <si>
+    <t>C000325</t>
+  </si>
+  <si>
+    <t>C000326</t>
+  </si>
+  <si>
+    <t>C000327</t>
+  </si>
+  <si>
+    <t>C000328</t>
+  </si>
+  <si>
+    <t>C000329</t>
+  </si>
+  <si>
+    <t>C000330</t>
+  </si>
+  <si>
+    <t>C000331</t>
+  </si>
+  <si>
+    <t>C000332</t>
+  </si>
+  <si>
+    <t>C000333</t>
+  </si>
+  <si>
+    <t>C000334</t>
+  </si>
+  <si>
+    <t>C000335</t>
+  </si>
+  <si>
+    <t>C000336</t>
+  </si>
+  <si>
+    <t>C000337</t>
+  </si>
+  <si>
+    <t>C000338</t>
+  </si>
+  <si>
+    <t>C000339</t>
+  </si>
+  <si>
+    <t>C000340</t>
+  </si>
+  <si>
+    <t>C000341</t>
+  </si>
+  <si>
+    <t>C000342</t>
+  </si>
+  <si>
+    <t>C000343</t>
+  </si>
+  <si>
+    <t>C000344</t>
+  </si>
+  <si>
+    <t>C000345</t>
+  </si>
+  <si>
+    <t>C000346</t>
+  </si>
+  <si>
+    <t>C000347</t>
+  </si>
+  <si>
+    <t>C000348</t>
+  </si>
+  <si>
+    <t>C000349</t>
+  </si>
+  <si>
+    <t>C000350</t>
+  </si>
+  <si>
+    <t>C000351</t>
+  </si>
+  <si>
+    <t>C000352</t>
+  </si>
+  <si>
+    <t>C000353</t>
+  </si>
+  <si>
+    <t>C000354</t>
+  </si>
+  <si>
+    <t>C000355</t>
+  </si>
+  <si>
+    <t>C000356</t>
+  </si>
+  <si>
+    <t>C000357</t>
+  </si>
+  <si>
+    <t>C000358</t>
+  </si>
+  <si>
+    <t>C000359</t>
+  </si>
+  <si>
+    <t>C000360</t>
+  </si>
+  <si>
+    <t>C000361</t>
+  </si>
+  <si>
+    <t>C000362</t>
+  </si>
+  <si>
+    <t>C000363</t>
+  </si>
+  <si>
+    <t>C000364</t>
+  </si>
+  <si>
+    <t>C000365</t>
+  </si>
+  <si>
+    <t>C000366</t>
+  </si>
+  <si>
+    <t>C000367</t>
+  </si>
+  <si>
+    <t>C000368</t>
+  </si>
+  <si>
+    <t>C000369</t>
+  </si>
+  <si>
+    <t>C000370</t>
+  </si>
+  <si>
+    <t>C000371</t>
+  </si>
+  <si>
+    <t>C000372</t>
+  </si>
+  <si>
+    <t>C000373</t>
+  </si>
+  <si>
+    <t>C000374</t>
+  </si>
+  <si>
+    <t>C000375</t>
+  </si>
+  <si>
+    <t>C000376</t>
+  </si>
+  <si>
+    <t>C000377</t>
+  </si>
+  <si>
+    <t>C000378</t>
+  </si>
+  <si>
+    <t>C000379</t>
+  </si>
+  <si>
+    <t>C000380</t>
+  </si>
+  <si>
+    <t>C000381</t>
+  </si>
+  <si>
+    <t>C000382</t>
+  </si>
+  <si>
+    <t>C000383</t>
+  </si>
+  <si>
+    <t>C000384</t>
+  </si>
+  <si>
+    <t>C000385</t>
   </si>
 </sst>
 </file>
@@ -4093,7 +4471,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4116,7 +4494,6 @@
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4456,7 +4833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D04F3C6-8190-4D94-9613-CDA0600594BA}">
-  <dimension ref="A1:P619"/>
+  <dimension ref="A1:P702"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -33939,7 +34316,7 @@
       <c r="F609" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G609" s="10">
+      <c r="G609" s="1">
         <v>10238869094</v>
       </c>
       <c r="H609" s="1" t="s">
@@ -33983,7 +34360,7 @@
       <c r="F610" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G610" s="10">
+      <c r="G610" s="1">
         <v>10247032270</v>
       </c>
       <c r="H610" s="1" t="s">
@@ -34002,7 +34379,7 @@
         <v>529</v>
       </c>
       <c r="N610" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O610" s="1" t="s">
         <v>50</v>
@@ -34027,7 +34404,7 @@
       <c r="F611" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G611" s="10">
+      <c r="G611" s="1">
         <v>20606059338</v>
       </c>
       <c r="H611" s="1" t="s">
@@ -34071,7 +34448,7 @@
       <c r="F612" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="G612" s="10">
+      <c r="G612" s="1">
         <v>47614294</v>
       </c>
       <c r="H612" s="1" t="s">
@@ -34115,7 +34492,7 @@
       <c r="F613" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="G613" s="10">
+      <c r="G613" s="1">
         <v>10450876700</v>
       </c>
       <c r="H613" s="1" t="s">
@@ -34159,7 +34536,7 @@
       <c r="F614" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="G614" s="10">
+      <c r="G614" s="1">
         <v>10400403061</v>
       </c>
       <c r="H614" s="1" t="s">
@@ -34203,7 +34580,7 @@
       <c r="F615" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="G615" s="10">
+      <c r="G615" s="1">
         <v>47656632</v>
       </c>
       <c r="H615" s="1" t="s">
@@ -34247,7 +34624,7 @@
       <c r="F616" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="G616" s="10">
+      <c r="G616" s="1">
         <v>47656632</v>
       </c>
       <c r="H616" s="1" t="s">
@@ -34291,7 +34668,7 @@
       <c r="F617" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="G617" s="10">
+      <c r="G617" s="1">
         <v>10462583996</v>
       </c>
       <c r="H617" s="1" t="s">
@@ -34335,7 +34712,7 @@
       <c r="F618" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="G618" s="10">
+      <c r="G618" s="1">
         <v>10462583996</v>
       </c>
       <c r="H618" s="1" t="s">
@@ -34379,7 +34756,7 @@
       <c r="F619" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="G619" s="10">
+      <c r="G619" s="1">
         <v>47925279</v>
       </c>
       <c r="H619" s="1" t="s">
@@ -34404,9 +34781,3910 @@
         <v>50</v>
       </c>
     </row>
+    <row r="620" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A620" s="1" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B620" s="7" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C620" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D620" s="1">
+        <v>7</v>
+      </c>
+      <c r="E620" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F620" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G620" s="1">
+        <v>10248679081</v>
+      </c>
+      <c r="H620" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I620" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J620" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K620" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="L620" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="M620" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N620" s="1">
+        <v>4</v>
+      </c>
+      <c r="O620" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="621" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A621" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B621" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C621" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D621" s="1">
+        <v>7</v>
+      </c>
+      <c r="E621" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F621" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G621" s="1">
+        <v>73321680</v>
+      </c>
+      <c r="H621" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="I621" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J621" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K621" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L621" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M621" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N621" s="1">
+        <v>1</v>
+      </c>
+      <c r="O621" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="622" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A622" s="1" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B622" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C622" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D622" s="1">
+        <v>7</v>
+      </c>
+      <c r="E622" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F622" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G622" s="1">
+        <v>71727977</v>
+      </c>
+      <c r="H622" s="1" t="s">
+        <v>1300</v>
+      </c>
+      <c r="I622" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J622" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K622" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L622" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M622" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N622" s="1">
+        <v>1</v>
+      </c>
+      <c r="O622" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="623" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A623" s="1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B623" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C623" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D623" s="1">
+        <v>7</v>
+      </c>
+      <c r="E623" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F623" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G623" s="1">
+        <v>74311690</v>
+      </c>
+      <c r="H623" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="I623" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J623" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K623" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L623" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M623" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N623" s="1">
+        <v>1</v>
+      </c>
+      <c r="O623" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="624" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A624" s="1" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B624" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C624" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D624" s="1">
+        <v>7</v>
+      </c>
+      <c r="E624" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F624" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G624" s="1">
+        <v>70117107</v>
+      </c>
+      <c r="H624" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="I624" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J624" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K624" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L624" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M624" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N624" s="1">
+        <v>1</v>
+      </c>
+      <c r="O624" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="625" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A625" s="1" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B625" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C625" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D625" s="1">
+        <v>7</v>
+      </c>
+      <c r="E625" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F625" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G625" s="1">
+        <v>60171003</v>
+      </c>
+      <c r="H625" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="I625" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J625" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K625" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L625" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M625" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N625" s="1">
+        <v>1</v>
+      </c>
+      <c r="O625" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="626" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A626" s="1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B626" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C626" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D626" s="1">
+        <v>7</v>
+      </c>
+      <c r="E626" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F626" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G626" s="1">
+        <v>71505538</v>
+      </c>
+      <c r="H626" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="I626" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J626" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K626" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L626" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M626" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N626" s="1">
+        <v>1</v>
+      </c>
+      <c r="O626" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="627" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A627" s="1" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B627" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C627" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D627" s="1">
+        <v>7</v>
+      </c>
+      <c r="E627" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F627" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G627" s="1">
+        <v>61094381</v>
+      </c>
+      <c r="H627" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="I627" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J627" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K627" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L627" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M627" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N627" s="1">
+        <v>1</v>
+      </c>
+      <c r="O627" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="628" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A628" s="1" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B628" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C628" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D628" s="1">
+        <v>7</v>
+      </c>
+      <c r="E628" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F628" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G628" s="1">
+        <v>60566010</v>
+      </c>
+      <c r="H628" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="I628" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J628" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K628" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L628" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M628" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N628" s="1">
+        <v>1</v>
+      </c>
+      <c r="O628" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="629" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A629" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B629" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C629" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D629" s="1">
+        <v>7</v>
+      </c>
+      <c r="E629" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F629" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G629" s="1">
+        <v>72471575</v>
+      </c>
+      <c r="H629" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="I629" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J629" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K629" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L629" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M629" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N629" s="1">
+        <v>1</v>
+      </c>
+      <c r="O629" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="630" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A630" s="1" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B630" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C630" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D630" s="1">
+        <v>7</v>
+      </c>
+      <c r="E630" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F630" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G630" s="1">
+        <v>71873373</v>
+      </c>
+      <c r="H630" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I630" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J630" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K630" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L630" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M630" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N630" s="1">
+        <v>1</v>
+      </c>
+      <c r="O630" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="631" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A631" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B631" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C631" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D631" s="1">
+        <v>7</v>
+      </c>
+      <c r="E631" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F631" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G631" s="1">
+        <v>76747062</v>
+      </c>
+      <c r="H631" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="I631" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J631" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K631" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L631" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M631" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N631" s="1">
+        <v>1</v>
+      </c>
+      <c r="O631" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="632" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A632" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B632" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C632" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D632" s="1">
+        <v>7</v>
+      </c>
+      <c r="E632" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F632" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G632" s="1">
+        <v>72076653</v>
+      </c>
+      <c r="H632" s="1" t="s">
+        <v>1310</v>
+      </c>
+      <c r="I632" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J632" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K632" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L632" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M632" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N632" s="1">
+        <v>1</v>
+      </c>
+      <c r="O632" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="633" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A633" s="1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B633" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C633" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D633" s="1">
+        <v>7</v>
+      </c>
+      <c r="E633" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F633" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G633" s="1">
+        <v>70117125</v>
+      </c>
+      <c r="H633" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="I633" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J633" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K633" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L633" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M633" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N633" s="1">
+        <v>1</v>
+      </c>
+      <c r="O633" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="634" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A634" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B634" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C634" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D634" s="1">
+        <v>7</v>
+      </c>
+      <c r="E634" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F634" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G634" s="1">
+        <v>72495328</v>
+      </c>
+      <c r="H634" s="1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="I634" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J634" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K634" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L634" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M634" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N634" s="1">
+        <v>1</v>
+      </c>
+      <c r="O634" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="635" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A635" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B635" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C635" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D635" s="1">
+        <v>7</v>
+      </c>
+      <c r="E635" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F635" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G635" s="1">
+        <v>75237035</v>
+      </c>
+      <c r="H635" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="I635" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J635" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K635" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L635" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M635" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N635" s="1">
+        <v>1</v>
+      </c>
+      <c r="O635" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="636" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A636" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B636" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C636" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D636" s="1">
+        <v>7</v>
+      </c>
+      <c r="E636" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F636" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G636" s="1">
+        <v>41005322</v>
+      </c>
+      <c r="H636" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="I636" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J636" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K636" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L636" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M636" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N636" s="1">
+        <v>1</v>
+      </c>
+      <c r="O636" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="637" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A637" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B637" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C637" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D637" s="1">
+        <v>7</v>
+      </c>
+      <c r="E637" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F637" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G637" s="1">
+        <v>76403635</v>
+      </c>
+      <c r="H637" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="I637" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J637" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K637" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L637" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M637" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N637" s="1">
+        <v>1</v>
+      </c>
+      <c r="O637" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="638" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A638" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B638" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C638" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D638" s="1">
+        <v>7</v>
+      </c>
+      <c r="E638" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F638" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G638" s="1">
+        <v>75282676</v>
+      </c>
+      <c r="H638" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="I638" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J638" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K638" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L638" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M638" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N638" s="1">
+        <v>1</v>
+      </c>
+      <c r="O638" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="639" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A639" s="1" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B639" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C639" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D639" s="1">
+        <v>7</v>
+      </c>
+      <c r="E639" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F639" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G639" s="1">
+        <v>71851516</v>
+      </c>
+      <c r="H639" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="I639" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J639" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K639" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L639" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="M639" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N639" s="1">
+        <v>1</v>
+      </c>
+      <c r="O639" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="640" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A640" s="1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B640" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C640" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D640" s="1">
+        <v>7</v>
+      </c>
+      <c r="E640" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F640" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="G640" s="1">
+        <v>24958286</v>
+      </c>
+      <c r="H640" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="I640" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J640" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K640" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L640" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M640" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N640" s="1">
+        <v>1</v>
+      </c>
+      <c r="O640" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="641" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A641" s="1" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B641" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C641" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D641" s="1">
+        <v>7</v>
+      </c>
+      <c r="E641" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F641" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="G641" s="1">
+        <v>44865906</v>
+      </c>
+      <c r="H641" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="I641" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J641" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K641" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L641" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M641" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N641" s="1">
+        <v>1</v>
+      </c>
+      <c r="O641" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="642" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A642" s="1" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B642" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C642" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D642" s="1">
+        <v>7</v>
+      </c>
+      <c r="E642" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F642" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="G642" s="1">
+        <v>23976901</v>
+      </c>
+      <c r="H642" s="1" t="s">
+        <v>1318</v>
+      </c>
+      <c r="I642" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J642" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K642" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L642" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M642" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N642" s="1">
+        <v>1</v>
+      </c>
+      <c r="O642" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="643" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A643" s="1" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B643" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C643" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D643" s="1">
+        <v>7</v>
+      </c>
+      <c r="E643" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F643" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="G643" s="1">
+        <v>42150509</v>
+      </c>
+      <c r="H643" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="I643" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J643" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K643" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L643" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M643" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N643" s="1">
+        <v>1</v>
+      </c>
+      <c r="O643" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="644" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A644" s="1" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B644" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C644" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D644" s="1">
+        <v>7</v>
+      </c>
+      <c r="E644" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F644" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="G644" s="1">
+        <v>44585239</v>
+      </c>
+      <c r="H644" s="1" t="s">
+        <v>1320</v>
+      </c>
+      <c r="I644" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J644" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K644" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L644" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M644" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N644" s="1">
+        <v>1</v>
+      </c>
+      <c r="O644" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="645" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A645" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B645" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C645" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D645" s="1">
+        <v>7</v>
+      </c>
+      <c r="E645" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F645" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="G645" s="1">
+        <v>41394354</v>
+      </c>
+      <c r="H645" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="I645" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J645" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K645" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L645" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M645" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N645" s="1">
+        <v>1</v>
+      </c>
+      <c r="O645" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="646" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A646" s="1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B646" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C646" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D646" s="1">
+        <v>7</v>
+      </c>
+      <c r="E646" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F646" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="G646" s="1">
+        <v>23975658</v>
+      </c>
+      <c r="H646" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="I646" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J646" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K646" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L646" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M646" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N646" s="1">
+        <v>1</v>
+      </c>
+      <c r="O646" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="647" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A647" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B647" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C647" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D647" s="1">
+        <v>7</v>
+      </c>
+      <c r="E647" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F647" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="G647" s="1">
+        <v>47474750</v>
+      </c>
+      <c r="H647" s="1" t="s">
+        <v>1322</v>
+      </c>
+      <c r="I647" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J647" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K647" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L647" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M647" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N647" s="1">
+        <v>1</v>
+      </c>
+      <c r="O647" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="648" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A648" s="1" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B648" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C648" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D648" s="1">
+        <v>7</v>
+      </c>
+      <c r="E648" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F648" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="G648" s="1">
+        <v>47327501</v>
+      </c>
+      <c r="H648" s="1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="I648" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J648" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K648" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L648" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M648" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N648" s="1">
+        <v>1</v>
+      </c>
+      <c r="O648" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="649" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A649" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B649" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C649" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D649" s="1">
+        <v>7</v>
+      </c>
+      <c r="E649" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F649" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="G649" s="1">
+        <v>25320147</v>
+      </c>
+      <c r="H649" s="1" t="s">
+        <v>1324</v>
+      </c>
+      <c r="I649" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J649" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K649" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L649" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M649" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N649" s="1">
+        <v>1</v>
+      </c>
+      <c r="O649" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="650" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A650" s="1" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B650" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C650" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D650" s="1">
+        <v>7</v>
+      </c>
+      <c r="E650" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F650" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="G650" s="1">
+        <v>42636193</v>
+      </c>
+      <c r="H650" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="I650" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J650" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K650" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L650" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M650" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N650" s="1">
+        <v>1</v>
+      </c>
+      <c r="O650" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="651" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A651" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B651" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C651" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D651" s="1">
+        <v>7</v>
+      </c>
+      <c r="E651" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F651" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G651" s="1">
+        <v>73321680</v>
+      </c>
+      <c r="H651" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="I651" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J651" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K651" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L651" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="M651" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N651" s="1">
+        <v>1</v>
+      </c>
+      <c r="O651" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="652" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A652" s="1" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B652" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C652" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D652" s="1">
+        <v>7</v>
+      </c>
+      <c r="E652" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F652" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G652" s="1">
+        <v>72495328</v>
+      </c>
+      <c r="H652" s="1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="I652" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J652" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K652" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L652" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="M652" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N652" s="1">
+        <v>1</v>
+      </c>
+      <c r="O652" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="653" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A653" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B653" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C653" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D653" s="1">
+        <v>7</v>
+      </c>
+      <c r="E653" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F653" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G653" s="1">
+        <v>75237035</v>
+      </c>
+      <c r="H653" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="I653" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J653" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K653" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L653" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="M653" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N653" s="1">
+        <v>1</v>
+      </c>
+      <c r="O653" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="654" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A654" s="1" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B654" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C654" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D654" s="1">
+        <v>7</v>
+      </c>
+      <c r="E654" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F654" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G654" s="1">
+        <v>71727977</v>
+      </c>
+      <c r="H654" s="1" t="s">
+        <v>1326</v>
+      </c>
+      <c r="I654" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J654" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K654" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L654" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="M654" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N654" s="1">
+        <v>1</v>
+      </c>
+      <c r="O654" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="655" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A655" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B655" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C655" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D655" s="1">
+        <v>7</v>
+      </c>
+      <c r="E655" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F655" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G655" s="1">
+        <v>76403635</v>
+      </c>
+      <c r="H655" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="I655" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J655" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K655" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L655" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="M655" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N655" s="1">
+        <v>1</v>
+      </c>
+      <c r="O655" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="656" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A656" s="1" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B656" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C656" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D656" s="1">
+        <v>7</v>
+      </c>
+      <c r="E656" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F656" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G656" s="1">
+        <v>70117107</v>
+      </c>
+      <c r="H656" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="I656" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J656" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K656" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L656" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="M656" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N656" s="1">
+        <v>1</v>
+      </c>
+      <c r="O656" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="657" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A657" s="1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B657" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C657" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D657" s="1">
+        <v>7</v>
+      </c>
+      <c r="E657" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F657" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G657" s="1">
+        <v>60171003</v>
+      </c>
+      <c r="H657" s="1" t="s">
+        <v>1328</v>
+      </c>
+      <c r="I657" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J657" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K657" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L657" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="M657" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N657" s="1">
+        <v>1</v>
+      </c>
+      <c r="O657" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="658" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A658" s="1" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B658" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C658" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D658" s="1">
+        <v>7</v>
+      </c>
+      <c r="E658" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F658" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G658" s="1">
+        <v>41005322</v>
+      </c>
+      <c r="H658" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="I658" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J658" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K658" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L658" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="M658" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N658" s="1">
+        <v>1</v>
+      </c>
+      <c r="O658" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="659" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A659" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B659" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C659" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D659" s="1">
+        <v>7</v>
+      </c>
+      <c r="E659" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F659" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G659" s="1">
+        <v>71505538</v>
+      </c>
+      <c r="H659" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="I659" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J659" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K659" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L659" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="M659" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N659" s="1">
+        <v>1</v>
+      </c>
+      <c r="O659" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="660" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A660" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B660" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C660" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D660" s="1">
+        <v>7</v>
+      </c>
+      <c r="E660" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F660" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G660" s="1">
+        <v>61094381</v>
+      </c>
+      <c r="H660" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="I660" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J660" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K660" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L660" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="M660" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N660" s="1">
+        <v>1</v>
+      </c>
+      <c r="O660" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="661" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A661" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B661" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C661" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D661" s="1">
+        <v>7</v>
+      </c>
+      <c r="E661" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F661" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G661" s="1">
+        <v>60566010</v>
+      </c>
+      <c r="H661" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="I661" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J661" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K661" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L661" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="M661" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N661" s="1">
+        <v>1</v>
+      </c>
+      <c r="O661" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="662" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A662" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B662" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C662" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D662" s="1">
+        <v>7</v>
+      </c>
+      <c r="E662" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F662" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G662" s="1">
+        <v>72471575</v>
+      </c>
+      <c r="H662" s="1" t="s">
+        <v>1332</v>
+      </c>
+      <c r="I662" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J662" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K662" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L662" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="M662" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N662" s="1">
+        <v>1</v>
+      </c>
+      <c r="O662" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="663" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A663" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B663" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C663" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D663" s="1">
+        <v>7</v>
+      </c>
+      <c r="E663" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F663" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G663" s="1">
+        <v>71873373</v>
+      </c>
+      <c r="H663" s="1" t="s">
+        <v>1333</v>
+      </c>
+      <c r="I663" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J663" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K663" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L663" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="M663" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N663" s="1">
+        <v>1</v>
+      </c>
+      <c r="O663" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="664" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A664" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B664" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C664" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D664" s="1">
+        <v>7</v>
+      </c>
+      <c r="E664" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F664" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G664" s="1">
+        <v>76747062</v>
+      </c>
+      <c r="H664" s="1" t="s">
+        <v>1334</v>
+      </c>
+      <c r="I664" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J664" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K664" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L664" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="M664" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N664" s="1">
+        <v>1</v>
+      </c>
+      <c r="O664" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="665" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A665" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B665" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C665" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D665" s="1">
+        <v>7</v>
+      </c>
+      <c r="E665" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F665" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G665" s="1">
+        <v>71851516</v>
+      </c>
+      <c r="H665" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="I665" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J665" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K665" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L665" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="M665" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N665" s="1">
+        <v>1</v>
+      </c>
+      <c r="O665" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="666" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A666" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B666" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C666" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D666" s="1">
+        <v>7</v>
+      </c>
+      <c r="E666" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F666" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G666" s="1">
+        <v>72076653</v>
+      </c>
+      <c r="H666" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="I666" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J666" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K666" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L666" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="M666" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N666" s="1">
+        <v>1</v>
+      </c>
+      <c r="O666" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="667" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A667" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B667" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C667" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D667" s="1">
+        <v>7</v>
+      </c>
+      <c r="E667" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F667" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G667" s="1">
+        <v>70117125</v>
+      </c>
+      <c r="H667" s="1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="I667" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J667" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K667" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L667" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="M667" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N667" s="1">
+        <v>1</v>
+      </c>
+      <c r="O667" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="668" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A668" s="1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B668" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C668" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D668" s="1">
+        <v>7</v>
+      </c>
+      <c r="E668" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F668" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G668" s="1">
+        <v>73321680</v>
+      </c>
+      <c r="H668" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="I668" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J668" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K668" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L668" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="M668" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N668" s="1">
+        <v>1</v>
+      </c>
+      <c r="O668" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="669" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A669" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B669" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C669" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D669" s="1">
+        <v>7</v>
+      </c>
+      <c r="E669" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F669" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G669" s="1">
+        <v>72495328</v>
+      </c>
+      <c r="H669" s="1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="I669" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J669" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K669" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L669" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="M669" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N669" s="1">
+        <v>1</v>
+      </c>
+      <c r="O669" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="670" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A670" s="1" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B670" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C670" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D670" s="1">
+        <v>7</v>
+      </c>
+      <c r="E670" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F670" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G670" s="1">
+        <v>75237035</v>
+      </c>
+      <c r="H670" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="I670" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J670" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K670" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L670" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="M670" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N670" s="1">
+        <v>1</v>
+      </c>
+      <c r="O670" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="671" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A671" s="1" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B671" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C671" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D671" s="1">
+        <v>7</v>
+      </c>
+      <c r="E671" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F671" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G671" s="1">
+        <v>71727977</v>
+      </c>
+      <c r="H671" s="1" t="s">
+        <v>1326</v>
+      </c>
+      <c r="I671" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J671" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K671" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L671" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="M671" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N671" s="1">
+        <v>1</v>
+      </c>
+      <c r="O671" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="672" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A672" s="1" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B672" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C672" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D672" s="1">
+        <v>7</v>
+      </c>
+      <c r="E672" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F672" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G672" s="1">
+        <v>76403635</v>
+      </c>
+      <c r="H672" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="I672" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J672" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K672" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L672" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="M672" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N672" s="1">
+        <v>1</v>
+      </c>
+      <c r="O672" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="673" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A673" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B673" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C673" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D673" s="1">
+        <v>7</v>
+      </c>
+      <c r="E673" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F673" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G673" s="1">
+        <v>70117107</v>
+      </c>
+      <c r="H673" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="I673" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J673" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K673" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L673" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="M673" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N673" s="1">
+        <v>1</v>
+      </c>
+      <c r="O673" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="674" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A674" s="1" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B674" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C674" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D674" s="1">
+        <v>7</v>
+      </c>
+      <c r="E674" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F674" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G674" s="1">
+        <v>60171003</v>
+      </c>
+      <c r="H674" s="1" t="s">
+        <v>1328</v>
+      </c>
+      <c r="I674" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J674" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K674" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L674" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="M674" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N674" s="1">
+        <v>1</v>
+      </c>
+      <c r="O674" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="675" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A675" s="1" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B675" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C675" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D675" s="1">
+        <v>7</v>
+      </c>
+      <c r="E675" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F675" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G675" s="1">
+        <v>41005322</v>
+      </c>
+      <c r="H675" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="I675" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J675" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K675" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L675" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="M675" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N675" s="1">
+        <v>1</v>
+      </c>
+      <c r="O675" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="676" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A676" s="1" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B676" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C676" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D676" s="1">
+        <v>7</v>
+      </c>
+      <c r="E676" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F676" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G676" s="1">
+        <v>71505538</v>
+      </c>
+      <c r="H676" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="I676" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J676" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K676" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L676" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="M676" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N676" s="1">
+        <v>1</v>
+      </c>
+      <c r="O676" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="677" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A677" s="1" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B677" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C677" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D677" s="1">
+        <v>7</v>
+      </c>
+      <c r="E677" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F677" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G677" s="1">
+        <v>61094381</v>
+      </c>
+      <c r="H677" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="I677" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J677" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K677" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L677" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="M677" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N677" s="1">
+        <v>1</v>
+      </c>
+      <c r="O677" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="678" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A678" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B678" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C678" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D678" s="1">
+        <v>7</v>
+      </c>
+      <c r="E678" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F678" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G678" s="1">
+        <v>60566010</v>
+      </c>
+      <c r="H678" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="I678" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J678" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K678" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L678" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="M678" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N678" s="1">
+        <v>1</v>
+      </c>
+      <c r="O678" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="679" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A679" s="1" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B679" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C679" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D679" s="1">
+        <v>7</v>
+      </c>
+      <c r="E679" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F679" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G679" s="1">
+        <v>72471575</v>
+      </c>
+      <c r="H679" s="1" t="s">
+        <v>1332</v>
+      </c>
+      <c r="I679" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J679" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K679" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L679" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="M679" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N679" s="1">
+        <v>1</v>
+      </c>
+      <c r="O679" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="680" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A680" s="1" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B680" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C680" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D680" s="1">
+        <v>7</v>
+      </c>
+      <c r="E680" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F680" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G680" s="1">
+        <v>71873373</v>
+      </c>
+      <c r="H680" s="1" t="s">
+        <v>1333</v>
+      </c>
+      <c r="I680" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J680" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K680" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L680" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="M680" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N680" s="1">
+        <v>1</v>
+      </c>
+      <c r="O680" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="681" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A681" s="1" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B681" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C681" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D681" s="1">
+        <v>7</v>
+      </c>
+      <c r="E681" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F681" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G681" s="1">
+        <v>76747062</v>
+      </c>
+      <c r="H681" s="1" t="s">
+        <v>1334</v>
+      </c>
+      <c r="I681" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J681" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K681" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L681" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="M681" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N681" s="1">
+        <v>1</v>
+      </c>
+      <c r="O681" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="682" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A682" s="1" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B682" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C682" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D682" s="1">
+        <v>7</v>
+      </c>
+      <c r="E682" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F682" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G682" s="1">
+        <v>72076653</v>
+      </c>
+      <c r="H682" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="I682" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J682" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K682" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L682" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="M682" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N682" s="1">
+        <v>1</v>
+      </c>
+      <c r="O682" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="683" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A683" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B683" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C683" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D683" s="1">
+        <v>7</v>
+      </c>
+      <c r="E683" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F683" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G683" s="1">
+        <v>70117125</v>
+      </c>
+      <c r="H683" s="1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="I683" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J683" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K683" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L683" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="M683" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N683" s="1">
+        <v>1</v>
+      </c>
+      <c r="O683" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="684" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A684" s="1" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B684" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C684" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D684" s="1">
+        <v>7</v>
+      </c>
+      <c r="E684" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F684" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="G684" s="1">
+        <v>71851516</v>
+      </c>
+      <c r="H684" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="I684" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J684" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K684" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L684" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="M684" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N684" s="1">
+        <v>1</v>
+      </c>
+      <c r="O684" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="685" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A685" s="1" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B685" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C685" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D685" s="1">
+        <v>7</v>
+      </c>
+      <c r="E685" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F685" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G685" s="1">
+        <v>73321680</v>
+      </c>
+      <c r="H685" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="I685" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J685" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K685" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L685" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="M685" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N685" s="1">
+        <v>1</v>
+      </c>
+      <c r="O685" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="686" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A686" s="1" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B686" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C686" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D686" s="1">
+        <v>7</v>
+      </c>
+      <c r="E686" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F686" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G686" s="1">
+        <v>72495328</v>
+      </c>
+      <c r="H686" s="1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="I686" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J686" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K686" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L686" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="M686" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N686" s="1">
+        <v>1</v>
+      </c>
+      <c r="O686" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="687" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A687" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B687" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C687" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D687" s="1">
+        <v>7</v>
+      </c>
+      <c r="E687" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F687" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G687" s="1">
+        <v>75237035</v>
+      </c>
+      <c r="H687" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="I687" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J687" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K687" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L687" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="M687" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N687" s="1">
+        <v>1</v>
+      </c>
+      <c r="O687" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="688" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A688" s="1" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B688" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C688" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D688" s="1">
+        <v>7</v>
+      </c>
+      <c r="E688" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F688" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G688" s="1">
+        <v>71727977</v>
+      </c>
+      <c r="H688" s="1" t="s">
+        <v>1326</v>
+      </c>
+      <c r="I688" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J688" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K688" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L688" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="M688" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N688" s="1">
+        <v>1</v>
+      </c>
+      <c r="O688" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="689" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A689" s="1" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B689" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C689" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D689" s="1">
+        <v>7</v>
+      </c>
+      <c r="E689" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F689" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G689" s="1">
+        <v>76403635</v>
+      </c>
+      <c r="H689" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="I689" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J689" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K689" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L689" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="M689" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N689" s="1">
+        <v>1</v>
+      </c>
+      <c r="O689" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="690" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A690" s="1" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B690" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C690" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D690" s="1">
+        <v>7</v>
+      </c>
+      <c r="E690" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F690" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G690" s="1">
+        <v>70117107</v>
+      </c>
+      <c r="H690" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="I690" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J690" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K690" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L690" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="M690" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N690" s="1">
+        <v>1</v>
+      </c>
+      <c r="O690" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="691" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A691" s="1" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B691" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C691" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D691" s="1">
+        <v>7</v>
+      </c>
+      <c r="E691" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F691" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G691" s="1">
+        <v>60171003</v>
+      </c>
+      <c r="H691" s="1" t="s">
+        <v>1328</v>
+      </c>
+      <c r="I691" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J691" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K691" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L691" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="M691" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N691" s="1">
+        <v>1</v>
+      </c>
+      <c r="O691" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="692" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A692" s="1" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B692" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C692" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D692" s="1">
+        <v>7</v>
+      </c>
+      <c r="E692" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F692" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G692" s="1">
+        <v>41005322</v>
+      </c>
+      <c r="H692" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="I692" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J692" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K692" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L692" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="M692" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N692" s="1">
+        <v>1</v>
+      </c>
+      <c r="O692" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="693" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A693" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B693" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C693" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D693" s="1">
+        <v>7</v>
+      </c>
+      <c r="E693" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F693" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G693" s="1">
+        <v>71505538</v>
+      </c>
+      <c r="H693" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="I693" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J693" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K693" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L693" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="M693" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N693" s="1">
+        <v>1</v>
+      </c>
+      <c r="O693" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="694" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A694" s="1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B694" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C694" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D694" s="1">
+        <v>7</v>
+      </c>
+      <c r="E694" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F694" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G694" s="1">
+        <v>61094381</v>
+      </c>
+      <c r="H694" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="I694" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J694" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K694" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L694" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="M694" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N694" s="1">
+        <v>1</v>
+      </c>
+      <c r="O694" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="695" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A695" s="1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B695" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C695" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D695" s="1">
+        <v>7</v>
+      </c>
+      <c r="E695" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F695" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G695" s="1">
+        <v>60566010</v>
+      </c>
+      <c r="H695" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="I695" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J695" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K695" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L695" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="M695" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N695" s="1">
+        <v>1</v>
+      </c>
+      <c r="O695" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="696" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A696" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B696" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C696" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D696" s="1">
+        <v>7</v>
+      </c>
+      <c r="E696" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F696" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G696" s="1">
+        <v>72471575</v>
+      </c>
+      <c r="H696" s="1" t="s">
+        <v>1332</v>
+      </c>
+      <c r="I696" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J696" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K696" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L696" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="M696" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N696" s="1">
+        <v>1</v>
+      </c>
+      <c r="O696" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="697" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A697" s="1" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B697" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C697" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D697" s="1">
+        <v>7</v>
+      </c>
+      <c r="E697" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F697" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G697" s="1">
+        <v>71873373</v>
+      </c>
+      <c r="H697" s="1" t="s">
+        <v>1333</v>
+      </c>
+      <c r="I697" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J697" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K697" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L697" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="M697" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N697" s="1">
+        <v>1</v>
+      </c>
+      <c r="O697" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="698" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A698" s="1" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B698" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C698" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D698" s="1">
+        <v>7</v>
+      </c>
+      <c r="E698" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F698" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G698" s="1">
+        <v>76747062</v>
+      </c>
+      <c r="H698" s="1" t="s">
+        <v>1334</v>
+      </c>
+      <c r="I698" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J698" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K698" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L698" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="M698" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N698" s="1">
+        <v>1</v>
+      </c>
+      <c r="O698" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="699" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A699" s="1" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B699" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C699" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D699" s="1">
+        <v>7</v>
+      </c>
+      <c r="E699" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F699" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G699" s="1">
+        <v>72076653</v>
+      </c>
+      <c r="H699" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="I699" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J699" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K699" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L699" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="M699" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N699" s="1">
+        <v>1</v>
+      </c>
+      <c r="O699" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="700" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A700" s="1" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B700" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C700" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D700" s="1">
+        <v>7</v>
+      </c>
+      <c r="E700" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F700" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G700" s="1">
+        <v>70117125</v>
+      </c>
+      <c r="H700" s="1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="I700" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J700" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K700" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L700" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="M700" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N700" s="1">
+        <v>1</v>
+      </c>
+      <c r="O700" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="701" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A701" s="1" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B701" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C701" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D701" s="1">
+        <v>7</v>
+      </c>
+      <c r="E701" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F701" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G701" s="1">
+        <v>71851516</v>
+      </c>
+      <c r="H701" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="I701" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J701" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K701" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="L701" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="M701" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="N701" s="1">
+        <v>1</v>
+      </c>
+      <c r="O701" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="702" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A702" s="1" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B702" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C702" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D702" s="1">
+        <v>7</v>
+      </c>
+      <c r="E702" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F702" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="G702" s="1">
+        <v>47316345</v>
+      </c>
+      <c r="H702" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="I702" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J702" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K702" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L702" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M702" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N702" s="1">
+        <v>1</v>
+      </c>
+      <c r="O702" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P621">
-    <sortCondition ref="D1:D621"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P619">
+    <sortCondition ref="D1:D619"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360A7E21-DC87-49CB-92C2-122CAD083B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC893FA-F86C-4513-8EC7-26E347C22003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7703" uniqueCount="1425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7714" uniqueCount="1429">
   <si>
     <t>ID_ACTIVIDAD</t>
   </si>
@@ -3930,33 +3930,6 @@
     <t>ELABORACIÓN DE FORMULA DE TEÑIDO</t>
   </si>
   <si>
-    <t>TEÑIDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEÑIDO ARTESANAL  CON COLORANTES NATURALES </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASISTENCIA TECNICA EN EXTRACCION DE COLORANTE NATURAL Y TEÑIDO EN FIBRA DE ALPACA </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ASISTENCIA TECNICA EN TEÑIDO NATURAL CON  COLORANTE NATURAL </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TEÑIDO CON ENFOQUE ECONOMIA CIRCULAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ASISTENCIA TECNICA EN TEÑIDO NATURAL CON COLORANTES NATURALES </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TEÑIDO ARTESANAL CON TINTES NATURALES </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TEÑIDO ARTESANAL CON COLORANTES NATURALES </t>
-  </si>
-  <si>
-    <t>TEÑIDO ARTESANAL</t>
-  </si>
-  <si>
     <t>C000292</t>
   </si>
   <si>
@@ -4005,45 +3978,6 @@
     <t>23/07/2026</t>
   </si>
   <si>
-    <t xml:space="preserve"> ROSENAL EVER</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RUTH KAREN</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ALEXANDER</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NANCY REBECA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> YULY LILIANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> VANESA JENNIFER</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MAICOOL LEONEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MARISOL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MAGNET GABRIELA</t>
-  </si>
-  <si>
-    <t>Vilcapaza Cutipa Laly Marguth</t>
-  </si>
-  <si>
-    <t>Ccallohuanca Burgos Gary Jordan</t>
-  </si>
-  <si>
-    <t>Cahuana Mamani Nedy Abigail</t>
-  </si>
-  <si>
-    <t>Pelinco Suasaca Sandra Raquel</t>
-  </si>
-  <si>
     <t>HANCCO CONDORI JAZMIN NAYSHA</t>
   </si>
   <si>
@@ -4056,9 +3990,6 @@
     <t>HANCCO LOAYZA ALEXANDRA ESTRELLA</t>
   </si>
   <si>
-    <t>HILASACA PAJSI FANNY JULIE</t>
-  </si>
-  <si>
     <t>ZAPANA PARRA DINA YESSICA</t>
   </si>
   <si>
@@ -4125,9 +4056,6 @@
     <t>CAPACITACION ESPECIALIZADA EN PRODUCCION SOSTENIBLE Y ECONOMIA CIRCULAR PARA LA EXPORTACION-I</t>
   </si>
   <si>
-    <t>CAPACITACIÓN EN ECONOMIA CIRCULAR</t>
-  </si>
-  <si>
     <t>CONCEPTOS APLICABLES A LA ECONOMÍA CIRCULAR Y SOSTENIBILIDAD PARA LAS MIPYMES</t>
   </si>
   <si>
@@ -4381,6 +4309,90 @@
   </si>
   <si>
     <t>C000385</t>
+  </si>
+  <si>
+    <t>EXTRACCIÓN DEL COLORANTE NATURAL DE MOLLE Y SU APLICACIÓN EN EL TEÑIDO DE FIBRA DE ALPACA</t>
+  </si>
+  <si>
+    <t>TEÑIDO ARTESANAL DE FIBRA DE ALPACA CON COLORANTE NATURAL DE EUCALIPTO</t>
+  </si>
+  <si>
+    <t>PROCESO DE TEÑIDO ARTESANAL CON COLORANTE NATURAL A BASE DE MOLLE EN FIBRA DE ALPACA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TEÑIDO CON ENFOQUE ECONOMIA CIRCULAR - Teñido artesanal con colorante natural de molle aplicado en fibra de alpaca</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ASISTENCIA TECNICA EN TEÑIDO NATURAL CON COLORANTES NATURALES DE MUÑA EN EL TEÑIDO DE FIBRA DE ALPACA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TEÑIDO ARTESANAL CON TINTES NATURALES DE DIENTE DE LEON Y SU APLICACIÓN EN LA FIBRA DE ALPACA </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TEÑIDO ARTESANAL CON COLORANTES NATURALES DE SUSTRATOS TEXTILES</t>
+  </si>
+  <si>
+    <t>EXTRACCIÓN DEL COLORANTE NATURAL DE FLOR DE JAMAICA Y SU USO EN EL TEÑIDO ARTESANAL DE FIBRA DE ALPACA</t>
+  </si>
+  <si>
+    <t>ROSENAL EVER MAMANI TIPULA</t>
+  </si>
+  <si>
+    <t>RUTH KAREN TIPO MULLISACA</t>
+  </si>
+  <si>
+    <t>ALEXANDER SUCASACA QUISPE</t>
+  </si>
+  <si>
+    <t>NANCY REBECA PELINCO SUASACA</t>
+  </si>
+  <si>
+    <t>YULY LILIANA QUISPE HUAMAN</t>
+  </si>
+  <si>
+    <t>VANESA JENNIFER AGUILAR MAYTA</t>
+  </si>
+  <si>
+    <t>MAICOOL LEONEL PARICELA MAMANI</t>
+  </si>
+  <si>
+    <t>MARISOL MALDONADO CHUMBES</t>
+  </si>
+  <si>
+    <t>MAGNET GABRIELA QUISPE CORIMAYHUA</t>
+  </si>
+  <si>
+    <t>Laly Marguth Vilcapaza Cutipa</t>
+  </si>
+  <si>
+    <t>Gary Jordan Ccallohuanca Burgos</t>
+  </si>
+  <si>
+    <t>Nedy Abigail Cahuana Mamani</t>
+  </si>
+  <si>
+    <t>Sandra Raquel Pelinco Suasaca</t>
+  </si>
+  <si>
+    <t>JAZMIN NAYSHA HANCCO CONDORI</t>
+  </si>
+  <si>
+    <t>FLORA FERMINA APAZA YUJRA</t>
+  </si>
+  <si>
+    <t>DANNI VIK SUCAPUCA TICONA</t>
+  </si>
+  <si>
+    <t>ALEXANDRA ESTRELLA HANCCO LOAYZA</t>
+  </si>
+  <si>
+    <t>FANNY JULIE HILASACA PAJSI</t>
+  </si>
+  <si>
+    <t>DINA YESSICA ZAPANA PARRA</t>
+  </si>
+  <si>
+    <t>CAPACITACIÓN EN INTRODUCCIÓN A LA ECONOMÍA CIRCULAR</t>
   </si>
 </sst>
 </file>
@@ -4471,7 +4483,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4494,6 +4506,7 @@
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -34299,7 +34312,7 @@
     </row>
     <row r="609" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
-        <v>1283</v>
+        <v>1274</v>
       </c>
       <c r="B609" s="7" t="s">
         <v>1193</v>
@@ -34316,12 +34329,15 @@
       <c r="F609" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G609" s="1">
+      <c r="G609" s="10">
         <v>10238869094</v>
       </c>
       <c r="H609" s="1" t="s">
         <v>373</v>
       </c>
+      <c r="I609" s="1" t="s">
+        <v>516</v>
+      </c>
       <c r="J609" s="1" t="s">
         <v>194</v>
       </c>
@@ -34329,12 +34345,12 @@
         <v>249</v>
       </c>
       <c r="L609" s="1" t="s">
-        <v>1273</v>
+        <v>399</v>
       </c>
       <c r="M609" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N609" s="1">
+      <c r="N609" s="10">
         <v>6</v>
       </c>
       <c r="O609" s="1" t="s">
@@ -34343,7 +34359,7 @@
     </row>
     <row r="610" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
-        <v>1284</v>
+        <v>1275</v>
       </c>
       <c r="B610" s="7" t="s">
         <v>1186</v>
@@ -34360,12 +34376,15 @@
       <c r="F610" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G610" s="1">
+      <c r="G610" s="10">
         <v>10247032270</v>
       </c>
       <c r="H610" s="1" t="s">
         <v>374</v>
       </c>
+      <c r="I610" s="1" t="s">
+        <v>516</v>
+      </c>
       <c r="J610" s="1" t="s">
         <v>194</v>
       </c>
@@ -34378,7 +34397,7 @@
       <c r="M610" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N610" s="1">
+      <c r="N610" s="10">
         <v>4</v>
       </c>
       <c r="O610" s="1" t="s">
@@ -34387,7 +34406,7 @@
     </row>
     <row r="611" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
-        <v>1285</v>
+        <v>1276</v>
       </c>
       <c r="B611" s="7" t="s">
         <v>1194</v>
@@ -34404,12 +34423,15 @@
       <c r="F611" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G611" s="1">
+      <c r="G611" s="10">
         <v>20606059338</v>
       </c>
       <c r="H611" s="1" t="s">
         <v>1269</v>
       </c>
+      <c r="I611" s="1" t="s">
+        <v>683</v>
+      </c>
       <c r="J611" s="1" t="s">
         <v>194</v>
       </c>
@@ -34417,12 +34439,12 @@
         <v>249</v>
       </c>
       <c r="L611" s="1" t="s">
-        <v>1274</v>
+        <v>399</v>
       </c>
       <c r="M611" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N611" s="1">
+      <c r="N611" s="10">
         <v>11</v>
       </c>
       <c r="O611" s="1" t="s">
@@ -34431,10 +34453,10 @@
     </row>
     <row r="612" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
-        <v>1286</v>
+        <v>1277</v>
       </c>
       <c r="B612" s="7" t="s">
-        <v>1294</v>
+        <v>1288</v>
       </c>
       <c r="C612" s="1">
         <v>2026</v>
@@ -34446,28 +34468,31 @@
         <v>27</v>
       </c>
       <c r="F612" s="1" t="s">
-        <v>1137</v>
-      </c>
-      <c r="G612" s="1">
-        <v>47614294</v>
+        <v>771</v>
+      </c>
+      <c r="G612" s="10">
+        <v>10248679081</v>
       </c>
       <c r="H612" s="1" t="s">
-        <v>382</v>
+        <v>44</v>
+      </c>
+      <c r="I612" s="1" t="s">
+        <v>516</v>
       </c>
       <c r="J612" s="1" t="s">
-        <v>242</v>
+        <v>14</v>
       </c>
       <c r="K612" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L612" s="1" t="s">
-        <v>1275</v>
+        <v>335</v>
       </c>
       <c r="M612" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N612" s="1">
-        <v>1</v>
+      <c r="N612" s="10">
+        <v>4</v>
       </c>
       <c r="O612" s="1" t="s">
         <v>50</v>
@@ -34475,10 +34500,10 @@
     </row>
     <row r="613" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
-        <v>1287</v>
+        <v>1278</v>
       </c>
       <c r="B613" s="7" t="s">
-        <v>1295</v>
+        <v>1192</v>
       </c>
       <c r="C613" s="1">
         <v>2026</v>
@@ -34490,27 +34515,30 @@
         <v>27</v>
       </c>
       <c r="F613" s="1" t="s">
-        <v>1137</v>
+        <v>771</v>
       </c>
       <c r="G613" s="1">
-        <v>10450876700</v>
+        <v>10733216803</v>
       </c>
       <c r="H613" s="1" t="s">
-        <v>381</v>
+        <v>1409</v>
+      </c>
+      <c r="I613" s="1" t="s">
+        <v>515</v>
       </c>
       <c r="J613" s="1" t="s">
-        <v>242</v>
+        <v>155</v>
       </c>
       <c r="K613" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="L613" s="1" t="s">
-        <v>1276</v>
+        <v>1314</v>
       </c>
       <c r="M613" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N613" s="1">
+      <c r="N613" s="10">
         <v>1</v>
       </c>
       <c r="O613" s="1" t="s">
@@ -34519,10 +34547,10 @@
     </row>
     <row r="614" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
-        <v>1288</v>
+        <v>1279</v>
       </c>
       <c r="B614" s="7" t="s">
-        <v>1296</v>
+        <v>1192</v>
       </c>
       <c r="C614" s="1">
         <v>2026</v>
@@ -34534,27 +34562,30 @@
         <v>27</v>
       </c>
       <c r="F614" s="1" t="s">
-        <v>1137</v>
-      </c>
-      <c r="G614" s="1">
-        <v>10400403061</v>
+        <v>771</v>
+      </c>
+      <c r="G614" s="10">
+        <v>71727977</v>
       </c>
       <c r="H614" s="1" t="s">
-        <v>1270</v>
+        <v>1410</v>
+      </c>
+      <c r="I614" s="1" t="s">
+        <v>511</v>
       </c>
       <c r="J614" s="1" t="s">
-        <v>242</v>
+        <v>155</v>
       </c>
       <c r="K614" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="L614" s="1" t="s">
-        <v>1277</v>
+        <v>1314</v>
       </c>
       <c r="M614" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N614" s="1">
+      <c r="N614" s="10">
         <v>1</v>
       </c>
       <c r="O614" s="1" t="s">
@@ -34563,10 +34594,10 @@
     </row>
     <row r="615" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
-        <v>1289</v>
+        <v>1280</v>
       </c>
       <c r="B615" s="7" t="s">
-        <v>1297</v>
+        <v>1192</v>
       </c>
       <c r="C615" s="1">
         <v>2026</v>
@@ -34578,27 +34609,30 @@
         <v>27</v>
       </c>
       <c r="F615" s="1" t="s">
-        <v>1137</v>
+        <v>771</v>
       </c>
       <c r="G615" s="1">
-        <v>47656632</v>
+        <v>10743116904</v>
       </c>
       <c r="H615" s="1" t="s">
-        <v>1271</v>
+        <v>1411</v>
+      </c>
+      <c r="I615" s="1" t="s">
+        <v>516</v>
       </c>
       <c r="J615" s="1" t="s">
-        <v>242</v>
+        <v>155</v>
       </c>
       <c r="K615" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="L615" s="1" t="s">
-        <v>1278</v>
+        <v>1314</v>
       </c>
       <c r="M615" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N615" s="1">
+      <c r="N615" s="10">
         <v>1</v>
       </c>
       <c r="O615" s="1" t="s">
@@ -34607,10 +34641,10 @@
     </row>
     <row r="616" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
-        <v>1290</v>
+        <v>1281</v>
       </c>
       <c r="B616" s="7" t="s">
-        <v>1298</v>
+        <v>1192</v>
       </c>
       <c r="C616" s="1">
         <v>2026</v>
@@ -34622,27 +34656,30 @@
         <v>27</v>
       </c>
       <c r="F616" s="1" t="s">
-        <v>1137</v>
+        <v>771</v>
       </c>
       <c r="G616" s="1">
-        <v>47656632</v>
+        <v>10701171077</v>
       </c>
       <c r="H616" s="1" t="s">
-        <v>1271</v>
+        <v>1412</v>
+      </c>
+      <c r="I616" s="1" t="s">
+        <v>515</v>
       </c>
       <c r="J616" s="1" t="s">
-        <v>242</v>
+        <v>155</v>
       </c>
       <c r="K616" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="L616" s="1" t="s">
-        <v>1279</v>
+        <v>1314</v>
       </c>
       <c r="M616" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N616" s="1">
+      <c r="N616" s="10">
         <v>1</v>
       </c>
       <c r="O616" s="1" t="s">
@@ -34651,10 +34688,10 @@
     </row>
     <row r="617" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
-        <v>1291</v>
+        <v>1282</v>
       </c>
       <c r="B617" s="7" t="s">
-        <v>1186</v>
+        <v>1192</v>
       </c>
       <c r="C617" s="1">
         <v>2026</v>
@@ -34666,27 +34703,30 @@
         <v>27</v>
       </c>
       <c r="F617" s="1" t="s">
-        <v>1137</v>
-      </c>
-      <c r="G617" s="1">
-        <v>10462583996</v>
+        <v>771</v>
+      </c>
+      <c r="G617" s="10">
+        <v>60171003</v>
       </c>
       <c r="H617" s="1" t="s">
-        <v>385</v>
+        <v>1413</v>
+      </c>
+      <c r="I617" s="1" t="s">
+        <v>511</v>
       </c>
       <c r="J617" s="1" t="s">
-        <v>242</v>
+        <v>155</v>
       </c>
       <c r="K617" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="L617" s="1" t="s">
-        <v>1280</v>
+        <v>1314</v>
       </c>
       <c r="M617" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N617" s="1">
+      <c r="N617" s="10">
         <v>1</v>
       </c>
       <c r="O617" s="1" t="s">
@@ -34695,10 +34735,10 @@
     </row>
     <row r="618" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
-        <v>1292</v>
+        <v>1283</v>
       </c>
       <c r="B618" s="7" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
       <c r="C618" s="1">
         <v>2026</v>
@@ -34710,28 +34750,31 @@
         <v>27</v>
       </c>
       <c r="F618" s="1" t="s">
-        <v>1137</v>
+        <v>771</v>
       </c>
       <c r="G618" s="1">
-        <v>10462583996</v>
+        <v>10715055380</v>
       </c>
       <c r="H618" s="1" t="s">
-        <v>385</v>
+        <v>1414</v>
+      </c>
+      <c r="I618" s="1" t="s">
+        <v>515</v>
       </c>
       <c r="J618" s="1" t="s">
-        <v>194</v>
+        <v>155</v>
       </c>
       <c r="K618" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L618" s="1" t="s">
-        <v>1281</v>
+        <v>1314</v>
       </c>
       <c r="M618" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N618" s="1">
-        <v>15</v>
+      <c r="N618" s="10">
+        <v>1</v>
       </c>
       <c r="O618" s="1" t="s">
         <v>50</v>
@@ -34739,10 +34782,10 @@
     </row>
     <row r="619" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
-        <v>1293</v>
+        <v>1284</v>
       </c>
       <c r="B619" s="7" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="C619" s="1">
         <v>2026</v>
@@ -34754,27 +34797,30 @@
         <v>27</v>
       </c>
       <c r="F619" s="1" t="s">
-        <v>1137</v>
-      </c>
-      <c r="G619" s="1">
-        <v>47925279</v>
+        <v>771</v>
+      </c>
+      <c r="G619" s="10">
+        <v>61094381</v>
       </c>
       <c r="H619" s="1" t="s">
-        <v>1272</v>
+        <v>1415</v>
+      </c>
+      <c r="I619" s="1" t="s">
+        <v>511</v>
       </c>
       <c r="J619" s="1" t="s">
-        <v>242</v>
+        <v>155</v>
       </c>
       <c r="K619" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="L619" s="1" t="s">
-        <v>1282</v>
+        <v>1314</v>
       </c>
       <c r="M619" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N619" s="1">
+      <c r="N619" s="10">
         <v>1</v>
       </c>
       <c r="O619" s="1" t="s">
@@ -34783,10 +34829,10 @@
     </row>
     <row r="620" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
-        <v>1342</v>
+        <v>1318</v>
       </c>
       <c r="B620" s="7" t="s">
-        <v>1297</v>
+        <v>1192</v>
       </c>
       <c r="C620" s="1">
         <v>2026</v>
@@ -34800,29 +34846,29 @@
       <c r="F620" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G620" s="1">
-        <v>10248679081</v>
+      <c r="G620" s="10">
+        <v>60566010</v>
       </c>
       <c r="H620" s="1" t="s">
-        <v>44</v>
+        <v>1416</v>
       </c>
       <c r="I620" s="1" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="J620" s="1" t="s">
-        <v>14</v>
+        <v>155</v>
       </c>
       <c r="K620" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="L620" s="1" t="s">
-        <v>335</v>
+        <v>1314</v>
       </c>
       <c r="M620" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N620" s="1">
-        <v>4</v>
+      <c r="N620" s="10">
+        <v>1</v>
       </c>
       <c r="O620" s="1" t="s">
         <v>50</v>
@@ -34830,7 +34876,7 @@
     </row>
     <row r="621" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
-        <v>1343</v>
+        <v>1319</v>
       </c>
       <c r="B621" s="7" t="s">
         <v>1192</v>
@@ -34848,13 +34894,13 @@
         <v>771</v>
       </c>
       <c r="G621" s="1">
-        <v>73321680</v>
+        <v>10724715759</v>
       </c>
       <c r="H621" s="1" t="s">
-        <v>1299</v>
+        <v>1417</v>
       </c>
       <c r="I621" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J621" s="1" t="s">
         <v>155</v>
@@ -34863,12 +34909,12 @@
         <v>251</v>
       </c>
       <c r="L621" s="1" t="s">
-        <v>1337</v>
+        <v>1314</v>
       </c>
       <c r="M621" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N621" s="1">
+      <c r="N621" s="10">
         <v>1</v>
       </c>
       <c r="O621" s="1" t="s">
@@ -34877,7 +34923,7 @@
     </row>
     <row r="622" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
-        <v>1344</v>
+        <v>1320</v>
       </c>
       <c r="B622" s="7" t="s">
         <v>1192</v>
@@ -34894,11 +34940,11 @@
       <c r="F622" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G622" s="1">
-        <v>71727977</v>
+      <c r="G622" s="10">
+        <v>71873373</v>
       </c>
       <c r="H622" s="1" t="s">
-        <v>1300</v>
+        <v>1418</v>
       </c>
       <c r="I622" s="1" t="s">
         <v>511</v>
@@ -34910,12 +34956,12 @@
         <v>251</v>
       </c>
       <c r="L622" s="1" t="s">
-        <v>1337</v>
+        <v>1314</v>
       </c>
       <c r="M622" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N622" s="1">
+      <c r="N622" s="10">
         <v>1</v>
       </c>
       <c r="O622" s="1" t="s">
@@ -34924,7 +34970,7 @@
     </row>
     <row r="623" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
-        <v>1345</v>
+        <v>1321</v>
       </c>
       <c r="B623" s="7" t="s">
         <v>1192</v>
@@ -34942,13 +34988,13 @@
         <v>771</v>
       </c>
       <c r="G623" s="1">
-        <v>74311690</v>
+        <v>10767470628</v>
       </c>
       <c r="H623" s="1" t="s">
-        <v>1301</v>
+        <v>1419</v>
       </c>
       <c r="I623" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J623" s="1" t="s">
         <v>155</v>
@@ -34957,12 +35003,12 @@
         <v>251</v>
       </c>
       <c r="L623" s="1" t="s">
-        <v>1337</v>
+        <v>1314</v>
       </c>
       <c r="M623" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N623" s="1">
+      <c r="N623" s="10">
         <v>1</v>
       </c>
       <c r="O623" s="1" t="s">
@@ -34971,7 +35017,7 @@
     </row>
     <row r="624" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
-        <v>1346</v>
+        <v>1322</v>
       </c>
       <c r="B624" s="7" t="s">
         <v>1192</v>
@@ -34988,11 +35034,11 @@
       <c r="F624" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G624" s="1">
-        <v>70117107</v>
+      <c r="G624" s="10">
+        <v>72076653</v>
       </c>
       <c r="H624" s="1" t="s">
-        <v>1302</v>
+        <v>1420</v>
       </c>
       <c r="I624" s="1" t="s">
         <v>511</v>
@@ -35004,12 +35050,12 @@
         <v>251</v>
       </c>
       <c r="L624" s="1" t="s">
-        <v>1337</v>
+        <v>1314</v>
       </c>
       <c r="M624" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N624" s="1">
+      <c r="N624" s="10">
         <v>1</v>
       </c>
       <c r="O624" s="1" t="s">
@@ -35018,7 +35064,7 @@
     </row>
     <row r="625" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
-        <v>1347</v>
+        <v>1323</v>
       </c>
       <c r="B625" s="7" t="s">
         <v>1192</v>
@@ -35036,13 +35082,13 @@
         <v>771</v>
       </c>
       <c r="G625" s="1">
-        <v>60171003</v>
+        <v>10701171255</v>
       </c>
       <c r="H625" s="1" t="s">
-        <v>1303</v>
+        <v>1421</v>
       </c>
       <c r="I625" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J625" s="1" t="s">
         <v>155</v>
@@ -35051,12 +35097,12 @@
         <v>251</v>
       </c>
       <c r="L625" s="1" t="s">
-        <v>1337</v>
+        <v>1314</v>
       </c>
       <c r="M625" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N625" s="1">
+      <c r="N625" s="10">
         <v>1</v>
       </c>
       <c r="O625" s="1" t="s">
@@ -35065,7 +35111,7 @@
     </row>
     <row r="626" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
-        <v>1348</v>
+        <v>1324</v>
       </c>
       <c r="B626" s="7" t="s">
         <v>1192</v>
@@ -35082,11 +35128,11 @@
       <c r="F626" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G626" s="1">
-        <v>71505538</v>
+      <c r="G626" s="10">
+        <v>72495328</v>
       </c>
       <c r="H626" s="1" t="s">
-        <v>1304</v>
+        <v>1422</v>
       </c>
       <c r="I626" s="1" t="s">
         <v>511</v>
@@ -35098,12 +35144,12 @@
         <v>251</v>
       </c>
       <c r="L626" s="1" t="s">
-        <v>1337</v>
+        <v>1314</v>
       </c>
       <c r="M626" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N626" s="1">
+      <c r="N626" s="10">
         <v>1</v>
       </c>
       <c r="O626" s="1" t="s">
@@ -35112,7 +35158,7 @@
     </row>
     <row r="627" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
-        <v>1349</v>
+        <v>1325</v>
       </c>
       <c r="B627" s="7" t="s">
         <v>1192</v>
@@ -35129,11 +35175,11 @@
       <c r="F627" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G627" s="1">
-        <v>61094381</v>
+      <c r="G627" s="10">
+        <v>75237035</v>
       </c>
       <c r="H627" s="1" t="s">
-        <v>1305</v>
+        <v>1423</v>
       </c>
       <c r="I627" s="1" t="s">
         <v>511</v>
@@ -35145,12 +35191,12 @@
         <v>251</v>
       </c>
       <c r="L627" s="1" t="s">
-        <v>1337</v>
+        <v>1314</v>
       </c>
       <c r="M627" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N627" s="1">
+      <c r="N627" s="10">
         <v>1</v>
       </c>
       <c r="O627" s="1" t="s">
@@ -35159,7 +35205,7 @@
     </row>
     <row r="628" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
-        <v>1350</v>
+        <v>1326</v>
       </c>
       <c r="B628" s="7" t="s">
         <v>1192</v>
@@ -35177,13 +35223,13 @@
         <v>771</v>
       </c>
       <c r="G628" s="1">
-        <v>60566010</v>
+        <v>10410053221</v>
       </c>
       <c r="H628" s="1" t="s">
-        <v>1306</v>
+        <v>1424</v>
       </c>
       <c r="I628" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J628" s="1" t="s">
         <v>155</v>
@@ -35192,12 +35238,12 @@
         <v>251</v>
       </c>
       <c r="L628" s="1" t="s">
-        <v>1337</v>
+        <v>1314</v>
       </c>
       <c r="M628" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N628" s="1">
+      <c r="N628" s="10">
         <v>1</v>
       </c>
       <c r="O628" s="1" t="s">
@@ -35206,7 +35252,7 @@
     </row>
     <row r="629" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
-        <v>1351</v>
+        <v>1327</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>1192</v>
@@ -35223,11 +35269,11 @@
       <c r="F629" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G629" s="1">
-        <v>72471575</v>
+      <c r="G629" s="10">
+        <v>76403635</v>
       </c>
       <c r="H629" s="1" t="s">
-        <v>1307</v>
+        <v>1425</v>
       </c>
       <c r="I629" s="1" t="s">
         <v>511</v>
@@ -35239,12 +35285,12 @@
         <v>251</v>
       </c>
       <c r="L629" s="1" t="s">
-        <v>1337</v>
+        <v>1314</v>
       </c>
       <c r="M629" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N629" s="1">
+      <c r="N629" s="10">
         <v>1</v>
       </c>
       <c r="O629" s="1" t="s">
@@ -35253,7 +35299,7 @@
     </row>
     <row r="630" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
-        <v>1352</v>
+        <v>1328</v>
       </c>
       <c r="B630" s="7" t="s">
         <v>1192</v>
@@ -35271,13 +35317,13 @@
         <v>771</v>
       </c>
       <c r="G630" s="1">
-        <v>71873373</v>
+        <v>10752826761</v>
       </c>
       <c r="H630" s="1" t="s">
-        <v>1308</v>
+        <v>1426</v>
       </c>
       <c r="I630" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="J630" s="1" t="s">
         <v>155</v>
@@ -35286,12 +35332,12 @@
         <v>251</v>
       </c>
       <c r="L630" s="1" t="s">
-        <v>1337</v>
+        <v>1314</v>
       </c>
       <c r="M630" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N630" s="1">
+      <c r="N630" s="10">
         <v>1</v>
       </c>
       <c r="O630" s="1" t="s">
@@ -35300,7 +35346,7 @@
     </row>
     <row r="631" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
-        <v>1353</v>
+        <v>1329</v>
       </c>
       <c r="B631" s="7" t="s">
         <v>1192</v>
@@ -35318,13 +35364,13 @@
         <v>771</v>
       </c>
       <c r="G631" s="1">
-        <v>76747062</v>
+        <v>10718515161</v>
       </c>
       <c r="H631" s="1" t="s">
-        <v>1309</v>
+        <v>1427</v>
       </c>
       <c r="I631" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J631" s="1" t="s">
         <v>155</v>
@@ -35333,12 +35379,12 @@
         <v>251</v>
       </c>
       <c r="L631" s="1" t="s">
-        <v>1337</v>
+        <v>1314</v>
       </c>
       <c r="M631" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N631" s="1">
+      <c r="N631" s="10">
         <v>1</v>
       </c>
       <c r="O631" s="1" t="s">
@@ -35347,10 +35393,10 @@
     </row>
     <row r="632" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
-        <v>1354</v>
+        <v>1330</v>
       </c>
       <c r="B632" s="7" t="s">
-        <v>1192</v>
+        <v>1141</v>
       </c>
       <c r="C632" s="1">
         <v>2026</v>
@@ -35362,16 +35408,16 @@
         <v>27</v>
       </c>
       <c r="F632" s="1" t="s">
-        <v>771</v>
+        <v>909</v>
       </c>
       <c r="G632" s="1">
-        <v>72076653</v>
+        <v>10249582862</v>
       </c>
       <c r="H632" s="1" t="s">
-        <v>1310</v>
+        <v>380</v>
       </c>
       <c r="I632" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="J632" s="1" t="s">
         <v>155</v>
@@ -35380,12 +35426,12 @@
         <v>251</v>
       </c>
       <c r="L632" s="1" t="s">
-        <v>1337</v>
+        <v>1315</v>
       </c>
       <c r="M632" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N632" s="1">
+      <c r="N632" s="10">
         <v>1</v>
       </c>
       <c r="O632" s="1" t="s">
@@ -35394,10 +35440,10 @@
     </row>
     <row r="633" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
-        <v>1355</v>
+        <v>1331</v>
       </c>
       <c r="B633" s="7" t="s">
-        <v>1192</v>
+        <v>1141</v>
       </c>
       <c r="C633" s="1">
         <v>2026</v>
@@ -35409,16 +35455,16 @@
         <v>27</v>
       </c>
       <c r="F633" s="1" t="s">
-        <v>771</v>
+        <v>909</v>
       </c>
       <c r="G633" s="1">
-        <v>70117125</v>
+        <v>10448659068</v>
       </c>
       <c r="H633" s="1" t="s">
-        <v>1311</v>
+        <v>376</v>
       </c>
       <c r="I633" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="J633" s="1" t="s">
         <v>155</v>
@@ -35427,12 +35473,12 @@
         <v>251</v>
       </c>
       <c r="L633" s="1" t="s">
-        <v>1337</v>
+        <v>1315</v>
       </c>
       <c r="M633" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N633" s="1">
+      <c r="N633" s="10">
         <v>1</v>
       </c>
       <c r="O633" s="1" t="s">
@@ -35441,10 +35487,10 @@
     </row>
     <row r="634" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
-        <v>1356</v>
+        <v>1332</v>
       </c>
       <c r="B634" s="7" t="s">
-        <v>1192</v>
+        <v>1141</v>
       </c>
       <c r="C634" s="1">
         <v>2026</v>
@@ -35456,16 +35502,16 @@
         <v>27</v>
       </c>
       <c r="F634" s="1" t="s">
-        <v>771</v>
+        <v>909</v>
       </c>
       <c r="G634" s="1">
-        <v>72495328</v>
+        <v>10239769018</v>
       </c>
       <c r="H634" s="1" t="s">
-        <v>1312</v>
+        <v>1295</v>
       </c>
       <c r="I634" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="J634" s="1" t="s">
         <v>155</v>
@@ -35474,12 +35520,12 @@
         <v>251</v>
       </c>
       <c r="L634" s="1" t="s">
-        <v>1337</v>
+        <v>1315</v>
       </c>
       <c r="M634" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N634" s="1">
+      <c r="N634" s="10">
         <v>1</v>
       </c>
       <c r="O634" s="1" t="s">
@@ -35488,10 +35534,10 @@
     </row>
     <row r="635" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
-        <v>1357</v>
+        <v>1333</v>
       </c>
       <c r="B635" s="7" t="s">
-        <v>1192</v>
+        <v>1141</v>
       </c>
       <c r="C635" s="1">
         <v>2026</v>
@@ -35503,16 +35549,16 @@
         <v>27</v>
       </c>
       <c r="F635" s="1" t="s">
-        <v>771</v>
+        <v>909</v>
       </c>
       <c r="G635" s="1">
-        <v>75237035</v>
+        <v>10421505093</v>
       </c>
       <c r="H635" s="1" t="s">
-        <v>1313</v>
+        <v>1296</v>
       </c>
       <c r="I635" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="J635" s="1" t="s">
         <v>155</v>
@@ -35521,12 +35567,12 @@
         <v>251</v>
       </c>
       <c r="L635" s="1" t="s">
-        <v>1337</v>
+        <v>1315</v>
       </c>
       <c r="M635" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N635" s="1">
+      <c r="N635" s="10">
         <v>1</v>
       </c>
       <c r="O635" s="1" t="s">
@@ -35535,10 +35581,10 @@
     </row>
     <row r="636" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
-        <v>1358</v>
+        <v>1334</v>
       </c>
       <c r="B636" s="7" t="s">
-        <v>1192</v>
+        <v>1141</v>
       </c>
       <c r="C636" s="1">
         <v>2026</v>
@@ -35550,16 +35596,16 @@
         <v>27</v>
       </c>
       <c r="F636" s="1" t="s">
-        <v>771</v>
+        <v>909</v>
       </c>
       <c r="G636" s="1">
-        <v>41005322</v>
+        <v>10445852398</v>
       </c>
       <c r="H636" s="1" t="s">
-        <v>1314</v>
+        <v>1297</v>
       </c>
       <c r="I636" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="J636" s="1" t="s">
         <v>155</v>
@@ -35568,12 +35614,12 @@
         <v>251</v>
       </c>
       <c r="L636" s="1" t="s">
-        <v>1337</v>
+        <v>1315</v>
       </c>
       <c r="M636" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N636" s="1">
+      <c r="N636" s="10">
         <v>1</v>
       </c>
       <c r="O636" s="1" t="s">
@@ -35582,10 +35628,10 @@
     </row>
     <row r="637" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
-        <v>1359</v>
+        <v>1335</v>
       </c>
       <c r="B637" s="7" t="s">
-        <v>1192</v>
+        <v>1141</v>
       </c>
       <c r="C637" s="1">
         <v>2026</v>
@@ -35597,16 +35643,16 @@
         <v>27</v>
       </c>
       <c r="F637" s="1" t="s">
-        <v>771</v>
+        <v>909</v>
       </c>
       <c r="G637" s="1">
-        <v>76403635</v>
+        <v>10413943545</v>
       </c>
       <c r="H637" s="1" t="s">
-        <v>1315</v>
+        <v>1298</v>
       </c>
       <c r="I637" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="J637" s="1" t="s">
         <v>155</v>
@@ -35615,12 +35661,12 @@
         <v>251</v>
       </c>
       <c r="L637" s="1" t="s">
-        <v>1337</v>
+        <v>1315</v>
       </c>
       <c r="M637" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N637" s="1">
+      <c r="N637" s="10">
         <v>1</v>
       </c>
       <c r="O637" s="1" t="s">
@@ -35629,10 +35675,10 @@
     </row>
     <row r="638" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
-        <v>1360</v>
+        <v>1336</v>
       </c>
       <c r="B638" s="7" t="s">
-        <v>1192</v>
+        <v>1141</v>
       </c>
       <c r="C638" s="1">
         <v>2026</v>
@@ -35644,16 +35690,16 @@
         <v>27</v>
       </c>
       <c r="F638" s="1" t="s">
-        <v>771</v>
+        <v>909</v>
       </c>
       <c r="G638" s="1">
-        <v>75282676</v>
+        <v>10239756587</v>
       </c>
       <c r="H638" s="1" t="s">
-        <v>1316</v>
+        <v>377</v>
       </c>
       <c r="I638" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="J638" s="1" t="s">
         <v>155</v>
@@ -35662,12 +35708,12 @@
         <v>251</v>
       </c>
       <c r="L638" s="1" t="s">
-        <v>1337</v>
+        <v>1315</v>
       </c>
       <c r="M638" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N638" s="1">
+      <c r="N638" s="10">
         <v>1</v>
       </c>
       <c r="O638" s="1" t="s">
@@ -35676,10 +35722,10 @@
     </row>
     <row r="639" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
-        <v>1361</v>
+        <v>1337</v>
       </c>
       <c r="B639" s="7" t="s">
-        <v>1192</v>
+        <v>1141</v>
       </c>
       <c r="C639" s="1">
         <v>2026</v>
@@ -35691,16 +35737,16 @@
         <v>27</v>
       </c>
       <c r="F639" s="1" t="s">
-        <v>771</v>
+        <v>909</v>
       </c>
       <c r="G639" s="1">
-        <v>71851516</v>
+        <v>10474747501</v>
       </c>
       <c r="H639" s="1" t="s">
-        <v>1317</v>
+        <v>1299</v>
       </c>
       <c r="I639" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="J639" s="1" t="s">
         <v>155</v>
@@ -35709,12 +35755,12 @@
         <v>251</v>
       </c>
       <c r="L639" s="1" t="s">
-        <v>1337</v>
+        <v>1315</v>
       </c>
       <c r="M639" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N639" s="1">
+      <c r="N639" s="10">
         <v>1</v>
       </c>
       <c r="O639" s="1" t="s">
@@ -35723,7 +35769,7 @@
     </row>
     <row r="640" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
-        <v>1362</v>
+        <v>1338</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>1141</v>
@@ -35741,13 +35787,13 @@
         <v>909</v>
       </c>
       <c r="G640" s="1">
-        <v>24958286</v>
+        <v>10473275011</v>
       </c>
       <c r="H640" s="1" t="s">
-        <v>380</v>
+        <v>1300</v>
       </c>
       <c r="I640" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="J640" s="1" t="s">
         <v>155</v>
@@ -35756,12 +35802,12 @@
         <v>251</v>
       </c>
       <c r="L640" s="1" t="s">
-        <v>1338</v>
+        <v>1315</v>
       </c>
       <c r="M640" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N640" s="1">
+      <c r="N640" s="10">
         <v>1</v>
       </c>
       <c r="O640" s="1" t="s">
@@ -35770,7 +35816,7 @@
     </row>
     <row r="641" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
-        <v>1363</v>
+        <v>1339</v>
       </c>
       <c r="B641" s="7" t="s">
         <v>1141</v>
@@ -35788,13 +35834,13 @@
         <v>909</v>
       </c>
       <c r="G641" s="1">
-        <v>44865906</v>
+        <v>10253201474</v>
       </c>
       <c r="H641" s="1" t="s">
-        <v>376</v>
+        <v>1301</v>
       </c>
       <c r="I641" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="J641" s="1" t="s">
         <v>155</v>
@@ -35803,12 +35849,12 @@
         <v>251</v>
       </c>
       <c r="L641" s="1" t="s">
-        <v>1338</v>
+        <v>1315</v>
       </c>
       <c r="M641" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N641" s="1">
+      <c r="N641" s="10">
         <v>1</v>
       </c>
       <c r="O641" s="1" t="s">
@@ -35817,7 +35863,7 @@
     </row>
     <row r="642" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
-        <v>1364</v>
+        <v>1340</v>
       </c>
       <c r="B642" s="7" t="s">
         <v>1141</v>
@@ -35835,13 +35881,13 @@
         <v>909</v>
       </c>
       <c r="G642" s="1">
-        <v>23976901</v>
+        <v>10426361936</v>
       </c>
       <c r="H642" s="1" t="s">
-        <v>1318</v>
+        <v>379</v>
       </c>
       <c r="I642" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="J642" s="1" t="s">
         <v>155</v>
@@ -35850,12 +35896,12 @@
         <v>251</v>
       </c>
       <c r="L642" s="1" t="s">
-        <v>1338</v>
+        <v>1315</v>
       </c>
       <c r="M642" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N642" s="1">
+      <c r="N642" s="10">
         <v>1</v>
       </c>
       <c r="O642" s="1" t="s">
@@ -35864,10 +35910,10 @@
     </row>
     <row r="643" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
-        <v>1365</v>
+        <v>1341</v>
       </c>
       <c r="B643" s="7" t="s">
-        <v>1141</v>
+        <v>1185</v>
       </c>
       <c r="C643" s="1">
         <v>2026</v>
@@ -35879,30 +35925,30 @@
         <v>27</v>
       </c>
       <c r="F643" s="1" t="s">
-        <v>909</v>
+        <v>771</v>
       </c>
       <c r="G643" s="1">
-        <v>42150509</v>
+        <v>10733216803</v>
       </c>
       <c r="H643" s="1" t="s">
-        <v>1319</v>
+        <v>1302</v>
       </c>
       <c r="I643" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J643" s="1" t="s">
         <v>155</v>
       </c>
       <c r="K643" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L643" s="1" t="s">
-        <v>1338</v>
+        <v>1428</v>
       </c>
       <c r="M643" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="N643" s="1">
+        <v>680</v>
+      </c>
+      <c r="N643" s="10">
         <v>1</v>
       </c>
       <c r="O643" s="1" t="s">
@@ -35911,10 +35957,10 @@
     </row>
     <row r="644" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
-        <v>1366</v>
+        <v>1342</v>
       </c>
       <c r="B644" s="7" t="s">
-        <v>1141</v>
+        <v>1185</v>
       </c>
       <c r="C644" s="1">
         <v>2026</v>
@@ -35926,13 +35972,13 @@
         <v>27</v>
       </c>
       <c r="F644" s="1" t="s">
-        <v>909</v>
-      </c>
-      <c r="G644" s="1">
-        <v>44585239</v>
+        <v>771</v>
+      </c>
+      <c r="G644" s="10">
+        <v>72495328</v>
       </c>
       <c r="H644" s="1" t="s">
-        <v>1320</v>
+        <v>1290</v>
       </c>
       <c r="I644" s="1" t="s">
         <v>511</v>
@@ -35941,15 +35987,15 @@
         <v>155</v>
       </c>
       <c r="K644" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L644" s="1" t="s">
-        <v>1338</v>
+        <v>1428</v>
       </c>
       <c r="M644" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="N644" s="1">
+        <v>680</v>
+      </c>
+      <c r="N644" s="10">
         <v>1</v>
       </c>
       <c r="O644" s="1" t="s">
@@ -35958,10 +36004,10 @@
     </row>
     <row r="645" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
-        <v>1367</v>
+        <v>1343</v>
       </c>
       <c r="B645" s="7" t="s">
-        <v>1141</v>
+        <v>1185</v>
       </c>
       <c r="C645" s="1">
         <v>2026</v>
@@ -35973,13 +36019,13 @@
         <v>27</v>
       </c>
       <c r="F645" s="1" t="s">
-        <v>909</v>
-      </c>
-      <c r="G645" s="1">
-        <v>41394354</v>
+        <v>771</v>
+      </c>
+      <c r="G645" s="10">
+        <v>75237035</v>
       </c>
       <c r="H645" s="1" t="s">
-        <v>1321</v>
+        <v>1291</v>
       </c>
       <c r="I645" s="1" t="s">
         <v>511</v>
@@ -35988,15 +36034,15 @@
         <v>155</v>
       </c>
       <c r="K645" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L645" s="1" t="s">
-        <v>1338</v>
+        <v>1428</v>
       </c>
       <c r="M645" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="N645" s="1">
+        <v>680</v>
+      </c>
+      <c r="N645" s="10">
         <v>1</v>
       </c>
       <c r="O645" s="1" t="s">
@@ -36005,10 +36051,10 @@
     </row>
     <row r="646" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
-        <v>1368</v>
+        <v>1344</v>
       </c>
       <c r="B646" s="7" t="s">
-        <v>1141</v>
+        <v>1185</v>
       </c>
       <c r="C646" s="1">
         <v>2026</v>
@@ -36020,13 +36066,13 @@
         <v>27</v>
       </c>
       <c r="F646" s="1" t="s">
-        <v>909</v>
-      </c>
-      <c r="G646" s="1">
-        <v>23975658</v>
+        <v>771</v>
+      </c>
+      <c r="G646" s="10">
+        <v>71727977</v>
       </c>
       <c r="H646" s="1" t="s">
-        <v>377</v>
+        <v>1303</v>
       </c>
       <c r="I646" s="1" t="s">
         <v>511</v>
@@ -36035,15 +36081,15 @@
         <v>155</v>
       </c>
       <c r="K646" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L646" s="1" t="s">
-        <v>1338</v>
+        <v>1428</v>
       </c>
       <c r="M646" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="N646" s="1">
+        <v>680</v>
+      </c>
+      <c r="N646" s="10">
         <v>1</v>
       </c>
       <c r="O646" s="1" t="s">
@@ -36052,10 +36098,10 @@
     </row>
     <row r="647" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
-        <v>1369</v>
+        <v>1345</v>
       </c>
       <c r="B647" s="7" t="s">
-        <v>1141</v>
+        <v>1185</v>
       </c>
       <c r="C647" s="1">
         <v>2026</v>
@@ -36067,13 +36113,13 @@
         <v>27</v>
       </c>
       <c r="F647" s="1" t="s">
-        <v>909</v>
-      </c>
-      <c r="G647" s="1">
-        <v>47474750</v>
+        <v>771</v>
+      </c>
+      <c r="G647" s="10">
+        <v>76403635</v>
       </c>
       <c r="H647" s="1" t="s">
-        <v>1322</v>
+        <v>1293</v>
       </c>
       <c r="I647" s="1" t="s">
         <v>511</v>
@@ -36082,15 +36128,15 @@
         <v>155</v>
       </c>
       <c r="K647" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L647" s="1" t="s">
-        <v>1338</v>
+        <v>1428</v>
       </c>
       <c r="M647" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="N647" s="1">
+        <v>680</v>
+      </c>
+      <c r="N647" s="10">
         <v>1</v>
       </c>
       <c r="O647" s="1" t="s">
@@ -36099,10 +36145,10 @@
     </row>
     <row r="648" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
-        <v>1370</v>
+        <v>1346</v>
       </c>
       <c r="B648" s="7" t="s">
-        <v>1141</v>
+        <v>1185</v>
       </c>
       <c r="C648" s="1">
         <v>2026</v>
@@ -36114,30 +36160,30 @@
         <v>27</v>
       </c>
       <c r="F648" s="1" t="s">
-        <v>909</v>
+        <v>771</v>
       </c>
       <c r="G648" s="1">
-        <v>47327501</v>
+        <v>10701171077</v>
       </c>
       <c r="H648" s="1" t="s">
-        <v>1323</v>
+        <v>1304</v>
       </c>
       <c r="I648" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J648" s="1" t="s">
         <v>155</v>
       </c>
       <c r="K648" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L648" s="1" t="s">
-        <v>1338</v>
+        <v>1428</v>
       </c>
       <c r="M648" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="N648" s="1">
+        <v>680</v>
+      </c>
+      <c r="N648" s="10">
         <v>1</v>
       </c>
       <c r="O648" s="1" t="s">
@@ -36146,10 +36192,10 @@
     </row>
     <row r="649" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
-        <v>1371</v>
+        <v>1347</v>
       </c>
       <c r="B649" s="7" t="s">
-        <v>1141</v>
+        <v>1185</v>
       </c>
       <c r="C649" s="1">
         <v>2026</v>
@@ -36161,13 +36207,13 @@
         <v>27</v>
       </c>
       <c r="F649" s="1" t="s">
-        <v>909</v>
-      </c>
-      <c r="G649" s="1">
-        <v>25320147</v>
+        <v>771</v>
+      </c>
+      <c r="G649" s="10">
+        <v>60171003</v>
       </c>
       <c r="H649" s="1" t="s">
-        <v>1324</v>
+        <v>1305</v>
       </c>
       <c r="I649" s="1" t="s">
         <v>511</v>
@@ -36176,15 +36222,15 @@
         <v>155</v>
       </c>
       <c r="K649" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L649" s="1" t="s">
-        <v>1338</v>
+        <v>1428</v>
       </c>
       <c r="M649" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="N649" s="1">
+        <v>680</v>
+      </c>
+      <c r="N649" s="10">
         <v>1</v>
       </c>
       <c r="O649" s="1" t="s">
@@ -36193,10 +36239,10 @@
     </row>
     <row r="650" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
-        <v>1372</v>
+        <v>1348</v>
       </c>
       <c r="B650" s="7" t="s">
-        <v>1141</v>
+        <v>1185</v>
       </c>
       <c r="C650" s="1">
         <v>2026</v>
@@ -36208,30 +36254,30 @@
         <v>27</v>
       </c>
       <c r="F650" s="1" t="s">
-        <v>909</v>
+        <v>771</v>
       </c>
       <c r="G650" s="1">
-        <v>42636193</v>
+        <v>10410053221</v>
       </c>
       <c r="H650" s="1" t="s">
-        <v>379</v>
+        <v>1292</v>
       </c>
       <c r="I650" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J650" s="1" t="s">
         <v>155</v>
       </c>
       <c r="K650" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L650" s="1" t="s">
-        <v>1338</v>
+        <v>1428</v>
       </c>
       <c r="M650" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="N650" s="1">
+        <v>680</v>
+      </c>
+      <c r="N650" s="10">
         <v>1</v>
       </c>
       <c r="O650" s="1" t="s">
@@ -36240,7 +36286,7 @@
     </row>
     <row r="651" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
-        <v>1373</v>
+        <v>1349</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>1185</v>
@@ -36258,13 +36304,13 @@
         <v>771</v>
       </c>
       <c r="G651" s="1">
-        <v>73321680</v>
+        <v>10715055380</v>
       </c>
       <c r="H651" s="1" t="s">
-        <v>1325</v>
+        <v>1306</v>
       </c>
       <c r="I651" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J651" s="1" t="s">
         <v>155</v>
@@ -36273,12 +36319,12 @@
         <v>252</v>
       </c>
       <c r="L651" s="1" t="s">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="M651" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N651" s="1">
+      <c r="N651" s="10">
         <v>1</v>
       </c>
       <c r="O651" s="1" t="s">
@@ -36287,7 +36333,7 @@
     </row>
     <row r="652" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
-        <v>1374</v>
+        <v>1350</v>
       </c>
       <c r="B652" s="7" t="s">
         <v>1185</v>
@@ -36304,11 +36350,11 @@
       <c r="F652" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G652" s="1">
-        <v>72495328</v>
+      <c r="G652" s="10">
+        <v>61094381</v>
       </c>
       <c r="H652" s="1" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="I652" s="1" t="s">
         <v>511</v>
@@ -36320,12 +36366,12 @@
         <v>252</v>
       </c>
       <c r="L652" s="1" t="s">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="M652" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N652" s="1">
+      <c r="N652" s="10">
         <v>1</v>
       </c>
       <c r="O652" s="1" t="s">
@@ -36334,7 +36380,7 @@
     </row>
     <row r="653" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
-        <v>1375</v>
+        <v>1351</v>
       </c>
       <c r="B653" s="7" t="s">
         <v>1185</v>
@@ -36351,11 +36397,11 @@
       <c r="F653" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G653" s="1">
-        <v>75237035</v>
+      <c r="G653" s="10">
+        <v>60566010</v>
       </c>
       <c r="H653" s="1" t="s">
-        <v>1313</v>
+        <v>1308</v>
       </c>
       <c r="I653" s="1" t="s">
         <v>511</v>
@@ -36367,12 +36413,12 @@
         <v>252</v>
       </c>
       <c r="L653" s="1" t="s">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="M653" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N653" s="1">
+      <c r="N653" s="10">
         <v>1</v>
       </c>
       <c r="O653" s="1" t="s">
@@ -36381,7 +36427,7 @@
     </row>
     <row r="654" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
-        <v>1376</v>
+        <v>1352</v>
       </c>
       <c r="B654" s="7" t="s">
         <v>1185</v>
@@ -36399,13 +36445,13 @@
         <v>771</v>
       </c>
       <c r="G654" s="1">
-        <v>71727977</v>
+        <v>10724715759</v>
       </c>
       <c r="H654" s="1" t="s">
-        <v>1326</v>
+        <v>1309</v>
       </c>
       <c r="I654" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J654" s="1" t="s">
         <v>155</v>
@@ -36414,12 +36460,12 @@
         <v>252</v>
       </c>
       <c r="L654" s="1" t="s">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="M654" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N654" s="1">
+      <c r="N654" s="10">
         <v>1</v>
       </c>
       <c r="O654" s="1" t="s">
@@ -36428,7 +36474,7 @@
     </row>
     <row r="655" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
-        <v>1377</v>
+        <v>1353</v>
       </c>
       <c r="B655" s="7" t="s">
         <v>1185</v>
@@ -36445,11 +36491,11 @@
       <c r="F655" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G655" s="1">
-        <v>76403635</v>
+      <c r="G655" s="10">
+        <v>71873373</v>
       </c>
       <c r="H655" s="1" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="I655" s="1" t="s">
         <v>511</v>
@@ -36461,12 +36507,12 @@
         <v>252</v>
       </c>
       <c r="L655" s="1" t="s">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="M655" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N655" s="1">
+      <c r="N655" s="10">
         <v>1</v>
       </c>
       <c r="O655" s="1" t="s">
@@ -36475,7 +36521,7 @@
     </row>
     <row r="656" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
-        <v>1378</v>
+        <v>1354</v>
       </c>
       <c r="B656" s="7" t="s">
         <v>1185</v>
@@ -36493,13 +36539,13 @@
         <v>771</v>
       </c>
       <c r="G656" s="1">
-        <v>70117107</v>
+        <v>10767470628</v>
       </c>
       <c r="H656" s="1" t="s">
-        <v>1327</v>
+        <v>1311</v>
       </c>
       <c r="I656" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J656" s="1" t="s">
         <v>155</v>
@@ -36508,12 +36554,12 @@
         <v>252</v>
       </c>
       <c r="L656" s="1" t="s">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="M656" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N656" s="1">
+      <c r="N656" s="10">
         <v>1</v>
       </c>
       <c r="O656" s="1" t="s">
@@ -36522,7 +36568,7 @@
     </row>
     <row r="657" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
-        <v>1379</v>
+        <v>1355</v>
       </c>
       <c r="B657" s="7" t="s">
         <v>1185</v>
@@ -36540,13 +36586,13 @@
         <v>771</v>
       </c>
       <c r="G657" s="1">
-        <v>60171003</v>
+        <v>10718515161</v>
       </c>
       <c r="H657" s="1" t="s">
-        <v>1328</v>
+        <v>1294</v>
       </c>
       <c r="I657" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J657" s="1" t="s">
         <v>155</v>
@@ -36555,12 +36601,12 @@
         <v>252</v>
       </c>
       <c r="L657" s="1" t="s">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="M657" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N657" s="1">
+      <c r="N657" s="10">
         <v>1</v>
       </c>
       <c r="O657" s="1" t="s">
@@ -36569,7 +36615,7 @@
     </row>
     <row r="658" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
-        <v>1380</v>
+        <v>1356</v>
       </c>
       <c r="B658" s="7" t="s">
         <v>1185</v>
@@ -36586,11 +36632,11 @@
       <c r="F658" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G658" s="1">
-        <v>41005322</v>
+      <c r="G658" s="10">
+        <v>72076653</v>
       </c>
       <c r="H658" s="1" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="I658" s="1" t="s">
         <v>511</v>
@@ -36602,12 +36648,12 @@
         <v>252</v>
       </c>
       <c r="L658" s="1" t="s">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="M658" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N658" s="1">
+      <c r="N658" s="10">
         <v>1</v>
       </c>
       <c r="O658" s="1" t="s">
@@ -36616,7 +36662,7 @@
     </row>
     <row r="659" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
-        <v>1381</v>
+        <v>1357</v>
       </c>
       <c r="B659" s="7" t="s">
         <v>1185</v>
@@ -36634,13 +36680,13 @@
         <v>771</v>
       </c>
       <c r="G659" s="1">
-        <v>71505538</v>
+        <v>10701171255</v>
       </c>
       <c r="H659" s="1" t="s">
-        <v>1329</v>
+        <v>1313</v>
       </c>
       <c r="I659" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J659" s="1" t="s">
         <v>155</v>
@@ -36649,12 +36695,12 @@
         <v>252</v>
       </c>
       <c r="L659" s="1" t="s">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="M659" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N659" s="1">
+      <c r="N659" s="10">
         <v>1</v>
       </c>
       <c r="O659" s="1" t="s">
@@ -36663,10 +36709,10 @@
     </row>
     <row r="660" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
-        <v>1382</v>
+        <v>1358</v>
       </c>
       <c r="B660" s="7" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="C660" s="1">
         <v>2026</v>
@@ -36681,13 +36727,13 @@
         <v>771</v>
       </c>
       <c r="G660" s="1">
-        <v>61094381</v>
+        <v>10733216803</v>
       </c>
       <c r="H660" s="1" t="s">
-        <v>1330</v>
+        <v>1302</v>
       </c>
       <c r="I660" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J660" s="1" t="s">
         <v>155</v>
@@ -36696,12 +36742,12 @@
         <v>252</v>
       </c>
       <c r="L660" s="1" t="s">
-        <v>1339</v>
+        <v>1316</v>
       </c>
       <c r="M660" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N660" s="1">
+      <c r="N660" s="10">
         <v>1</v>
       </c>
       <c r="O660" s="1" t="s">
@@ -36710,10 +36756,10 @@
     </row>
     <row r="661" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
-        <v>1383</v>
+        <v>1359</v>
       </c>
       <c r="B661" s="7" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="C661" s="1">
         <v>2026</v>
@@ -36727,11 +36773,11 @@
       <c r="F661" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G661" s="1">
-        <v>60566010</v>
+      <c r="G661" s="10">
+        <v>72495328</v>
       </c>
       <c r="H661" s="1" t="s">
-        <v>1331</v>
+        <v>1290</v>
       </c>
       <c r="I661" s="1" t="s">
         <v>511</v>
@@ -36743,12 +36789,12 @@
         <v>252</v>
       </c>
       <c r="L661" s="1" t="s">
-        <v>1339</v>
+        <v>1316</v>
       </c>
       <c r="M661" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N661" s="1">
+      <c r="N661" s="10">
         <v>1</v>
       </c>
       <c r="O661" s="1" t="s">
@@ -36757,10 +36803,10 @@
     </row>
     <row r="662" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
-        <v>1384</v>
+        <v>1360</v>
       </c>
       <c r="B662" s="7" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="C662" s="1">
         <v>2026</v>
@@ -36774,11 +36820,11 @@
       <c r="F662" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G662" s="1">
-        <v>72471575</v>
+      <c r="G662" s="10">
+        <v>75237035</v>
       </c>
       <c r="H662" s="1" t="s">
-        <v>1332</v>
+        <v>1291</v>
       </c>
       <c r="I662" s="1" t="s">
         <v>511</v>
@@ -36790,12 +36836,12 @@
         <v>252</v>
       </c>
       <c r="L662" s="1" t="s">
-        <v>1339</v>
+        <v>1316</v>
       </c>
       <c r="M662" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N662" s="1">
+      <c r="N662" s="10">
         <v>1</v>
       </c>
       <c r="O662" s="1" t="s">
@@ -36804,10 +36850,10 @@
     </row>
     <row r="663" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
-        <v>1385</v>
+        <v>1361</v>
       </c>
       <c r="B663" s="7" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="C663" s="1">
         <v>2026</v>
@@ -36821,11 +36867,11 @@
       <c r="F663" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G663" s="1">
-        <v>71873373</v>
+      <c r="G663" s="10">
+        <v>71727977</v>
       </c>
       <c r="H663" s="1" t="s">
-        <v>1333</v>
+        <v>1303</v>
       </c>
       <c r="I663" s="1" t="s">
         <v>511</v>
@@ -36837,12 +36883,12 @@
         <v>252</v>
       </c>
       <c r="L663" s="1" t="s">
-        <v>1339</v>
+        <v>1316</v>
       </c>
       <c r="M663" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N663" s="1">
+      <c r="N663" s="10">
         <v>1</v>
       </c>
       <c r="O663" s="1" t="s">
@@ -36851,10 +36897,10 @@
     </row>
     <row r="664" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
-        <v>1386</v>
+        <v>1362</v>
       </c>
       <c r="B664" s="7" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="C664" s="1">
         <v>2026</v>
@@ -36868,11 +36914,11 @@
       <c r="F664" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G664" s="1">
-        <v>76747062</v>
+      <c r="G664" s="10">
+        <v>76403635</v>
       </c>
       <c r="H664" s="1" t="s">
-        <v>1334</v>
+        <v>1293</v>
       </c>
       <c r="I664" s="1" t="s">
         <v>511</v>
@@ -36884,12 +36930,12 @@
         <v>252</v>
       </c>
       <c r="L664" s="1" t="s">
-        <v>1339</v>
+        <v>1316</v>
       </c>
       <c r="M664" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N664" s="1">
+      <c r="N664" s="10">
         <v>1</v>
       </c>
       <c r="O664" s="1" t="s">
@@ -36898,10 +36944,10 @@
     </row>
     <row r="665" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
-        <v>1387</v>
+        <v>1363</v>
       </c>
       <c r="B665" s="7" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="C665" s="1">
         <v>2026</v>
@@ -36916,13 +36962,13 @@
         <v>771</v>
       </c>
       <c r="G665" s="1">
-        <v>71851516</v>
+        <v>10701171077</v>
       </c>
       <c r="H665" s="1" t="s">
-        <v>1317</v>
+        <v>1304</v>
       </c>
       <c r="I665" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J665" s="1" t="s">
         <v>155</v>
@@ -36931,12 +36977,12 @@
         <v>252</v>
       </c>
       <c r="L665" s="1" t="s">
-        <v>1339</v>
+        <v>1316</v>
       </c>
       <c r="M665" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N665" s="1">
+      <c r="N665" s="10">
         <v>1</v>
       </c>
       <c r="O665" s="1" t="s">
@@ -36945,10 +36991,10 @@
     </row>
     <row r="666" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
-        <v>1388</v>
+        <v>1364</v>
       </c>
       <c r="B666" s="7" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="C666" s="1">
         <v>2026</v>
@@ -36962,11 +37008,11 @@
       <c r="F666" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G666" s="1">
-        <v>72076653</v>
+      <c r="G666" s="10">
+        <v>60171003</v>
       </c>
       <c r="H666" s="1" t="s">
-        <v>1335</v>
+        <v>1305</v>
       </c>
       <c r="I666" s="1" t="s">
         <v>511</v>
@@ -36978,12 +37024,12 @@
         <v>252</v>
       </c>
       <c r="L666" s="1" t="s">
-        <v>1339</v>
+        <v>1316</v>
       </c>
       <c r="M666" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N666" s="1">
+      <c r="N666" s="10">
         <v>1</v>
       </c>
       <c r="O666" s="1" t="s">
@@ -36992,10 +37038,10 @@
     </row>
     <row r="667" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
-        <v>1389</v>
+        <v>1365</v>
       </c>
       <c r="B667" s="7" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="C667" s="1">
         <v>2026</v>
@@ -37010,13 +37056,13 @@
         <v>771</v>
       </c>
       <c r="G667" s="1">
-        <v>70117125</v>
+        <v>10410053221</v>
       </c>
       <c r="H667" s="1" t="s">
-        <v>1336</v>
+        <v>1292</v>
       </c>
       <c r="I667" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J667" s="1" t="s">
         <v>155</v>
@@ -37025,12 +37071,12 @@
         <v>252</v>
       </c>
       <c r="L667" s="1" t="s">
-        <v>1339</v>
+        <v>1316</v>
       </c>
       <c r="M667" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N667" s="1">
+      <c r="N667" s="10">
         <v>1</v>
       </c>
       <c r="O667" s="1" t="s">
@@ -37039,7 +37085,7 @@
     </row>
     <row r="668" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
-        <v>1390</v>
+        <v>1366</v>
       </c>
       <c r="B668" s="7" t="s">
         <v>1193</v>
@@ -37057,13 +37103,13 @@
         <v>771</v>
       </c>
       <c r="G668" s="1">
-        <v>73321680</v>
+        <v>10715055380</v>
       </c>
       <c r="H668" s="1" t="s">
-        <v>1325</v>
+        <v>1306</v>
       </c>
       <c r="I668" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J668" s="1" t="s">
         <v>155</v>
@@ -37072,12 +37118,12 @@
         <v>252</v>
       </c>
       <c r="L668" s="1" t="s">
-        <v>1340</v>
+        <v>1316</v>
       </c>
       <c r="M668" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N668" s="1">
+      <c r="N668" s="10">
         <v>1</v>
       </c>
       <c r="O668" s="1" t="s">
@@ -37086,7 +37132,7 @@
     </row>
     <row r="669" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
-        <v>1391</v>
+        <v>1367</v>
       </c>
       <c r="B669" s="7" t="s">
         <v>1193</v>
@@ -37103,11 +37149,11 @@
       <c r="F669" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G669" s="1">
-        <v>72495328</v>
+      <c r="G669" s="10">
+        <v>61094381</v>
       </c>
       <c r="H669" s="1" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="I669" s="1" t="s">
         <v>511</v>
@@ -37119,12 +37165,12 @@
         <v>252</v>
       </c>
       <c r="L669" s="1" t="s">
-        <v>1340</v>
+        <v>1316</v>
       </c>
       <c r="M669" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N669" s="1">
+      <c r="N669" s="10">
         <v>1</v>
       </c>
       <c r="O669" s="1" t="s">
@@ -37133,7 +37179,7 @@
     </row>
     <row r="670" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
-        <v>1392</v>
+        <v>1368</v>
       </c>
       <c r="B670" s="7" t="s">
         <v>1193</v>
@@ -37150,11 +37196,11 @@
       <c r="F670" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G670" s="1">
-        <v>75237035</v>
+      <c r="G670" s="10">
+        <v>60566010</v>
       </c>
       <c r="H670" s="1" t="s">
-        <v>1313</v>
+        <v>1308</v>
       </c>
       <c r="I670" s="1" t="s">
         <v>511</v>
@@ -37166,12 +37212,12 @@
         <v>252</v>
       </c>
       <c r="L670" s="1" t="s">
-        <v>1340</v>
+        <v>1316</v>
       </c>
       <c r="M670" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N670" s="1">
+      <c r="N670" s="10">
         <v>1</v>
       </c>
       <c r="O670" s="1" t="s">
@@ -37180,7 +37226,7 @@
     </row>
     <row r="671" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
-        <v>1393</v>
+        <v>1369</v>
       </c>
       <c r="B671" s="7" t="s">
         <v>1193</v>
@@ -37198,13 +37244,13 @@
         <v>771</v>
       </c>
       <c r="G671" s="1">
-        <v>71727977</v>
+        <v>10724715759</v>
       </c>
       <c r="H671" s="1" t="s">
-        <v>1326</v>
+        <v>1309</v>
       </c>
       <c r="I671" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J671" s="1" t="s">
         <v>155</v>
@@ -37213,12 +37259,12 @@
         <v>252</v>
       </c>
       <c r="L671" s="1" t="s">
-        <v>1340</v>
+        <v>1316</v>
       </c>
       <c r="M671" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N671" s="1">
+      <c r="N671" s="10">
         <v>1</v>
       </c>
       <c r="O671" s="1" t="s">
@@ -37227,7 +37273,7 @@
     </row>
     <row r="672" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
-        <v>1394</v>
+        <v>1370</v>
       </c>
       <c r="B672" s="7" t="s">
         <v>1193</v>
@@ -37244,11 +37290,11 @@
       <c r="F672" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G672" s="1">
-        <v>76403635</v>
+      <c r="G672" s="10">
+        <v>71873373</v>
       </c>
       <c r="H672" s="1" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="I672" s="1" t="s">
         <v>511</v>
@@ -37260,12 +37306,12 @@
         <v>252</v>
       </c>
       <c r="L672" s="1" t="s">
-        <v>1340</v>
+        <v>1316</v>
       </c>
       <c r="M672" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N672" s="1">
+      <c r="N672" s="10">
         <v>1</v>
       </c>
       <c r="O672" s="1" t="s">
@@ -37274,7 +37320,7 @@
     </row>
     <row r="673" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
-        <v>1395</v>
+        <v>1371</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>1193</v>
@@ -37292,13 +37338,13 @@
         <v>771</v>
       </c>
       <c r="G673" s="1">
-        <v>70117107</v>
+        <v>10767470628</v>
       </c>
       <c r="H673" s="1" t="s">
-        <v>1327</v>
+        <v>1311</v>
       </c>
       <c r="I673" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J673" s="1" t="s">
         <v>155</v>
@@ -37307,12 +37353,12 @@
         <v>252</v>
       </c>
       <c r="L673" s="1" t="s">
-        <v>1340</v>
+        <v>1316</v>
       </c>
       <c r="M673" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N673" s="1">
+      <c r="N673" s="10">
         <v>1</v>
       </c>
       <c r="O673" s="1" t="s">
@@ -37321,7 +37367,7 @@
     </row>
     <row r="674" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
-        <v>1396</v>
+        <v>1372</v>
       </c>
       <c r="B674" s="7" t="s">
         <v>1193</v>
@@ -37339,13 +37385,13 @@
         <v>771</v>
       </c>
       <c r="G674" s="1">
-        <v>60171003</v>
+        <v>10718515161</v>
       </c>
       <c r="H674" s="1" t="s">
-        <v>1328</v>
+        <v>1294</v>
       </c>
       <c r="I674" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J674" s="1" t="s">
         <v>155</v>
@@ -37354,12 +37400,12 @@
         <v>252</v>
       </c>
       <c r="L674" s="1" t="s">
-        <v>1340</v>
+        <v>1316</v>
       </c>
       <c r="M674" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N674" s="1">
+      <c r="N674" s="10">
         <v>1</v>
       </c>
       <c r="O674" s="1" t="s">
@@ -37368,7 +37414,7 @@
     </row>
     <row r="675" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
-        <v>1397</v>
+        <v>1373</v>
       </c>
       <c r="B675" s="7" t="s">
         <v>1193</v>
@@ -37385,11 +37431,11 @@
       <c r="F675" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G675" s="1">
-        <v>41005322</v>
+      <c r="G675" s="10">
+        <v>72076653</v>
       </c>
       <c r="H675" s="1" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="I675" s="1" t="s">
         <v>511</v>
@@ -37401,12 +37447,12 @@
         <v>252</v>
       </c>
       <c r="L675" s="1" t="s">
-        <v>1340</v>
+        <v>1316</v>
       </c>
       <c r="M675" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N675" s="1">
+      <c r="N675" s="10">
         <v>1</v>
       </c>
       <c r="O675" s="1" t="s">
@@ -37415,7 +37461,7 @@
     </row>
     <row r="676" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
-        <v>1398</v>
+        <v>1374</v>
       </c>
       <c r="B676" s="7" t="s">
         <v>1193</v>
@@ -37433,13 +37479,13 @@
         <v>771</v>
       </c>
       <c r="G676" s="1">
-        <v>71505538</v>
+        <v>10701171255</v>
       </c>
       <c r="H676" s="1" t="s">
-        <v>1329</v>
+        <v>1313</v>
       </c>
       <c r="I676" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J676" s="1" t="s">
         <v>155</v>
@@ -37448,12 +37494,12 @@
         <v>252</v>
       </c>
       <c r="L676" s="1" t="s">
-        <v>1340</v>
+        <v>1316</v>
       </c>
       <c r="M676" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N676" s="1">
+      <c r="N676" s="10">
         <v>1</v>
       </c>
       <c r="O676" s="1" t="s">
@@ -37462,10 +37508,10 @@
     </row>
     <row r="677" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
-        <v>1399</v>
+        <v>1375</v>
       </c>
       <c r="B677" s="7" t="s">
-        <v>1193</v>
+        <v>1186</v>
       </c>
       <c r="C677" s="1">
         <v>2026</v>
@@ -37477,16 +37523,16 @@
         <v>27</v>
       </c>
       <c r="F677" s="1" t="s">
-        <v>771</v>
+        <v>562</v>
       </c>
       <c r="G677" s="1">
-        <v>61094381</v>
+        <v>10733216803</v>
       </c>
       <c r="H677" s="1" t="s">
-        <v>1330</v>
+        <v>1302</v>
       </c>
       <c r="I677" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J677" s="1" t="s">
         <v>155</v>
@@ -37495,12 +37541,12 @@
         <v>252</v>
       </c>
       <c r="L677" s="1" t="s">
-        <v>1340</v>
+        <v>1317</v>
       </c>
       <c r="M677" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N677" s="1">
+      <c r="N677" s="10">
         <v>1</v>
       </c>
       <c r="O677" s="1" t="s">
@@ -37509,10 +37555,10 @@
     </row>
     <row r="678" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
-        <v>1400</v>
+        <v>1376</v>
       </c>
       <c r="B678" s="7" t="s">
-        <v>1193</v>
+        <v>1186</v>
       </c>
       <c r="C678" s="1">
         <v>2026</v>
@@ -37524,13 +37570,13 @@
         <v>27</v>
       </c>
       <c r="F678" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G678" s="1">
-        <v>60566010</v>
+        <v>562</v>
+      </c>
+      <c r="G678" s="10">
+        <v>72495328</v>
       </c>
       <c r="H678" s="1" t="s">
-        <v>1331</v>
+        <v>1290</v>
       </c>
       <c r="I678" s="1" t="s">
         <v>511</v>
@@ -37542,12 +37588,12 @@
         <v>252</v>
       </c>
       <c r="L678" s="1" t="s">
-        <v>1340</v>
+        <v>1317</v>
       </c>
       <c r="M678" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N678" s="1">
+      <c r="N678" s="10">
         <v>1</v>
       </c>
       <c r="O678" s="1" t="s">
@@ -37556,10 +37602,10 @@
     </row>
     <row r="679" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
-        <v>1401</v>
+        <v>1377</v>
       </c>
       <c r="B679" s="7" t="s">
-        <v>1193</v>
+        <v>1186</v>
       </c>
       <c r="C679" s="1">
         <v>2026</v>
@@ -37571,13 +37617,13 @@
         <v>27</v>
       </c>
       <c r="F679" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G679" s="1">
-        <v>72471575</v>
+        <v>562</v>
+      </c>
+      <c r="G679" s="10">
+        <v>75237035</v>
       </c>
       <c r="H679" s="1" t="s">
-        <v>1332</v>
+        <v>1291</v>
       </c>
       <c r="I679" s="1" t="s">
         <v>511</v>
@@ -37589,12 +37635,12 @@
         <v>252</v>
       </c>
       <c r="L679" s="1" t="s">
-        <v>1340</v>
+        <v>1317</v>
       </c>
       <c r="M679" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N679" s="1">
+      <c r="N679" s="10">
         <v>1</v>
       </c>
       <c r="O679" s="1" t="s">
@@ -37603,10 +37649,10 @@
     </row>
     <row r="680" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
-        <v>1402</v>
+        <v>1378</v>
       </c>
       <c r="B680" s="7" t="s">
-        <v>1193</v>
+        <v>1186</v>
       </c>
       <c r="C680" s="1">
         <v>2026</v>
@@ -37618,13 +37664,13 @@
         <v>27</v>
       </c>
       <c r="F680" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G680" s="1">
-        <v>71873373</v>
+        <v>562</v>
+      </c>
+      <c r="G680" s="10">
+        <v>71727977</v>
       </c>
       <c r="H680" s="1" t="s">
-        <v>1333</v>
+        <v>1303</v>
       </c>
       <c r="I680" s="1" t="s">
         <v>511</v>
@@ -37636,12 +37682,12 @@
         <v>252</v>
       </c>
       <c r="L680" s="1" t="s">
-        <v>1340</v>
+        <v>1317</v>
       </c>
       <c r="M680" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N680" s="1">
+      <c r="N680" s="10">
         <v>1</v>
       </c>
       <c r="O680" s="1" t="s">
@@ -37650,10 +37696,10 @@
     </row>
     <row r="681" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
-        <v>1403</v>
+        <v>1379</v>
       </c>
       <c r="B681" s="7" t="s">
-        <v>1193</v>
+        <v>1186</v>
       </c>
       <c r="C681" s="1">
         <v>2026</v>
@@ -37665,13 +37711,13 @@
         <v>27</v>
       </c>
       <c r="F681" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G681" s="1">
-        <v>76747062</v>
+        <v>562</v>
+      </c>
+      <c r="G681" s="10">
+        <v>76403635</v>
       </c>
       <c r="H681" s="1" t="s">
-        <v>1334</v>
+        <v>1293</v>
       </c>
       <c r="I681" s="1" t="s">
         <v>511</v>
@@ -37683,12 +37729,12 @@
         <v>252</v>
       </c>
       <c r="L681" s="1" t="s">
-        <v>1340</v>
+        <v>1317</v>
       </c>
       <c r="M681" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N681" s="1">
+      <c r="N681" s="10">
         <v>1</v>
       </c>
       <c r="O681" s="1" t="s">
@@ -37697,10 +37743,10 @@
     </row>
     <row r="682" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
-        <v>1404</v>
+        <v>1380</v>
       </c>
       <c r="B682" s="7" t="s">
-        <v>1193</v>
+        <v>1186</v>
       </c>
       <c r="C682" s="1">
         <v>2026</v>
@@ -37712,16 +37758,16 @@
         <v>27</v>
       </c>
       <c r="F682" s="1" t="s">
-        <v>771</v>
+        <v>562</v>
       </c>
       <c r="G682" s="1">
-        <v>72076653</v>
+        <v>10701171077</v>
       </c>
       <c r="H682" s="1" t="s">
-        <v>1335</v>
+        <v>1304</v>
       </c>
       <c r="I682" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J682" s="1" t="s">
         <v>155</v>
@@ -37730,12 +37776,12 @@
         <v>252</v>
       </c>
       <c r="L682" s="1" t="s">
-        <v>1340</v>
+        <v>1317</v>
       </c>
       <c r="M682" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N682" s="1">
+      <c r="N682" s="10">
         <v>1</v>
       </c>
       <c r="O682" s="1" t="s">
@@ -37744,10 +37790,10 @@
     </row>
     <row r="683" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
-        <v>1405</v>
+        <v>1381</v>
       </c>
       <c r="B683" s="7" t="s">
-        <v>1193</v>
+        <v>1186</v>
       </c>
       <c r="C683" s="1">
         <v>2026</v>
@@ -37759,13 +37805,13 @@
         <v>27</v>
       </c>
       <c r="F683" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G683" s="1">
-        <v>70117125</v>
+        <v>562</v>
+      </c>
+      <c r="G683" s="10">
+        <v>60171003</v>
       </c>
       <c r="H683" s="1" t="s">
-        <v>1336</v>
+        <v>1305</v>
       </c>
       <c r="I683" s="1" t="s">
         <v>511</v>
@@ -37777,12 +37823,12 @@
         <v>252</v>
       </c>
       <c r="L683" s="1" t="s">
-        <v>1340</v>
+        <v>1317</v>
       </c>
       <c r="M683" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N683" s="1">
+      <c r="N683" s="10">
         <v>1</v>
       </c>
       <c r="O683" s="1" t="s">
@@ -37791,10 +37837,10 @@
     </row>
     <row r="684" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
-        <v>1406</v>
+        <v>1382</v>
       </c>
       <c r="B684" s="7" t="s">
-        <v>1193</v>
+        <v>1186</v>
       </c>
       <c r="C684" s="1">
         <v>2026</v>
@@ -37806,16 +37852,16 @@
         <v>27</v>
       </c>
       <c r="F684" s="1" t="s">
-        <v>771</v>
+        <v>562</v>
       </c>
       <c r="G684" s="1">
-        <v>71851516</v>
+        <v>10410053221</v>
       </c>
       <c r="H684" s="1" t="s">
-        <v>1317</v>
+        <v>1292</v>
       </c>
       <c r="I684" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J684" s="1" t="s">
         <v>155</v>
@@ -37824,12 +37870,12 @@
         <v>252</v>
       </c>
       <c r="L684" s="1" t="s">
-        <v>1340</v>
+        <v>1317</v>
       </c>
       <c r="M684" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N684" s="1">
+      <c r="N684" s="10">
         <v>1</v>
       </c>
       <c r="O684" s="1" t="s">
@@ -37838,7 +37884,7 @@
     </row>
     <row r="685" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
-        <v>1407</v>
+        <v>1383</v>
       </c>
       <c r="B685" s="7" t="s">
         <v>1186</v>
@@ -37856,13 +37902,13 @@
         <v>562</v>
       </c>
       <c r="G685" s="1">
-        <v>73321680</v>
+        <v>10715055380</v>
       </c>
       <c r="H685" s="1" t="s">
-        <v>1325</v>
+        <v>1306</v>
       </c>
       <c r="I685" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J685" s="1" t="s">
         <v>155</v>
@@ -37871,12 +37917,12 @@
         <v>252</v>
       </c>
       <c r="L685" s="1" t="s">
-        <v>1341</v>
+        <v>1317</v>
       </c>
       <c r="M685" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N685" s="1">
+      <c r="N685" s="10">
         <v>1</v>
       </c>
       <c r="O685" s="1" t="s">
@@ -37885,7 +37931,7 @@
     </row>
     <row r="686" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
-        <v>1408</v>
+        <v>1384</v>
       </c>
       <c r="B686" s="7" t="s">
         <v>1186</v>
@@ -37902,11 +37948,11 @@
       <c r="F686" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="G686" s="1">
-        <v>72495328</v>
+      <c r="G686" s="10">
+        <v>61094381</v>
       </c>
       <c r="H686" s="1" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="I686" s="1" t="s">
         <v>511</v>
@@ -37918,12 +37964,12 @@
         <v>252</v>
       </c>
       <c r="L686" s="1" t="s">
-        <v>1341</v>
+        <v>1317</v>
       </c>
       <c r="M686" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N686" s="1">
+      <c r="N686" s="10">
         <v>1</v>
       </c>
       <c r="O686" s="1" t="s">
@@ -37932,7 +37978,7 @@
     </row>
     <row r="687" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
-        <v>1409</v>
+        <v>1385</v>
       </c>
       <c r="B687" s="7" t="s">
         <v>1186</v>
@@ -37949,11 +37995,11 @@
       <c r="F687" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="G687" s="1">
-        <v>75237035</v>
+      <c r="G687" s="10">
+        <v>60566010</v>
       </c>
       <c r="H687" s="1" t="s">
-        <v>1313</v>
+        <v>1308</v>
       </c>
       <c r="I687" s="1" t="s">
         <v>511</v>
@@ -37965,12 +38011,12 @@
         <v>252</v>
       </c>
       <c r="L687" s="1" t="s">
-        <v>1341</v>
+        <v>1317</v>
       </c>
       <c r="M687" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N687" s="1">
+      <c r="N687" s="10">
         <v>1</v>
       </c>
       <c r="O687" s="1" t="s">
@@ -37979,7 +38025,7 @@
     </row>
     <row r="688" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
-        <v>1410</v>
+        <v>1386</v>
       </c>
       <c r="B688" s="7" t="s">
         <v>1186</v>
@@ -37997,13 +38043,13 @@
         <v>562</v>
       </c>
       <c r="G688" s="1">
-        <v>71727977</v>
+        <v>10724715759</v>
       </c>
       <c r="H688" s="1" t="s">
-        <v>1326</v>
+        <v>1309</v>
       </c>
       <c r="I688" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J688" s="1" t="s">
         <v>155</v>
@@ -38012,12 +38058,12 @@
         <v>252</v>
       </c>
       <c r="L688" s="1" t="s">
-        <v>1341</v>
+        <v>1317</v>
       </c>
       <c r="M688" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N688" s="1">
+      <c r="N688" s="10">
         <v>1</v>
       </c>
       <c r="O688" s="1" t="s">
@@ -38026,7 +38072,7 @@
     </row>
     <row r="689" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
-        <v>1411</v>
+        <v>1387</v>
       </c>
       <c r="B689" s="7" t="s">
         <v>1186</v>
@@ -38043,11 +38089,11 @@
       <c r="F689" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="G689" s="1">
-        <v>76403635</v>
+      <c r="G689" s="10">
+        <v>71873373</v>
       </c>
       <c r="H689" s="1" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="I689" s="1" t="s">
         <v>511</v>
@@ -38059,12 +38105,12 @@
         <v>252</v>
       </c>
       <c r="L689" s="1" t="s">
-        <v>1341</v>
+        <v>1317</v>
       </c>
       <c r="M689" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N689" s="1">
+      <c r="N689" s="10">
         <v>1</v>
       </c>
       <c r="O689" s="1" t="s">
@@ -38073,7 +38119,7 @@
     </row>
     <row r="690" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
-        <v>1412</v>
+        <v>1388</v>
       </c>
       <c r="B690" s="7" t="s">
         <v>1186</v>
@@ -38091,13 +38137,13 @@
         <v>562</v>
       </c>
       <c r="G690" s="1">
-        <v>70117107</v>
+        <v>10767470628</v>
       </c>
       <c r="H690" s="1" t="s">
-        <v>1327</v>
+        <v>1311</v>
       </c>
       <c r="I690" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J690" s="1" t="s">
         <v>155</v>
@@ -38106,12 +38152,12 @@
         <v>252</v>
       </c>
       <c r="L690" s="1" t="s">
-        <v>1341</v>
+        <v>1317</v>
       </c>
       <c r="M690" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N690" s="1">
+      <c r="N690" s="10">
         <v>1</v>
       </c>
       <c r="O690" s="1" t="s">
@@ -38120,7 +38166,7 @@
     </row>
     <row r="691" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
-        <v>1413</v>
+        <v>1389</v>
       </c>
       <c r="B691" s="7" t="s">
         <v>1186</v>
@@ -38137,11 +38183,11 @@
       <c r="F691" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="G691" s="1">
-        <v>60171003</v>
+      <c r="G691" s="10">
+        <v>72076653</v>
       </c>
       <c r="H691" s="1" t="s">
-        <v>1328</v>
+        <v>1312</v>
       </c>
       <c r="I691" s="1" t="s">
         <v>511</v>
@@ -38153,12 +38199,12 @@
         <v>252</v>
       </c>
       <c r="L691" s="1" t="s">
-        <v>1341</v>
+        <v>1317</v>
       </c>
       <c r="M691" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N691" s="1">
+      <c r="N691" s="10">
         <v>1</v>
       </c>
       <c r="O691" s="1" t="s">
@@ -38167,7 +38213,7 @@
     </row>
     <row r="692" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
-        <v>1414</v>
+        <v>1390</v>
       </c>
       <c r="B692" s="7" t="s">
         <v>1186</v>
@@ -38185,13 +38231,13 @@
         <v>562</v>
       </c>
       <c r="G692" s="1">
-        <v>41005322</v>
+        <v>10701171255</v>
       </c>
       <c r="H692" s="1" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I692" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J692" s="1" t="s">
         <v>155</v>
@@ -38200,12 +38246,12 @@
         <v>252</v>
       </c>
       <c r="L692" s="1" t="s">
-        <v>1341</v>
+        <v>1317</v>
       </c>
       <c r="M692" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N692" s="1">
+      <c r="N692" s="10">
         <v>1</v>
       </c>
       <c r="O692" s="1" t="s">
@@ -38214,7 +38260,7 @@
     </row>
     <row r="693" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
-        <v>1415</v>
+        <v>1391</v>
       </c>
       <c r="B693" s="7" t="s">
         <v>1186</v>
@@ -38232,13 +38278,13 @@
         <v>562</v>
       </c>
       <c r="G693" s="1">
-        <v>71505538</v>
+        <v>10718515161</v>
       </c>
       <c r="H693" s="1" t="s">
-        <v>1329</v>
+        <v>1294</v>
       </c>
       <c r="I693" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J693" s="1" t="s">
         <v>155</v>
@@ -38247,12 +38293,12 @@
         <v>252</v>
       </c>
       <c r="L693" s="1" t="s">
-        <v>1341</v>
+        <v>1317</v>
       </c>
       <c r="M693" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N693" s="1">
+      <c r="N693" s="10">
         <v>1</v>
       </c>
       <c r="O693" s="1" t="s">
@@ -38261,10 +38307,10 @@
     </row>
     <row r="694" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
-        <v>1416</v>
+        <v>1392</v>
       </c>
       <c r="B694" s="7" t="s">
-        <v>1186</v>
+        <v>1285</v>
       </c>
       <c r="C694" s="1">
         <v>2026</v>
@@ -38276,30 +38322,30 @@
         <v>27</v>
       </c>
       <c r="F694" s="1" t="s">
-        <v>562</v>
+        <v>1137</v>
       </c>
       <c r="G694" s="1">
-        <v>61094381</v>
+        <v>10476142941</v>
       </c>
       <c r="H694" s="1" t="s">
-        <v>1330</v>
+        <v>382</v>
       </c>
       <c r="I694" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J694" s="1" t="s">
-        <v>155</v>
+        <v>242</v>
       </c>
       <c r="K694" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="L694" s="1" t="s">
-        <v>1341</v>
+        <v>1401</v>
       </c>
       <c r="M694" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="N694" s="1">
+        <v>529</v>
+      </c>
+      <c r="N694" s="10">
         <v>1</v>
       </c>
       <c r="O694" s="1" t="s">
@@ -38308,10 +38354,10 @@
     </row>
     <row r="695" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A695" s="1" t="s">
-        <v>1417</v>
+        <v>1393</v>
       </c>
       <c r="B695" s="7" t="s">
-        <v>1186</v>
+        <v>1286</v>
       </c>
       <c r="C695" s="1">
         <v>2026</v>
@@ -38323,30 +38369,30 @@
         <v>27</v>
       </c>
       <c r="F695" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="G695" s="1">
-        <v>60566010</v>
+        <v>1137</v>
+      </c>
+      <c r="G695" s="10">
+        <v>10450876700</v>
       </c>
       <c r="H695" s="1" t="s">
-        <v>1331</v>
+        <v>381</v>
       </c>
       <c r="I695" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J695" s="1" t="s">
-        <v>155</v>
+        <v>242</v>
       </c>
       <c r="K695" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="L695" s="1" t="s">
-        <v>1341</v>
+        <v>1402</v>
       </c>
       <c r="M695" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="N695" s="1">
+        <v>529</v>
+      </c>
+      <c r="N695" s="10">
         <v>1</v>
       </c>
       <c r="O695" s="1" t="s">
@@ -38355,10 +38401,10 @@
     </row>
     <row r="696" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
-        <v>1418</v>
+        <v>1394</v>
       </c>
       <c r="B696" s="7" t="s">
-        <v>1186</v>
+        <v>1287</v>
       </c>
       <c r="C696" s="1">
         <v>2026</v>
@@ -38370,30 +38416,30 @@
         <v>27</v>
       </c>
       <c r="F696" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="G696" s="1">
-        <v>72471575</v>
+        <v>1137</v>
+      </c>
+      <c r="G696" s="10">
+        <v>10400403061</v>
       </c>
       <c r="H696" s="1" t="s">
-        <v>1332</v>
+        <v>1270</v>
       </c>
       <c r="I696" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="J696" s="1" t="s">
-        <v>155</v>
+        <v>242</v>
       </c>
       <c r="K696" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="L696" s="1" t="s">
-        <v>1341</v>
+        <v>1403</v>
       </c>
       <c r="M696" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="N696" s="1">
+        <v>529</v>
+      </c>
+      <c r="N696" s="10">
         <v>1</v>
       </c>
       <c r="O696" s="1" t="s">
@@ -38402,10 +38448,10 @@
     </row>
     <row r="697" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
-        <v>1419</v>
+        <v>1395</v>
       </c>
       <c r="B697" s="7" t="s">
-        <v>1186</v>
+        <v>1288</v>
       </c>
       <c r="C697" s="1">
         <v>2026</v>
@@ -38417,30 +38463,30 @@
         <v>27</v>
       </c>
       <c r="F697" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="G697" s="1">
-        <v>71873373</v>
+        <v>1137</v>
+      </c>
+      <c r="G697" s="10">
+        <v>47656632</v>
       </c>
       <c r="H697" s="1" t="s">
-        <v>1333</v>
+        <v>1271</v>
       </c>
       <c r="I697" s="1" t="s">
         <v>511</v>
       </c>
       <c r="J697" s="1" t="s">
-        <v>155</v>
+        <v>242</v>
       </c>
       <c r="K697" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="L697" s="1" t="s">
-        <v>1341</v>
+        <v>1404</v>
       </c>
       <c r="M697" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="N697" s="1">
+        <v>529</v>
+      </c>
+      <c r="N697" s="10">
         <v>1</v>
       </c>
       <c r="O697" s="1" t="s">
@@ -38449,10 +38495,10 @@
     </row>
     <row r="698" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A698" s="1" t="s">
-        <v>1420</v>
+        <v>1396</v>
       </c>
       <c r="B698" s="7" t="s">
-        <v>1186</v>
+        <v>1289</v>
       </c>
       <c r="C698" s="1">
         <v>2026</v>
@@ -38464,30 +38510,30 @@
         <v>27</v>
       </c>
       <c r="F698" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="G698" s="1">
-        <v>76747062</v>
+        <v>1137</v>
+      </c>
+      <c r="G698" s="10">
+        <v>47656632</v>
       </c>
       <c r="H698" s="1" t="s">
-        <v>1334</v>
+        <v>1271</v>
       </c>
       <c r="I698" s="1" t="s">
         <v>511</v>
       </c>
       <c r="J698" s="1" t="s">
-        <v>155</v>
+        <v>242</v>
       </c>
       <c r="K698" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="L698" s="1" t="s">
-        <v>1341</v>
+        <v>1405</v>
       </c>
       <c r="M698" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="N698" s="1">
+        <v>529</v>
+      </c>
+      <c r="N698" s="10">
         <v>1</v>
       </c>
       <c r="O698" s="1" t="s">
@@ -38496,7 +38542,7 @@
     </row>
     <row r="699" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A699" s="1" t="s">
-        <v>1421</v>
+        <v>1397</v>
       </c>
       <c r="B699" s="7" t="s">
         <v>1186</v>
@@ -38511,30 +38557,30 @@
         <v>27</v>
       </c>
       <c r="F699" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="G699" s="1">
-        <v>72076653</v>
+        <v>1137</v>
+      </c>
+      <c r="G699" s="10">
+        <v>10462583996</v>
       </c>
       <c r="H699" s="1" t="s">
-        <v>1335</v>
+        <v>385</v>
       </c>
       <c r="I699" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="J699" s="1" t="s">
-        <v>155</v>
+        <v>242</v>
       </c>
       <c r="K699" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="L699" s="1" t="s">
-        <v>1341</v>
+        <v>1406</v>
       </c>
       <c r="M699" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="N699" s="1">
+        <v>529</v>
+      </c>
+      <c r="N699" s="10">
         <v>1</v>
       </c>
       <c r="O699" s="1" t="s">
@@ -38543,10 +38589,10 @@
     </row>
     <row r="700" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A700" s="1" t="s">
-        <v>1422</v>
+        <v>1398</v>
       </c>
       <c r="B700" s="7" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="C700" s="1">
         <v>2026</v>
@@ -38558,31 +38604,31 @@
         <v>27</v>
       </c>
       <c r="F700" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="G700" s="1">
-        <v>70117125</v>
+        <v>1137</v>
+      </c>
+      <c r="G700" s="10">
+        <v>10462583996</v>
       </c>
       <c r="H700" s="1" t="s">
-        <v>1336</v>
+        <v>385</v>
       </c>
       <c r="I700" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="J700" s="1" t="s">
-        <v>155</v>
+        <v>194</v>
       </c>
       <c r="K700" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="L700" s="1" t="s">
-        <v>1341</v>
+        <v>1407</v>
       </c>
       <c r="M700" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="N700" s="1">
-        <v>1</v>
+        <v>529</v>
+      </c>
+      <c r="N700" s="10">
+        <v>15</v>
       </c>
       <c r="O700" s="1" t="s">
         <v>50</v>
@@ -38590,10 +38636,10 @@
     </row>
     <row r="701" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A701" s="1" t="s">
-        <v>1423</v>
+        <v>1399</v>
       </c>
       <c r="B701" s="7" t="s">
-        <v>1186</v>
+        <v>1191</v>
       </c>
       <c r="C701" s="1">
         <v>2026</v>
@@ -38605,30 +38651,30 @@
         <v>27</v>
       </c>
       <c r="F701" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="G701" s="1">
-        <v>71851516</v>
+        <v>1137</v>
+      </c>
+      <c r="G701" s="10">
+        <v>47925279</v>
       </c>
       <c r="H701" s="1" t="s">
-        <v>1317</v>
+        <v>1272</v>
       </c>
       <c r="I701" s="1" t="s">
         <v>511</v>
       </c>
       <c r="J701" s="1" t="s">
-        <v>155</v>
+        <v>242</v>
       </c>
       <c r="K701" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="L701" s="1" t="s">
-        <v>1341</v>
+        <v>1408</v>
       </c>
       <c r="M701" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="N701" s="1">
+        <v>529</v>
+      </c>
+      <c r="N701" s="10">
         <v>1</v>
       </c>
       <c r="O701" s="1" t="s">
@@ -38637,7 +38683,7 @@
     </row>
     <row r="702" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A702" s="1" t="s">
-        <v>1424</v>
+        <v>1400</v>
       </c>
       <c r="B702" s="7" t="s">
         <v>1141</v>
@@ -38655,13 +38701,13 @@
         <v>909</v>
       </c>
       <c r="G702" s="1">
-        <v>47316345</v>
+        <v>10473163450</v>
       </c>
       <c r="H702" s="1" t="s">
         <v>202</v>
       </c>
       <c r="I702" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="J702" s="1" t="s">
         <v>155</v>
@@ -38670,12 +38716,12 @@
         <v>251</v>
       </c>
       <c r="L702" s="1" t="s">
-        <v>1338</v>
+        <v>1315</v>
       </c>
       <c r="M702" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N702" s="1">
+      <c r="N702" s="10">
         <v>1</v>
       </c>
       <c r="O702" s="1" t="s">

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC893FA-F86C-4513-8EC7-26E347C22003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5586578-FB81-434F-B0BC-496F30A2DC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$608</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$702</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7714" uniqueCount="1429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7714" uniqueCount="1430">
   <si>
     <t>ID_ACTIVIDAD</t>
   </si>
@@ -4393,6 +4393,9 @@
   </si>
   <si>
     <t>CAPACITACIÓN EN INTRODUCCIÓN A LA ECONOMÍA CIRCULAR</t>
+  </si>
+  <si>
+    <t>FERNANDO YUPANQUI</t>
   </si>
 </sst>
 </file>
@@ -4483,7 +4486,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4506,7 +4509,6 @@
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4846,6 +4848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D04F3C6-8190-4D94-9613-CDA0600594BA}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:P702"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4917,7 +4920,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>509</v>
       </c>
@@ -4964,7 +4967,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>531</v>
       </c>
@@ -5011,7 +5014,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>532</v>
       </c>
@@ -5058,7 +5061,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>533</v>
       </c>
@@ -5105,7 +5108,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>534</v>
       </c>
@@ -5152,7 +5155,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>535</v>
       </c>
@@ -5199,7 +5202,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>536</v>
       </c>
@@ -5246,7 +5249,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>537</v>
       </c>
@@ -5293,7 +5296,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>538</v>
       </c>
@@ -5340,7 +5343,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>539</v>
       </c>
@@ -5387,7 +5390,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>540</v>
       </c>
@@ -5434,7 +5437,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>541</v>
       </c>
@@ -5481,7 +5484,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>542</v>
       </c>
@@ -5528,7 +5531,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>543</v>
       </c>
@@ -5575,7 +5578,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>544</v>
       </c>
@@ -5622,7 +5625,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>545</v>
       </c>
@@ -5669,7 +5672,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>546</v>
       </c>
@@ -5716,7 +5719,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>547</v>
       </c>
@@ -5763,7 +5766,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>548</v>
       </c>
@@ -5810,7 +5813,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>549</v>
       </c>
@@ -5857,7 +5860,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>550</v>
       </c>
@@ -5904,7 +5907,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>551</v>
       </c>
@@ -5951,7 +5954,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>552</v>
       </c>
@@ -5998,7 +6001,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>553</v>
       </c>
@@ -6045,7 +6048,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>554</v>
       </c>
@@ -6092,7 +6095,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>555</v>
       </c>
@@ -6139,7 +6142,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>556</v>
       </c>
@@ -6186,7 +6189,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>557</v>
       </c>
@@ -6233,7 +6236,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>558</v>
       </c>
@@ -6280,7 +6283,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>559</v>
       </c>
@@ -6327,7 +6330,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>560</v>
       </c>
@@ -6374,7 +6377,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>561</v>
       </c>
@@ -6421,7 +6424,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>566</v>
       </c>
@@ -6468,7 +6471,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>567</v>
       </c>
@@ -6515,7 +6518,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>568</v>
       </c>
@@ -6562,7 +6565,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>569</v>
       </c>
@@ -6609,7 +6612,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>570</v>
       </c>
@@ -6656,7 +6659,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>571</v>
       </c>
@@ -6703,7 +6706,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>572</v>
       </c>
@@ -6750,7 +6753,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>573</v>
       </c>
@@ -6797,7 +6800,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>574</v>
       </c>
@@ -6844,7 +6847,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>575</v>
       </c>
@@ -6891,7 +6894,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>576</v>
       </c>
@@ -6938,7 +6941,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>577</v>
       </c>
@@ -6985,7 +6988,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>578</v>
       </c>
@@ -7032,7 +7035,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>579</v>
       </c>
@@ -7079,7 +7082,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>580</v>
       </c>
@@ -7126,7 +7129,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>581</v>
       </c>
@@ -7173,7 +7176,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>582</v>
       </c>
@@ -7220,7 +7223,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>583</v>
       </c>
@@ -7267,7 +7270,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>584</v>
       </c>
@@ -7314,7 +7317,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>585</v>
       </c>
@@ -7361,7 +7364,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>586</v>
       </c>
@@ -7408,7 +7411,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>587</v>
       </c>
@@ -7455,7 +7458,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>588</v>
       </c>
@@ -7502,7 +7505,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>589</v>
       </c>
@@ -7549,7 +7552,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>590</v>
       </c>
@@ -7596,7 +7599,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>591</v>
       </c>
@@ -7643,7 +7646,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>592</v>
       </c>
@@ -7690,7 +7693,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>593</v>
       </c>
@@ -7737,7 +7740,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>594</v>
       </c>
@@ -7784,7 +7787,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>595</v>
       </c>
@@ -7831,7 +7834,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>596</v>
       </c>
@@ -7878,7 +7881,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>597</v>
       </c>
@@ -7925,7 +7928,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>598</v>
       </c>
@@ -7972,7 +7975,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>599</v>
       </c>
@@ -8019,7 +8022,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>600</v>
       </c>
@@ -8066,7 +8069,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>601</v>
       </c>
@@ -8113,7 +8116,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>602</v>
       </c>
@@ -8160,7 +8163,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>603</v>
       </c>
@@ -8207,7 +8210,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>604</v>
       </c>
@@ -8254,7 +8257,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>605</v>
       </c>
@@ -8301,7 +8304,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>606</v>
       </c>
@@ -8348,7 +8351,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>607</v>
       </c>
@@ -8395,7 +8398,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>608</v>
       </c>
@@ -8442,7 +8445,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>609</v>
       </c>
@@ -8489,7 +8492,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>610</v>
       </c>
@@ -8536,7 +8539,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>611</v>
       </c>
@@ -8583,7 +8586,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>612</v>
       </c>
@@ -8630,7 +8633,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>613</v>
       </c>
@@ -8677,7 +8680,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>614</v>
       </c>
@@ -8724,7 +8727,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>615</v>
       </c>
@@ -8771,7 +8774,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>616</v>
       </c>
@@ -8818,7 +8821,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>617</v>
       </c>
@@ -8865,7 +8868,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>618</v>
       </c>
@@ -8912,7 +8915,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>619</v>
       </c>
@@ -8959,7 +8962,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>620</v>
       </c>
@@ -9006,7 +9009,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>621</v>
       </c>
@@ -9053,7 +9056,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>622</v>
       </c>
@@ -9100,7 +9103,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>623</v>
       </c>
@@ -9147,7 +9150,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>624</v>
       </c>
@@ -9194,7 +9197,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>625</v>
       </c>
@@ -9241,7 +9244,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>626</v>
       </c>
@@ -9288,7 +9291,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>627</v>
       </c>
@@ -9335,7 +9338,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>628</v>
       </c>
@@ -9382,7 +9385,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>629</v>
       </c>
@@ -9429,7 +9432,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>630</v>
       </c>
@@ -9476,7 +9479,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>631</v>
       </c>
@@ -9523,7 +9526,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>632</v>
       </c>
@@ -9570,7 +9573,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>633</v>
       </c>
@@ -9617,7 +9620,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>634</v>
       </c>
@@ -9664,7 +9667,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>635</v>
       </c>
@@ -9711,7 +9714,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>636</v>
       </c>
@@ -9758,7 +9761,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>637</v>
       </c>
@@ -9805,7 +9808,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>638</v>
       </c>
@@ -9852,7 +9855,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>639</v>
       </c>
@@ -9899,7 +9902,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>640</v>
       </c>
@@ -9946,7 +9949,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>641</v>
       </c>
@@ -9993,7 +9996,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>642</v>
       </c>
@@ -10040,7 +10043,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>643</v>
       </c>
@@ -10087,7 +10090,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>644</v>
       </c>
@@ -10134,7 +10137,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>645</v>
       </c>
@@ -10181,7 +10184,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>646</v>
       </c>
@@ -10228,7 +10231,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>647</v>
       </c>
@@ -10275,7 +10278,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>648</v>
       </c>
@@ -10322,7 +10325,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>649</v>
       </c>
@@ -10369,7 +10372,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>650</v>
       </c>
@@ -10416,7 +10419,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>651</v>
       </c>
@@ -10463,7 +10466,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>652</v>
       </c>
@@ -10510,7 +10513,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>653</v>
       </c>
@@ -10557,7 +10560,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>654</v>
       </c>
@@ -10604,7 +10607,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>655</v>
       </c>
@@ -10651,7 +10654,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>656</v>
       </c>
@@ -10698,7 +10701,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>657</v>
       </c>
@@ -10745,7 +10748,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>658</v>
       </c>
@@ -10792,7 +10795,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>659</v>
       </c>
@@ -10839,7 +10842,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>660</v>
       </c>
@@ -10886,7 +10889,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>661</v>
       </c>
@@ -10933,7 +10936,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>662</v>
       </c>
@@ -10980,7 +10983,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>663</v>
       </c>
@@ -11027,7 +11030,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>664</v>
       </c>
@@ -11074,7 +11077,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>665</v>
       </c>
@@ -11121,7 +11124,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>666</v>
       </c>
@@ -11168,7 +11171,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>667</v>
       </c>
@@ -11215,7 +11218,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>693</v>
       </c>
@@ -11262,7 +11265,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>694</v>
       </c>
@@ -11309,7 +11312,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>695</v>
       </c>
@@ -11356,7 +11359,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>696</v>
       </c>
@@ -11403,7 +11406,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>697</v>
       </c>
@@ -11450,7 +11453,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>698</v>
       </c>
@@ -11497,7 +11500,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>699</v>
       </c>
@@ -11544,7 +11547,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>700</v>
       </c>
@@ -11591,7 +11594,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>701</v>
       </c>
@@ -11638,7 +11641,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>702</v>
       </c>
@@ -11685,7 +11688,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>703</v>
       </c>
@@ -11732,7 +11735,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>704</v>
       </c>
@@ -11779,7 +11782,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>705</v>
       </c>
@@ -11826,7 +11829,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>706</v>
       </c>
@@ -11873,7 +11876,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>707</v>
       </c>
@@ -11920,7 +11923,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>708</v>
       </c>
@@ -11967,7 +11970,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>709</v>
       </c>
@@ -12014,7 +12017,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>710</v>
       </c>
@@ -12061,7 +12064,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>711</v>
       </c>
@@ -12108,7 +12111,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>712</v>
       </c>
@@ -12155,7 +12158,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>713</v>
       </c>
@@ -12202,7 +12205,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>714</v>
       </c>
@@ -12249,7 +12252,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>715</v>
       </c>
@@ -12296,7 +12299,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>716</v>
       </c>
@@ -12343,7 +12346,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>717</v>
       </c>
@@ -12390,7 +12393,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>718</v>
       </c>
@@ -12437,7 +12440,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>719</v>
       </c>
@@ -12484,7 +12487,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>720</v>
       </c>
@@ -12531,7 +12534,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>721</v>
       </c>
@@ -12578,7 +12581,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>722</v>
       </c>
@@ -12625,7 +12628,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>723</v>
       </c>
@@ -12672,7 +12675,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>724</v>
       </c>
@@ -12719,7 +12722,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>725</v>
       </c>
@@ -12766,7 +12769,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>911</v>
       </c>
@@ -12816,7 +12819,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>913</v>
       </c>
@@ -12866,7 +12869,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>914</v>
       </c>
@@ -12916,7 +12919,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>915</v>
       </c>
@@ -12966,7 +12969,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>916</v>
       </c>
@@ -13016,7 +13019,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>917</v>
       </c>
@@ -13066,7 +13069,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>918</v>
       </c>
@@ -13116,7 +13119,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>919</v>
       </c>
@@ -13166,7 +13169,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>920</v>
       </c>
@@ -13216,7 +13219,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>921</v>
       </c>
@@ -13266,7 +13269,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>922</v>
       </c>
@@ -13316,7 +13319,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>923</v>
       </c>
@@ -13366,7 +13369,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>924</v>
       </c>
@@ -13416,7 +13419,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>925</v>
       </c>
@@ -13466,7 +13469,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>926</v>
       </c>
@@ -13516,7 +13519,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>927</v>
       </c>
@@ -13566,7 +13569,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>928</v>
       </c>
@@ -13616,7 +13619,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>929</v>
       </c>
@@ -13666,7 +13669,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>930</v>
       </c>
@@ -13716,7 +13719,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>931</v>
       </c>
@@ -13766,7 +13769,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>932</v>
       </c>
@@ -13816,7 +13819,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>933</v>
       </c>
@@ -13866,7 +13869,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>934</v>
       </c>
@@ -13916,7 +13919,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>935</v>
       </c>
@@ -13966,7 +13969,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>936</v>
       </c>
@@ -14016,7 +14019,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>937</v>
       </c>
@@ -14066,7 +14069,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>938</v>
       </c>
@@ -14116,7 +14119,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>939</v>
       </c>
@@ -14166,7 +14169,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>940</v>
       </c>
@@ -14216,7 +14219,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>941</v>
       </c>
@@ -14266,7 +14269,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>942</v>
       </c>
@@ -14316,7 +14319,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>943</v>
       </c>
@@ -14366,7 +14369,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>944</v>
       </c>
@@ -14416,7 +14419,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>945</v>
       </c>
@@ -14466,7 +14469,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>946</v>
       </c>
@@ -14516,7 +14519,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>947</v>
       </c>
@@ -14566,7 +14569,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>948</v>
       </c>
@@ -14616,7 +14619,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>949</v>
       </c>
@@ -14666,7 +14669,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>950</v>
       </c>
@@ -14716,7 +14719,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>951</v>
       </c>
@@ -14766,7 +14769,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>952</v>
       </c>
@@ -14816,7 +14819,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>953</v>
       </c>
@@ -14866,7 +14869,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>954</v>
       </c>
@@ -14916,7 +14919,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>955</v>
       </c>
@@ -14966,7 +14969,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>956</v>
       </c>
@@ -15016,7 +15019,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>957</v>
       </c>
@@ -15066,7 +15069,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>958</v>
       </c>
@@ -15116,7 +15119,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>959</v>
       </c>
@@ -15166,7 +15169,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>960</v>
       </c>
@@ -15216,7 +15219,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>961</v>
       </c>
@@ -15266,7 +15269,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>962</v>
       </c>
@@ -15316,7 +15319,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>963</v>
       </c>
@@ -15366,7 +15369,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>964</v>
       </c>
@@ -15416,7 +15419,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>965</v>
       </c>
@@ -15466,7 +15469,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>966</v>
       </c>
@@ -15516,7 +15519,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>967</v>
       </c>
@@ -15566,7 +15569,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>968</v>
       </c>
@@ -15616,7 +15619,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>742</v>
       </c>
@@ -15663,7 +15666,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>743</v>
       </c>
@@ -15710,7 +15713,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>744</v>
       </c>
@@ -15757,7 +15760,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>745</v>
       </c>
@@ -15804,7 +15807,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>746</v>
       </c>
@@ -15851,7 +15854,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>747</v>
       </c>
@@ -15898,7 +15901,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>748</v>
       </c>
@@ -15945,7 +15948,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>749</v>
       </c>
@@ -15992,7 +15995,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>750</v>
       </c>
@@ -16039,7 +16042,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>751</v>
       </c>
@@ -16086,7 +16089,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>752</v>
       </c>
@@ -16133,7 +16136,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>753</v>
       </c>
@@ -16180,7 +16183,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>754</v>
       </c>
@@ -16227,7 +16230,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>755</v>
       </c>
@@ -16274,7 +16277,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>756</v>
       </c>
@@ -16321,7 +16324,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>757</v>
       </c>
@@ -16368,7 +16371,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="242" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>758</v>
       </c>
@@ -16415,7 +16418,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>759</v>
       </c>
@@ -16462,7 +16465,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="244" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>760</v>
       </c>
@@ -16509,7 +16512,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="245" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>761</v>
       </c>
@@ -16556,7 +16559,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>762</v>
       </c>
@@ -16603,7 +16606,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>763</v>
       </c>
@@ -16650,7 +16653,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="248" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>764</v>
       </c>
@@ -16697,7 +16700,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>765</v>
       </c>
@@ -16744,7 +16747,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="250" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>766</v>
       </c>
@@ -16791,7 +16794,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>767</v>
       </c>
@@ -16838,7 +16841,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>768</v>
       </c>
@@ -16885,7 +16888,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>769</v>
       </c>
@@ -16932,7 +16935,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>770</v>
       </c>
@@ -16979,7 +16982,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>969</v>
       </c>
@@ -17029,7 +17032,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>970</v>
       </c>
@@ -17079,7 +17082,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="257" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>971</v>
       </c>
@@ -17129,7 +17132,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>972</v>
       </c>
@@ -17179,7 +17182,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>973</v>
       </c>
@@ -17229,7 +17232,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="260" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>974</v>
       </c>
@@ -17279,7 +17282,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="261" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>975</v>
       </c>
@@ -17329,7 +17332,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>976</v>
       </c>
@@ -17379,7 +17382,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="263" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>977</v>
       </c>
@@ -17429,7 +17432,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="264" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>978</v>
       </c>
@@ -17479,7 +17482,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>979</v>
       </c>
@@ -17529,7 +17532,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="266" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>980</v>
       </c>
@@ -17579,7 +17582,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>981</v>
       </c>
@@ -17629,7 +17632,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>982</v>
       </c>
@@ -17679,7 +17682,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="269" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>983</v>
       </c>
@@ -17729,7 +17732,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>984</v>
       </c>
@@ -17779,7 +17782,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="271" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>985</v>
       </c>
@@ -17829,7 +17832,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>986</v>
       </c>
@@ -17879,7 +17882,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>987</v>
       </c>
@@ -17929,7 +17932,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="274" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>988</v>
       </c>
@@ -17979,7 +17982,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="275" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>989</v>
       </c>
@@ -18029,7 +18032,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>990</v>
       </c>
@@ -18079,7 +18082,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>991</v>
       </c>
@@ -18129,7 +18132,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="278" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>992</v>
       </c>
@@ -18179,7 +18182,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>993</v>
       </c>
@@ -18229,7 +18232,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="280" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>994</v>
       </c>
@@ -18279,7 +18282,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>995</v>
       </c>
@@ -18329,7 +18332,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="282" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>996</v>
       </c>
@@ -18379,7 +18382,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="283" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>997</v>
       </c>
@@ -18429,7 +18432,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="284" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>998</v>
       </c>
@@ -18479,7 +18482,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>999</v>
       </c>
@@ -18529,7 +18532,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="286" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>1000</v>
       </c>
@@ -18579,7 +18582,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="287" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>1001</v>
       </c>
@@ -18629,7 +18632,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="288" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>1002</v>
       </c>
@@ -18679,7 +18682,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>1003</v>
       </c>
@@ -18729,7 +18732,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>1004</v>
       </c>
@@ -18779,7 +18782,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="291" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>1005</v>
       </c>
@@ -18829,7 +18832,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>1006</v>
       </c>
@@ -18879,7 +18882,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="293" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>1007</v>
       </c>
@@ -18929,7 +18932,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>1008</v>
       </c>
@@ -18979,7 +18982,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="295" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>1009</v>
       </c>
@@ -19029,7 +19032,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>1010</v>
       </c>
@@ -19079,7 +19082,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="297" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>1011</v>
       </c>
@@ -19129,7 +19132,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>773</v>
       </c>
@@ -19176,7 +19179,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="299" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>774</v>
       </c>
@@ -19223,7 +19226,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="300" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>775</v>
       </c>
@@ -19270,7 +19273,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="301" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>776</v>
       </c>
@@ -19317,7 +19320,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="302" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>777</v>
       </c>
@@ -19364,7 +19367,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="303" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>778</v>
       </c>
@@ -19411,7 +19414,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="304" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>779</v>
       </c>
@@ -19458,7 +19461,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="305" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>780</v>
       </c>
@@ -19505,7 +19508,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="306" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>781</v>
       </c>
@@ -19552,7 +19555,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="307" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>782</v>
       </c>
@@ -19599,7 +19602,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="308" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>1012</v>
       </c>
@@ -19649,7 +19652,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="309" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>1013</v>
       </c>
@@ -19699,7 +19702,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="310" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>1014</v>
       </c>
@@ -19749,7 +19752,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="311" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>1015</v>
       </c>
@@ -19799,7 +19802,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="312" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>1016</v>
       </c>
@@ -19849,7 +19852,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="313" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>1017</v>
       </c>
@@ -19899,7 +19902,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="314" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>1018</v>
       </c>
@@ -19949,7 +19952,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="315" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>1019</v>
       </c>
@@ -19999,7 +20002,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="316" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>1020</v>
       </c>
@@ -20049,7 +20052,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="317" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>1021</v>
       </c>
@@ -20099,7 +20102,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="318" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>1022</v>
       </c>
@@ -20149,7 +20152,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="319" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>1023</v>
       </c>
@@ -20199,7 +20202,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="320" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>1024</v>
       </c>
@@ -20249,7 +20252,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="321" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>1025</v>
       </c>
@@ -20299,7 +20302,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="322" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>1026</v>
       </c>
@@ -20349,7 +20352,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="323" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>1027</v>
       </c>
@@ -20399,7 +20402,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="324" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>1028</v>
       </c>
@@ -20449,7 +20452,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="325" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>1029</v>
       </c>
@@ -20499,7 +20502,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="326" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>1030</v>
       </c>
@@ -20549,7 +20552,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="327" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>1031</v>
       </c>
@@ -20599,7 +20602,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="328" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>1032</v>
       </c>
@@ -20649,7 +20652,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="329" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>1033</v>
       </c>
@@ -20699,7 +20702,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="330" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>1034</v>
       </c>
@@ -20749,7 +20752,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="331" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>1035</v>
       </c>
@@ -20799,7 +20802,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="332" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>1036</v>
       </c>
@@ -20849,7 +20852,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="333" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>1037</v>
       </c>
@@ -20899,7 +20902,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="334" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>1038</v>
       </c>
@@ -20949,7 +20952,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="335" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>1039</v>
       </c>
@@ -20999,7 +21002,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="336" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>1040</v>
       </c>
@@ -21049,7 +21052,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="337" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>1041</v>
       </c>
@@ -21099,7 +21102,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="338" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>1042</v>
       </c>
@@ -21149,7 +21152,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="339" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>1043</v>
       </c>
@@ -21199,7 +21202,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="340" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>1044</v>
       </c>
@@ -21249,7 +21252,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="341" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>1045</v>
       </c>
@@ -21299,7 +21302,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="342" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>1046</v>
       </c>
@@ -21349,7 +21352,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="343" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>1047</v>
       </c>
@@ -21399,7 +21402,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="344" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>1048</v>
       </c>
@@ -21449,7 +21452,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="345" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>1049</v>
       </c>
@@ -21499,7 +21502,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="346" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>1050</v>
       </c>
@@ -21549,7 +21552,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="347" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>1051</v>
       </c>
@@ -21599,7 +21602,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="348" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>1052</v>
       </c>
@@ -21649,7 +21652,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="349" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>1053</v>
       </c>
@@ -21699,7 +21702,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="350" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>1054</v>
       </c>
@@ -21749,7 +21752,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="351" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>1055</v>
       </c>
@@ -21799,7 +21802,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="352" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>1056</v>
       </c>
@@ -21849,7 +21852,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="353" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>1057</v>
       </c>
@@ -21899,7 +21902,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="354" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>1058</v>
       </c>
@@ -21949,7 +21952,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="355" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>1059</v>
       </c>
@@ -21999,7 +22002,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="356" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>1060</v>
       </c>
@@ -22049,7 +22052,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="357" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>1061</v>
       </c>
@@ -22099,7 +22102,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="358" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>1062</v>
       </c>
@@ -22149,7 +22152,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="359" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>1063</v>
       </c>
@@ -22199,7 +22202,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="360" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>1064</v>
       </c>
@@ -22249,7 +22252,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="361" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>1065</v>
       </c>
@@ -22299,7 +22302,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="362" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>1066</v>
       </c>
@@ -22349,7 +22352,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="363" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>1067</v>
       </c>
@@ -22399,7 +22402,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="364" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>1068</v>
       </c>
@@ -22449,7 +22452,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="365" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>1069</v>
       </c>
@@ -22499,7 +22502,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="366" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>1070</v>
       </c>
@@ -22549,7 +22552,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="367" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>1071</v>
       </c>
@@ -22599,7 +22602,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="368" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>1072</v>
       </c>
@@ -22649,7 +22652,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="369" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>1073</v>
       </c>
@@ -22699,7 +22702,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="370" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>1074</v>
       </c>
@@ -22749,7 +22752,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="371" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>1075</v>
       </c>
@@ -22799,7 +22802,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="372" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>1076</v>
       </c>
@@ -22849,7 +22852,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="373" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>1077</v>
       </c>
@@ -22899,7 +22902,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="374" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>1078</v>
       </c>
@@ -22949,7 +22952,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="375" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>1079</v>
       </c>
@@ -22999,7 +23002,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="376" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>1080</v>
       </c>
@@ -23049,7 +23052,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="377" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>1081</v>
       </c>
@@ -23099,7 +23102,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="378" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>1082</v>
       </c>
@@ -23149,7 +23152,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="379" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>1083</v>
       </c>
@@ -23199,7 +23202,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="380" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>1084</v>
       </c>
@@ -23249,7 +23252,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="381" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>1085</v>
       </c>
@@ -23299,7 +23302,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="382" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>1086</v>
       </c>
@@ -23349,7 +23352,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="383" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>1087</v>
       </c>
@@ -23399,7 +23402,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="384" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>1088</v>
       </c>
@@ -23449,7 +23452,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="385" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>1089</v>
       </c>
@@ -23499,7 +23502,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="386" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>1090</v>
       </c>
@@ -23549,7 +23552,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="387" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>1091</v>
       </c>
@@ -23599,7 +23602,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="388" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>1092</v>
       </c>
@@ -23649,7 +23652,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="389" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>1093</v>
       </c>
@@ -23699,7 +23702,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="390" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>1094</v>
       </c>
@@ -23749,7 +23752,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="391" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>1095</v>
       </c>
@@ -23799,7 +23802,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="392" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>1096</v>
       </c>
@@ -23849,7 +23852,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="393" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>1097</v>
       </c>
@@ -23899,7 +23902,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="394" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>1098</v>
       </c>
@@ -23949,7 +23952,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="395" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>1099</v>
       </c>
@@ -23999,7 +24002,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="396" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>1100</v>
       </c>
@@ -24049,7 +24052,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="397" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>1101</v>
       </c>
@@ -24099,7 +24102,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="398" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>1102</v>
       </c>
@@ -24149,7 +24152,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="399" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>1103</v>
       </c>
@@ -24199,7 +24202,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="400" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>1104</v>
       </c>
@@ -24249,7 +24252,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="401" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>1105</v>
       </c>
@@ -24299,7 +24302,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="402" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>1106</v>
       </c>
@@ -24349,7 +24352,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="403" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>1107</v>
       </c>
@@ -24399,7 +24402,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="404" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>1108</v>
       </c>
@@ -24449,7 +24452,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="405" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>1109</v>
       </c>
@@ -24499,7 +24502,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="406" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>1110</v>
       </c>
@@ -24549,7 +24552,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="407" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>1111</v>
       </c>
@@ -24599,7 +24602,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="408" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>1112</v>
       </c>
@@ -24649,7 +24652,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="409" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>1113</v>
       </c>
@@ -24699,7 +24702,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="410" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>1114</v>
       </c>
@@ -24749,7 +24752,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="411" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>1115</v>
       </c>
@@ -24799,7 +24802,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="412" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>1116</v>
       </c>
@@ -24849,7 +24852,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="413" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>1117</v>
       </c>
@@ -24899,7 +24902,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="414" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>1118</v>
       </c>
@@ -24949,7 +24952,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="415" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>1119</v>
       </c>
@@ -24999,7 +25002,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="416" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>1120</v>
       </c>
@@ -25049,7 +25052,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="417" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>1121</v>
       </c>
@@ -25099,7 +25102,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="418" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>1122</v>
       </c>
@@ -25149,7 +25152,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="419" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>1123</v>
       </c>
@@ -25199,7 +25202,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="420" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>1124</v>
       </c>
@@ -25249,7 +25252,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="421" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>1125</v>
       </c>
@@ -25299,7 +25302,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="422" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>1126</v>
       </c>
@@ -25349,7 +25352,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="423" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>1127</v>
       </c>
@@ -25399,7 +25402,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="424" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
         <v>1128</v>
       </c>
@@ -25449,7 +25452,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="425" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>1129</v>
       </c>
@@ -25499,7 +25502,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="426" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>1130</v>
       </c>
@@ -25549,7 +25552,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="427" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>1131</v>
       </c>
@@ -25599,7 +25602,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="428" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>1132</v>
       </c>
@@ -25649,7 +25652,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="429" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>1151</v>
       </c>
@@ -25699,7 +25702,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="430" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>1152</v>
       </c>
@@ -25749,7 +25752,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="431" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>1153</v>
       </c>
@@ -25799,7 +25802,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="432" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>1154</v>
       </c>
@@ -25849,7 +25852,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="433" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
         <v>1155</v>
       </c>
@@ -25899,7 +25902,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="434" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>1156</v>
       </c>
@@ -25949,7 +25952,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="435" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>1157</v>
       </c>
@@ -25999,7 +26002,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="436" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
         <v>1158</v>
       </c>
@@ -26049,7 +26052,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="437" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
         <v>1159</v>
       </c>
@@ -26099,7 +26102,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="438" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>1160</v>
       </c>
@@ -26149,7 +26152,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="439" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
         <v>1161</v>
       </c>
@@ -26199,7 +26202,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="440" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
         <v>1162</v>
       </c>
@@ -26249,7 +26252,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="441" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
         <v>1163</v>
       </c>
@@ -26299,7 +26302,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="442" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>1164</v>
       </c>
@@ -26349,7 +26352,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="443" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
         <v>1165</v>
       </c>
@@ -26399,7 +26402,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="444" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
         <v>1166</v>
       </c>
@@ -26449,7 +26452,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="445" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
         <v>1167</v>
       </c>
@@ -26499,7 +26502,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="446" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
         <v>797</v>
       </c>
@@ -26546,7 +26549,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="447" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
         <v>798</v>
       </c>
@@ -26593,7 +26596,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="448" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
         <v>799</v>
       </c>
@@ -26640,7 +26643,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="449" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
         <v>800</v>
       </c>
@@ -26687,7 +26690,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="450" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
         <v>801</v>
       </c>
@@ -26734,7 +26737,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="451" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
         <v>802</v>
       </c>
@@ -26781,7 +26784,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="452" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
         <v>803</v>
       </c>
@@ -26828,7 +26831,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="453" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
         <v>804</v>
       </c>
@@ -26875,7 +26878,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="454" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
         <v>805</v>
       </c>
@@ -26922,7 +26925,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="455" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
         <v>806</v>
       </c>
@@ -26969,7 +26972,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="456" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
         <v>807</v>
       </c>
@@ -27016,7 +27019,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="457" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
         <v>808</v>
       </c>
@@ -27063,7 +27066,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="458" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
         <v>809</v>
       </c>
@@ -27110,7 +27113,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="459" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
         <v>810</v>
       </c>
@@ -27157,7 +27160,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="460" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
         <v>811</v>
       </c>
@@ -27204,7 +27207,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="461" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
         <v>812</v>
       </c>
@@ -27251,7 +27254,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="462" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
         <v>813</v>
       </c>
@@ -27298,7 +27301,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="463" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
         <v>814</v>
       </c>
@@ -27345,7 +27348,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="464" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
         <v>815</v>
       </c>
@@ -27392,7 +27395,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="465" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
         <v>816</v>
       </c>
@@ -27439,7 +27442,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="466" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
         <v>817</v>
       </c>
@@ -27486,7 +27489,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="467" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
         <v>818</v>
       </c>
@@ -27533,7 +27536,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="468" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
         <v>819</v>
       </c>
@@ -27580,7 +27583,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="469" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
         <v>820</v>
       </c>
@@ -27627,7 +27630,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="470" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
         <v>821</v>
       </c>
@@ -27674,7 +27677,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="471" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
         <v>822</v>
       </c>
@@ -27721,7 +27724,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="472" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
         <v>823</v>
       </c>
@@ -27768,7 +27771,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="473" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
         <v>824</v>
       </c>
@@ -27815,7 +27818,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="474" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
         <v>825</v>
       </c>
@@ -27862,7 +27865,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="475" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
         <v>826</v>
       </c>
@@ -27909,7 +27912,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="476" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
         <v>827</v>
       </c>
@@ -27956,7 +27959,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="477" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
         <v>828</v>
       </c>
@@ -28003,7 +28006,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="478" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
         <v>829</v>
       </c>
@@ -28050,7 +28053,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="479" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
         <v>830</v>
       </c>
@@ -28097,7 +28100,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="480" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
         <v>831</v>
       </c>
@@ -28144,7 +28147,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="481" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
         <v>832</v>
       </c>
@@ -28191,7 +28194,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="482" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
         <v>833</v>
       </c>
@@ -28238,7 +28241,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="483" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
         <v>834</v>
       </c>
@@ -28285,7 +28288,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="484" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
         <v>835</v>
       </c>
@@ -28332,7 +28335,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="485" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
         <v>836</v>
       </c>
@@ -28379,7 +28382,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="486" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
         <v>837</v>
       </c>
@@ -28426,7 +28429,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="487" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
         <v>838</v>
       </c>
@@ -28473,7 +28476,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="488" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
         <v>839</v>
       </c>
@@ -28520,7 +28523,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="489" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
         <v>840</v>
       </c>
@@ -28567,7 +28570,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="490" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
         <v>841</v>
       </c>
@@ -28614,7 +28617,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="491" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
         <v>842</v>
       </c>
@@ -28661,7 +28664,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="492" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
         <v>843</v>
       </c>
@@ -28708,7 +28711,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="493" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
         <v>844</v>
       </c>
@@ -28755,7 +28758,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="494" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
         <v>845</v>
       </c>
@@ -28802,7 +28805,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="495" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
         <v>846</v>
       </c>
@@ -28849,7 +28852,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="496" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
         <v>847</v>
       </c>
@@ -28896,7 +28899,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="497" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
         <v>848</v>
       </c>
@@ -28943,7 +28946,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="498" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
         <v>849</v>
       </c>
@@ -28990,7 +28993,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="499" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
         <v>850</v>
       </c>
@@ -29037,7 +29040,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="500" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
         <v>851</v>
       </c>
@@ -29084,7 +29087,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="501" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
         <v>852</v>
       </c>
@@ -29131,7 +29134,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="502" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
         <v>853</v>
       </c>
@@ -29178,7 +29181,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="503" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
         <v>854</v>
       </c>
@@ -29225,7 +29228,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="504" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
         <v>855</v>
       </c>
@@ -29272,7 +29275,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="505" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
         <v>856</v>
       </c>
@@ -29319,7 +29322,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="506" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
         <v>857</v>
       </c>
@@ -29366,7 +29369,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="507" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
         <v>858</v>
       </c>
@@ -29413,7 +29416,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="508" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
         <v>859</v>
       </c>
@@ -29460,7 +29463,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="509" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
         <v>860</v>
       </c>
@@ -29507,7 +29510,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="510" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
         <v>861</v>
       </c>
@@ -29554,7 +29557,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="511" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
         <v>862</v>
       </c>
@@ -29601,7 +29604,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="512" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
         <v>863</v>
       </c>
@@ -29648,7 +29651,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="513" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
         <v>864</v>
       </c>
@@ -29695,7 +29698,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="514" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
         <v>865</v>
       </c>
@@ -29742,7 +29745,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="515" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
         <v>866</v>
       </c>
@@ -29789,7 +29792,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="516" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
         <v>867</v>
       </c>
@@ -29836,7 +29839,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="517" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
         <v>868</v>
       </c>
@@ -29883,7 +29886,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="518" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
         <v>869</v>
       </c>
@@ -29930,7 +29933,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="519" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
         <v>870</v>
       </c>
@@ -29977,7 +29980,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="520" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
         <v>871</v>
       </c>
@@ -30024,7 +30027,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="521" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
         <v>872</v>
       </c>
@@ -30071,7 +30074,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="522" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
         <v>873</v>
       </c>
@@ -30118,7 +30121,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="523" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
         <v>874</v>
       </c>
@@ -30165,7 +30168,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="524" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
         <v>875</v>
       </c>
@@ -30212,7 +30215,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="525" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
         <v>876</v>
       </c>
@@ -30259,7 +30262,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="526" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
         <v>877</v>
       </c>
@@ -30306,7 +30309,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="527" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
         <v>878</v>
       </c>
@@ -30353,7 +30356,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="528" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
         <v>879</v>
       </c>
@@ -30400,7 +30403,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="529" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
         <v>880</v>
       </c>
@@ -30447,7 +30450,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="530" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
         <v>881</v>
       </c>
@@ -30491,7 +30494,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="531" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
         <v>882</v>
       </c>
@@ -30535,7 +30538,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="532" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
         <v>883</v>
       </c>
@@ -30582,7 +30585,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="533" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
         <v>884</v>
       </c>
@@ -30629,7 +30632,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="534" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
         <v>885</v>
       </c>
@@ -30676,7 +30679,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="535" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
         <v>886</v>
       </c>
@@ -30723,7 +30726,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="536" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
         <v>887</v>
       </c>
@@ -30770,7 +30773,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="537" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
         <v>888</v>
       </c>
@@ -30817,7 +30820,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="538" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
         <v>889</v>
       </c>
@@ -30861,7 +30864,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="539" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
         <v>890</v>
       </c>
@@ -30905,7 +30908,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="540" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
         <v>891</v>
       </c>
@@ -30952,7 +30955,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="541" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
         <v>892</v>
       </c>
@@ -30999,7 +31002,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="542" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
         <v>893</v>
       </c>
@@ -31046,7 +31049,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="543" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
         <v>894</v>
       </c>
@@ -31093,7 +31096,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="544" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
         <v>895</v>
       </c>
@@ -31140,7 +31143,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="545" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
         <v>896</v>
       </c>
@@ -31187,7 +31190,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="546" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
         <v>897</v>
       </c>
@@ -31234,7 +31237,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="547" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
         <v>898</v>
       </c>
@@ -31281,7 +31284,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="548" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
         <v>899</v>
       </c>
@@ -31328,7 +31331,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="549" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
         <v>900</v>
       </c>
@@ -31375,7 +31378,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="550" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
         <v>901</v>
       </c>
@@ -31422,7 +31425,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="551" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
         <v>902</v>
       </c>
@@ -31469,7 +31472,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="552" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
         <v>903</v>
       </c>
@@ -31516,7 +31519,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="553" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
         <v>904</v>
       </c>
@@ -31563,7 +31566,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="554" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
         <v>905</v>
       </c>
@@ -31610,7 +31613,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="555" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
         <v>1195</v>
       </c>
@@ -31660,7 +31663,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="556" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
         <v>1196</v>
       </c>
@@ -31710,7 +31713,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="557" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
         <v>1197</v>
       </c>
@@ -31760,7 +31763,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="558" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
         <v>1198</v>
       </c>
@@ -31810,7 +31813,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="559" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
         <v>1199</v>
       </c>
@@ -31860,7 +31863,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="560" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
         <v>1200</v>
       </c>
@@ -31910,7 +31913,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="561" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
         <v>1201</v>
       </c>
@@ -31960,7 +31963,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="562" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
         <v>1202</v>
       </c>
@@ -32010,7 +32013,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="563" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
         <v>1203</v>
       </c>
@@ -32060,7 +32063,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="564" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
         <v>1204</v>
       </c>
@@ -32110,7 +32113,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="565" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
         <v>1205</v>
       </c>
@@ -32160,7 +32163,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="566" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
         <v>1206</v>
       </c>
@@ -32210,7 +32213,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="567" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
         <v>1207</v>
       </c>
@@ -32260,7 +32263,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="568" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
         <v>1208</v>
       </c>
@@ -32310,7 +32313,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="569" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
         <v>1209</v>
       </c>
@@ -32360,7 +32363,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="570" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
         <v>1210</v>
       </c>
@@ -32410,7 +32413,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="571" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
         <v>1211</v>
       </c>
@@ -32460,7 +32463,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="572" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
         <v>1212</v>
       </c>
@@ -32510,7 +32513,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="573" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
         <v>1213</v>
       </c>
@@ -32560,7 +32563,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="574" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
         <v>1214</v>
       </c>
@@ -32610,7 +32613,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="575" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
         <v>1215</v>
       </c>
@@ -32660,7 +32663,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="576" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
         <v>1216</v>
       </c>
@@ -32710,7 +32713,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="577" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
         <v>1217</v>
       </c>
@@ -32760,7 +32763,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="578" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
         <v>1218</v>
       </c>
@@ -32810,7 +32813,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="579" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
         <v>1219</v>
       </c>
@@ -32860,7 +32863,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="580" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
         <v>1220</v>
       </c>
@@ -32910,7 +32913,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="581" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
         <v>1221</v>
       </c>
@@ -32960,7 +32963,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="582" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
         <v>1222</v>
       </c>
@@ -33010,7 +33013,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="583" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
         <v>1223</v>
       </c>
@@ -33060,7 +33063,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="584" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
         <v>1224</v>
       </c>
@@ -33110,7 +33113,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="585" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
         <v>1225</v>
       </c>
@@ -33160,7 +33163,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="586" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
         <v>1226</v>
       </c>
@@ -33210,7 +33213,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="587" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
         <v>1227</v>
       </c>
@@ -33260,7 +33263,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="588" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
         <v>1228</v>
       </c>
@@ -33310,7 +33313,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="589" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
         <v>1229</v>
       </c>
@@ -33360,7 +33363,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="590" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
         <v>1230</v>
       </c>
@@ -33410,7 +33413,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="591" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
         <v>1231</v>
       </c>
@@ -33460,7 +33463,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="592" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
         <v>1232</v>
       </c>
@@ -33510,7 +33513,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="593" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
         <v>1233</v>
       </c>
@@ -33560,7 +33563,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="594" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
         <v>1234</v>
       </c>
@@ -33610,7 +33613,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="595" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
         <v>1235</v>
       </c>
@@ -33660,7 +33663,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="596" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
         <v>1236</v>
       </c>
@@ -33710,7 +33713,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="597" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
         <v>1237</v>
       </c>
@@ -33760,7 +33763,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="598" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
         <v>1238</v>
       </c>
@@ -33810,7 +33813,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="599" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
         <v>1239</v>
       </c>
@@ -33860,7 +33863,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="600" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
         <v>1240</v>
       </c>
@@ -33910,7 +33913,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="601" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
         <v>1241</v>
       </c>
@@ -33960,7 +33963,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="602" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
         <v>1242</v>
       </c>
@@ -34010,7 +34013,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="603" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
         <v>1243</v>
       </c>
@@ -34060,7 +34063,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="604" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
         <v>1244</v>
       </c>
@@ -34110,7 +34113,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="605" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
         <v>1245</v>
       </c>
@@ -34160,7 +34163,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="606" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
         <v>1246</v>
       </c>
@@ -34210,7 +34213,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="607" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
         <v>1247</v>
       </c>
@@ -34260,7 +34263,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="608" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
         <v>1247</v>
       </c>
@@ -34329,7 +34332,7 @@
       <c r="F609" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G609" s="10">
+      <c r="G609" s="1">
         <v>10238869094</v>
       </c>
       <c r="H609" s="1" t="s">
@@ -34350,7 +34353,7 @@
       <c r="M609" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N609" s="10">
+      <c r="N609" s="1">
         <v>6</v>
       </c>
       <c r="O609" s="1" t="s">
@@ -34376,7 +34379,7 @@
       <c r="F610" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G610" s="10">
+      <c r="G610" s="1">
         <v>10247032270</v>
       </c>
       <c r="H610" s="1" t="s">
@@ -34397,7 +34400,7 @@
       <c r="M610" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N610" s="10">
+      <c r="N610" s="1">
         <v>4</v>
       </c>
       <c r="O610" s="1" t="s">
@@ -34423,7 +34426,7 @@
       <c r="F611" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G611" s="10">
+      <c r="G611" s="1">
         <v>20606059338</v>
       </c>
       <c r="H611" s="1" t="s">
@@ -34444,7 +34447,7 @@
       <c r="M611" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N611" s="10">
+      <c r="N611" s="1">
         <v>11</v>
       </c>
       <c r="O611" s="1" t="s">
@@ -34470,7 +34473,7 @@
       <c r="F612" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G612" s="10">
+      <c r="G612" s="1">
         <v>10248679081</v>
       </c>
       <c r="H612" s="1" t="s">
@@ -34491,7 +34494,7 @@
       <c r="M612" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N612" s="10">
+      <c r="N612" s="1">
         <v>4</v>
       </c>
       <c r="O612" s="1" t="s">
@@ -34538,7 +34541,7 @@
       <c r="M613" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N613" s="10">
+      <c r="N613" s="1">
         <v>1</v>
       </c>
       <c r="O613" s="1" t="s">
@@ -34564,7 +34567,7 @@
       <c r="F614" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G614" s="10">
+      <c r="G614" s="1">
         <v>71727977</v>
       </c>
       <c r="H614" s="1" t="s">
@@ -34585,7 +34588,7 @@
       <c r="M614" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N614" s="10">
+      <c r="N614" s="1">
         <v>1</v>
       </c>
       <c r="O614" s="1" t="s">
@@ -34632,7 +34635,7 @@
       <c r="M615" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N615" s="10">
+      <c r="N615" s="1">
         <v>1</v>
       </c>
       <c r="O615" s="1" t="s">
@@ -34679,7 +34682,7 @@
       <c r="M616" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N616" s="10">
+      <c r="N616" s="1">
         <v>1</v>
       </c>
       <c r="O616" s="1" t="s">
@@ -34705,7 +34708,7 @@
       <c r="F617" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G617" s="10">
+      <c r="G617" s="1">
         <v>60171003</v>
       </c>
       <c r="H617" s="1" t="s">
@@ -34726,7 +34729,7 @@
       <c r="M617" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N617" s="10">
+      <c r="N617" s="1">
         <v>1</v>
       </c>
       <c r="O617" s="1" t="s">
@@ -34773,7 +34776,7 @@
       <c r="M618" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N618" s="10">
+      <c r="N618" s="1">
         <v>1</v>
       </c>
       <c r="O618" s="1" t="s">
@@ -34799,7 +34802,7 @@
       <c r="F619" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G619" s="10">
+      <c r="G619" s="1">
         <v>61094381</v>
       </c>
       <c r="H619" s="1" t="s">
@@ -34820,7 +34823,7 @@
       <c r="M619" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N619" s="10">
+      <c r="N619" s="1">
         <v>1</v>
       </c>
       <c r="O619" s="1" t="s">
@@ -34846,7 +34849,7 @@
       <c r="F620" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G620" s="10">
+      <c r="G620" s="1">
         <v>60566010</v>
       </c>
       <c r="H620" s="1" t="s">
@@ -34867,7 +34870,7 @@
       <c r="M620" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N620" s="10">
+      <c r="N620" s="1">
         <v>1</v>
       </c>
       <c r="O620" s="1" t="s">
@@ -34914,7 +34917,7 @@
       <c r="M621" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N621" s="10">
+      <c r="N621" s="1">
         <v>1</v>
       </c>
       <c r="O621" s="1" t="s">
@@ -34940,7 +34943,7 @@
       <c r="F622" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G622" s="10">
+      <c r="G622" s="1">
         <v>71873373</v>
       </c>
       <c r="H622" s="1" t="s">
@@ -34961,7 +34964,7 @@
       <c r="M622" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N622" s="10">
+      <c r="N622" s="1">
         <v>1</v>
       </c>
       <c r="O622" s="1" t="s">
@@ -35008,7 +35011,7 @@
       <c r="M623" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N623" s="10">
+      <c r="N623" s="1">
         <v>1</v>
       </c>
       <c r="O623" s="1" t="s">
@@ -35034,7 +35037,7 @@
       <c r="F624" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G624" s="10">
+      <c r="G624" s="1">
         <v>72076653</v>
       </c>
       <c r="H624" s="1" t="s">
@@ -35055,7 +35058,7 @@
       <c r="M624" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N624" s="10">
+      <c r="N624" s="1">
         <v>1</v>
       </c>
       <c r="O624" s="1" t="s">
@@ -35102,7 +35105,7 @@
       <c r="M625" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N625" s="10">
+      <c r="N625" s="1">
         <v>1</v>
       </c>
       <c r="O625" s="1" t="s">
@@ -35128,7 +35131,7 @@
       <c r="F626" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G626" s="10">
+      <c r="G626" s="1">
         <v>72495328</v>
       </c>
       <c r="H626" s="1" t="s">
@@ -35149,7 +35152,7 @@
       <c r="M626" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N626" s="10">
+      <c r="N626" s="1">
         <v>1</v>
       </c>
       <c r="O626" s="1" t="s">
@@ -35175,7 +35178,7 @@
       <c r="F627" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G627" s="10">
+      <c r="G627" s="1">
         <v>75237035</v>
       </c>
       <c r="H627" s="1" t="s">
@@ -35196,7 +35199,7 @@
       <c r="M627" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N627" s="10">
+      <c r="N627" s="1">
         <v>1</v>
       </c>
       <c r="O627" s="1" t="s">
@@ -35243,7 +35246,7 @@
       <c r="M628" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N628" s="10">
+      <c r="N628" s="1">
         <v>1</v>
       </c>
       <c r="O628" s="1" t="s">
@@ -35269,7 +35272,7 @@
       <c r="F629" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="G629" s="10">
+      <c r="G629" s="1">
         <v>76403635</v>
       </c>
       <c r="H629" s="1" t="s">
@@ -35290,7 +35293,7 @@
       <c r="M629" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N629" s="10">
+      <c r="N629" s="1">
         <v>1</v>
       </c>
       <c r="O629" s="1" t="s">
@@ -35337,7 +35340,7 @@
       <c r="M630" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N630" s="10">
+      <c r="N630" s="1">
         <v>1</v>
       </c>
       <c r="O630" s="1" t="s">
@@ -35384,14 +35387,14 @@
       <c r="M631" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N631" s="10">
+      <c r="N631" s="1">
         <v>1</v>
       </c>
       <c r="O631" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="632" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
         <v>1330</v>
       </c>
@@ -35431,14 +35434,14 @@
       <c r="M632" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N632" s="10">
+      <c r="N632" s="1">
         <v>1</v>
       </c>
       <c r="O632" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="633" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
         <v>1331</v>
       </c>
@@ -35478,14 +35481,14 @@
       <c r="M633" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N633" s="10">
+      <c r="N633" s="1">
         <v>1</v>
       </c>
       <c r="O633" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="634" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
         <v>1332</v>
       </c>
@@ -35525,14 +35528,14 @@
       <c r="M634" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N634" s="10">
+      <c r="N634" s="1">
         <v>1</v>
       </c>
       <c r="O634" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="635" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
         <v>1333</v>
       </c>
@@ -35572,14 +35575,14 @@
       <c r="M635" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N635" s="10">
+      <c r="N635" s="1">
         <v>1</v>
       </c>
       <c r="O635" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="636" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
         <v>1334</v>
       </c>
@@ -35619,14 +35622,14 @@
       <c r="M636" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N636" s="10">
+      <c r="N636" s="1">
         <v>1</v>
       </c>
       <c r="O636" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="637" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
         <v>1335</v>
       </c>
@@ -35666,14 +35669,14 @@
       <c r="M637" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N637" s="10">
+      <c r="N637" s="1">
         <v>1</v>
       </c>
       <c r="O637" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="638" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
         <v>1336</v>
       </c>
@@ -35713,14 +35716,14 @@
       <c r="M638" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N638" s="10">
+      <c r="N638" s="1">
         <v>1</v>
       </c>
       <c r="O638" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="639" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
         <v>1337</v>
       </c>
@@ -35760,14 +35763,14 @@
       <c r="M639" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N639" s="10">
+      <c r="N639" s="1">
         <v>1</v>
       </c>
       <c r="O639" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="640" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
         <v>1338</v>
       </c>
@@ -35807,14 +35810,14 @@
       <c r="M640" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N640" s="10">
+      <c r="N640" s="1">
         <v>1</v>
       </c>
       <c r="O640" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="641" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
         <v>1339</v>
       </c>
@@ -35854,14 +35857,14 @@
       <c r="M641" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N641" s="10">
+      <c r="N641" s="1">
         <v>1</v>
       </c>
       <c r="O641" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="642" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
         <v>1340</v>
       </c>
@@ -35901,7 +35904,7 @@
       <c r="M642" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N642" s="10">
+      <c r="N642" s="1">
         <v>1</v>
       </c>
       <c r="O642" s="1" t="s">
@@ -35925,7 +35928,7 @@
         <v>27</v>
       </c>
       <c r="F643" s="1" t="s">
-        <v>771</v>
+        <v>910</v>
       </c>
       <c r="G643" s="1">
         <v>10733216803</v>
@@ -35948,7 +35951,7 @@
       <c r="M643" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N643" s="10">
+      <c r="N643" s="1">
         <v>1</v>
       </c>
       <c r="O643" s="1" t="s">
@@ -35972,9 +35975,9 @@
         <v>27</v>
       </c>
       <c r="F644" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G644" s="10">
+        <v>910</v>
+      </c>
+      <c r="G644" s="1">
         <v>72495328</v>
       </c>
       <c r="H644" s="1" t="s">
@@ -35995,7 +35998,7 @@
       <c r="M644" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N644" s="10">
+      <c r="N644" s="1">
         <v>1</v>
       </c>
       <c r="O644" s="1" t="s">
@@ -36019,9 +36022,9 @@
         <v>27</v>
       </c>
       <c r="F645" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G645" s="10">
+        <v>910</v>
+      </c>
+      <c r="G645" s="1">
         <v>75237035</v>
       </c>
       <c r="H645" s="1" t="s">
@@ -36042,7 +36045,7 @@
       <c r="M645" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N645" s="10">
+      <c r="N645" s="1">
         <v>1</v>
       </c>
       <c r="O645" s="1" t="s">
@@ -36066,9 +36069,9 @@
         <v>27</v>
       </c>
       <c r="F646" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G646" s="10">
+        <v>910</v>
+      </c>
+      <c r="G646" s="1">
         <v>71727977</v>
       </c>
       <c r="H646" s="1" t="s">
@@ -36089,7 +36092,7 @@
       <c r="M646" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N646" s="10">
+      <c r="N646" s="1">
         <v>1</v>
       </c>
       <c r="O646" s="1" t="s">
@@ -36113,9 +36116,9 @@
         <v>27</v>
       </c>
       <c r="F647" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G647" s="10">
+        <v>910</v>
+      </c>
+      <c r="G647" s="1">
         <v>76403635</v>
       </c>
       <c r="H647" s="1" t="s">
@@ -36136,7 +36139,7 @@
       <c r="M647" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N647" s="10">
+      <c r="N647" s="1">
         <v>1</v>
       </c>
       <c r="O647" s="1" t="s">
@@ -36160,7 +36163,7 @@
         <v>27</v>
       </c>
       <c r="F648" s="1" t="s">
-        <v>771</v>
+        <v>910</v>
       </c>
       <c r="G648" s="1">
         <v>10701171077</v>
@@ -36183,7 +36186,7 @@
       <c r="M648" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N648" s="10">
+      <c r="N648" s="1">
         <v>1</v>
       </c>
       <c r="O648" s="1" t="s">
@@ -36207,9 +36210,9 @@
         <v>27</v>
       </c>
       <c r="F649" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G649" s="10">
+        <v>910</v>
+      </c>
+      <c r="G649" s="1">
         <v>60171003</v>
       </c>
       <c r="H649" s="1" t="s">
@@ -36230,7 +36233,7 @@
       <c r="M649" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N649" s="10">
+      <c r="N649" s="1">
         <v>1</v>
       </c>
       <c r="O649" s="1" t="s">
@@ -36254,7 +36257,7 @@
         <v>27</v>
       </c>
       <c r="F650" s="1" t="s">
-        <v>771</v>
+        <v>910</v>
       </c>
       <c r="G650" s="1">
         <v>10410053221</v>
@@ -36277,7 +36280,7 @@
       <c r="M650" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N650" s="10">
+      <c r="N650" s="1">
         <v>1</v>
       </c>
       <c r="O650" s="1" t="s">
@@ -36301,7 +36304,7 @@
         <v>27</v>
       </c>
       <c r="F651" s="1" t="s">
-        <v>771</v>
+        <v>910</v>
       </c>
       <c r="G651" s="1">
         <v>10715055380</v>
@@ -36324,7 +36327,7 @@
       <c r="M651" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N651" s="10">
+      <c r="N651" s="1">
         <v>1</v>
       </c>
       <c r="O651" s="1" t="s">
@@ -36348,9 +36351,9 @@
         <v>27</v>
       </c>
       <c r="F652" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G652" s="10">
+        <v>910</v>
+      </c>
+      <c r="G652" s="1">
         <v>61094381</v>
       </c>
       <c r="H652" s="1" t="s">
@@ -36371,7 +36374,7 @@
       <c r="M652" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N652" s="10">
+      <c r="N652" s="1">
         <v>1</v>
       </c>
       <c r="O652" s="1" t="s">
@@ -36395,9 +36398,9 @@
         <v>27</v>
       </c>
       <c r="F653" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G653" s="10">
+        <v>910</v>
+      </c>
+      <c r="G653" s="1">
         <v>60566010</v>
       </c>
       <c r="H653" s="1" t="s">
@@ -36418,7 +36421,7 @@
       <c r="M653" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N653" s="10">
+      <c r="N653" s="1">
         <v>1</v>
       </c>
       <c r="O653" s="1" t="s">
@@ -36442,7 +36445,7 @@
         <v>27</v>
       </c>
       <c r="F654" s="1" t="s">
-        <v>771</v>
+        <v>910</v>
       </c>
       <c r="G654" s="1">
         <v>10724715759</v>
@@ -36465,7 +36468,7 @@
       <c r="M654" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N654" s="10">
+      <c r="N654" s="1">
         <v>1</v>
       </c>
       <c r="O654" s="1" t="s">
@@ -36489,9 +36492,9 @@
         <v>27</v>
       </c>
       <c r="F655" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G655" s="10">
+        <v>910</v>
+      </c>
+      <c r="G655" s="1">
         <v>71873373</v>
       </c>
       <c r="H655" s="1" t="s">
@@ -36512,7 +36515,7 @@
       <c r="M655" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N655" s="10">
+      <c r="N655" s="1">
         <v>1</v>
       </c>
       <c r="O655" s="1" t="s">
@@ -36536,7 +36539,7 @@
         <v>27</v>
       </c>
       <c r="F656" s="1" t="s">
-        <v>771</v>
+        <v>910</v>
       </c>
       <c r="G656" s="1">
         <v>10767470628</v>
@@ -36559,7 +36562,7 @@
       <c r="M656" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N656" s="10">
+      <c r="N656" s="1">
         <v>1</v>
       </c>
       <c r="O656" s="1" t="s">
@@ -36583,7 +36586,7 @@
         <v>27</v>
       </c>
       <c r="F657" s="1" t="s">
-        <v>771</v>
+        <v>910</v>
       </c>
       <c r="G657" s="1">
         <v>10718515161</v>
@@ -36606,7 +36609,7 @@
       <c r="M657" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N657" s="10">
+      <c r="N657" s="1">
         <v>1</v>
       </c>
       <c r="O657" s="1" t="s">
@@ -36630,9 +36633,9 @@
         <v>27</v>
       </c>
       <c r="F658" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G658" s="10">
+        <v>910</v>
+      </c>
+      <c r="G658" s="1">
         <v>72076653</v>
       </c>
       <c r="H658" s="1" t="s">
@@ -36653,7 +36656,7 @@
       <c r="M658" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N658" s="10">
+      <c r="N658" s="1">
         <v>1</v>
       </c>
       <c r="O658" s="1" t="s">
@@ -36677,7 +36680,7 @@
         <v>27</v>
       </c>
       <c r="F659" s="1" t="s">
-        <v>771</v>
+        <v>910</v>
       </c>
       <c r="G659" s="1">
         <v>10701171255</v>
@@ -36700,7 +36703,7 @@
       <c r="M659" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N659" s="10">
+      <c r="N659" s="1">
         <v>1</v>
       </c>
       <c r="O659" s="1" t="s">
@@ -36724,7 +36727,7 @@
         <v>27</v>
       </c>
       <c r="F660" s="1" t="s">
-        <v>771</v>
+        <v>1429</v>
       </c>
       <c r="G660" s="1">
         <v>10733216803</v>
@@ -36747,7 +36750,7 @@
       <c r="M660" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N660" s="10">
+      <c r="N660" s="1">
         <v>1</v>
       </c>
       <c r="O660" s="1" t="s">
@@ -36771,9 +36774,9 @@
         <v>27</v>
       </c>
       <c r="F661" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G661" s="10">
+        <v>1429</v>
+      </c>
+      <c r="G661" s="1">
         <v>72495328</v>
       </c>
       <c r="H661" s="1" t="s">
@@ -36794,7 +36797,7 @@
       <c r="M661" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N661" s="10">
+      <c r="N661" s="1">
         <v>1</v>
       </c>
       <c r="O661" s="1" t="s">
@@ -36818,9 +36821,9 @@
         <v>27</v>
       </c>
       <c r="F662" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G662" s="10">
+        <v>1429</v>
+      </c>
+      <c r="G662" s="1">
         <v>75237035</v>
       </c>
       <c r="H662" s="1" t="s">
@@ -36841,7 +36844,7 @@
       <c r="M662" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N662" s="10">
+      <c r="N662" s="1">
         <v>1</v>
       </c>
       <c r="O662" s="1" t="s">
@@ -36865,9 +36868,9 @@
         <v>27</v>
       </c>
       <c r="F663" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G663" s="10">
+        <v>1429</v>
+      </c>
+      <c r="G663" s="1">
         <v>71727977</v>
       </c>
       <c r="H663" s="1" t="s">
@@ -36888,7 +36891,7 @@
       <c r="M663" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N663" s="10">
+      <c r="N663" s="1">
         <v>1</v>
       </c>
       <c r="O663" s="1" t="s">
@@ -36912,9 +36915,9 @@
         <v>27</v>
       </c>
       <c r="F664" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G664" s="10">
+        <v>1429</v>
+      </c>
+      <c r="G664" s="1">
         <v>76403635</v>
       </c>
       <c r="H664" s="1" t="s">
@@ -36935,7 +36938,7 @@
       <c r="M664" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N664" s="10">
+      <c r="N664" s="1">
         <v>1</v>
       </c>
       <c r="O664" s="1" t="s">
@@ -36959,7 +36962,7 @@
         <v>27</v>
       </c>
       <c r="F665" s="1" t="s">
-        <v>771</v>
+        <v>1429</v>
       </c>
       <c r="G665" s="1">
         <v>10701171077</v>
@@ -36982,7 +36985,7 @@
       <c r="M665" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N665" s="10">
+      <c r="N665" s="1">
         <v>1</v>
       </c>
       <c r="O665" s="1" t="s">
@@ -37006,9 +37009,9 @@
         <v>27</v>
       </c>
       <c r="F666" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G666" s="10">
+        <v>1429</v>
+      </c>
+      <c r="G666" s="1">
         <v>60171003</v>
       </c>
       <c r="H666" s="1" t="s">
@@ -37029,7 +37032,7 @@
       <c r="M666" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N666" s="10">
+      <c r="N666" s="1">
         <v>1</v>
       </c>
       <c r="O666" s="1" t="s">
@@ -37053,7 +37056,7 @@
         <v>27</v>
       </c>
       <c r="F667" s="1" t="s">
-        <v>771</v>
+        <v>1429</v>
       </c>
       <c r="G667" s="1">
         <v>10410053221</v>
@@ -37076,7 +37079,7 @@
       <c r="M667" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N667" s="10">
+      <c r="N667" s="1">
         <v>1</v>
       </c>
       <c r="O667" s="1" t="s">
@@ -37100,7 +37103,7 @@
         <v>27</v>
       </c>
       <c r="F668" s="1" t="s">
-        <v>771</v>
+        <v>1429</v>
       </c>
       <c r="G668" s="1">
         <v>10715055380</v>
@@ -37123,7 +37126,7 @@
       <c r="M668" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N668" s="10">
+      <c r="N668" s="1">
         <v>1</v>
       </c>
       <c r="O668" s="1" t="s">
@@ -37147,9 +37150,9 @@
         <v>27</v>
       </c>
       <c r="F669" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G669" s="10">
+        <v>1429</v>
+      </c>
+      <c r="G669" s="1">
         <v>61094381</v>
       </c>
       <c r="H669" s="1" t="s">
@@ -37170,7 +37173,7 @@
       <c r="M669" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N669" s="10">
+      <c r="N669" s="1">
         <v>1</v>
       </c>
       <c r="O669" s="1" t="s">
@@ -37194,9 +37197,9 @@
         <v>27</v>
       </c>
       <c r="F670" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G670" s="10">
+        <v>1429</v>
+      </c>
+      <c r="G670" s="1">
         <v>60566010</v>
       </c>
       <c r="H670" s="1" t="s">
@@ -37217,7 +37220,7 @@
       <c r="M670" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N670" s="10">
+      <c r="N670" s="1">
         <v>1</v>
       </c>
       <c r="O670" s="1" t="s">
@@ -37241,7 +37244,7 @@
         <v>27</v>
       </c>
       <c r="F671" s="1" t="s">
-        <v>771</v>
+        <v>1429</v>
       </c>
       <c r="G671" s="1">
         <v>10724715759</v>
@@ -37264,7 +37267,7 @@
       <c r="M671" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N671" s="10">
+      <c r="N671" s="1">
         <v>1</v>
       </c>
       <c r="O671" s="1" t="s">
@@ -37288,9 +37291,9 @@
         <v>27</v>
       </c>
       <c r="F672" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G672" s="10">
+        <v>1429</v>
+      </c>
+      <c r="G672" s="1">
         <v>71873373</v>
       </c>
       <c r="H672" s="1" t="s">
@@ -37311,7 +37314,7 @@
       <c r="M672" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N672" s="10">
+      <c r="N672" s="1">
         <v>1</v>
       </c>
       <c r="O672" s="1" t="s">
@@ -37335,7 +37338,7 @@
         <v>27</v>
       </c>
       <c r="F673" s="1" t="s">
-        <v>771</v>
+        <v>1429</v>
       </c>
       <c r="G673" s="1">
         <v>10767470628</v>
@@ -37358,7 +37361,7 @@
       <c r="M673" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N673" s="10">
+      <c r="N673" s="1">
         <v>1</v>
       </c>
       <c r="O673" s="1" t="s">
@@ -37382,7 +37385,7 @@
         <v>27</v>
       </c>
       <c r="F674" s="1" t="s">
-        <v>771</v>
+        <v>1429</v>
       </c>
       <c r="G674" s="1">
         <v>10718515161</v>
@@ -37405,7 +37408,7 @@
       <c r="M674" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N674" s="10">
+      <c r="N674" s="1">
         <v>1</v>
       </c>
       <c r="O674" s="1" t="s">
@@ -37429,9 +37432,9 @@
         <v>27</v>
       </c>
       <c r="F675" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="G675" s="10">
+        <v>1429</v>
+      </c>
+      <c r="G675" s="1">
         <v>72076653</v>
       </c>
       <c r="H675" s="1" t="s">
@@ -37452,7 +37455,7 @@
       <c r="M675" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N675" s="10">
+      <c r="N675" s="1">
         <v>1</v>
       </c>
       <c r="O675" s="1" t="s">
@@ -37476,7 +37479,7 @@
         <v>27</v>
       </c>
       <c r="F676" s="1" t="s">
-        <v>771</v>
+        <v>1429</v>
       </c>
       <c r="G676" s="1">
         <v>10701171255</v>
@@ -37499,14 +37502,14 @@
       <c r="M676" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N676" s="10">
+      <c r="N676" s="1">
         <v>1</v>
       </c>
       <c r="O676" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="677" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
         <v>1375</v>
       </c>
@@ -37546,14 +37549,14 @@
       <c r="M677" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N677" s="10">
+      <c r="N677" s="1">
         <v>1</v>
       </c>
       <c r="O677" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="678" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
         <v>1376</v>
       </c>
@@ -37572,7 +37575,7 @@
       <c r="F678" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="G678" s="10">
+      <c r="G678" s="1">
         <v>72495328</v>
       </c>
       <c r="H678" s="1" t="s">
@@ -37593,14 +37596,14 @@
       <c r="M678" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N678" s="10">
+      <c r="N678" s="1">
         <v>1</v>
       </c>
       <c r="O678" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="679" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
         <v>1377</v>
       </c>
@@ -37619,7 +37622,7 @@
       <c r="F679" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="G679" s="10">
+      <c r="G679" s="1">
         <v>75237035</v>
       </c>
       <c r="H679" s="1" t="s">
@@ -37640,14 +37643,14 @@
       <c r="M679" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N679" s="10">
+      <c r="N679" s="1">
         <v>1</v>
       </c>
       <c r="O679" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="680" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
         <v>1378</v>
       </c>
@@ -37666,7 +37669,7 @@
       <c r="F680" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="G680" s="10">
+      <c r="G680" s="1">
         <v>71727977</v>
       </c>
       <c r="H680" s="1" t="s">
@@ -37687,14 +37690,14 @@
       <c r="M680" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N680" s="10">
+      <c r="N680" s="1">
         <v>1</v>
       </c>
       <c r="O680" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="681" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
         <v>1379</v>
       </c>
@@ -37713,7 +37716,7 @@
       <c r="F681" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="G681" s="10">
+      <c r="G681" s="1">
         <v>76403635</v>
       </c>
       <c r="H681" s="1" t="s">
@@ -37734,14 +37737,14 @@
       <c r="M681" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N681" s="10">
+      <c r="N681" s="1">
         <v>1</v>
       </c>
       <c r="O681" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="682" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
         <v>1380</v>
       </c>
@@ -37781,14 +37784,14 @@
       <c r="M682" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N682" s="10">
+      <c r="N682" s="1">
         <v>1</v>
       </c>
       <c r="O682" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="683" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
         <v>1381</v>
       </c>
@@ -37807,7 +37810,7 @@
       <c r="F683" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="G683" s="10">
+      <c r="G683" s="1">
         <v>60171003</v>
       </c>
       <c r="H683" s="1" t="s">
@@ -37828,14 +37831,14 @@
       <c r="M683" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N683" s="10">
+      <c r="N683" s="1">
         <v>1</v>
       </c>
       <c r="O683" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="684" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
         <v>1382</v>
       </c>
@@ -37875,14 +37878,14 @@
       <c r="M684" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N684" s="10">
+      <c r="N684" s="1">
         <v>1</v>
       </c>
       <c r="O684" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="685" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
         <v>1383</v>
       </c>
@@ -37922,14 +37925,14 @@
       <c r="M685" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N685" s="10">
+      <c r="N685" s="1">
         <v>1</v>
       </c>
       <c r="O685" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="686" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
         <v>1384</v>
       </c>
@@ -37948,7 +37951,7 @@
       <c r="F686" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="G686" s="10">
+      <c r="G686" s="1">
         <v>61094381</v>
       </c>
       <c r="H686" s="1" t="s">
@@ -37969,14 +37972,14 @@
       <c r="M686" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N686" s="10">
+      <c r="N686" s="1">
         <v>1</v>
       </c>
       <c r="O686" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="687" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
         <v>1385</v>
       </c>
@@ -37995,7 +37998,7 @@
       <c r="F687" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="G687" s="10">
+      <c r="G687" s="1">
         <v>60566010</v>
       </c>
       <c r="H687" s="1" t="s">
@@ -38016,14 +38019,14 @@
       <c r="M687" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N687" s="10">
+      <c r="N687" s="1">
         <v>1</v>
       </c>
       <c r="O687" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="688" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
         <v>1386</v>
       </c>
@@ -38063,14 +38066,14 @@
       <c r="M688" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N688" s="10">
+      <c r="N688" s="1">
         <v>1</v>
       </c>
       <c r="O688" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="689" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
         <v>1387</v>
       </c>
@@ -38089,7 +38092,7 @@
       <c r="F689" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="G689" s="10">
+      <c r="G689" s="1">
         <v>71873373</v>
       </c>
       <c r="H689" s="1" t="s">
@@ -38110,14 +38113,14 @@
       <c r="M689" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N689" s="10">
+      <c r="N689" s="1">
         <v>1</v>
       </c>
       <c r="O689" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="690" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
         <v>1388</v>
       </c>
@@ -38157,14 +38160,14 @@
       <c r="M690" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N690" s="10">
+      <c r="N690" s="1">
         <v>1</v>
       </c>
       <c r="O690" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="691" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
         <v>1389</v>
       </c>
@@ -38183,7 +38186,7 @@
       <c r="F691" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="G691" s="10">
+      <c r="G691" s="1">
         <v>72076653</v>
       </c>
       <c r="H691" s="1" t="s">
@@ -38204,14 +38207,14 @@
       <c r="M691" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N691" s="10">
+      <c r="N691" s="1">
         <v>1</v>
       </c>
       <c r="O691" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="692" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
         <v>1390</v>
       </c>
@@ -38251,14 +38254,14 @@
       <c r="M692" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N692" s="10">
+      <c r="N692" s="1">
         <v>1</v>
       </c>
       <c r="O692" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="693" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
         <v>1391</v>
       </c>
@@ -38298,14 +38301,14 @@
       <c r="M693" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N693" s="10">
+      <c r="N693" s="1">
         <v>1</v>
       </c>
       <c r="O693" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="694" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
         <v>1392</v>
       </c>
@@ -38345,14 +38348,14 @@
       <c r="M694" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N694" s="10">
+      <c r="N694" s="1">
         <v>1</v>
       </c>
       <c r="O694" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="695" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" s="1" t="s">
         <v>1393</v>
       </c>
@@ -38371,7 +38374,7 @@
       <c r="F695" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="G695" s="10">
+      <c r="G695" s="1">
         <v>10450876700</v>
       </c>
       <c r="H695" s="1" t="s">
@@ -38392,14 +38395,14 @@
       <c r="M695" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N695" s="10">
+      <c r="N695" s="1">
         <v>1</v>
       </c>
       <c r="O695" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="696" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
         <v>1394</v>
       </c>
@@ -38418,7 +38421,7 @@
       <c r="F696" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="G696" s="10">
+      <c r="G696" s="1">
         <v>10400403061</v>
       </c>
       <c r="H696" s="1" t="s">
@@ -38439,14 +38442,14 @@
       <c r="M696" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N696" s="10">
+      <c r="N696" s="1">
         <v>1</v>
       </c>
       <c r="O696" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="697" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
         <v>1395</v>
       </c>
@@ -38465,7 +38468,7 @@
       <c r="F697" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="G697" s="10">
+      <c r="G697" s="1">
         <v>47656632</v>
       </c>
       <c r="H697" s="1" t="s">
@@ -38486,14 +38489,14 @@
       <c r="M697" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N697" s="10">
+      <c r="N697" s="1">
         <v>1</v>
       </c>
       <c r="O697" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="698" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" s="1" t="s">
         <v>1396</v>
       </c>
@@ -38512,7 +38515,7 @@
       <c r="F698" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="G698" s="10">
+      <c r="G698" s="1">
         <v>47656632</v>
       </c>
       <c r="H698" s="1" t="s">
@@ -38533,14 +38536,14 @@
       <c r="M698" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N698" s="10">
+      <c r="N698" s="1">
         <v>1</v>
       </c>
       <c r="O698" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="699" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" s="1" t="s">
         <v>1397</v>
       </c>
@@ -38559,7 +38562,7 @@
       <c r="F699" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="G699" s="10">
+      <c r="G699" s="1">
         <v>10462583996</v>
       </c>
       <c r="H699" s="1" t="s">
@@ -38580,14 +38583,14 @@
       <c r="M699" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N699" s="10">
+      <c r="N699" s="1">
         <v>1</v>
       </c>
       <c r="O699" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="700" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" s="1" t="s">
         <v>1398</v>
       </c>
@@ -38606,7 +38609,7 @@
       <c r="F700" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="G700" s="10">
+      <c r="G700" s="1">
         <v>10462583996</v>
       </c>
       <c r="H700" s="1" t="s">
@@ -38627,14 +38630,14 @@
       <c r="M700" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N700" s="10">
+      <c r="N700" s="1">
         <v>15</v>
       </c>
       <c r="O700" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="701" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" s="1" t="s">
         <v>1399</v>
       </c>
@@ -38653,7 +38656,7 @@
       <c r="F701" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="G701" s="10">
+      <c r="G701" s="1">
         <v>47925279</v>
       </c>
       <c r="H701" s="1" t="s">
@@ -38674,14 +38677,14 @@
       <c r="M701" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N701" s="10">
+      <c r="N701" s="1">
         <v>1</v>
       </c>
       <c r="O701" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="702" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" s="1" t="s">
         <v>1400</v>
       </c>
@@ -38721,7 +38724,7 @@
       <c r="M702" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N702" s="10">
+      <c r="N702" s="1">
         <v>1</v>
       </c>
       <c r="O702" s="1" t="s">
@@ -38729,6 +38732,23 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P702" xr:uid="{8D04F3C6-8190-4D94-9613-CDA0600594BA}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="7"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="POI"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="5">
+      <filters>
+        <filter val="LITA CASTILLO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P619">
     <sortCondition ref="D1:D619"/>
   </sortState>

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5586578-FB81-434F-B0BC-496F30A2DC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04962942-50E2-481E-9625-19B2AB298D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32313,7 +32313,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="569" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
         <v>1209</v>
       </c>
@@ -32413,7 +32413,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="571" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
         <v>1211</v>
       </c>
@@ -32513,7 +32513,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="573" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
         <v>1213</v>
       </c>
@@ -32613,7 +32613,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="575" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
         <v>1215</v>
       </c>
@@ -32713,7 +32713,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="577" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
         <v>1217</v>
       </c>
@@ -32813,7 +32813,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="579" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
         <v>1219</v>
       </c>
@@ -32913,7 +32913,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="581" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
         <v>1221</v>
       </c>
@@ -33013,7 +33013,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="583" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
         <v>1223</v>
       </c>
@@ -33113,7 +33113,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="585" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
         <v>1225</v>
       </c>
@@ -33213,7 +33213,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="587" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
         <v>1227</v>
       </c>
@@ -33313,7 +33313,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="589" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
         <v>1229</v>
       </c>
@@ -33413,7 +33413,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="591" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
         <v>1231</v>
       </c>
@@ -33513,7 +33513,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="593" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
         <v>1233</v>
       </c>
@@ -33613,7 +33613,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="595" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
         <v>1235</v>
       </c>
@@ -33713,7 +33713,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="597" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
         <v>1237</v>
       </c>
@@ -33813,7 +33813,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="599" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
         <v>1239</v>
       </c>
@@ -33863,7 +33863,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="600" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
         <v>1240</v>
       </c>
@@ -33913,7 +33913,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="601" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
         <v>1241</v>
       </c>
@@ -34313,7 +34313,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="609" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
         <v>1274</v>
       </c>
@@ -34360,7 +34360,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="610" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
         <v>1275</v>
       </c>
@@ -34407,7 +34407,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="611" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
         <v>1276</v>
       </c>
@@ -34471,7 +34471,7 @@
         <v>27</v>
       </c>
       <c r="F612" s="1" t="s">
-        <v>771</v>
+        <v>565</v>
       </c>
       <c r="G612" s="1">
         <v>10248679081</v>
@@ -34501,7 +34501,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="613" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
         <v>1278</v>
       </c>
@@ -34548,7 +34548,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="614" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
         <v>1279</v>
       </c>
@@ -34595,7 +34595,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="615" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
         <v>1280</v>
       </c>
@@ -34642,7 +34642,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="616" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
         <v>1281</v>
       </c>
@@ -34689,7 +34689,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="617" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
         <v>1282</v>
       </c>
@@ -34736,7 +34736,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="618" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
         <v>1283</v>
       </c>
@@ -34783,7 +34783,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="619" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
         <v>1284</v>
       </c>
@@ -34830,7 +34830,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="620" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
         <v>1318</v>
       </c>
@@ -34877,7 +34877,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="621" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
         <v>1319</v>
       </c>
@@ -34924,7 +34924,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="622" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
         <v>1320</v>
       </c>
@@ -34971,7 +34971,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="623" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
         <v>1321</v>
       </c>
@@ -35018,7 +35018,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="624" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
         <v>1322</v>
       </c>
@@ -35065,7 +35065,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="625" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
         <v>1323</v>
       </c>
@@ -35112,7 +35112,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="626" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
         <v>1324</v>
       </c>
@@ -35159,7 +35159,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="627" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
         <v>1325</v>
       </c>
@@ -35206,7 +35206,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="628" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
         <v>1326</v>
       </c>
@@ -35253,7 +35253,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="629" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
         <v>1327</v>
       </c>
@@ -35300,7 +35300,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="630" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
         <v>1328</v>
       </c>
@@ -35347,7 +35347,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="631" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
         <v>1329</v>
       </c>
@@ -35911,7 +35911,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="643" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
         <v>1341</v>
       </c>
@@ -35958,7 +35958,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="644" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
         <v>1342</v>
       </c>
@@ -36005,7 +36005,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="645" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
         <v>1343</v>
       </c>
@@ -36052,7 +36052,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="646" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
         <v>1344</v>
       </c>
@@ -36099,7 +36099,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="647" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
         <v>1345</v>
       </c>
@@ -36146,7 +36146,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="648" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
         <v>1346</v>
       </c>
@@ -36193,7 +36193,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="649" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
         <v>1347</v>
       </c>
@@ -36240,7 +36240,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="650" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
         <v>1348</v>
       </c>
@@ -36287,7 +36287,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="651" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
         <v>1349</v>
       </c>
@@ -36334,7 +36334,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="652" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
         <v>1350</v>
       </c>
@@ -36381,7 +36381,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="653" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
         <v>1351</v>
       </c>
@@ -36428,7 +36428,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="654" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
         <v>1352</v>
       </c>
@@ -36475,7 +36475,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="655" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
         <v>1353</v>
       </c>
@@ -36522,7 +36522,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="656" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
         <v>1354</v>
       </c>
@@ -36569,7 +36569,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="657" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
         <v>1355</v>
       </c>
@@ -36616,7 +36616,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="658" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
         <v>1356</v>
       </c>
@@ -36663,7 +36663,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="659" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
         <v>1357</v>
       </c>
@@ -36710,7 +36710,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="660" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
         <v>1358</v>
       </c>
@@ -36757,7 +36757,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="661" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
         <v>1359</v>
       </c>
@@ -36804,7 +36804,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="662" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
         <v>1360</v>
       </c>
@@ -36851,7 +36851,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="663" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
         <v>1361</v>
       </c>
@@ -36898,7 +36898,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="664" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
         <v>1362</v>
       </c>
@@ -36945,7 +36945,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="665" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
         <v>1363</v>
       </c>
@@ -36992,7 +36992,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="666" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
         <v>1364</v>
       </c>
@@ -37039,7 +37039,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="667" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
         <v>1365</v>
       </c>
@@ -37086,7 +37086,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="668" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
         <v>1366</v>
       </c>
@@ -37133,7 +37133,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="669" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
         <v>1367</v>
       </c>
@@ -37180,7 +37180,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="670" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
         <v>1368</v>
       </c>
@@ -37227,7 +37227,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="671" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
         <v>1369</v>
       </c>
@@ -37274,7 +37274,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="672" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
         <v>1370</v>
       </c>
@@ -37321,7 +37321,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="673" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
         <v>1371</v>
       </c>
@@ -37368,7 +37368,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="674" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
         <v>1372</v>
       </c>
@@ -37415,7 +37415,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="675" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
         <v>1373</v>
       </c>
@@ -37462,7 +37462,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="676" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
         <v>1374</v>
       </c>
@@ -38738,14 +38738,9 @@
         <filter val="7"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="4">
+    <filterColumn colId="9">
       <filters>
-        <filter val="POI"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="5">
-      <filters>
-        <filter val="LITA CASTILLO"/>
+        <filter val="2. Diseño y/o desarrollo de productos"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04962942-50E2-481E-9625-19B2AB298D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{708CBE13-F23B-4B4B-9375-D8F60A13F2C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
